--- a/docs/spec/TEA-SPEC-001_programming-specification.xlsx
+++ b/docs/spec/TEA-SPEC-001_programming-specification.xlsx
@@ -30,8 +30,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Definitions'!$A$3:$C$49</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Rules'!$A$3:$N$87</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Rule_Messages'!$A$3:$J$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Rules'!$A$3:$N$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Rule_Messages'!$A$3:$J$88</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -695,7 +695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Executable definition of the review logic: derivations, the 84-point rule catalog with confidence base rates, data contracts, LLM integration and the query reconciliation model.</t>
+          <t>Executable definition of the review logic: derivations, the 85-point rule catalog with confidence base rates, data contracts, LLM integration and the query reconciliation model.</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>84 review points across 7 families</t>
+          <t>85 review points across 7 families</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>•  Two rules are switched off by default and need an explicit decision: TE-BL-016 and TE-IR-008, both marked PROPOSED_OPTIONAL.</t>
+          <t>•  Three rules are switched off by default and need an explicit decision: TE-BL-016, TE-IR-008 and TE-RS-021, all marked PROPOSED_OPTIONAL.</t>
         </is>
       </c>
     </row>
@@ -915,33 +915,40 @@
     <row r="28" ht="26" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>•  Confidence base rate added to all 84 rules (OBJ-03).</t>
+          <t>•  Confidence base rate added to all rules (OBJ-03).</t>
         </is>
       </c>
     </row>
     <row r="29" ht="26" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>•  TE-QM-002 rewritten: the agent assesses whether a site's answer justified the data, rather than escalating whenever data still fails (OBJ-04).</t>
+          <t>•  TE-RS-021 added: cytological confirmation of an effusion used as evidence of progression. Proposed following the OI-01 discussion; off by default.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="26" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>•  Query reconciliation gains a JUSTIFIED_BY_ANSWER outcome with permanent suppression for MINOR and INFO findings.</t>
+          <t>•  TE-QM-002 rewritten: the agent assesses whether a site's answer justified the data, rather than escalating whenever data still fails (OBJ-04).</t>
         </is>
       </c>
     </row>
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
+          <t>•  Query reconciliation gains a JUSTIFIED_BY_ANSWER outcome with permanent suppression for MINOR and INFO findings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
           <t>•  Veeva EDC is the primary input profile; SDTM is secondary (OQ-01).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="25">
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="A27:F27"/>
@@ -950,6 +957,7 @@
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A32:F32"/>
     <mergeCell ref="A22:F22"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B8:F8"/>
@@ -3593,7 +3601,7 @@
       </c>
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>Confirm whether the two PROPOSED_OPTIONAL rules should be activated: TE-BL-016 (lesion location versus coded organ) and TE-IR-008 (clinical stability documented at treatment beyond iUPD).</t>
+          <t>Confirm whether the three PROPOSED_OPTIONAL rules should be activated: TE-BL-016 (lesion location versus coded organ), TE-IR-008 (clinical stability documented at treatment beyond iUPD) and TE-RS-021 (cytological confirmation of an effusion driving progression).</t>
         </is>
       </c>
       <c r="C7" s="44" t="inlineStr">
@@ -3911,11 +3919,11 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>84 review points: logic, severity, confidence</t>
+          <t>85 review points: logic, severity, confidence</t>
         </is>
       </c>
       <c r="C10" s="16">
-        <f>COUNTA(Rules!A4:A87)</f>
+        <f>COUNTA(Rules!A4:A88)</f>
         <v/>
       </c>
       <c r="D10" s="17" t="inlineStr">
@@ -3941,7 +3949,7 @@
         </is>
       </c>
       <c r="C11" s="16">
-        <f>COUNTA(Rule_Messages!A4:A87)</f>
+        <f>COUNTA(Rule_Messages!A4:A88)</f>
         <v/>
       </c>
       <c r="D11" s="17" t="inlineStr">
@@ -4320,7 +4328,7 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>all 84</t>
+          <t>all 85</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -4342,7 +4350,7 @@
       </c>
       <c r="C7" s="22" t="inlineStr">
         <is>
-          <t>all 84</t>
+          <t>all 85</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -4562,7 +4570,7 @@
       </c>
       <c r="C17" s="22" t="inlineStr">
         <is>
-          <t>all 84 base rates</t>
+          <t>all 85 base rates</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -6957,7 +6965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O87"/>
+  <dimension ref="A1:O88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -6979,7 +6987,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>Rule catalog — 84 review points</t>
+          <t>Rule catalog — 85 review points</t>
         </is>
       </c>
     </row>
@@ -11751,14 +11759,86 @@
       <c r="M87" s="25" t="n"/>
       <c r="N87" s="26" t="n"/>
     </row>
+    <row r="88" ht="96" customHeight="1">
+      <c r="A88" s="11" t="inlineStr">
+        <is>
+          <t>TE-RS-021</t>
+        </is>
+      </c>
+      <c r="B88" s="24" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="C88" s="12" t="inlineStr">
+        <is>
+          <t>New or worsening effusion used as evidence of progression without cytological confirmation</t>
+        </is>
+      </c>
+      <c r="D88" s="24" t="inlineStr">
+        <is>
+          <t>RECIST 1.1 + iRECIST</t>
+        </is>
+      </c>
+      <c r="E88" s="32" t="inlineStr">
+        <is>
+          <t>MAJOR</t>
+        </is>
+      </c>
+      <c r="F88" s="24" t="inlineStr">
+        <is>
+          <t>HYBRID</t>
+        </is>
+      </c>
+      <c r="G88" s="38" t="inlineStr">
+        <is>
+          <t>PROPOSED_OPTIONAL</t>
+        </is>
+      </c>
+      <c r="H88" s="34" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I88" s="12" t="inlineStr">
+        <is>
+          <t>Progression driven by an effusion must rest on cytological confirmation where the measurable disease is responding or stable.</t>
+        </is>
+      </c>
+      <c r="J88" s="12" t="inlineStr">
+        <is>
+          <t>reported_responses.overall, non_target_state, lesion description text, derived target response, cytology result where collected</t>
+        </is>
+      </c>
+      <c r="K88" s="30" t="inlineStr">
+        <is>
+          <t>for each assessment a where reported overall response == PD:
+    effusions = non-target or new-lesion records at a whose organ or description
+                matches an effusion pattern (pleural, pericardial, peritoneal / ascites)
+    for e in effusions:
+        appeared  = e not present at the previous assessment
+        worsened  = e.non_target_state moved toward worsening since the previous assessment
+        if (appeared or worsened)
+           and derived target_response at a in (CR, PR, SD)
+           and no cytology or histology result recorded for e:
+               raise finding
+guards:
+  - suppress when unequivocal progression is evidenced independently of the effusion
+  - suppress when derived target response is itself PD
+  - deactivate when the protocol waives cytological confirmation (set at AC-11 intake)
+  - deactivate when no cytology field is collected, reporting NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="L88" s="25" t="n"/>
+      <c r="M88" s="25" t="n"/>
+      <c r="N88" s="26" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:N87"/>
+  <autoFilter ref="A3:N88"/>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A2:O2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="L4:L87" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L4:L88" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Accept,Amend,Reject,Discuss"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11772,7 +11852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J87"/>
+  <dimension ref="A1:J88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -15213,14 +15293,54 @@
       <c r="I87" s="25" t="n"/>
       <c r="J87" s="26" t="n"/>
     </row>
+    <row r="88" ht="108" customHeight="1">
+      <c r="A88" s="23" t="inlineStr">
+        <is>
+          <t>TE-RS-021</t>
+        </is>
+      </c>
+      <c r="B88" s="12" t="inlineStr">
+        <is>
+          <t>New or worsening effusion used as evidence of progression without cytological confirmation</t>
+        </is>
+      </c>
+      <c r="C88" s="12" t="inlineStr">
+        <is>
+          <t>Whether a new or worsening effusion used to support progression carries the cytological confirmation RECIST requires.</t>
+        </is>
+      </c>
+      <c r="D88" s="12" t="inlineStr">
+        <is>
+          <t>Progressive disease is recorded at {visit} for subject {subject_id}. The supporting non-target finding is {effusion_description}, which {appeared_or_worsened} at this visit, while target lesions show {target_response_derived}. No cytological result is recorded for the effusion.</t>
+        </is>
+      </c>
+      <c r="E88" s="12" t="inlineStr">
+        <is>
+          <t>RECIST 1.1 requires that an effusion appearing or worsening during treatment be confirmed cytologically before it is taken as evidence of progression, where the measurable disease is responding or stable. Effusions arise from causes unrelated to tumor progression, including the treatment itself and intercurrent illness. An unconfirmed effusion is a recognised source of spurious progression, which censors the subject early and shortens progression-free survival.</t>
+        </is>
+      </c>
+      <c r="F88" s="40" t="inlineStr">
+        <is>
+          <t>Progressive disease is recorded at {visit}, supported by {effusion_description}, while target lesions show {target_response_derived}. Please confirm whether cytological assessment of the effusion was performed and record the result. If cytology was not performed, please confirm the basis on which progression was assessed.</t>
+        </is>
+      </c>
+      <c r="G88" s="12" t="inlineStr">
+        <is>
+          <t>This matters most where the effusion is the sole basis for progression; where other unequivocal progression exists the finding is suppressed. Some protocols explicitly waive cytological confirmation — check the protocol before querying, and if it is waived, deactivate this rule at the AC-11 intake rather than dispositioning each occurrence.</t>
+        </is>
+      </c>
+      <c r="H88" s="25" t="n"/>
+      <c r="I88" s="25" t="n"/>
+      <c r="J88" s="26" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:J87"/>
+  <autoFilter ref="A3:J88"/>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="H4:H87" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H4:H88" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Accept,Amend,Reject,Discuss"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/spec/TEA-SPEC-001_programming-specification.xlsx
+++ b/docs/spec/TEA-SPEC-001_programming-specification.xlsx
@@ -803,7 +803,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>1.1.0 — Step 2 review, round 1 applied</t>
+          <t>1.1.1 — Step 2 review, round 1 applied</t>
         </is>
       </c>
     </row>
@@ -7001,7 +7001,6 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <dataValidations count="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/spec/TEA-SPEC-001_programming-specification.xlsx
+++ b/docs/spec/TEA-SPEC-001_programming-specification.xlsx
@@ -1,37 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Contents" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Definitions" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Guideline_Profiles" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Interpretations" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Derivations" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Pipeline" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Rules" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Rule_Messages" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Confidence_Model" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Query_Reconciliation" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Prioritisation" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Input_Contract" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Finding_Contract" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="LLM_Integration" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="API" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Testing" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Extensibility" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Open_Questions" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Traceability" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Review_Log" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contents" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Definitions" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guideline_Profiles" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interpretations" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Derivations" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pipeline" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rules" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rule_Messages" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Confidence_Model" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Query_Reconciliation" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prioritisation" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Input_Contract" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Finding_Contract" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LLM_Integration" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Testing" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Extensibility" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Log" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Definitions'!$A$3:$C$50</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Rules'!$A$3:$R$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Rules'!$A$3:$Q$88</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Rule_Messages'!$A$3:$J$88</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -201,12 +201,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF9D6"/>
+        <fgColor rgb="00F2F6F3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F6F3"/>
+        <fgColor rgb="00FFF9D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -236,7 +236,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -320,17 +320,14 @@
     <xf numFmtId="9" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="9" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -369,7 +366,16 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -750,7 +756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -803,7 +809,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>1.1.1 — Step 2 review, round 1 applied</t>
+          <t>1.2.0 — rule logic confirmed</t>
         </is>
       </c>
     </row>
@@ -815,7 +821,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>DRAFT — round 2 review of the 14 amended rules</t>
+          <t>DRAFT — rule logic settled; Rule_Messages outstanding</t>
         </is>
       </c>
     </row>
@@ -827,7 +833,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -851,7 +857,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>v1.0.0, issued 2026-08-17</t>
+          <t>v1.1.1, issued 2026-08-19</t>
         </is>
       </c>
     </row>
@@ -899,144 +905,99 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>The 14 amended rules on Rules (R2 decision column), then Rule_Messages</t>
+          <t>Rule_Messages — the query wording. Rules is complete.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>HOW TO REVIEW THIS REVISION</t>
+          <t>WHERE THE REVIEW STANDS</t>
         </is>
       </c>
     </row>
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>•  Round 1 dispositioned all 85 rules: 70 Accept, 14 Discuss, 1 Reject. Every Discuss item is resolved on the Rules sheet.</t>
+          <t>•  Rules is COMPLETE. All 85 dispositioned at round 1 (70 accept, 14 discuss, 1 reject), and all 16 amended or explained rules confirmed at round 2 with no further comments.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>•  Your round-1 decision and comment are preserved on each rule, next to a Response / action column saying what was done.</t>
+          <t>•  The rule logic, severities, modes and confidence base rates are therefore settled. Both rounds are recorded on each rule and narrated on Review_Log.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>•  Only the amended rules need your attention now. Filter the Rules sheet on R1 decision to see them, and record your verdict in the yellow R2 decision column.</t>
+          <t>•  Rule_Messages has NOT been reviewed. It holds the query wording that reaches a site, so it is the one remaining surface before the Step 2 gate.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>•  A new Rationale / source column states where each threshold comes from — and says plainly where no guideline source exists, rather than implying one.</t>
+          <t>•  The rule pack is not frozen yet. It freezes when Rule_Messages is accepted — that is the gate, and Step 3 starts behind it.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>•  Review_Log carries the same record as a narrative, in review order, for anyone who was not in the round-1 discussion.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>•  Two rules are now RETIRED: TE-RS-010 (subsumed) and TE-RS-011 (rejected). Their ids are retained permanently and never reused.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="26" customHeight="1"/>
+          <t>•  Open_Questions still carries SQ-01 to SQ-09. SQ-08 was answered by the TE-BL-011 decision; SQ-01 and SQ-02 are covered by the rule-by-rule acceptance but have no separate recorded decision — confirm or correct them there.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1"/>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>WHAT CHANGED AT THIS REVISION</t>
+        </is>
+      </c>
+    </row>
     <row r="26" ht="26" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>WHAT CHANGED AT THIS REVISION</t>
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>•  Round-2 confirmations recorded against all 16 amended rules. No rule logic changed at this revision — this is a disposition record, not an edit.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="26" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>•  TE-RS-010 retired as subsumed by TE-RS-008, TE-RS-009 and TE-IR-001. TE-RS-011 retired as rejected.</t>
+          <t>•  The Rules sheet no longer offers a reviewer input column: it is complete, and its decision columns are now read-only history.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="26" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>•  TE-RS-003 gate widened as you suggested; the baseline comparison is now a message discriminator, not a condition.</t>
+          <t>•  Review_Log gains the round-2 outcome alongside round 1.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="26" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>•  TE-RS-007 severity lowered to INFO, which removes it from the default query worklist.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>•  TE-RS-002 and TE-RS-003 declared cascade children of TE-RS-001; TE-RS-008 suppressed behind its component rules, so one visit yields one query.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>•  TE-BL-011 and TE-FU-001 become CONDITIONAL on the sum being site-entered rather than system-derived. This answers SQ-08.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>•  TE-FU-007 now takes a per-visit assessment schedule from the protocol intake instead of a single interval.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>•  TE-FU-009 restricted to follow-up and excludes the too-small-to-measure state.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="26" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>•  TE-ST-003 resolves nodal axis from the CRF specification where no axis-type field is collected.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="26" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>•  Rationale added to TE-FU-004, TE-FU-005, TE-RS-014 and TE-XD-007; interpretations ID-05 and ID-06 amended.</t>
+          <t>•  Open_Questions gains a decision column, pre-filled where the two review rounds already settled the answer.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="22">
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="A27:F27"/>
     <mergeCell ref="A26:F26"/>
     <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A33:F33"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A32:F32"/>
     <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A35:F35"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="A20:F20"/>
@@ -1045,9 +1006,6 @@
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="B10:F10"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A30:F30"/>
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="B15:F15"/>
@@ -1108,9 +1066,9 @@
 # so certainty is never total. A 100% display would invite unread query issuance.</t>
         </is>
       </c>
-      <c r="B4" s="52" t="n"/>
-      <c r="C4" s="52" t="n"/>
-      <c r="D4" s="52" t="n"/>
+      <c r="B4" s="54" t="n"/>
+      <c r="C4" s="54" t="n"/>
+      <c r="D4" s="54" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
@@ -1449,9 +1407,9 @@
         f.status = RECURRENT</t>
         </is>
       </c>
-      <c r="B4" s="52" t="n"/>
-      <c r="C4" s="52" t="n"/>
-      <c r="D4" s="52" t="n"/>
+      <c r="B4" s="54" t="n"/>
+      <c r="C4" s="54" t="n"/>
+      <c r="D4" s="54" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -1546,9 +1504,9 @@
 it necessarily causes, so the reviewer fixes the baseline once instead of querying ten visits.</t>
         </is>
       </c>
-      <c r="B4" s="52" t="n"/>
-      <c r="C4" s="52" t="n"/>
-      <c r="D4" s="52" t="n"/>
+      <c r="B4" s="54" t="n"/>
+      <c r="C4" s="54" t="n"/>
+      <c r="D4" s="54" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -1571,9 +1529,9 @@
 where it does rather than having to trust the ordering.</t>
         </is>
       </c>
-      <c r="B7" s="52" t="n"/>
-      <c r="C7" s="52" t="n"/>
-      <c r="D7" s="52" t="n"/>
+      <c r="B7" s="54" t="n"/>
+      <c r="C7" s="54" t="n"/>
+      <c r="D7" s="54" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1648,7 +1606,7 @@
           <t>study</t>
         </is>
       </c>
-      <c r="B4" s="53" t="inlineStr">
+      <c r="B4" s="55" t="inlineStr">
         <is>
           <t>study_id</t>
         </is>
@@ -1671,7 +1629,7 @@
           <t>study</t>
         </is>
       </c>
-      <c r="B5" s="54" t="inlineStr">
+      <c r="B5" s="56" t="inlineStr">
         <is>
           <t>indication</t>
         </is>
@@ -1698,7 +1656,7 @@
           <t>study</t>
         </is>
       </c>
-      <c r="B6" s="53" t="inlineStr">
+      <c r="B6" s="55" t="inlineStr">
         <is>
           <t>guideline_version</t>
         </is>
@@ -1725,7 +1683,7 @@
           <t>protocol_config</t>
         </is>
       </c>
-      <c r="B7" s="54" t="inlineStr">
+      <c r="B7" s="56" t="inlineStr">
         <is>
           <t>(28 parameters)</t>
         </is>
@@ -1752,7 +1710,7 @@
           <t>subjects</t>
         </is>
       </c>
-      <c r="B8" s="53" t="inlineStr">
+      <c r="B8" s="55" t="inlineStr">
         <is>
           <t>subject_id, site_id, first_dose_date, discontinuation_date, death_date, has_measurable_disease_at_baseline</t>
         </is>
@@ -1775,7 +1733,7 @@
           <t>lesions</t>
         </is>
       </c>
-      <c r="B9" s="54" t="inlineStr">
+      <c r="B9" s="56" t="inlineStr">
         <is>
           <t>lesion_id, category, is_nodal, organ, location_detail, laterality, method, new_lesion_certainty, previously_irradiated</t>
         </is>
@@ -1802,7 +1760,7 @@
           <t>assessments</t>
         </is>
       </c>
-      <c r="B10" s="53" t="inlineStr">
+      <c r="B10" s="55" t="inlineStr">
         <is>
           <t>assessment_id, visit_name, visit_number, assessment_date, scan_dates, is_baseline, evaluator</t>
         </is>
@@ -1825,7 +1783,7 @@
           <t>measurements</t>
         </is>
       </c>
-      <c r="B11" s="54" t="inlineStr">
+      <c r="B11" s="56" t="inlineStr">
         <is>
           <t>assessment_id, lesion_id, value_mm, original_unit, axis_recorded, state, non_target_state, comment_text</t>
         </is>
@@ -1852,7 +1810,7 @@
           <t>reported_responses</t>
         </is>
       </c>
-      <c r="B12" s="53" t="inlineStr">
+      <c r="B12" s="55" t="inlineStr">
         <is>
           <t>target, non_target, new_lesion, overall, irecist, sum_of_diameters_reported, best_overall_response, progression_date</t>
         </is>
@@ -1879,7 +1837,7 @@
           <t>queries</t>
         </is>
       </c>
-      <c r="B13" s="54" t="inlineStr">
+      <c r="B13" s="56" t="inlineStr">
         <is>
           <t>query_id, query_text, answer_text, status, opened/answered/closed dates, tea_rule_id</t>
         </is>
@@ -1906,7 +1864,7 @@
           <t>cross_domain</t>
         </is>
       </c>
-      <c r="B14" s="53" t="inlineStr">
+      <c r="B14" s="55" t="inlineStr">
         <is>
           <t>exposure, anticancer_therapy, radiotherapy, procedures, adverse_events, lab_markers, performance_status</t>
         </is>
@@ -1933,7 +1891,7 @@
           <t>imaging_metadata</t>
         </is>
       </c>
-      <c r="B15" s="54" t="inlineStr">
+      <c r="B15" s="56" t="inlineStr">
         <is>
           <t>modality, scan_date, slice_thickness_mm, regions_imaged, contrast_used</t>
         </is>
@@ -2609,7 +2567,7 @@
           <t>Lesion organ, laterality, location text, description text, method, guideline extract</t>
         </is>
       </c>
-      <c r="D5" s="53" t="inlineStr">
+      <c r="D5" s="55" t="inlineStr">
         <is>
           <t>{is_non_measurable, category, confidence, rationale}</t>
         </is>
@@ -2631,7 +2589,7 @@
           <t>Non-target descriptions at this and the previous timepoint, target response, sum change, guideline extract</t>
         </is>
       </c>
-      <c r="D6" s="54" t="inlineStr">
+      <c r="D6" s="56" t="inlineStr">
         <is>
           <t>{supports_unequivocal, magnitude_comment, confidence, rationale}</t>
         </is>
@@ -2653,7 +2611,7 @@
           <t>Candidate finding summary; historical queries for the subject</t>
         </is>
       </c>
-      <c r="D7" s="53" t="inlineStr">
+      <c r="D7" s="55" t="inlineStr">
         <is>
           <t>{matches:[{query_id, relation, confidence}]}</t>
         </is>
@@ -2675,7 +2633,7 @@
           <t>Query text, answer text, current values of the queried fields  (NEW at review)</t>
         </is>
       </c>
-      <c r="D8" s="54" t="inlineStr">
+      <c r="D8" s="56" t="inlineStr">
         <is>
           <t>{classification, confidence, rationale, quoted_span}</t>
         </is>
@@ -2697,7 +2655,7 @@
           <t>Evidence object, rule metadata, message templates, guideline citation, indication context</t>
         </is>
       </c>
-      <c r="D9" s="53" t="inlineStr">
+      <c r="D9" s="55" t="inlineStr">
         <is>
           <t>{five narrative fields}</t>
         </is>
@@ -2719,7 +2677,7 @@
           <t>Protocol and imaging charter text  (NEW at review, AC-11)</t>
         </is>
       </c>
-      <c r="D10" s="54" t="inlineStr">
+      <c r="D10" s="56" t="inlineStr">
         <is>
           <t>{checkpoints:[{parameter, value_found, page_ref, confidence}]}</t>
         </is>
@@ -2895,9 +2853,9 @@
 log the event. The finding is still produced, with template text.</t>
         </is>
       </c>
-      <c r="B23" s="52" t="n"/>
-      <c r="C23" s="52" t="n"/>
-      <c r="D23" s="52" t="n"/>
+      <c r="B23" s="54" t="n"/>
+      <c r="C23" s="54" t="n"/>
+      <c r="D23" s="54" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3564,14 +3522,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="96" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="72" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="66" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -3584,7 +3543,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>For decision at the Step 2 gate.</t>
+          <t>For decision at the Step 2 gate. The status column records what the two review rounds already settled; the yellow columns are for the rest.</t>
         </is>
       </c>
     </row>
@@ -3606,10 +3565,15 @@
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
+          <t>Status after 2 rounds</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>Reviewer</t>
         </is>
@@ -3623,16 +3587,21 @@
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>Confirm the severity assigned to each of the 84 rules against sponsor conventions. Severity drives prioritisation and the database-lock criteria.</t>
-        </is>
-      </c>
-      <c r="C4" s="38" t="inlineStr">
+          <t>Confirm the severity assigned to each rule against sponsor conventions. Severity drives prioritisation and the database-lock criteria.</t>
+        </is>
+      </c>
+      <c r="C4" s="37" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="D4" s="33" t="n"/>
-      <c r="E4" s="34" t="n"/>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>Covered by the rule-by-rule acceptance — every accepted row carried its severity. No separate decision recorded; confirm or correct.</t>
+        </is>
+      </c>
+      <c r="E4" s="52" t="n"/>
+      <c r="F4" s="53" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="25" t="inlineStr">
@@ -3645,13 +3614,18 @@
           <t>Confirm the confidence base rate proposed for each rule (Open Item OI-02). These drive triage for every finding the agent produces.</t>
         </is>
       </c>
-      <c r="C5" s="55" t="inlineStr">
+      <c r="C5" s="57" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="D5" s="33" t="n"/>
-      <c r="E5" s="34" t="n"/>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>Covered by the rule-by-rule acceptance — every accepted row carried its base rate. No separate decision recorded; confirm or correct.</t>
+        </is>
+      </c>
+      <c r="E5" s="52" t="n"/>
+      <c r="F5" s="53" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="23" t="inlineStr">
@@ -3664,13 +3638,18 @@
           <t>Confirm the interpretation decisions ID-01 to ID-08, particularly the too-small-to-measure convention and the treatment of reappearing lesions.</t>
         </is>
       </c>
-      <c r="C6" s="38" t="inlineStr">
+      <c r="C6" s="37" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="D6" s="33" t="n"/>
-      <c r="E6" s="34" t="n"/>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Six accepted at round 1. ID-05 expanded and ID-06 amended, neither re-reviewed since.</t>
+        </is>
+      </c>
+      <c r="E6" s="52" t="n"/>
+      <c r="F6" s="53" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="25" t="inlineStr">
@@ -3688,8 +3667,13 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="D7" s="33" t="n"/>
-      <c r="E7" s="34" t="n"/>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>All three accepted as rules, but acceptance is not activation. They remain off by default pending this decision.</t>
+        </is>
+      </c>
+      <c r="E7" s="52" t="n"/>
+      <c r="F7" s="53" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="23" t="inlineStr">
@@ -3707,8 +3691,13 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="D8" s="33" t="n"/>
-      <c r="E8" s="34" t="n"/>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>OPEN — settle this alongside the Rule_Messages review, since it governs all 85 query texts at once.</t>
+        </is>
+      </c>
+      <c r="E8" s="52" t="n"/>
+      <c r="F8" s="53" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="25" t="inlineStr">
@@ -3726,8 +3715,13 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="D9" s="33" t="n"/>
-      <c r="E9" s="34" t="n"/>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>OPEN. Defaults are on the Interpretations sheet under ID-05.</t>
+        </is>
+      </c>
+      <c r="E9" s="52" t="n"/>
+      <c r="F9" s="53" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="23" t="inlineStr">
@@ -3745,8 +3739,13 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="D10" s="33" t="n"/>
-      <c r="E10" s="34" t="n"/>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>OPEN. TE-RS-007 joined this group at round 1 when it dropped to INFO.</t>
+        </is>
+      </c>
+      <c r="E10" s="52" t="n"/>
+      <c r="F10" s="53" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="25" t="inlineStr">
@@ -3759,13 +3758,26 @@
           <t>Confirm whether the Veeva CRF collects a sum of diameters at all. If it is derived only, TE-BL-011 and TE-FU-001 do not apply and weight shifts onto TE-RS-001.</t>
         </is>
       </c>
-      <c r="C11" s="55" t="inlineStr">
+      <c r="C11" s="57" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="D11" s="33" t="n"/>
-      <c r="E11" s="34" t="n"/>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>ANSWERED at round 1. Both rules are CONDITIONAL on a site-entered sum, determined from the CRF specification at the AC-11 intake.</t>
+        </is>
+      </c>
+      <c r="E11" s="52" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="F11" s="53" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="23" t="inlineStr">
@@ -3778,21 +3790,26 @@
           <t>Confirm the confidence threshold at which a JUSTIFIED_BY_ANSWER suppression may occur without human confirmation. Currently 0.70, and never for CRITICAL or MAJOR.</t>
         </is>
       </c>
-      <c r="C12" s="38" t="inlineStr">
+      <c r="C12" s="37" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="D12" s="33" t="n"/>
-      <c r="E12" s="34" t="n"/>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>OPEN. TE-QM-002 was accepted at round 1, but the threshold itself has no recorded decision.</t>
+        </is>
+      </c>
+      <c r="E12" s="52" t="n"/>
+      <c r="F12" s="53" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="D4:D12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E4:E12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Accept,Amend,Reject,Discuss"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3826,7 +3843,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>TEA-SPEC-001 v1.1.0 — Step 2 review round 1 applied; round 2 covers the amended rules and Rule_Messages.</t>
+          <t>TEA-SPEC-001 v1.2.0 — rule logic confirmed over two review rounds. Rule_Messages is the one surface still to review.</t>
         </is>
       </c>
     </row>
@@ -3933,12 +3950,12 @@
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>re-check</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
         <is>
-          <t>ID-05 expanded, ID-06 amended</t>
+          <t>ID-05, ID-06 not re-reviewed</t>
         </is>
       </c>
     </row>
@@ -3950,7 +3967,7 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>Round-1 disposition and resolutions</t>
+          <t>Both rounds: what was raised and how it closed</t>
         </is>
       </c>
       <c r="C8" s="16">
@@ -3960,7 +3977,7 @@
       <c r="D8" s="14" t="inlineStr"/>
       <c r="E8" s="15" t="inlineStr">
         <is>
-          <t>18 items resolved</t>
+          <t>18 items, all resolved</t>
         </is>
       </c>
     </row>
@@ -4029,12 +4046,12 @@
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
-          <t>round 2</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
         <is>
-          <t>14 amended rules to confirm</t>
+          <t>both rounds recorded</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4072,12 @@
       </c>
       <c r="D12" s="17" t="inlineStr">
         <is>
-          <t>round 2</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E12" s="15" t="inlineStr">
         <is>
-          <t>not yet reviewed</t>
+          <t>the remaining surface</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4286,7 @@
       </c>
       <c r="E22" s="15" t="inlineStr">
         <is>
-          <t>SQ-02 and SQ-09 are new</t>
+          <t>SQ-08 answered; 8 open</t>
         </is>
       </c>
     </row>
@@ -4828,27 +4845,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="56" customWidth="1" min="3" max="3"/>
-    <col width="78" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>Step 2 review — round 1 disposition</t>
+          <t>Step 2 review — rounds 1 and 2</t>
         </is>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>Daniel, 2026-08-19. 85 rules and 8 interpretation decisions dispositioned. Everything raised is resolved below; nothing is left pending a later conversation.</t>
+          <t>Round 1 (2026-08-19) raised 15 items across 85 rules; round 2 (2026-08-21) confirmed every resolution with no further comments. The rule logic is settled. Rule_Messages is not yet reviewed.</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4878,7 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
@@ -4876,6 +4894,11 @@
       <c r="E3" s="10" t="inlineStr">
         <is>
           <t>Outcome</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>R2</t>
         </is>
       </c>
     </row>
@@ -4905,6 +4928,11 @@
           <t>Amended</t>
         </is>
       </c>
+      <c r="F4" s="24" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="25" t="inlineStr">
@@ -4932,6 +4960,11 @@
           <t>Amended</t>
         </is>
       </c>
+      <c r="F5" s="24" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="23" t="inlineStr">
@@ -4955,6 +4988,11 @@
           <t>Amended</t>
         </is>
       </c>
+      <c r="F6" s="24" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="25" t="inlineStr">
@@ -4982,6 +5020,11 @@
           <t>Amended</t>
         </is>
       </c>
+      <c r="F7" s="24" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="23" t="inlineStr">
@@ -5009,6 +5052,11 @@
           <t>Amended</t>
         </is>
       </c>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="25" t="inlineStr">
@@ -5036,6 +5084,11 @@
           <t>Amended</t>
         </is>
       </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="23" t="inlineStr">
@@ -5061,6 +5114,11 @@
       <c r="E10" s="24" t="inlineStr">
         <is>
           <t>Amended</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>Accept</t>
         </is>
       </c>
     </row>
@@ -5094,6 +5152,11 @@
           <t>Amended</t>
         </is>
       </c>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="23" t="inlineStr">
@@ -5121,6 +5184,11 @@
           <t>Amended</t>
         </is>
       </c>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="25" t="inlineStr">
@@ -5148,6 +5216,11 @@
           <t>Amended</t>
         </is>
       </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="23" t="inlineStr">
@@ -5175,6 +5248,11 @@
           <t>Amended</t>
         </is>
       </c>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="25" t="inlineStr">
@@ -5203,6 +5281,11 @@
           <t>Retired</t>
         </is>
       </c>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="23" t="inlineStr">
@@ -5210,7 +5293,7 @@
           <t>TE-RS-011</t>
         </is>
       </c>
-      <c r="B16" s="38" t="inlineStr">
+      <c r="B16" s="37" t="inlineStr">
         <is>
           <t>Reject</t>
         </is>
@@ -5228,6 +5311,11 @@
       <c r="E16" s="24" t="inlineStr">
         <is>
           <t>Retired</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>Accept</t>
         </is>
       </c>
     </row>
@@ -5257,6 +5345,11 @@
           <t>Amended</t>
         </is>
       </c>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="23" t="inlineStr">
@@ -5284,6 +5377,11 @@
           <t>Amended</t>
         </is>
       </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="25" t="inlineStr">
@@ -5311,6 +5409,11 @@
           <t>Amended</t>
         </is>
       </c>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="23" t="inlineStr">
@@ -5338,6 +5441,11 @@
           <t>Amended</t>
         </is>
       </c>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>not re-reviewed</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="25" t="inlineStr">
@@ -5369,79 +5477,105 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Round 1 summary</t>
+          <t>Where the review stands</t>
         </is>
       </c>
     </row>
     <row r="24" ht="44" customHeight="1">
       <c r="A24" s="30" t="inlineStr">
         <is>
-          <t>Rules</t>
+          <t>Round 1</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>85 dispositioned — 70 Accept, 14 Discuss, 1 Reject. 12 rules amended, 2 retired, 1 unchanged with rationale added.</t>
+          <t>85 rules dispositioned — 70 Accept, 14 Discuss, 1 Reject. 12 rules amended, 2 retired, 1 unchanged with rationale added.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="44" customHeight="1">
       <c r="A25" s="30" t="inlineStr">
         <is>
-          <t>Interpretations</t>
+          <t>Round 2</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>8 dispositioned — 6 Accept, 1 Discuss (ID-05, expanded), 1 Amend (ID-06, applied).</t>
+          <t>All 16 amended or explained rules confirmed Accept, no comments. The rule logic, severities, modes and confidence base rates are settled.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="44" customHeight="1">
       <c r="A26" s="30" t="inlineStr">
         <is>
-          <t>Raised proactively</t>
+          <t>Interpretations</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>TE-FU-001 was accepted at round 1 but carries the identical CRF dependency as TE-BL-011, so it was amended alongside it. Applying the guard at baseline but not at follow-up would be incoherent.</t>
+          <t>8 dispositioned — 6 Accept, 1 Discuss (ID-05, expanded), 1 Amend (ID-06, applied).</t>
         </is>
       </c>
     </row>
     <row r="27" ht="44" customHeight="1">
       <c r="A27" s="30" t="inlineStr">
         <is>
-          <t>Answered</t>
+          <t>Raised proactively</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>SQ-08 is settled by the TE-BL-011 decision: the sum check is CONDITIONAL on the sum being site-entered, determined from the CRF specification at intake.</t>
+          <t>TE-FU-001 was accepted at round 1 but carries the identical CRF dependency as TE-BL-011, so it was amended alongside it. Applying the guard at baseline but not at follow-up would be incoherent.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="44" customHeight="1">
       <c r="A28" s="30" t="inlineStr">
         <is>
+          <t>Answered</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>SQ-08 is settled by the TE-BL-011 decision: the sum check is CONDITIONAL on the sum being site-entered, determined from the CRF specification at intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="44" customHeight="1">
+      <c r="A29" s="30" t="inlineStr">
+        <is>
           <t>Still open</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>SQ-01 to SQ-07 and SQ-09 remain for the Step 2 gate. Rule_Messages has not been reviewed yet — that is the round-2 surface alongside the 14 amended rules.</t>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Rule_Messages has not been reviewed — the query wording that reaches a site. That is the last surface before the Step 2 gate, and the rule pack cannot freeze until it is accepted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="44" customHeight="1">
+      <c r="A30" s="30" t="inlineStr">
+        <is>
+          <t>Not re-reviewed</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Interpretations ID-05 and ID-06 were amended at round 1 and were not looked at again in round 2. They are flagged rather than assumed accepted.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="B28:E28"/>
+  <mergeCells count="9">
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B27:F27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7818,20 +7952,20 @@
     <col width="66" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="11" customWidth="1" min="17" max="17"/>
-    <col width="32" customWidth="1" min="18" max="18"/>
+    <col width="2" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>Rule catalog — 85 review points, 83 live</t>
+          <t>Rule catalog — 85 review points, 83 live — REVIEW COMPLETE</t>
         </is>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>Round 1 of the Step 2 review is recorded here: your decision and comment, and what was done about it. Record round-2 verdicts in the yellow R2 decision column. Retired rules are greyed and keep their ids permanently.</t>
+          <t>Both review rounds are recorded here and no further input is needed on this sheet. R2 shows a dash where a rule was accepted outright at round 1 and never re-opened. Retired rules are greyed and keep their ids permanently.</t>
         </is>
       </c>
     </row>
@@ -7918,14 +8052,10 @@
       </c>
       <c r="Q3" s="10" t="inlineStr">
         <is>
-          <t>Reviewer</t>
-        </is>
-      </c>
-      <c r="R3" s="10" t="inlineStr">
-        <is>
-          <t>Comment</t>
-        </is>
-      </c>
+          <t>R2 by</t>
+        </is>
+      </c>
+      <c r="R3" s="10" t="inlineStr"/>
     </row>
     <row r="4" ht="96" customHeight="1">
       <c r="A4" s="11" t="inlineStr">
@@ -7989,9 +8119,12 @@
       </c>
       <c r="N4" s="12" t="inlineStr"/>
       <c r="O4" s="12" t="inlineStr"/>
-      <c r="P4" s="33" t="n"/>
-      <c r="Q4" s="33" t="n"/>
-      <c r="R4" s="34" t="n"/>
+      <c r="P4" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q4" s="24" t="inlineStr"/>
     </row>
     <row r="5" ht="96" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
@@ -8029,7 +8162,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="H5" s="35" t="n">
+      <c r="H5" s="33" t="n">
         <v>0.72</v>
       </c>
       <c r="I5" s="12" t="inlineStr">
@@ -8052,9 +8185,12 @@
       </c>
       <c r="N5" s="12" t="inlineStr"/>
       <c r="O5" s="12" t="inlineStr"/>
-      <c r="P5" s="33" t="n"/>
-      <c r="Q5" s="33" t="n"/>
-      <c r="R5" s="34" t="n"/>
+      <c r="P5" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q5" s="24" t="inlineStr"/>
     </row>
     <row r="6" ht="96" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
@@ -8133,14 +8269,21 @@
           <t>Some CRF doesn't collect the type of size, instead the CRF directly asks sites to enter size based on the appropriate type. Consider the field name directly mentions right size type, if there's no size type selection field in the CRF.</t>
         </is>
       </c>
-      <c r="O6" s="36" t="inlineStr">
+      <c r="O6" s="34" t="inlineStr">
         <is>
           <t>AMENDED. Axis type is now resolved at ingestion in priority order rather than assumed to be a collected field: an explicit axis-type field if one exists, otherwise the axis implied by the CRF field itself as declared in the structured CRF specification, otherwise the protocol default. The rule fires only when no source establishes that a nodal measurement is a short axis.</t>
         </is>
       </c>
-      <c r="P6" s="33" t="n"/>
-      <c r="Q6" s="33" t="n"/>
-      <c r="R6" s="34" t="n"/>
+      <c r="P6" s="35" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="Q6" s="24" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="96" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
@@ -8163,7 +8306,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E7" s="37" t="inlineStr">
+      <c r="E7" s="36" t="inlineStr">
         <is>
           <t>MINOR</t>
         </is>
@@ -8201,9 +8344,12 @@
       </c>
       <c r="N7" s="12" t="inlineStr"/>
       <c r="O7" s="12" t="inlineStr"/>
-      <c r="P7" s="33" t="n"/>
-      <c r="Q7" s="33" t="n"/>
-      <c r="R7" s="34" t="n"/>
+      <c r="P7" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q7" s="24" t="inlineStr"/>
     </row>
     <row r="8" ht="96" customHeight="1">
       <c r="A8" s="11" t="inlineStr">
@@ -8226,7 +8372,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E8" s="37" t="inlineStr">
+      <c r="E8" s="36" t="inlineStr">
         <is>
           <t>MINOR</t>
         </is>
@@ -8263,9 +8409,12 @@
       </c>
       <c r="N8" s="12" t="inlineStr"/>
       <c r="O8" s="12" t="inlineStr"/>
-      <c r="P8" s="33" t="n"/>
-      <c r="Q8" s="33" t="n"/>
-      <c r="R8" s="34" t="n"/>
+      <c r="P8" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q8" s="24" t="inlineStr"/>
     </row>
     <row r="9" ht="96" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
@@ -8288,7 +8437,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E9" s="38" t="inlineStr">
+      <c r="E9" s="37" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -8330,9 +8479,12 @@
       </c>
       <c r="N9" s="12" t="inlineStr"/>
       <c r="O9" s="12" t="inlineStr"/>
-      <c r="P9" s="33" t="n"/>
-      <c r="Q9" s="33" t="n"/>
-      <c r="R9" s="34" t="n"/>
+      <c r="P9" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q9" s="24" t="inlineStr"/>
     </row>
     <row r="10" ht="96" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
@@ -8355,7 +8507,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E10" s="38" t="inlineStr">
+      <c r="E10" s="37" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -8393,9 +8545,12 @@
       </c>
       <c r="N10" s="12" t="inlineStr"/>
       <c r="O10" s="12" t="inlineStr"/>
-      <c r="P10" s="33" t="n"/>
-      <c r="Q10" s="33" t="n"/>
-      <c r="R10" s="34" t="n"/>
+      <c r="P10" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q10" s="24" t="inlineStr"/>
     </row>
     <row r="11" ht="96" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
@@ -8418,7 +8573,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E11" s="38" t="inlineStr">
+      <c r="E11" s="37" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -8459,9 +8614,12 @@
       </c>
       <c r="N11" s="12" t="inlineStr"/>
       <c r="O11" s="12" t="inlineStr"/>
-      <c r="P11" s="33" t="n"/>
-      <c r="Q11" s="33" t="n"/>
-      <c r="R11" s="34" t="n"/>
+      <c r="P11" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q11" s="24" t="inlineStr"/>
     </row>
     <row r="12" ht="96" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
@@ -8484,7 +8642,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E12" s="38" t="inlineStr">
+      <c r="E12" s="37" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -8522,9 +8680,12 @@
       </c>
       <c r="N12" s="12" t="inlineStr"/>
       <c r="O12" s="12" t="inlineStr"/>
-      <c r="P12" s="33" t="n"/>
-      <c r="Q12" s="33" t="n"/>
-      <c r="R12" s="34" t="n"/>
+      <c r="P12" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q12" s="24" t="inlineStr"/>
     </row>
     <row r="13" ht="96" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
@@ -8585,9 +8746,12 @@
       </c>
       <c r="N13" s="12" t="inlineStr"/>
       <c r="O13" s="12" t="inlineStr"/>
-      <c r="P13" s="33" t="n"/>
-      <c r="Q13" s="33" t="n"/>
-      <c r="R13" s="34" t="n"/>
+      <c r="P13" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q13" s="24" t="inlineStr"/>
     </row>
     <row r="14" ht="96" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
@@ -8625,7 +8789,7 @@
           <t>CONDITIONAL</t>
         </is>
       </c>
-      <c r="H14" s="35" t="n">
+      <c r="H14" s="33" t="n">
         <v>0.7</v>
       </c>
       <c r="I14" s="12" t="inlineStr">
@@ -8651,9 +8815,12 @@
       </c>
       <c r="N14" s="12" t="inlineStr"/>
       <c r="O14" s="12" t="inlineStr"/>
-      <c r="P14" s="33" t="n"/>
-      <c r="Q14" s="33" t="n"/>
-      <c r="R14" s="34" t="n"/>
+      <c r="P14" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q14" s="24" t="inlineStr"/>
     </row>
     <row r="15" ht="96" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
@@ -8691,7 +8858,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="H15" s="35" t="n">
+      <c r="H15" s="33" t="n">
         <v>0.65</v>
       </c>
       <c r="I15" s="12" t="inlineStr">
@@ -8724,9 +8891,12 @@
       </c>
       <c r="N15" s="12" t="inlineStr"/>
       <c r="O15" s="12" t="inlineStr"/>
-      <c r="P15" s="33" t="n"/>
-      <c r="Q15" s="33" t="n"/>
-      <c r="R15" s="34" t="n"/>
+      <c r="P15" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q15" s="24" t="inlineStr"/>
     </row>
     <row r="16" ht="96" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
@@ -8764,7 +8934,7 @@
           <t>CONDITIONAL</t>
         </is>
       </c>
-      <c r="H16" s="35" t="n">
+      <c r="H16" s="33" t="n">
         <v>0.72</v>
       </c>
       <c r="I16" s="12" t="inlineStr">
@@ -8791,9 +8961,12 @@
       </c>
       <c r="N16" s="12" t="inlineStr"/>
       <c r="O16" s="12" t="inlineStr"/>
-      <c r="P16" s="33" t="n"/>
-      <c r="Q16" s="33" t="n"/>
-      <c r="R16" s="34" t="n"/>
+      <c r="P16" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q16" s="24" t="inlineStr"/>
     </row>
     <row r="17" ht="96" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
@@ -8816,7 +8989,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E17" s="38" t="inlineStr">
+      <c r="E17" s="37" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -8854,9 +9027,12 @@
       </c>
       <c r="N17" s="12" t="inlineStr"/>
       <c r="O17" s="12" t="inlineStr"/>
-      <c r="P17" s="33" t="n"/>
-      <c r="Q17" s="33" t="n"/>
-      <c r="R17" s="34" t="n"/>
+      <c r="P17" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q17" s="24" t="inlineStr"/>
     </row>
     <row r="18" ht="96" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
@@ -8921,9 +9097,12 @@
       </c>
       <c r="N18" s="12" t="inlineStr"/>
       <c r="O18" s="12" t="inlineStr"/>
-      <c r="P18" s="33" t="n"/>
-      <c r="Q18" s="33" t="n"/>
-      <c r="R18" s="34" t="n"/>
+      <c r="P18" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q18" s="24" t="inlineStr"/>
     </row>
     <row r="19" ht="96" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
@@ -9000,14 +9179,21 @@
           <t>In case of the CRF not collecting manual entry for the reported sum, this rule should be ignored. The LLM needs to identify study's CRF capture the information by CRF specification.</t>
         </is>
       </c>
-      <c r="O19" s="36" t="inlineStr">
+      <c r="O19" s="34" t="inlineStr">
         <is>
           <t>AMENDED, and this answers SQ-08. Status moves from ACTIVE to CONDITIONAL: the rule requires a site-entered sum field. Whether the sum is site-entered or system-derived is determined from the structured CRF specification at the AC-11 intake, and a derived sum deactivates the rule with an explicit NOT_EVALUATED in the coverage report rather than a silent pass. Applied to TE-FU-001 as well, which carries the identical condition at follow-up.</t>
         </is>
       </c>
-      <c r="P19" s="33" t="n"/>
-      <c r="Q19" s="33" t="n"/>
-      <c r="R19" s="34" t="n"/>
+      <c r="P19" s="35" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="Q19" s="24" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="96" customHeight="1">
       <c r="A20" s="11" t="inlineStr">
@@ -9030,7 +9216,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E20" s="37" t="inlineStr">
+      <c r="E20" s="36" t="inlineStr">
         <is>
           <t>MINOR</t>
         </is>
@@ -9045,7 +9231,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="H20" s="39" t="n">
+      <c r="H20" s="38" t="n">
         <v>0.35</v>
       </c>
       <c r="I20" s="12" t="inlineStr">
@@ -9068,9 +9254,12 @@
       </c>
       <c r="N20" s="12" t="inlineStr"/>
       <c r="O20" s="12" t="inlineStr"/>
-      <c r="P20" s="33" t="n"/>
-      <c r="Q20" s="33" t="n"/>
-      <c r="R20" s="34" t="n"/>
+      <c r="P20" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q20" s="24" t="inlineStr"/>
     </row>
     <row r="21" ht="96" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
@@ -9130,9 +9319,12 @@
       </c>
       <c r="N21" s="12" t="inlineStr"/>
       <c r="O21" s="12" t="inlineStr"/>
-      <c r="P21" s="33" t="n"/>
-      <c r="Q21" s="33" t="n"/>
-      <c r="R21" s="34" t="n"/>
+      <c r="P21" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q21" s="24" t="inlineStr"/>
     </row>
     <row r="22" ht="96" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
@@ -9155,7 +9347,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E22" s="37" t="inlineStr">
+      <c r="E22" s="36" t="inlineStr">
         <is>
           <t>MINOR</t>
         </is>
@@ -9170,7 +9362,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="H22" s="35" t="n">
+      <c r="H22" s="33" t="n">
         <v>0.55</v>
       </c>
       <c r="I22" s="12" t="inlineStr">
@@ -9193,9 +9385,12 @@
       </c>
       <c r="N22" s="12" t="inlineStr"/>
       <c r="O22" s="12" t="inlineStr"/>
-      <c r="P22" s="33" t="n"/>
-      <c r="Q22" s="33" t="n"/>
-      <c r="R22" s="34" t="n"/>
+      <c r="P22" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q22" s="24" t="inlineStr"/>
     </row>
     <row r="23" ht="96" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
@@ -9218,7 +9413,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E23" s="37" t="inlineStr">
+      <c r="E23" s="36" t="inlineStr">
         <is>
           <t>MINOR</t>
         </is>
@@ -9233,7 +9428,7 @@
           <t>CONDITIONAL</t>
         </is>
       </c>
-      <c r="H23" s="35" t="n">
+      <c r="H23" s="33" t="n">
         <v>0.6</v>
       </c>
       <c r="I23" s="12" t="inlineStr">
@@ -9260,9 +9455,12 @@
       </c>
       <c r="N23" s="12" t="inlineStr"/>
       <c r="O23" s="12" t="inlineStr"/>
-      <c r="P23" s="33" t="n"/>
-      <c r="Q23" s="33" t="n"/>
-      <c r="R23" s="34" t="n"/>
+      <c r="P23" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q23" s="24" t="inlineStr"/>
     </row>
     <row r="24" ht="96" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
@@ -9295,12 +9493,12 @@
           <t>LLM_ADJUDICATED</t>
         </is>
       </c>
-      <c r="G24" s="40" t="inlineStr">
+      <c r="G24" s="39" t="inlineStr">
         <is>
           <t>PROPOSED_OPTIONAL</t>
         </is>
       </c>
-      <c r="H24" s="35" t="n">
+      <c r="H24" s="33" t="n">
         <v>0.55</v>
       </c>
       <c r="I24" s="12" t="inlineStr">
@@ -9323,9 +9521,12 @@
       </c>
       <c r="N24" s="12" t="inlineStr"/>
       <c r="O24" s="12" t="inlineStr"/>
-      <c r="P24" s="33" t="n"/>
-      <c r="Q24" s="33" t="n"/>
-      <c r="R24" s="34" t="n"/>
+      <c r="P24" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q24" s="24" t="inlineStr"/>
     </row>
     <row r="25" ht="96" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
@@ -9385,9 +9586,12 @@
       </c>
       <c r="N25" s="12" t="inlineStr"/>
       <c r="O25" s="12" t="inlineStr"/>
-      <c r="P25" s="33" t="n"/>
-      <c r="Q25" s="33" t="n"/>
-      <c r="R25" s="34" t="n"/>
+      <c r="P25" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q25" s="24" t="inlineStr"/>
     </row>
     <row r="26" ht="96" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
@@ -9460,14 +9664,21 @@
         </is>
       </c>
       <c r="N26" s="12" t="inlineStr"/>
-      <c r="O26" s="36" t="inlineStr">
+      <c r="O26" s="34" t="inlineStr">
         <is>
           <t>AMENDED alongside TE-BL-011, which carries the identical condition. Accepted at round 1, but the same CRF-dependency applies at follow-up and the pair must move together.</t>
         </is>
       </c>
-      <c r="P26" s="33" t="n"/>
-      <c r="Q26" s="33" t="n"/>
-      <c r="R26" s="34" t="n"/>
+      <c r="P26" s="35" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="Q26" s="24" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="96" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
@@ -9528,9 +9739,12 @@
       </c>
       <c r="N27" s="12" t="inlineStr"/>
       <c r="O27" s="12" t="inlineStr"/>
-      <c r="P27" s="33" t="n"/>
-      <c r="Q27" s="33" t="n"/>
-      <c r="R27" s="34" t="n"/>
+      <c r="P27" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q27" s="24" t="inlineStr"/>
     </row>
     <row r="28" ht="96" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
@@ -9592,9 +9806,12 @@
       </c>
       <c r="N28" s="12" t="inlineStr"/>
       <c r="O28" s="12" t="inlineStr"/>
-      <c r="P28" s="33" t="n"/>
-      <c r="Q28" s="33" t="n"/>
-      <c r="R28" s="34" t="n"/>
+      <c r="P28" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q28" s="24" t="inlineStr"/>
     </row>
     <row r="29" ht="96" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
@@ -9617,7 +9834,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E29" s="37" t="inlineStr">
+      <c r="E29" s="36" t="inlineStr">
         <is>
           <t>MINOR</t>
         </is>
@@ -9632,7 +9849,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="H29" s="39" t="n">
+      <c r="H29" s="38" t="n">
         <v>0.45</v>
       </c>
       <c r="I29" s="12" t="inlineStr">
@@ -9664,14 +9881,21 @@
           <t>Provide the rationale insisting the proposed threshold. What material or information is referred to make this validation rule.</t>
         </is>
       </c>
-      <c r="O29" s="36" t="inlineStr">
+      <c r="O29" s="34" t="inlineStr">
         <is>
           <t>RATIONALE ADDED. These thresholds are not drawn from RECIST — the guideline sets no outlier limits. They are heuristics aimed at transcription error, and they are declared as such rather than dressed up with a citation. Proposed for calibration against the golden dataset at Step 3, where the false-positive rate can actually be measured.</t>
         </is>
       </c>
-      <c r="P29" s="33" t="n"/>
-      <c r="Q29" s="33" t="n"/>
-      <c r="R29" s="34" t="n"/>
+      <c r="P29" s="35" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="Q29" s="24" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="96" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
@@ -9740,14 +9964,21 @@
           <t>Provide the rationale insisting the proposed threshold. What material or information is referred to make this validation rule.</t>
         </is>
       </c>
-      <c r="O30" s="36" t="inlineStr">
+      <c r="O30" s="34" t="inlineStr">
         <is>
           <t>RATIONALE ADDED. This rule carries no numeric threshold; the parameter in it is the interpretation decision ID-01, which is a protocol question rather than a guideline constant.</t>
         </is>
       </c>
-      <c r="P30" s="33" t="n"/>
-      <c r="Q30" s="33" t="n"/>
-      <c r="R30" s="34" t="n"/>
+      <c r="P30" s="35" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="Q30" s="24" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="96" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
@@ -9770,7 +10001,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E31" s="37" t="inlineStr">
+      <c r="E31" s="36" t="inlineStr">
         <is>
           <t>MINOR</t>
         </is>
@@ -9785,7 +10016,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="H31" s="35" t="n">
+      <c r="H31" s="33" t="n">
         <v>0.7</v>
       </c>
       <c r="I31" s="12" t="inlineStr">
@@ -9808,9 +10039,12 @@
       </c>
       <c r="N31" s="12" t="inlineStr"/>
       <c r="O31" s="12" t="inlineStr"/>
-      <c r="P31" s="33" t="n"/>
-      <c r="Q31" s="33" t="n"/>
-      <c r="R31" s="34" t="n"/>
+      <c r="P31" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q31" s="24" t="inlineStr"/>
     </row>
     <row r="32" ht="96" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
@@ -9896,14 +10130,21 @@
           <t>The proposed condition is fine. Since a protocol may define different assessment window for particular assessment timing, consider to get information about study's individual tumor assessment window period.</t>
         </is>
       </c>
-      <c r="O32" s="36" t="inlineStr">
+      <c r="O32" s="34" t="inlineStr">
         <is>
           <t>AMENDED. The scalar interval and window are replaced by a per-visit schedule captured at the AC-11 protocol intake, so a protocol that tightens or widens the window at particular timepoints is honoured. The scalar remains as a fallback for protocols with a uniform interval.</t>
         </is>
       </c>
-      <c r="P32" s="33" t="n"/>
-      <c r="Q32" s="33" t="n"/>
-      <c r="R32" s="34" t="n"/>
+      <c r="P32" s="35" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="Q32" s="24" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="96" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
@@ -9964,9 +10205,12 @@
       </c>
       <c r="N33" s="12" t="inlineStr"/>
       <c r="O33" s="12" t="inlineStr"/>
-      <c r="P33" s="33" t="n"/>
-      <c r="Q33" s="33" t="n"/>
-      <c r="R33" s="34" t="n"/>
+      <c r="P33" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q33" s="24" t="inlineStr"/>
     </row>
     <row r="34" ht="96" customHeight="1">
       <c r="A34" s="11" t="inlineStr">
@@ -9989,7 +10233,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E34" s="38" t="inlineStr">
+      <c r="E34" s="37" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -10038,14 +10282,21 @@
           <t>The proposed condition could be applied to follow-up assessment? It's okay to check at baseline's tumor identification, but I'm not sure to check under follow-up assessment.</t>
         </is>
       </c>
-      <c r="O34" s="36" t="inlineStr">
+      <c r="O34" s="34" t="inlineStr">
         <is>
           <t>AMENDED, and the scope was the wrong way round. The rule is only meaningful at follow-up: a nodal target cannot be absent at baseline, since it was selected for having a short axis of at least 15 mm. What it catches is a node recorded as absent or zero at follow-up once it has normalised, which drops it out of the sum and produces a falsely low sum and a spurious response. The rule is now explicitly restricted to follow-up, and the too-small-to-measure state is excluded so that ID-02 handling is not flagged as an error.</t>
         </is>
       </c>
-      <c r="P34" s="33" t="n"/>
-      <c r="Q34" s="33" t="n"/>
-      <c r="R34" s="34" t="n"/>
+      <c r="P34" s="35" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="Q34" s="24" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="96" customHeight="1">
       <c r="A35" s="11" t="inlineStr">
@@ -10068,7 +10319,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E35" s="37" t="inlineStr">
+      <c r="E35" s="36" t="inlineStr">
         <is>
           <t>MINOR</t>
         </is>
@@ -10105,9 +10356,12 @@
       </c>
       <c r="N35" s="12" t="inlineStr"/>
       <c r="O35" s="12" t="inlineStr"/>
-      <c r="P35" s="33" t="n"/>
-      <c r="Q35" s="33" t="n"/>
-      <c r="R35" s="34" t="n"/>
+      <c r="P35" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q35" s="24" t="inlineStr"/>
     </row>
     <row r="36" ht="96" customHeight="1">
       <c r="A36" s="11" t="inlineStr">
@@ -10172,9 +10426,12 @@
       </c>
       <c r="N36" s="12" t="inlineStr"/>
       <c r="O36" s="12" t="inlineStr"/>
-      <c r="P36" s="33" t="n"/>
-      <c r="Q36" s="33" t="n"/>
-      <c r="R36" s="34" t="n"/>
+      <c r="P36" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q36" s="24" t="inlineStr"/>
     </row>
     <row r="37" ht="96" customHeight="1">
       <c r="A37" s="11" t="inlineStr">
@@ -10197,7 +10454,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E37" s="37" t="inlineStr">
+      <c r="E37" s="36" t="inlineStr">
         <is>
           <t>MINOR</t>
         </is>
@@ -10235,9 +10492,12 @@
       </c>
       <c r="N37" s="12" t="inlineStr"/>
       <c r="O37" s="12" t="inlineStr"/>
-      <c r="P37" s="33" t="n"/>
-      <c r="Q37" s="33" t="n"/>
-      <c r="R37" s="34" t="n"/>
+      <c r="P37" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q37" s="24" t="inlineStr"/>
     </row>
     <row r="38" ht="96" customHeight="1">
       <c r="A38" s="11" t="inlineStr">
@@ -10260,7 +10520,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E38" s="37" t="inlineStr">
+      <c r="E38" s="36" t="inlineStr">
         <is>
           <t>MINOR</t>
         </is>
@@ -10275,7 +10535,7 @@
           <t>CONDITIONAL</t>
         </is>
       </c>
-      <c r="H38" s="35" t="n">
+      <c r="H38" s="33" t="n">
         <v>0.58</v>
       </c>
       <c r="I38" s="12" t="inlineStr">
@@ -10301,9 +10561,12 @@
       </c>
       <c r="N38" s="12" t="inlineStr"/>
       <c r="O38" s="12" t="inlineStr"/>
-      <c r="P38" s="33" t="n"/>
-      <c r="Q38" s="33" t="n"/>
-      <c r="R38" s="34" t="n"/>
+      <c r="P38" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q38" s="24" t="inlineStr"/>
     </row>
     <row r="39" ht="96" customHeight="1">
       <c r="A39" s="11" t="inlineStr">
@@ -10326,7 +10589,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E39" s="41" t="inlineStr">
+      <c r="E39" s="40" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -10341,7 +10604,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="H39" s="39" t="n">
+      <c r="H39" s="38" t="n">
         <v>0.3</v>
       </c>
       <c r="I39" s="12" t="inlineStr">
@@ -10364,9 +10627,12 @@
       </c>
       <c r="N39" s="12" t="inlineStr"/>
       <c r="O39" s="12" t="inlineStr"/>
-      <c r="P39" s="33" t="n"/>
-      <c r="Q39" s="33" t="n"/>
-      <c r="R39" s="34" t="n"/>
+      <c r="P39" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q39" s="24" t="inlineStr"/>
     </row>
     <row r="40" ht="96" customHeight="1">
       <c r="A40" s="11" t="inlineStr">
@@ -10389,7 +10655,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E40" s="38" t="inlineStr">
+      <c r="E40" s="37" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -10428,9 +10694,12 @@
       </c>
       <c r="N40" s="12" t="inlineStr"/>
       <c r="O40" s="12" t="inlineStr"/>
-      <c r="P40" s="33" t="n"/>
-      <c r="Q40" s="33" t="n"/>
-      <c r="R40" s="34" t="n"/>
+      <c r="P40" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q40" s="24" t="inlineStr"/>
     </row>
     <row r="41" ht="96" customHeight="1">
       <c r="A41" s="11" t="inlineStr">
@@ -10453,7 +10722,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E41" s="38" t="inlineStr">
+      <c r="E41" s="37" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -10503,14 +10772,21 @@
 In addition, the 'TE-RS-002' and 'TE-RS-003' are duplicate with 'TE-RS-001'? If yes, should we keep the two rules in the rule list?</t>
         </is>
       </c>
-      <c r="O41" s="36" t="inlineStr">
+      <c r="O41" s="34" t="inlineStr">
         <is>
           <t>KEPT, with the relationship now declared explicitly. On the logic: the proposed variant uses AND, but PD requires both criteria, so 'PD not met' is pct &lt; 20 OR abs &lt; 5 — the AND form is narrower than the correct negation and would miss cases. That complete check already exists as TE-RS-001, which recomputes the response and compares. On duplication: yes, TE-RS-002 and TE-RS-003 are both subsumed by TE-RS-001 for detection. Their value is diagnostic, not detective — TE-RS-001 says the response is wrong, these say why, and the query text differs accordingly. They are now declared as cascade children of TE-RS-001, so when both fire the reviewer sees one finding carrying the specific reason, not two.</t>
         </is>
       </c>
-      <c r="P41" s="33" t="n"/>
-      <c r="Q41" s="33" t="n"/>
-      <c r="R41" s="34" t="n"/>
+      <c r="P41" s="35" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="Q41" s="24" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="96" customHeight="1">
       <c r="A42" s="11" t="inlineStr">
@@ -10533,7 +10809,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E42" s="38" t="inlineStr">
+      <c r="E42" s="37" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -10585,14 +10861,21 @@
           <t>Question to this rule. Should it consider the pct_from_baseline condition? Given that the proposed condition could check incorrect data well with the 1st and 2nd line (i.e. "if reported_target_response != PD and pct_from_nadir &gt;= pd_pct and abs_from_nadir_mm &gt;= pd_abs"), if 3rd line condition isn't definitely deciding data consistency, I suggest to have rule conditions without 3rd line condition.</t>
         </is>
       </c>
-      <c r="O42" s="36" t="inlineStr">
+      <c r="O42" s="34" t="inlineStr">
         <is>
           <t>AMENDED as suggested. The baseline comparison is removed from the gate, so the rule now catches every case where progression criteria are met from nadir but progression was not reported. The baseline comparison is retained purely as a discriminator: where percent change from baseline also falls short of the threshold, the site almost certainly compared against baseline instead of nadir, and the finding carries that specific wording and a higher confidence. Where it does not, the finding is still raised with generic wording.</t>
         </is>
       </c>
-      <c r="P42" s="33" t="n"/>
-      <c r="Q42" s="33" t="n"/>
-      <c r="R42" s="34" t="n"/>
+      <c r="P42" s="35" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="Q42" s="24" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="96" customHeight="1">
       <c r="A43" s="11" t="inlineStr">
@@ -10615,7 +10898,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E43" s="38" t="inlineStr">
+      <c r="E43" s="37" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -10655,9 +10938,12 @@
       </c>
       <c r="N43" s="12" t="inlineStr"/>
       <c r="O43" s="12" t="inlineStr"/>
-      <c r="P43" s="33" t="n"/>
-      <c r="Q43" s="33" t="n"/>
-      <c r="R43" s="34" t="n"/>
+      <c r="P43" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q43" s="24" t="inlineStr"/>
     </row>
     <row r="44" ht="96" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
@@ -10680,7 +10966,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E44" s="38" t="inlineStr">
+      <c r="E44" s="37" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -10718,9 +11004,12 @@
       </c>
       <c r="N44" s="12" t="inlineStr"/>
       <c r="O44" s="12" t="inlineStr"/>
-      <c r="P44" s="33" t="n"/>
-      <c r="Q44" s="33" t="n"/>
-      <c r="R44" s="34" t="n"/>
+      <c r="P44" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q44" s="24" t="inlineStr"/>
     </row>
     <row r="45" ht="96" customHeight="1">
       <c r="A45" s="11" t="inlineStr">
@@ -10781,9 +11070,12 @@
       </c>
       <c r="N45" s="12" t="inlineStr"/>
       <c r="O45" s="12" t="inlineStr"/>
-      <c r="P45" s="33" t="n"/>
-      <c r="Q45" s="33" t="n"/>
-      <c r="R45" s="34" t="n"/>
+      <c r="P45" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q45" s="24" t="inlineStr"/>
     </row>
     <row r="46" ht="96" customHeight="1">
       <c r="A46" s="11" t="inlineStr">
@@ -10806,7 +11098,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E46" s="41" t="inlineStr">
+      <c r="E46" s="40" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -10821,7 +11113,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="H46" s="39" t="n">
+      <c r="H46" s="38" t="n">
         <v>0.45</v>
       </c>
       <c r="I46" s="12" t="inlineStr">
@@ -10853,14 +11145,21 @@
           <t>This isn't decisive with entered data only. Check whether it could downgrade the severity to 'INFO'.</t>
         </is>
       </c>
-      <c r="O46" s="36" t="inlineStr">
+      <c r="O46" s="34" t="inlineStr">
         <is>
           <t>AMENDED to INFO. You are right that collected data cannot settle this — the guideline's test is a judgement about overall tumor burden that the recorded non-target states do not capture. Note the consequence, which is intended: INFO findings do not enter the default query worklist, so this becomes a study-team observation rather than a site query. The adjudicator can still escalate to MAJOR where the recorded descriptions actively contradict the reported progression.</t>
         </is>
       </c>
-      <c r="P46" s="33" t="n"/>
-      <c r="Q46" s="33" t="n"/>
-      <c r="R46" s="34" t="n"/>
+      <c r="P46" s="35" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="Q46" s="24" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="96" customHeight="1">
       <c r="A47" s="11" t="inlineStr">
@@ -10883,7 +11182,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E47" s="38" t="inlineStr">
+      <c r="E47" s="37" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -10937,14 +11236,21 @@
           <t>Is it possible to give information whether any issue in the individual response (target, non-target) and their relevant detail data (e.g. tumor size, individual lesion response) in order not to avoid duplicate query in both sides (i.e. overall response, target/non-target response)</t>
         </is>
       </c>
-      <c r="O47" s="36" t="inlineStr">
+      <c r="O47" s="34" t="inlineStr">
         <is>
           <t>AMENDED. The rule now declares its component dependencies, and the cascade grouping suppresses the separate overall-response query whenever a component finding is already open for the same assessment. Where no component finding exists, the overall-response finding is raised alone and names which component drove the expected value, so the site receives one query identifying the specific field rather than two queries about the same visit.</t>
         </is>
       </c>
-      <c r="P47" s="33" t="n"/>
-      <c r="Q47" s="33" t="n"/>
-      <c r="R47" s="34" t="n"/>
+      <c r="P47" s="35" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="Q47" s="24" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="96" customHeight="1">
       <c r="A48" s="11" t="inlineStr">
@@ -11005,141 +11311,151 @@
       </c>
       <c r="N48" s="12" t="inlineStr"/>
       <c r="O48" s="12" t="inlineStr"/>
-      <c r="P48" s="33" t="n"/>
-      <c r="Q48" s="33" t="n"/>
-      <c r="R48" s="34" t="n"/>
+      <c r="P48" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q48" s="24" t="inlineStr"/>
     </row>
     <row r="49" ht="96" customHeight="1">
-      <c r="A49" s="42" t="inlineStr">
+      <c r="A49" s="41" t="inlineStr">
         <is>
           <t>TE-RS-010</t>
         </is>
       </c>
-      <c r="B49" s="43" t="inlineStr">
+      <c r="B49" s="42" t="inlineStr">
         <is>
           <t>RS</t>
         </is>
       </c>
-      <c r="C49" s="44" t="inlineStr">
+      <c r="C49" s="43" t="inlineStr">
         <is>
           <t>New lesion recorded but overall response is not progression</t>
         </is>
       </c>
-      <c r="D49" s="43" t="inlineStr">
+      <c r="D49" s="42" t="inlineStr">
         <is>
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E49" s="43" t="inlineStr">
+      <c r="E49" s="42" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="F49" s="43" t="inlineStr">
+      <c r="F49" s="42" t="inlineStr">
         <is>
           <t>DETERMINISTIC</t>
         </is>
       </c>
-      <c r="G49" s="45" t="inlineStr">
+      <c r="G49" s="44" t="inlineStr">
         <is>
           <t>RETIRED</t>
         </is>
       </c>
-      <c r="H49" s="46" t="n">
+      <c r="H49" s="45" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="I49" s="44" t="inlineStr">
+      <c r="I49" s="43" t="inlineStr">
         <is>
           <t>A confirmed new lesion always means progression under RECIST 1.1.</t>
         </is>
       </c>
-      <c r="J49" s="44" t="inlineStr">
+      <c r="J49" s="43" t="inlineStr">
         <is>
           <t>Retired at the Step 2 review as fully subsumed by TE-RS-008 (overall response versus the component table), TE-RS-009 (flag versus recorded lesions) and TE-IR-001 (iUPD under iRECIST).</t>
         </is>
       </c>
-      <c r="K49" s="44" t="inlineStr"/>
-      <c r="L49" s="47" t="inlineStr">
+      <c r="K49" s="43" t="inlineStr"/>
+      <c r="L49" s="46" t="inlineStr">
         <is>
           <t>if new_lesion_flag == YES and reported_overall != PD: raise finding
    (under iRECIST the expected value is iUPD; see TE-IR-001)</t>
         </is>
       </c>
-      <c r="M49" s="48" t="inlineStr">
+      <c r="M49" s="47" t="inlineStr">
         <is>
           <t>Discuss</t>
         </is>
       </c>
-      <c r="N49" s="49" t="inlineStr">
+      <c r="N49" s="48" t="inlineStr">
         <is>
           <t>Check if this rule is duplicate, considering TE-RS-008.
 If duplicate rule, I suggest remove this rule, instead, add only iRECIST condition to the TE-RS-008.</t>
         </is>
       </c>
-      <c r="O49" s="49" t="inlineStr">
+      <c r="O49" s="48" t="inlineStr">
         <is>
           <t>RETIRED — you are right. TE-RS-008 derives the overall response from the reported components, and the new-lesion flag is one of those components, so a recorded new lesion with a non-PD overall response already fires TE-RS-008. The one case that is not covered — a new lesion present in the lesion table while the flag says NO — is TE-RS-009. The iRECIST expectation needs no folding in, because TE-IR-001 already requires iUPD rather than PD where iRECIST applies. The id is retained permanently and never reused, so historical findings stay interpretable.</t>
         </is>
       </c>
-      <c r="P49" s="33" t="n"/>
-      <c r="Q49" s="33" t="n"/>
-      <c r="R49" s="34" t="n"/>
+      <c r="P49" s="49" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="Q49" s="47" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="96" customHeight="1">
-      <c r="A50" s="42" t="inlineStr">
+      <c r="A50" s="41" t="inlineStr">
         <is>
           <t>TE-RS-011</t>
         </is>
       </c>
-      <c r="B50" s="43" t="inlineStr">
+      <c r="B50" s="42" t="inlineStr">
         <is>
           <t>RS</t>
         </is>
       </c>
-      <c r="C50" s="44" t="inlineStr">
+      <c r="C50" s="43" t="inlineStr">
         <is>
           <t>New lesion in an anatomical region not imaged at baseline</t>
         </is>
       </c>
-      <c r="D50" s="43" t="inlineStr">
+      <c r="D50" s="42" t="inlineStr">
         <is>
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E50" s="43" t="inlineStr">
+      <c r="E50" s="42" t="inlineStr">
         <is>
           <t>MAJOR</t>
         </is>
       </c>
-      <c r="F50" s="43" t="inlineStr">
+      <c r="F50" s="42" t="inlineStr">
         <is>
           <t>HYBRID</t>
         </is>
       </c>
-      <c r="G50" s="45" t="inlineStr">
+      <c r="G50" s="44" t="inlineStr">
         <is>
           <t>RETIRED</t>
         </is>
       </c>
-      <c r="H50" s="46" t="n">
+      <c r="H50" s="45" t="n">
         <v>0.62</v>
       </c>
-      <c r="I50" s="44" t="inlineStr">
+      <c r="I50" s="43" t="inlineStr">
         <is>
           <t>Ensure the region-not-imaged case was considered explicitly.</t>
         </is>
       </c>
-      <c r="J50" s="44" t="inlineStr">
+      <c r="J50" s="43" t="inlineStr">
         <is>
           <t>Rejected at the Step 2 review. The premise does not hold: investigator-discretion imaging routinely covers regions absent from the baseline protocol imaging, so region coverage is not evidence of a data problem.</t>
         </is>
       </c>
-      <c r="K50" s="44" t="inlineStr">
+      <c r="K50" s="43" t="inlineStr">
         <is>
           <t>imaging_metadata.regions_imaged (or inferred from baseline lesion organs and modality)</t>
         </is>
       </c>
-      <c r="L50" s="47" t="inlineStr">
+      <c r="L50" s="46" t="inlineStr">
         <is>
           <t>if new lesion organ/region was not covered by the baseline imaging: raise finding</t>
         </is>
@@ -11149,19 +11465,26 @@
           <t>Reject</t>
         </is>
       </c>
-      <c r="N50" s="49" t="inlineStr">
+      <c r="N50" s="48" t="inlineStr">
         <is>
           <t>New lesion could be confirmed by other organ/region not covered by the baseline image, because of doing other image by investigator's discretion. Suggest not to run this rule.</t>
         </is>
       </c>
-      <c r="O50" s="49" t="inlineStr">
+      <c r="O50" s="48" t="inlineStr">
         <is>
           <t>RETIRED as rejected. Imaging performed at investigator discretion outside the baseline coverage is routine and entirely legitimate, and a new lesion found that way is a real new lesion. The rule assumed baseline coverage bounded where disease could be found, which is not how imaging is actually ordered. The id is retained permanently and never reused.</t>
         </is>
       </c>
-      <c r="P50" s="33" t="n"/>
-      <c r="Q50" s="33" t="n"/>
-      <c r="R50" s="34" t="n"/>
+      <c r="P50" s="49" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="Q50" s="47" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="96" customHeight="1">
       <c r="A51" s="11" t="inlineStr">
@@ -11199,7 +11522,7 @@
           <t>CONDITIONAL</t>
         </is>
       </c>
-      <c r="H51" s="35" t="n">
+      <c r="H51" s="33" t="n">
         <v>0.68</v>
       </c>
       <c r="I51" s="12" t="inlineStr">
@@ -11226,9 +11549,12 @@
       </c>
       <c r="N51" s="12" t="inlineStr"/>
       <c r="O51" s="12" t="inlineStr"/>
-      <c r="P51" s="33" t="n"/>
-      <c r="Q51" s="33" t="n"/>
-      <c r="R51" s="34" t="n"/>
+      <c r="P51" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q51" s="24" t="inlineStr"/>
     </row>
     <row r="52" ht="96" customHeight="1">
       <c r="A52" s="11" t="inlineStr">
@@ -11301,14 +11627,21 @@
           <t>This rule should consider the case that the visit j's data has definitive rationale of PD. E.g. At the visit j, there is evidence to determine PD due to other conditions (e.g. target lesion sum mm passes 20% worsen and over minimum increase)</t>
         </is>
       </c>
-      <c r="O52" s="36" t="inlineStr">
+      <c r="O52" s="34" t="inlineStr">
         <is>
           <t>AMENDED. A guard now suppresses the finding where progression at visit j is independently established by the target or non-target criteria. Back-dating is only correct where the equivocal-then-confirmed lesion is what drove progression; where the target sum crossed the threshold at visit j in its own right, visit j is the correct progression date and the earlier equivocal observation is irrelevant to it.</t>
         </is>
       </c>
-      <c r="P52" s="33" t="n"/>
-      <c r="Q52" s="33" t="n"/>
-      <c r="R52" s="34" t="n"/>
+      <c r="P52" s="35" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="Q52" s="24" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="96" customHeight="1">
       <c r="A53" s="11" t="inlineStr">
@@ -11331,7 +11664,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E53" s="38" t="inlineStr">
+      <c r="E53" s="37" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -11382,14 +11715,21 @@
           <t>Provide the rationale insisting the proposed threshold. What material or information is referred to make this validation rule.</t>
         </is>
       </c>
-      <c r="O53" s="36" t="inlineStr">
+      <c r="O53" s="34" t="inlineStr">
         <is>
           <t>RATIONALE ADDED, and this one does have a guideline source, unlike TE-FU-004.</t>
         </is>
       </c>
-      <c r="P53" s="33" t="n"/>
-      <c r="Q53" s="33" t="n"/>
-      <c r="R53" s="34" t="n"/>
+      <c r="P53" s="35" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="Q53" s="24" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="96" customHeight="1">
       <c r="A54" s="11" t="inlineStr">
@@ -11412,7 +11752,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E54" s="38" t="inlineStr">
+      <c r="E54" s="37" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -11450,9 +11790,12 @@
       </c>
       <c r="N54" s="12" t="inlineStr"/>
       <c r="O54" s="12" t="inlineStr"/>
-      <c r="P54" s="33" t="n"/>
-      <c r="Q54" s="33" t="n"/>
-      <c r="R54" s="34" t="n"/>
+      <c r="P54" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q54" s="24" t="inlineStr"/>
     </row>
     <row r="55" ht="96" customHeight="1">
       <c r="A55" s="11" t="inlineStr">
@@ -11475,7 +11818,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E55" s="38" t="inlineStr">
+      <c r="E55" s="37" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -11513,9 +11856,12 @@
       </c>
       <c r="N55" s="12" t="inlineStr"/>
       <c r="O55" s="12" t="inlineStr"/>
-      <c r="P55" s="33" t="n"/>
-      <c r="Q55" s="33" t="n"/>
-      <c r="R55" s="34" t="n"/>
+      <c r="P55" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q55" s="24" t="inlineStr"/>
     </row>
     <row r="56" ht="96" customHeight="1">
       <c r="A56" s="11" t="inlineStr">
@@ -11580,9 +11926,12 @@
       </c>
       <c r="N56" s="12" t="inlineStr"/>
       <c r="O56" s="12" t="inlineStr"/>
-      <c r="P56" s="33" t="n"/>
-      <c r="Q56" s="33" t="n"/>
-      <c r="R56" s="34" t="n"/>
+      <c r="P56" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q56" s="24" t="inlineStr"/>
     </row>
     <row r="57" ht="96" customHeight="1">
       <c r="A57" s="11" t="inlineStr">
@@ -11643,9 +11992,12 @@
       </c>
       <c r="N57" s="12" t="inlineStr"/>
       <c r="O57" s="12" t="inlineStr"/>
-      <c r="P57" s="33" t="n"/>
-      <c r="Q57" s="33" t="n"/>
-      <c r="R57" s="34" t="n"/>
+      <c r="P57" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q57" s="24" t="inlineStr"/>
     </row>
     <row r="58" ht="96" customHeight="1">
       <c r="A58" s="11" t="inlineStr">
@@ -11706,9 +12058,12 @@
       </c>
       <c r="N58" s="12" t="inlineStr"/>
       <c r="O58" s="12" t="inlineStr"/>
-      <c r="P58" s="33" t="n"/>
-      <c r="Q58" s="33" t="n"/>
-      <c r="R58" s="34" t="n"/>
+      <c r="P58" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q58" s="24" t="inlineStr"/>
     </row>
     <row r="59" ht="96" customHeight="1">
       <c r="A59" s="11" t="inlineStr">
@@ -11746,7 +12101,7 @@
           <t>CONDITIONAL</t>
         </is>
       </c>
-      <c r="H59" s="35" t="n">
+      <c r="H59" s="33" t="n">
         <v>0.5</v>
       </c>
       <c r="I59" s="12" t="inlineStr">
@@ -11774,9 +12129,12 @@
       </c>
       <c r="N59" s="12" t="inlineStr"/>
       <c r="O59" s="12" t="inlineStr"/>
-      <c r="P59" s="33" t="n"/>
-      <c r="Q59" s="33" t="n"/>
-      <c r="R59" s="34" t="n"/>
+      <c r="P59" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q59" s="24" t="inlineStr"/>
     </row>
     <row r="60" ht="96" customHeight="1">
       <c r="A60" s="11" t="inlineStr">
@@ -11799,7 +12157,7 @@
           <t>iRECIST only</t>
         </is>
       </c>
-      <c r="E60" s="38" t="inlineStr">
+      <c r="E60" s="37" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -11838,9 +12196,12 @@
       </c>
       <c r="N60" s="12" t="inlineStr"/>
       <c r="O60" s="12" t="inlineStr"/>
-      <c r="P60" s="33" t="n"/>
-      <c r="Q60" s="33" t="n"/>
-      <c r="R60" s="34" t="n"/>
+      <c r="P60" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q60" s="24" t="inlineStr"/>
     </row>
     <row r="61" ht="96" customHeight="1">
       <c r="A61" s="11" t="inlineStr">
@@ -11863,7 +12224,7 @@
           <t>iRECIST only</t>
         </is>
       </c>
-      <c r="E61" s="38" t="inlineStr">
+      <c r="E61" s="37" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -11904,9 +12265,12 @@
       </c>
       <c r="N61" s="12" t="inlineStr"/>
       <c r="O61" s="12" t="inlineStr"/>
-      <c r="P61" s="33" t="n"/>
-      <c r="Q61" s="33" t="n"/>
-      <c r="R61" s="34" t="n"/>
+      <c r="P61" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q61" s="24" t="inlineStr"/>
     </row>
     <row r="62" ht="96" customHeight="1">
       <c r="A62" s="11" t="inlineStr">
@@ -11929,7 +12293,7 @@
           <t>iRECIST only</t>
         </is>
       </c>
-      <c r="E62" s="38" t="inlineStr">
+      <c r="E62" s="37" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -11973,9 +12337,12 @@
       </c>
       <c r="N62" s="12" t="inlineStr"/>
       <c r="O62" s="12" t="inlineStr"/>
-      <c r="P62" s="33" t="n"/>
-      <c r="Q62" s="33" t="n"/>
-      <c r="R62" s="34" t="n"/>
+      <c r="P62" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q62" s="24" t="inlineStr"/>
     </row>
     <row r="63" ht="96" customHeight="1">
       <c r="A63" s="11" t="inlineStr">
@@ -11998,7 +12365,7 @@
           <t>iRECIST only</t>
         </is>
       </c>
-      <c r="E63" s="38" t="inlineStr">
+      <c r="E63" s="37" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -12036,9 +12403,12 @@
       </c>
       <c r="N63" s="12" t="inlineStr"/>
       <c r="O63" s="12" t="inlineStr"/>
-      <c r="P63" s="33" t="n"/>
-      <c r="Q63" s="33" t="n"/>
-      <c r="R63" s="34" t="n"/>
+      <c r="P63" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q63" s="24" t="inlineStr"/>
     </row>
     <row r="64" ht="96" customHeight="1">
       <c r="A64" s="11" t="inlineStr">
@@ -12100,9 +12470,12 @@
       </c>
       <c r="N64" s="12" t="inlineStr"/>
       <c r="O64" s="12" t="inlineStr"/>
-      <c r="P64" s="33" t="n"/>
-      <c r="Q64" s="33" t="n"/>
-      <c r="R64" s="34" t="n"/>
+      <c r="P64" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q64" s="24" t="inlineStr"/>
     </row>
     <row r="65" ht="96" customHeight="1">
       <c r="A65" s="11" t="inlineStr">
@@ -12163,9 +12536,12 @@
       </c>
       <c r="N65" s="12" t="inlineStr"/>
       <c r="O65" s="12" t="inlineStr"/>
-      <c r="P65" s="33" t="n"/>
-      <c r="Q65" s="33" t="n"/>
-      <c r="R65" s="34" t="n"/>
+      <c r="P65" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q65" s="24" t="inlineStr"/>
     </row>
     <row r="66" ht="96" customHeight="1">
       <c r="A66" s="11" t="inlineStr">
@@ -12226,9 +12602,12 @@
       </c>
       <c r="N66" s="12" t="inlineStr"/>
       <c r="O66" s="12" t="inlineStr"/>
-      <c r="P66" s="33" t="n"/>
-      <c r="Q66" s="33" t="n"/>
-      <c r="R66" s="34" t="n"/>
+      <c r="P66" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q66" s="24" t="inlineStr"/>
     </row>
     <row r="67" ht="96" customHeight="1">
       <c r="A67" s="11" t="inlineStr">
@@ -12261,12 +12640,12 @@
           <t>HYBRID</t>
         </is>
       </c>
-      <c r="G67" s="40" t="inlineStr">
+      <c r="G67" s="39" t="inlineStr">
         <is>
           <t>PROPOSED_OPTIONAL</t>
         </is>
       </c>
-      <c r="H67" s="39" t="n">
+      <c r="H67" s="38" t="n">
         <v>0.48</v>
       </c>
       <c r="I67" s="12" t="inlineStr">
@@ -12293,9 +12672,12 @@
       </c>
       <c r="N67" s="12" t="inlineStr"/>
       <c r="O67" s="12" t="inlineStr"/>
-      <c r="P67" s="33" t="n"/>
-      <c r="Q67" s="33" t="n"/>
-      <c r="R67" s="34" t="n"/>
+      <c r="P67" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q67" s="24" t="inlineStr"/>
     </row>
     <row r="68" ht="96" customHeight="1">
       <c r="A68" s="11" t="inlineStr">
@@ -12356,9 +12738,12 @@
       </c>
       <c r="N68" s="12" t="inlineStr"/>
       <c r="O68" s="12" t="inlineStr"/>
-      <c r="P68" s="33" t="n"/>
-      <c r="Q68" s="33" t="n"/>
-      <c r="R68" s="34" t="n"/>
+      <c r="P68" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q68" s="24" t="inlineStr"/>
     </row>
     <row r="69" ht="96" customHeight="1">
       <c r="A69" s="11" t="inlineStr">
@@ -12423,9 +12808,12 @@
       </c>
       <c r="N69" s="12" t="inlineStr"/>
       <c r="O69" s="12" t="inlineStr"/>
-      <c r="P69" s="33" t="n"/>
-      <c r="Q69" s="33" t="n"/>
-      <c r="R69" s="34" t="n"/>
+      <c r="P69" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q69" s="24" t="inlineStr"/>
     </row>
     <row r="70" ht="96" customHeight="1">
       <c r="A70" s="11" t="inlineStr">
@@ -12486,9 +12874,12 @@
       </c>
       <c r="N70" s="12" t="inlineStr"/>
       <c r="O70" s="12" t="inlineStr"/>
-      <c r="P70" s="33" t="n"/>
-      <c r="Q70" s="33" t="n"/>
-      <c r="R70" s="34" t="n"/>
+      <c r="P70" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q70" s="24" t="inlineStr"/>
     </row>
     <row r="71" ht="96" customHeight="1">
       <c r="A71" s="11" t="inlineStr">
@@ -12526,7 +12917,7 @@
           <t>CONDITIONAL</t>
         </is>
       </c>
-      <c r="H71" s="35" t="n">
+      <c r="H71" s="33" t="n">
         <v>0.62</v>
       </c>
       <c r="I71" s="12" t="inlineStr"/>
@@ -12550,9 +12941,12 @@
       </c>
       <c r="N71" s="12" t="inlineStr"/>
       <c r="O71" s="12" t="inlineStr"/>
-      <c r="P71" s="33" t="n"/>
-      <c r="Q71" s="33" t="n"/>
-      <c r="R71" s="34" t="n"/>
+      <c r="P71" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q71" s="24" t="inlineStr"/>
     </row>
     <row r="72" ht="96" customHeight="1">
       <c r="A72" s="11" t="inlineStr">
@@ -12590,7 +12984,7 @@
           <t>CONDITIONAL</t>
         </is>
       </c>
-      <c r="H72" s="35" t="n">
+      <c r="H72" s="33" t="n">
         <v>0.7</v>
       </c>
       <c r="I72" s="12" t="inlineStr"/>
@@ -12613,9 +13007,12 @@
       </c>
       <c r="N72" s="12" t="inlineStr"/>
       <c r="O72" s="12" t="inlineStr"/>
-      <c r="P72" s="33" t="n"/>
-      <c r="Q72" s="33" t="n"/>
-      <c r="R72" s="34" t="n"/>
+      <c r="P72" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q72" s="24" t="inlineStr"/>
     </row>
     <row r="73" ht="96" customHeight="1">
       <c r="A73" s="11" t="inlineStr">
@@ -12676,9 +13073,12 @@
       </c>
       <c r="N73" s="12" t="inlineStr"/>
       <c r="O73" s="12" t="inlineStr"/>
-      <c r="P73" s="33" t="n"/>
-      <c r="Q73" s="33" t="n"/>
-      <c r="R73" s="34" t="n"/>
+      <c r="P73" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q73" s="24" t="inlineStr"/>
     </row>
     <row r="74" ht="96" customHeight="1">
       <c r="A74" s="11" t="inlineStr">
@@ -12716,7 +13116,7 @@
           <t>CONDITIONAL</t>
         </is>
       </c>
-      <c r="H74" s="35" t="n">
+      <c r="H74" s="33" t="n">
         <v>0.65</v>
       </c>
       <c r="I74" s="12" t="inlineStr"/>
@@ -12739,9 +13139,12 @@
       </c>
       <c r="N74" s="12" t="inlineStr"/>
       <c r="O74" s="12" t="inlineStr"/>
-      <c r="P74" s="33" t="n"/>
-      <c r="Q74" s="33" t="n"/>
-      <c r="R74" s="34" t="n"/>
+      <c r="P74" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q74" s="24" t="inlineStr"/>
     </row>
     <row r="75" ht="96" customHeight="1">
       <c r="A75" s="11" t="inlineStr">
@@ -12764,7 +13167,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E75" s="38" t="inlineStr">
+      <c r="E75" s="37" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -12801,9 +13204,12 @@
       </c>
       <c r="N75" s="12" t="inlineStr"/>
       <c r="O75" s="12" t="inlineStr"/>
-      <c r="P75" s="33" t="n"/>
-      <c r="Q75" s="33" t="n"/>
-      <c r="R75" s="34" t="n"/>
+      <c r="P75" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q75" s="24" t="inlineStr"/>
     </row>
     <row r="76" ht="96" customHeight="1">
       <c r="A76" s="11" t="inlineStr">
@@ -12826,7 +13232,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E76" s="37" t="inlineStr">
+      <c r="E76" s="36" t="inlineStr">
         <is>
           <t>MINOR</t>
         </is>
@@ -12841,7 +13247,7 @@
           <t>CONDITIONAL</t>
         </is>
       </c>
-      <c r="H76" s="35" t="n">
+      <c r="H76" s="33" t="n">
         <v>0.6</v>
       </c>
       <c r="I76" s="12" t="inlineStr"/>
@@ -12870,14 +13276,21 @@
           <t>Provide the rationale insisting the proposed threshold. What material or information is referred to make this validation rule.</t>
         </is>
       </c>
-      <c r="O76" s="36" t="inlineStr">
+      <c r="O76" s="34" t="inlineStr">
         <is>
           <t>RATIONALE ADDED. The threshold is the laboratory's own upper limit of normal, not a value the agent chooses.</t>
         </is>
       </c>
-      <c r="P76" s="33" t="n"/>
-      <c r="Q76" s="33" t="n"/>
-      <c r="R76" s="34" t="n"/>
+      <c r="P76" s="35" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="Q76" s="24" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="96" customHeight="1">
       <c r="A77" s="11" t="inlineStr">
@@ -12900,7 +13313,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E77" s="37" t="inlineStr">
+      <c r="E77" s="36" t="inlineStr">
         <is>
           <t>MINOR</t>
         </is>
@@ -12915,7 +13328,7 @@
           <t>CONDITIONAL</t>
         </is>
       </c>
-      <c r="H77" s="35" t="n">
+      <c r="H77" s="33" t="n">
         <v>0.58</v>
       </c>
       <c r="I77" s="12" t="inlineStr"/>
@@ -12937,9 +13350,12 @@
       </c>
       <c r="N77" s="12" t="inlineStr"/>
       <c r="O77" s="12" t="inlineStr"/>
-      <c r="P77" s="33" t="n"/>
-      <c r="Q77" s="33" t="n"/>
-      <c r="R77" s="34" t="n"/>
+      <c r="P77" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q77" s="24" t="inlineStr"/>
     </row>
     <row r="78" ht="96" customHeight="1">
       <c r="A78" s="11" t="inlineStr">
@@ -12962,7 +13378,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E78" s="37" t="inlineStr">
+      <c r="E78" s="36" t="inlineStr">
         <is>
           <t>MINOR</t>
         </is>
@@ -12977,7 +13393,7 @@
           <t>CONDITIONAL</t>
         </is>
       </c>
-      <c r="H78" s="35" t="n">
+      <c r="H78" s="33" t="n">
         <v>0.62</v>
       </c>
       <c r="I78" s="12" t="inlineStr"/>
@@ -13000,9 +13416,12 @@
       </c>
       <c r="N78" s="12" t="inlineStr"/>
       <c r="O78" s="12" t="inlineStr"/>
-      <c r="P78" s="33" t="n"/>
-      <c r="Q78" s="33" t="n"/>
-      <c r="R78" s="34" t="n"/>
+      <c r="P78" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q78" s="24" t="inlineStr"/>
     </row>
     <row r="79" ht="96" customHeight="1">
       <c r="A79" s="11" t="inlineStr">
@@ -13058,9 +13477,12 @@
       </c>
       <c r="N79" s="12" t="inlineStr"/>
       <c r="O79" s="12" t="inlineStr"/>
-      <c r="P79" s="33" t="n"/>
-      <c r="Q79" s="33" t="n"/>
-      <c r="R79" s="34" t="n"/>
+      <c r="P79" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q79" s="24" t="inlineStr"/>
     </row>
     <row r="80" ht="96" customHeight="1">
       <c r="A80" s="11" t="inlineStr">
@@ -13083,7 +13505,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E80" s="41" t="inlineStr">
+      <c r="E80" s="40" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -13098,7 +13520,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="H80" s="35" t="n">
+      <c r="H80" s="33" t="n">
         <v>0.55</v>
       </c>
       <c r="I80" s="12" t="inlineStr"/>
@@ -13117,9 +13539,12 @@
       </c>
       <c r="N80" s="12" t="inlineStr"/>
       <c r="O80" s="12" t="inlineStr"/>
-      <c r="P80" s="33" t="n"/>
-      <c r="Q80" s="33" t="n"/>
-      <c r="R80" s="34" t="n"/>
+      <c r="P80" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q80" s="24" t="inlineStr"/>
     </row>
     <row r="81" ht="96" customHeight="1">
       <c r="A81" s="11" t="inlineStr">
@@ -13142,7 +13567,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E81" s="37" t="inlineStr">
+      <c r="E81" s="36" t="inlineStr">
         <is>
           <t>MINOR</t>
         </is>
@@ -13157,7 +13582,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="H81" s="35" t="n">
+      <c r="H81" s="33" t="n">
         <v>0.7</v>
       </c>
       <c r="I81" s="12" t="inlineStr"/>
@@ -13177,9 +13602,12 @@
       </c>
       <c r="N81" s="12" t="inlineStr"/>
       <c r="O81" s="12" t="inlineStr"/>
-      <c r="P81" s="33" t="n"/>
-      <c r="Q81" s="33" t="n"/>
-      <c r="R81" s="34" t="n"/>
+      <c r="P81" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q81" s="24" t="inlineStr"/>
     </row>
     <row r="82" ht="96" customHeight="1">
       <c r="A82" s="11" t="inlineStr">
@@ -13202,7 +13630,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E82" s="41" t="inlineStr">
+      <c r="E82" s="40" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -13235,9 +13663,12 @@
       </c>
       <c r="N82" s="12" t="inlineStr"/>
       <c r="O82" s="12" t="inlineStr"/>
-      <c r="P82" s="33" t="n"/>
-      <c r="Q82" s="33" t="n"/>
-      <c r="R82" s="34" t="n"/>
+      <c r="P82" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q82" s="24" t="inlineStr"/>
     </row>
     <row r="83" ht="96" customHeight="1">
       <c r="A83" s="11" t="inlineStr">
@@ -13308,9 +13739,12 @@
       </c>
       <c r="N83" s="12" t="inlineStr"/>
       <c r="O83" s="12" t="inlineStr"/>
-      <c r="P83" s="33" t="n"/>
-      <c r="Q83" s="33" t="n"/>
-      <c r="R83" s="34" t="n"/>
+      <c r="P83" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q83" s="24" t="inlineStr"/>
     </row>
     <row r="84" ht="96" customHeight="1">
       <c r="A84" s="11" t="inlineStr">
@@ -13367,9 +13801,12 @@
       </c>
       <c r="N84" s="12" t="inlineStr"/>
       <c r="O84" s="12" t="inlineStr"/>
-      <c r="P84" s="33" t="n"/>
-      <c r="Q84" s="33" t="n"/>
-      <c r="R84" s="34" t="n"/>
+      <c r="P84" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q84" s="24" t="inlineStr"/>
     </row>
     <row r="85" ht="96" customHeight="1">
       <c r="A85" s="11" t="inlineStr">
@@ -13392,7 +13829,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E85" s="37" t="inlineStr">
+      <c r="E85" s="36" t="inlineStr">
         <is>
           <t>MINOR</t>
         </is>
@@ -13426,9 +13863,12 @@
       </c>
       <c r="N85" s="12" t="inlineStr"/>
       <c r="O85" s="12" t="inlineStr"/>
-      <c r="P85" s="33" t="n"/>
-      <c r="Q85" s="33" t="n"/>
-      <c r="R85" s="34" t="n"/>
+      <c r="P85" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q85" s="24" t="inlineStr"/>
     </row>
     <row r="86" ht="96" customHeight="1">
       <c r="A86" s="11" t="inlineStr">
@@ -13451,7 +13891,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E86" s="41" t="inlineStr">
+      <c r="E86" s="40" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -13466,7 +13906,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="H86" s="35" t="n">
+      <c r="H86" s="33" t="n">
         <v>0.55</v>
       </c>
       <c r="I86" s="12" t="inlineStr"/>
@@ -13487,9 +13927,12 @@
       </c>
       <c r="N86" s="12" t="inlineStr"/>
       <c r="O86" s="12" t="inlineStr"/>
-      <c r="P86" s="33" t="n"/>
-      <c r="Q86" s="33" t="n"/>
-      <c r="R86" s="34" t="n"/>
+      <c r="P86" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q86" s="24" t="inlineStr"/>
     </row>
     <row r="87" ht="96" customHeight="1">
       <c r="A87" s="11" t="inlineStr">
@@ -13512,7 +13955,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E87" s="41" t="inlineStr">
+      <c r="E87" s="40" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -13527,7 +13970,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="H87" s="35" t="n">
+      <c r="H87" s="33" t="n">
         <v>0.72</v>
       </c>
       <c r="I87" s="12" t="inlineStr"/>
@@ -13546,9 +13989,12 @@
       </c>
       <c r="N87" s="12" t="inlineStr"/>
       <c r="O87" s="12" t="inlineStr"/>
-      <c r="P87" s="33" t="n"/>
-      <c r="Q87" s="33" t="n"/>
-      <c r="R87" s="34" t="n"/>
+      <c r="P87" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q87" s="24" t="inlineStr"/>
     </row>
     <row r="88" ht="96" customHeight="1">
       <c r="A88" s="11" t="inlineStr">
@@ -13581,12 +14027,12 @@
           <t>HYBRID</t>
         </is>
       </c>
-      <c r="G88" s="40" t="inlineStr">
+      <c r="G88" s="39" t="inlineStr">
         <is>
           <t>PROPOSED_OPTIONAL</t>
         </is>
       </c>
-      <c r="H88" s="35" t="n">
+      <c r="H88" s="33" t="n">
         <v>0.55</v>
       </c>
       <c r="I88" s="12" t="inlineStr">
@@ -13630,21 +14076,19 @@
       </c>
       <c r="N88" s="12" t="inlineStr"/>
       <c r="O88" s="12" t="inlineStr"/>
-      <c r="P88" s="33" t="n"/>
-      <c r="Q88" s="33" t="n"/>
-      <c r="R88" s="34" t="n"/>
+      <c r="P88" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q88" s="24" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:R88"/>
+  <autoFilter ref="A3:Q88"/>
   <mergeCells count="2">
     <mergeCell ref="A2:R2"/>
     <mergeCell ref="A1:R1"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="P4:P88" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Accept,Amend,Reject,Discuss"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13772,9 +14216,9 @@
           <t>Most often a lesion numbering typo, or a new lesion measured before it was formally recorded as new. Check whether the number matches an existing lesion at another site of disease.</t>
         </is>
       </c>
-      <c r="H4" s="33" t="n"/>
-      <c r="I4" s="33" t="n"/>
-      <c r="J4" s="34" t="n"/>
+      <c r="H4" s="52" t="n"/>
+      <c r="I4" s="52" t="n"/>
+      <c r="J4" s="53" t="n"/>
     </row>
     <row r="5" ht="108" customHeight="1">
       <c r="A5" s="25" t="inlineStr">
@@ -13812,9 +14256,9 @@
           <t>Compare the baseline sizes and the size trajectory: identical or near-identical values across visits strongly suggests duplication.</t>
         </is>
       </c>
-      <c r="H5" s="33" t="n"/>
-      <c r="I5" s="33" t="n"/>
-      <c r="J5" s="34" t="n"/>
+      <c r="H5" s="52" t="n"/>
+      <c r="I5" s="52" t="n"/>
+      <c r="J5" s="53" t="n"/>
     </row>
     <row r="6" ht="108" customHeight="1">
       <c r="A6" s="23" t="inlineStr">
@@ -13852,9 +14296,9 @@
           <t>Nodal lesions were only formally distinguished from RECIST 1.0 onwards in version 1.1; sites experienced with older studies frequently record the long axis out of habit.</t>
         </is>
       </c>
-      <c r="H6" s="33" t="n"/>
-      <c r="I6" s="33" t="n"/>
-      <c r="J6" s="34" t="n"/>
+      <c r="H6" s="52" t="n"/>
+      <c r="I6" s="52" t="n"/>
+      <c r="J6" s="53" t="n"/>
     </row>
     <row r="7" ht="108" customHeight="1">
       <c r="A7" s="25" t="inlineStr">
@@ -13892,9 +14336,9 @@
           <t>Check the trajectory of the same lesion across visits — a tenfold step between adjacent visits is diagnostic of a unit error.</t>
         </is>
       </c>
-      <c r="H7" s="33" t="n"/>
-      <c r="I7" s="33" t="n"/>
-      <c r="J7" s="34" t="n"/>
+      <c r="H7" s="52" t="n"/>
+      <c r="I7" s="52" t="n"/>
+      <c r="J7" s="53" t="n"/>
     </row>
     <row r="8" ht="108" customHeight="1">
       <c r="A8" s="23" t="inlineStr">
@@ -13932,9 +14376,9 @@
           <t>Confirm against the scan dates in the imaging report rather than the visit date, which may reflect the clinic visit rather than the scan.</t>
         </is>
       </c>
-      <c r="H8" s="33" t="n"/>
-      <c r="I8" s="33" t="n"/>
-      <c r="J8" s="34" t="n"/>
+      <c r="H8" s="52" t="n"/>
+      <c r="I8" s="52" t="n"/>
+      <c r="J8" s="53" t="n"/>
     </row>
     <row r="9" ht="108" customHeight="1">
       <c r="A9" s="25" t="inlineStr">
@@ -13972,9 +14416,9 @@
           <t>Re-selection changes the baseline sum and therefore every subsequent percent change; expect all downstream responses to require re-derivation. Prioritise this issue before reviewing any response mismatch for this subject.</t>
         </is>
       </c>
-      <c r="H9" s="33" t="n"/>
-      <c r="I9" s="33" t="n"/>
-      <c r="J9" s="34" t="n"/>
+      <c r="H9" s="52" t="n"/>
+      <c r="I9" s="52" t="n"/>
+      <c r="J9" s="53" t="n"/>
     </row>
     <row r="10" ht="108" customHeight="1">
       <c r="A10" s="23" t="inlineStr">
@@ -14012,9 +14456,9 @@
           <t>Lymph nodes in different nodal stations are commonly all coded to a single "lymph node" organ; confirm whether the sponsor's convention treats nodal stations as separate organs before raising.</t>
         </is>
       </c>
-      <c r="H10" s="33" t="n"/>
-      <c r="I10" s="33" t="n"/>
-      <c r="J10" s="34" t="n"/>
+      <c r="H10" s="52" t="n"/>
+      <c r="I10" s="52" t="n"/>
+      <c r="J10" s="53" t="n"/>
     </row>
     <row r="11" ht="108" customHeight="1">
       <c r="A11" s="25" t="inlineStr">
@@ -14052,9 +14496,9 @@
           <t>Check the imaging slice thickness where available: a lesion must be at least twice the slice thickness to be measurable, so a 10 mm lesion on 8 mm slices is not measurable even though it meets the nominal threshold.</t>
         </is>
       </c>
-      <c r="H11" s="33" t="n"/>
-      <c r="I11" s="33" t="n"/>
-      <c r="J11" s="34" t="n"/>
+      <c r="H11" s="52" t="n"/>
+      <c r="I11" s="52" t="n"/>
+      <c r="J11" s="53" t="n"/>
     </row>
     <row r="12" ht="108" customHeight="1">
       <c r="A12" s="23" t="inlineStr">
@@ -14092,9 +14536,9 @@
           <t>This is one of the most frequent baseline errors. Verify that the recorded value is a short axis and not a longest diameter before concluding the selection was wrong.</t>
         </is>
       </c>
-      <c r="H12" s="33" t="n"/>
-      <c r="I12" s="33" t="n"/>
-      <c r="J12" s="34" t="n"/>
+      <c r="H12" s="52" t="n"/>
+      <c r="I12" s="52" t="n"/>
+      <c r="J12" s="53" t="n"/>
     </row>
     <row r="13" ht="108" customHeight="1">
       <c r="A13" s="25" t="inlineStr">
@@ -14132,9 +14576,9 @@
           <t>Where a node is clinically relevant despite being below threshold (for example biopsy-proven involvement), the site should document the rationale; consider accepting with a comment rather than a data change.</t>
         </is>
       </c>
-      <c r="H13" s="33" t="n"/>
-      <c r="I13" s="33" t="n"/>
-      <c r="J13" s="34" t="n"/>
+      <c r="H13" s="52" t="n"/>
+      <c r="I13" s="52" t="n"/>
+      <c r="J13" s="53" t="n"/>
     </row>
     <row r="14" ht="108" customHeight="1">
       <c r="A14" s="23" t="inlineStr">
@@ -14172,9 +14616,9 @@
           <t>Slice thickness often varies between the baseline and follow-up scans; if so, the comparison itself is compromised and merits a note to the imaging vendor.</t>
         </is>
       </c>
-      <c r="H14" s="33" t="n"/>
-      <c r="I14" s="33" t="n"/>
-      <c r="J14" s="34" t="n"/>
+      <c r="H14" s="52" t="n"/>
+      <c r="I14" s="52" t="n"/>
+      <c r="J14" s="53" t="n"/>
     </row>
     <row r="15" ht="108" customHeight="1">
       <c r="A15" s="25" t="inlineStr">
@@ -14212,9 +14656,9 @@
           <t>Blastic bone lesions are non-measurable, but a lytic or mixed lytic-blastic lesion with an identifiable soft tissue component can be measurable on CT/MRI. Cystic metastases can be measurable, but where non-cystic lesions are available they are preferred as targets.</t>
         </is>
       </c>
-      <c r="H15" s="33" t="n"/>
-      <c r="I15" s="33" t="n"/>
-      <c r="J15" s="34" t="n"/>
+      <c r="H15" s="52" t="n"/>
+      <c r="I15" s="52" t="n"/>
+      <c r="J15" s="53" t="n"/>
     </row>
     <row r="16" ht="108" customHeight="1">
       <c r="A16" s="23" t="inlineStr">
@@ -14252,9 +14696,9 @@
           <t>Also relevant for lesions treated with ablation, embolisation or surgery during the study — see TE-XD-004 for on-study local therapy.</t>
         </is>
       </c>
-      <c r="H16" s="33" t="n"/>
-      <c r="I16" s="33" t="n"/>
-      <c r="J16" s="34" t="n"/>
+      <c r="H16" s="52" t="n"/>
+      <c r="I16" s="52" t="n"/>
+      <c r="J16" s="53" t="n"/>
     </row>
     <row r="17" ht="108" customHeight="1">
       <c r="A17" s="25" t="inlineStr">
@@ -14292,9 +14736,9 @@
           <t>Check eligibility criteria: if the protocol requires measurable disease, this may also be an eligibility deviation requiring separate escalation.</t>
         </is>
       </c>
-      <c r="H17" s="33" t="n"/>
-      <c r="I17" s="33" t="n"/>
-      <c r="J17" s="34" t="n"/>
+      <c r="H17" s="52" t="n"/>
+      <c r="I17" s="52" t="n"/>
+      <c r="J17" s="53" t="n"/>
     </row>
     <row r="18" ht="108" customHeight="1">
       <c r="A18" s="23" t="inlineStr">
@@ -14332,9 +14776,9 @@
           <t>Distinguish the scan date from the assessment or read date; the protocol window normally applies to the scan.</t>
         </is>
       </c>
-      <c r="H18" s="33" t="n"/>
-      <c r="I18" s="33" t="n"/>
-      <c r="J18" s="34" t="n"/>
+      <c r="H18" s="52" t="n"/>
+      <c r="I18" s="52" t="n"/>
+      <c r="J18" s="53" t="n"/>
     </row>
     <row r="19" ht="108" customHeight="1">
       <c r="A19" s="25" t="inlineStr">
@@ -14372,9 +14816,9 @@
           <t>Check first whether a nodal target was included using its longest diameter, and whether all target lesions have a baseline measurement.</t>
         </is>
       </c>
-      <c r="H19" s="33" t="n"/>
-      <c r="I19" s="33" t="n"/>
-      <c r="J19" s="34" t="n"/>
+      <c r="H19" s="52" t="n"/>
+      <c r="I19" s="52" t="n"/>
+      <c r="J19" s="53" t="n"/>
     </row>
     <row r="20" ht="108" customHeight="1">
       <c r="A20" s="23" t="inlineStr">
@@ -14412,9 +14856,9 @@
           <t>Reproducibility legitimately overrides size — a large but ill-defined or confluent mass is a poor target. Expect a proportion of these to be correctly explained rather than corrected.</t>
         </is>
       </c>
-      <c r="H20" s="33" t="n"/>
-      <c r="I20" s="33" t="n"/>
-      <c r="J20" s="34" t="n"/>
+      <c r="H20" s="52" t="n"/>
+      <c r="I20" s="52" t="n"/>
+      <c r="J20" s="53" t="n"/>
     </row>
     <row r="21" ht="108" customHeight="1">
       <c r="A21" s="25" t="inlineStr">
@@ -14452,9 +14896,9 @@
           <t>A target lesion that was not evaluable at baseline should not have been selected as a target; check whether re-selection is required.</t>
         </is>
       </c>
-      <c r="H21" s="33" t="n"/>
-      <c r="I21" s="33" t="n"/>
-      <c r="J21" s="34" t="n"/>
+      <c r="H21" s="52" t="n"/>
+      <c r="I21" s="52" t="n"/>
+      <c r="J21" s="53" t="n"/>
     </row>
     <row r="22" ht="108" customHeight="1">
       <c r="A22" s="23" t="inlineStr">
@@ -14492,9 +14936,9 @@
           <t>Where a modality change was unavoidable, the affected timepoint may need to be treated as not evaluable for that lesion rather than measured.</t>
         </is>
       </c>
-      <c r="H22" s="33" t="n"/>
-      <c r="I22" s="33" t="n"/>
-      <c r="J22" s="34" t="n"/>
+      <c r="H22" s="52" t="n"/>
+      <c r="I22" s="52" t="n"/>
+      <c r="J22" s="53" t="n"/>
     </row>
     <row r="23" ht="108" customHeight="1">
       <c r="A23" s="25" t="inlineStr">
@@ -14532,9 +14976,9 @@
           <t>Commonly caused by brain MRI scheduled separately from body CT; confirm the imaging manual's tolerance before raising.</t>
         </is>
       </c>
-      <c r="H23" s="33" t="n"/>
-      <c r="I23" s="33" t="n"/>
-      <c r="J23" s="34" t="n"/>
+      <c r="H23" s="52" t="n"/>
+      <c r="I23" s="52" t="n"/>
+      <c r="J23" s="53" t="n"/>
     </row>
     <row r="24" ht="108" customHeight="1">
       <c r="A24" s="23" t="inlineStr">
@@ -14572,9 +15016,9 @@
           <t>Laterality errors are the most common subtype and matter most for paired organs (lung, kidney, breast, adnexa).</t>
         </is>
       </c>
-      <c r="H24" s="33" t="n"/>
-      <c r="I24" s="33" t="n"/>
-      <c r="J24" s="34" t="n"/>
+      <c r="H24" s="52" t="n"/>
+      <c r="I24" s="52" t="n"/>
+      <c r="J24" s="53" t="n"/>
     </row>
     <row r="25" ht="108" customHeight="1">
       <c r="A25" s="25" t="inlineStr">
@@ -14612,9 +15056,9 @@
           <t>Check whether the baseline was entered under a screening visit name that failed to map; this is frequently a data-transfer issue rather than missing data.</t>
         </is>
       </c>
-      <c r="H25" s="33" t="n"/>
-      <c r="I25" s="33" t="n"/>
-      <c r="J25" s="34" t="n"/>
+      <c r="H25" s="52" t="n"/>
+      <c r="I25" s="52" t="n"/>
+      <c r="J25" s="53" t="n"/>
     </row>
     <row r="26" ht="108" customHeight="1">
       <c r="A26" s="23" t="inlineStr">
@@ -14652,9 +15096,9 @@
           <t>Check for a lesion measured but omitted from the sum, a lesion recorded as absent but still included, and nodal lesions entered with the wrong axis.</t>
         </is>
       </c>
-      <c r="H26" s="33" t="n"/>
-      <c r="I26" s="33" t="n"/>
-      <c r="J26" s="34" t="n"/>
+      <c r="H26" s="52" t="n"/>
+      <c r="I26" s="52" t="n"/>
+      <c r="J26" s="53" t="n"/>
     </row>
     <row r="27" ht="108" customHeight="1">
       <c r="A27" s="25" t="inlineStr">
@@ -14692,9 +15136,9 @@
           <t>Distinguish "not evaluable" (lesion could not be assessed) from "absent" (lesion no longer visible); the two have opposite consequences for response.</t>
         </is>
       </c>
-      <c r="H27" s="33" t="n"/>
-      <c r="I27" s="33" t="n"/>
-      <c r="J27" s="34" t="n"/>
+      <c r="H27" s="52" t="n"/>
+      <c r="I27" s="52" t="n"/>
+      <c r="J27" s="53" t="n"/>
     </row>
     <row r="28" ht="108" customHeight="1">
       <c r="A28" s="23" t="inlineStr">
@@ -14732,9 +15176,9 @@
           <t>This is a systematic misunderstanding at many sites: a lesion that is "not seen because it resolved" should be recorded as absent, not as not evaluable.</t>
         </is>
       </c>
-      <c r="H28" s="33" t="n"/>
-      <c r="I28" s="33" t="n"/>
-      <c r="J28" s="34" t="n"/>
+      <c r="H28" s="52" t="n"/>
+      <c r="I28" s="52" t="n"/>
+      <c r="J28" s="53" t="n"/>
     </row>
     <row r="29" ht="108" customHeight="1">
       <c r="A29" s="25" t="inlineStr">
@@ -14772,9 +15216,9 @@
           <t>Genuine large changes do occur — rapid response to targeted therapy, cavitation, haemorrhage into a lesion, or coalescence of adjacent lesions. Look for a comment or a matching change in a neighbouring lesion.</t>
         </is>
       </c>
-      <c r="H29" s="33" t="n"/>
-      <c r="I29" s="33" t="n"/>
-      <c r="J29" s="34" t="n"/>
+      <c r="H29" s="52" t="n"/>
+      <c r="I29" s="52" t="n"/>
+      <c r="J29" s="53" t="n"/>
     </row>
     <row r="30" ht="108" customHeight="1">
       <c r="A30" s="23" t="inlineStr">
@@ -14812,9 +15256,9 @@
           <t>Confirm the protocol's position: some protocols treat reappearance after a complete response as progression in itself. The study configuration setting is reappearance_is_progression = {reappearance_is_progression}.</t>
         </is>
       </c>
-      <c r="H30" s="33" t="n"/>
-      <c r="I30" s="33" t="n"/>
-      <c r="J30" s="34" t="n"/>
+      <c r="H30" s="52" t="n"/>
+      <c r="I30" s="52" t="n"/>
+      <c r="J30" s="53" t="n"/>
     </row>
     <row r="31" ht="108" customHeight="1">
       <c r="A31" s="25" t="inlineStr">
@@ -14852,9 +15296,9 @@
           <t>Agree the convention centrally and document it in the imaging manual; retrospective harmonisation is usually preferable to leaving the study mixed.</t>
         </is>
       </c>
-      <c r="H31" s="33" t="n"/>
-      <c r="I31" s="33" t="n"/>
-      <c r="J31" s="34" t="n"/>
+      <c r="H31" s="52" t="n"/>
+      <c r="I31" s="52" t="n"/>
+      <c r="J31" s="53" t="n"/>
     </row>
     <row r="32" ht="108" customHeight="1">
       <c r="A32" s="23" t="inlineStr">
@@ -14892,9 +15336,9 @@
           <t>Cluster by site: isolated deviations are scheduling reality, but a site with a consistent bias is a monitoring signal.</t>
         </is>
       </c>
-      <c r="H32" s="33" t="n"/>
-      <c r="I32" s="33" t="n"/>
-      <c r="J32" s="34" t="n"/>
+      <c r="H32" s="52" t="n"/>
+      <c r="I32" s="52" t="n"/>
+      <c r="J32" s="53" t="n"/>
     </row>
     <row r="33" ht="108" customHeight="1">
       <c r="A33" s="25" t="inlineStr">
@@ -14932,9 +15376,9 @@
           <t>Cross-check against the visit schedule and any unscheduled visits; assessments performed but entered under an unmapped visit name are a common cause.</t>
         </is>
       </c>
-      <c r="H33" s="33" t="n"/>
-      <c r="I33" s="33" t="n"/>
-      <c r="J33" s="34" t="n"/>
+      <c r="H33" s="52" t="n"/>
+      <c r="I33" s="52" t="n"/>
+      <c r="J33" s="53" t="n"/>
     </row>
     <row r="34" ht="108" customHeight="1">
       <c r="A34" s="23" t="inlineStr">
@@ -14972,9 +15416,9 @@
           <t>This is the single most common nodal error and it usually reflects a well-intentioned attempt to make the arithmetic produce a complete response. Explain the rule to the site rather than only requesting the correction.</t>
         </is>
       </c>
-      <c r="H34" s="33" t="n"/>
-      <c r="I34" s="33" t="n"/>
-      <c r="J34" s="34" t="n"/>
+      <c r="H34" s="52" t="n"/>
+      <c r="I34" s="52" t="n"/>
+      <c r="J34" s="53" t="n"/>
     </row>
     <row r="35" ht="108" customHeight="1">
       <c r="A35" s="25" t="inlineStr">
@@ -15012,9 +15456,9 @@
           <t>Sites often assess non-target disease collectively rather than lesion by lesion; check whether the eCRF expects a per-lesion or an overall non-target response.</t>
         </is>
       </c>
-      <c r="H35" s="33" t="n"/>
-      <c r="I35" s="33" t="n"/>
-      <c r="J35" s="34" t="n"/>
+      <c r="H35" s="52" t="n"/>
+      <c r="I35" s="52" t="n"/>
+      <c r="J35" s="53" t="n"/>
     </row>
     <row r="36" ht="108" customHeight="1">
       <c r="A36" s="23" t="inlineStr">
@@ -15052,9 +15496,9 @@
           <t>Post-treatment follow-up assessments are legitimate in many protocols; confirm the follow-up period before treating a post-discontinuation assessment as an error.</t>
         </is>
       </c>
-      <c r="H36" s="33" t="n"/>
-      <c r="I36" s="33" t="n"/>
-      <c r="J36" s="34" t="n"/>
+      <c r="H36" s="52" t="n"/>
+      <c r="I36" s="52" t="n"/>
+      <c r="J36" s="53" t="n"/>
     </row>
     <row r="37" ht="108" customHeight="1">
       <c r="A37" s="25" t="inlineStr">
@@ -15092,9 +15536,9 @@
           <t>Where the lesion was visible in retrospect on an earlier scan, the progression date is normally the earlier scan; this requires a documented radiology decision.</t>
         </is>
       </c>
-      <c r="H37" s="33" t="n"/>
-      <c r="I37" s="33" t="n"/>
-      <c r="J37" s="34" t="n"/>
+      <c r="H37" s="52" t="n"/>
+      <c r="I37" s="52" t="n"/>
+      <c r="J37" s="53" t="n"/>
     </row>
     <row r="38" ht="108" customHeight="1">
       <c r="A38" s="23" t="inlineStr">
@@ -15132,9 +15576,9 @@
           <t>Where the span is unavoidable, the assessment date convention (earliest scan or latest scan) should be applied consistently across the study.</t>
         </is>
       </c>
-      <c r="H38" s="33" t="n"/>
-      <c r="I38" s="33" t="n"/>
-      <c r="J38" s="34" t="n"/>
+      <c r="H38" s="52" t="n"/>
+      <c r="I38" s="52" t="n"/>
+      <c r="J38" s="53" t="n"/>
     </row>
     <row r="39" ht="108" customHeight="1">
       <c r="A39" s="25" t="inlineStr">
@@ -15172,9 +15616,9 @@
           <t>Small and stable lesions genuinely produce repeated values; this check is deliberately informational and should be reviewed in the context of the whole subject rather than raised as a query in isolation.</t>
         </is>
       </c>
-      <c r="H39" s="33" t="n"/>
-      <c r="I39" s="33" t="n"/>
-      <c r="J39" s="34" t="n"/>
+      <c r="H39" s="52" t="n"/>
+      <c r="I39" s="52" t="n"/>
+      <c r="J39" s="53" t="n"/>
     </row>
     <row r="40" ht="108" customHeight="1">
       <c r="A40" s="23" t="inlineStr">
@@ -15212,9 +15656,9 @@
           <t>Before querying the response, confirm the measurements themselves: a response mismatch is frequently a symptom of a measurement or sum error already flagged for this subject. Check the linked findings for this subject first.</t>
         </is>
       </c>
-      <c r="H40" s="33" t="n"/>
-      <c r="I40" s="33" t="n"/>
-      <c r="J40" s="34" t="n"/>
+      <c r="H40" s="52" t="n"/>
+      <c r="I40" s="52" t="n"/>
+      <c r="J40" s="53" t="n"/>
     </row>
     <row r="41" ht="108" customHeight="1">
       <c r="A41" s="25" t="inlineStr">
@@ -15252,9 +15696,9 @@
           <t>Confirm first whether progression was actually driven by a new lesion or by non-target progression, in which case the response is correct and this finding can be rejected. This check applies only to progression driven by the target sum.</t>
         </is>
       </c>
-      <c r="H41" s="33" t="n"/>
-      <c r="I41" s="33" t="n"/>
-      <c r="J41" s="34" t="n"/>
+      <c r="H41" s="52" t="n"/>
+      <c r="I41" s="52" t="n"/>
+      <c r="J41" s="53" t="n"/>
     </row>
     <row r="42" ht="108" customHeight="1">
       <c r="A42" s="23" t="inlineStr">
@@ -15292,9 +15736,9 @@
           <t>This is the most consequential single error class in tumor data: it delays or entirely misses the progression date and directly biases progression-free survival. Always check the nadir visit shown above is itself a complete assessment.</t>
         </is>
       </c>
-      <c r="H42" s="33" t="n"/>
-      <c r="I42" s="33" t="n"/>
-      <c r="J42" s="34" t="n"/>
+      <c r="H42" s="52" t="n"/>
+      <c r="I42" s="52" t="n"/>
+      <c r="J42" s="53" t="n"/>
     </row>
     <row r="43" ht="108" customHeight="1">
       <c r="A43" s="25" t="inlineStr">
@@ -15332,9 +15776,9 @@
           <t>Note the asymmetry that causes most of these: the sum of diameters can be very small without a complete response being appropriate, because nodes retain a short axis. Conversely, complete response does not require the sum to be zero.</t>
         </is>
       </c>
-      <c r="H43" s="33" t="n"/>
-      <c r="I43" s="33" t="n"/>
-      <c r="J43" s="34" t="n"/>
+      <c r="H43" s="52" t="n"/>
+      <c r="I43" s="52" t="n"/>
+      <c r="J43" s="53" t="n"/>
     </row>
     <row r="44" ht="108" customHeight="1">
       <c r="A44" s="23" t="inlineStr">
@@ -15372,9 +15816,9 @@
           <t>A complete response of non-target disease additionally requires every pathological lymph node to be below 10 mm short axis, and where the protocol uses tumor markers, normalisation of those markers.</t>
         </is>
       </c>
-      <c r="H44" s="33" t="n"/>
-      <c r="I44" s="33" t="n"/>
-      <c r="J44" s="34" t="n"/>
+      <c r="H44" s="52" t="n"/>
+      <c r="I44" s="52" t="n"/>
+      <c r="J44" s="53" t="n"/>
     </row>
     <row r="45" ht="108" customHeight="1">
       <c r="A45" s="25" t="inlineStr">
@@ -15412,9 +15856,9 @@
           <t>Non-target nodes are often not measured at all; where the eCRF does not capture a short axis for non-target nodes, this check depends on the radiology narrative and may need to be raised as a clarification rather than a correction.</t>
         </is>
       </c>
-      <c r="H45" s="33" t="n"/>
-      <c r="I45" s="33" t="n"/>
-      <c r="J45" s="34" t="n"/>
+      <c r="H45" s="52" t="n"/>
+      <c r="I45" s="52" t="n"/>
+      <c r="J45" s="53" t="n"/>
     </row>
     <row r="46" ht="108" customHeight="1">
       <c r="A46" s="23" t="inlineStr">
@@ -15452,9 +15896,9 @@
           <t>Genuine cases exist — for example a marked increase in a pleural effusion or in lymphangitic disease. The question to the site is not "is this wrong" but "what supports unequivocal". Where the answer supports it, accept and record the rationale so the same finding is not re-raised.</t>
         </is>
       </c>
-      <c r="H46" s="33" t="n"/>
-      <c r="I46" s="33" t="n"/>
-      <c r="J46" s="34" t="n"/>
+      <c r="H46" s="52" t="n"/>
+      <c r="I46" s="52" t="n"/>
+      <c r="J46" s="53" t="n"/>
     </row>
     <row r="47" ht="108" customHeight="1">
       <c r="A47" s="25" t="inlineStr">
@@ -15492,9 +15936,9 @@
           <t>The combinations most often mis-applied are: target complete response with persisting non-target disease, which is a partial response rather than a complete response; and any new lesion, which is progression regardless of the target and non-target results.</t>
         </is>
       </c>
-      <c r="H47" s="33" t="n"/>
-      <c r="I47" s="33" t="n"/>
-      <c r="J47" s="34" t="n"/>
+      <c r="H47" s="52" t="n"/>
+      <c r="I47" s="52" t="n"/>
+      <c r="J47" s="53" t="n"/>
     </row>
     <row r="48" ht="108" customHeight="1">
       <c r="A48" s="23" t="inlineStr">
@@ -15532,9 +15976,9 @@
           <t>Check whether the lesion was recorded as a new lesion at a later visit than the one where it was first seen; the progression date follows the first observation.</t>
         </is>
       </c>
-      <c r="H48" s="33" t="n"/>
-      <c r="I48" s="33" t="n"/>
-      <c r="J48" s="34" t="n"/>
+      <c r="H48" s="52" t="n"/>
+      <c r="I48" s="52" t="n"/>
+      <c r="J48" s="53" t="n"/>
     </row>
     <row r="49" ht="108" customHeight="1">
       <c r="A49" s="25" t="inlineStr">
@@ -15572,9 +16016,9 @@
           <t>Where the finding is equivocal rather than unequivocal, the correct handling is to record it as equivocal and continue treatment, treating the timepoint as not evaluable and re-assessing at the next visit; if later confirmed, progression is dated to this visit.</t>
         </is>
       </c>
-      <c r="H49" s="33" t="n"/>
-      <c r="I49" s="33" t="n"/>
-      <c r="J49" s="34" t="n"/>
+      <c r="H49" s="52" t="n"/>
+      <c r="I49" s="52" t="n"/>
+      <c r="J49" s="53" t="n"/>
     </row>
     <row r="50" ht="108" customHeight="1">
       <c r="A50" s="23" t="inlineStr">
@@ -15612,9 +16056,9 @@
           <t>Brain metastases are the usual case: many protocols do not require baseline brain imaging, so a first brain scan performed for symptoms yields lesions that must be treated as new. Confirm the protocol's imaging requirements before raising.</t>
         </is>
       </c>
-      <c r="H50" s="33" t="n"/>
-      <c r="I50" s="33" t="n"/>
-      <c r="J50" s="34" t="n"/>
+      <c r="H50" s="52" t="n"/>
+      <c r="I50" s="52" t="n"/>
+      <c r="J50" s="53" t="n"/>
     </row>
     <row r="51" ht="108" customHeight="1">
       <c r="A51" s="25" t="inlineStr">
@@ -15652,9 +16096,9 @@
           <t>Inflammatory and infectious uptake is common, particularly under immunotherapy; anatomical confirmation matters most in that setting.</t>
         </is>
       </c>
-      <c r="H51" s="33" t="n"/>
-      <c r="I51" s="33" t="n"/>
-      <c r="J51" s="34" t="n"/>
+      <c r="H51" s="52" t="n"/>
+      <c r="I51" s="52" t="n"/>
+      <c r="J51" s="53" t="n"/>
     </row>
     <row r="52" ht="108" customHeight="1">
       <c r="A52" s="23" t="inlineStr">
@@ -15692,9 +16136,9 @@
           <t>Under iRECIST the handling differs — the iUPD and iCPD dates are both retained and the analysis convention is protocol-specific. Check which criteria govern before applying this rule.</t>
         </is>
       </c>
-      <c r="H52" s="33" t="n"/>
-      <c r="I52" s="33" t="n"/>
-      <c r="J52" s="34" t="n"/>
+      <c r="H52" s="52" t="n"/>
+      <c r="I52" s="52" t="n"/>
+      <c r="J52" s="53" t="n"/>
     </row>
     <row r="53" ht="108" customHeight="1">
       <c r="A53" s="25" t="inlineStr">
@@ -15732,9 +16176,9 @@
           <t>Check whether a confirmatory scan exists but was entered as an unscheduled visit; also check the interval, since a confirmation performed too early does not satisfy the requirement.</t>
         </is>
       </c>
-      <c r="H53" s="33" t="n"/>
-      <c r="I53" s="33" t="n"/>
-      <c r="J53" s="34" t="n"/>
+      <c r="H53" s="52" t="n"/>
+      <c r="I53" s="52" t="n"/>
+      <c r="J53" s="53" t="n"/>
     </row>
     <row r="54" ht="108" customHeight="1">
       <c r="A54" s="23" t="inlineStr">
@@ -15772,9 +16216,9 @@
           <t>Two frequent causes: a response recorded after progression being counted, and a stable disease result assigned before the protocol's minimum duration from baseline has elapsed.</t>
         </is>
       </c>
-      <c r="H54" s="33" t="n"/>
-      <c r="I54" s="33" t="n"/>
-      <c r="J54" s="34" t="n"/>
+      <c r="H54" s="52" t="n"/>
+      <c r="I54" s="52" t="n"/>
+      <c r="J54" s="53" t="n"/>
     </row>
     <row r="55" ht="108" customHeight="1">
       <c r="A55" s="25" t="inlineStr">
@@ -15812,9 +16256,9 @@
           <t>Check first whether target lesions were in fact selected but failed to load — a missing target lesion record produces this finding spuriously. Look for a companion structural finding on this subject.</t>
         </is>
       </c>
-      <c r="H55" s="33" t="n"/>
-      <c r="I55" s="33" t="n"/>
-      <c r="J55" s="34" t="n"/>
+      <c r="H55" s="52" t="n"/>
+      <c r="I55" s="52" t="n"/>
+      <c r="J55" s="53" t="n"/>
     </row>
     <row r="56" ht="108" customHeight="1">
       <c r="A56" s="23" t="inlineStr">
@@ -15852,9 +16296,9 @@
           <t>This affects best overall response rather than the timepoint response in many conventions; confirm the sponsor's derivation convention before querying the site.</t>
         </is>
       </c>
-      <c r="H56" s="33" t="n"/>
-      <c r="I56" s="33" t="n"/>
-      <c r="J56" s="34" t="n"/>
+      <c r="H56" s="52" t="n"/>
+      <c r="I56" s="52" t="n"/>
+      <c r="J56" s="53" t="n"/>
     </row>
     <row r="57" ht="108" customHeight="1">
       <c r="A57" s="25" t="inlineStr">
@@ -15892,9 +16336,9 @@
           <t>Where the subject continued treatment beyond progression, the later assessments are legitimate data; the issue is their use in derivation, not their existence. If iRECIST applies, progression may have been unconfirmed and the later assessments are then fully valid — check the applicable criteria.</t>
         </is>
       </c>
-      <c r="H57" s="33" t="n"/>
-      <c r="I57" s="33" t="n"/>
-      <c r="J57" s="34" t="n"/>
+      <c r="H57" s="52" t="n"/>
+      <c r="I57" s="52" t="n"/>
+      <c r="J57" s="53" t="n"/>
     </row>
     <row r="58" ht="108" customHeight="1">
       <c r="A58" s="23" t="inlineStr">
@@ -15932,9 +16376,9 @@
           <t>Distinguish radiological progression from clinical progression: if progression was determined clinically, the date may legitimately precede any imaging, and the record should say so.</t>
         </is>
       </c>
-      <c r="H58" s="33" t="n"/>
-      <c r="I58" s="33" t="n"/>
-      <c r="J58" s="34" t="n"/>
+      <c r="H58" s="52" t="n"/>
+      <c r="I58" s="52" t="n"/>
+      <c r="J58" s="53" t="n"/>
     </row>
     <row r="59" ht="108" customHeight="1">
       <c r="A59" s="25" t="inlineStr">
@@ -15972,9 +16416,9 @@
           <t>Review the lesion-level data from both readers side by side. Consistent directional discordance at one site is a monitoring signal; scattered discordance is normal reader variability. Where the sponsor keeps the two streams deliberately separated, this rule should be disabled in configuration.</t>
         </is>
       </c>
-      <c r="H59" s="33" t="n"/>
-      <c r="I59" s="33" t="n"/>
-      <c r="J59" s="34" t="n"/>
+      <c r="H59" s="52" t="n"/>
+      <c r="I59" s="52" t="n"/>
+      <c r="J59" s="53" t="n"/>
     </row>
     <row r="60" ht="108" customHeight="1">
       <c r="A60" s="23" t="inlineStr">
@@ -16012,9 +16456,9 @@
           <t>The commonest cause is the site applying RECIST 1.1 habits to an iRECIST study. Where both RECIST 1.1 and iRECIST responses are collected, the RECIST 1.1 field correctly reads PD while the iRECIST field should read iUPD — the two are not in conflict.</t>
         </is>
       </c>
-      <c r="H60" s="33" t="n"/>
-      <c r="I60" s="33" t="n"/>
-      <c r="J60" s="34" t="n"/>
+      <c r="H60" s="52" t="n"/>
+      <c r="I60" s="52" t="n"/>
+      <c r="J60" s="53" t="n"/>
     </row>
     <row r="61" ht="108" customHeight="1">
       <c r="A61" s="25" t="inlineStr">
@@ -16052,9 +16496,9 @@
           <t>Where the subject discontinued treatment at unconfirmed progression, no confirmation is expected and this finding should be rejected with that reason; check the disposition data before querying.</t>
         </is>
       </c>
-      <c r="H61" s="33" t="n"/>
-      <c r="I61" s="33" t="n"/>
-      <c r="J61" s="34" t="n"/>
+      <c r="H61" s="52" t="n"/>
+      <c r="I61" s="52" t="n"/>
+      <c r="J61" s="53" t="n"/>
     </row>
     <row r="62" ht="108" customHeight="1">
       <c r="A62" s="23" t="inlineStr">
@@ -16092,9 +16536,9 @@
           <t>Note the reference point: confirmation compares against the unconfirmed progression timepoint, not against the nadir. This differs from RECIST 1.1 and is a frequent source of confusion.</t>
         </is>
       </c>
-      <c r="H62" s="33" t="n"/>
-      <c r="I62" s="33" t="n"/>
-      <c r="J62" s="34" t="n"/>
+      <c r="H62" s="52" t="n"/>
+      <c r="I62" s="52" t="n"/>
+      <c r="J62" s="53" t="n"/>
     </row>
     <row r="63" ht="108" customHeight="1">
       <c r="A63" s="25" t="inlineStr">
@@ -16132,9 +16576,9 @@
           <t>Confirm the eCRF design supports separate new lesion recording; where it does not, this is a study set-up issue affecting every iRECIST subject rather than a site error.</t>
         </is>
       </c>
-      <c r="H63" s="33" t="n"/>
-      <c r="I63" s="33" t="n"/>
-      <c r="J63" s="34" t="n"/>
+      <c r="H63" s="52" t="n"/>
+      <c r="I63" s="52" t="n"/>
+      <c r="J63" s="53" t="n"/>
     </row>
     <row r="64" ht="108" customHeight="1">
       <c r="A64" s="23" t="inlineStr">
@@ -16172,9 +16616,9 @@
           <t>Multiple episodes of unconfirmed progression are permitted and are not an error. What is not permitted is treating the unconfirmed progression sum as the new reference.</t>
         </is>
       </c>
-      <c r="H64" s="33" t="n"/>
-      <c r="I64" s="33" t="n"/>
-      <c r="J64" s="34" t="n"/>
+      <c r="H64" s="52" t="n"/>
+      <c r="I64" s="52" t="n"/>
+      <c r="J64" s="53" t="n"/>
     </row>
     <row r="65" ht="108" customHeight="1">
       <c r="A65" s="25" t="inlineStr">
@@ -16212,9 +16656,9 @@
           <t>The appearance of numerous new lesions is itself strong evidence of true progression, so this finding is usually a recording issue rather than a clinical question.</t>
         </is>
       </c>
-      <c r="H65" s="33" t="n"/>
-      <c r="I65" s="33" t="n"/>
-      <c r="J65" s="34" t="n"/>
+      <c r="H65" s="52" t="n"/>
+      <c r="I65" s="52" t="n"/>
+      <c r="J65" s="53" t="n"/>
     </row>
     <row r="66" ht="108" customHeight="1">
       <c r="A66" s="23" t="inlineStr">
@@ -16252,9 +16696,9 @@
           <t>Check whether the earlier assessment was in fact unconfirmed rather than confirmed progression; a mislabelled iCPD is the more likely error.</t>
         </is>
       </c>
-      <c r="H66" s="33" t="n"/>
-      <c r="I66" s="33" t="n"/>
-      <c r="J66" s="34" t="n"/>
+      <c r="H66" s="52" t="n"/>
+      <c r="I66" s="52" t="n"/>
+      <c r="J66" s="53" t="n"/>
     </row>
     <row r="67" ht="108" customHeight="1">
       <c r="A67" s="25" t="inlineStr">
@@ -16292,9 +16736,9 @@
           <t>This is a protocol compliance point as much as a data point; where the eCRF has no field for it, escalate to the monitoring team rather than issuing a data query.</t>
         </is>
       </c>
-      <c r="H67" s="33" t="n"/>
-      <c r="I67" s="33" t="n"/>
-      <c r="J67" s="34" t="n"/>
+      <c r="H67" s="52" t="n"/>
+      <c r="I67" s="52" t="n"/>
+      <c r="J67" s="53" t="n"/>
     </row>
     <row r="68" ht="108" customHeight="1">
       <c r="A68" s="23" t="inlineStr">
@@ -16332,9 +16776,9 @@
           <t>Where the two fields are on separate forms completed by different people, expect systematic divergence at a site; treat that as a training signal rather than a per-record query.</t>
         </is>
       </c>
-      <c r="H68" s="33" t="n"/>
-      <c r="I68" s="33" t="n"/>
-      <c r="J68" s="34" t="n"/>
+      <c r="H68" s="52" t="n"/>
+      <c r="I68" s="52" t="n"/>
+      <c r="J68" s="53" t="n"/>
     </row>
     <row r="69" ht="108" customHeight="1">
       <c r="A69" s="25" t="inlineStr">
@@ -16372,9 +16816,9 @@
           <t>Raise with the study data manager and the biostatistician; resolution usually requires a database change rather than data correction.</t>
         </is>
       </c>
-      <c r="H69" s="33" t="n"/>
-      <c r="I69" s="33" t="n"/>
-      <c r="J69" s="34" t="n"/>
+      <c r="H69" s="52" t="n"/>
+      <c r="I69" s="52" t="n"/>
+      <c r="J69" s="53" t="n"/>
     </row>
     <row r="70" ht="108" customHeight="1">
       <c r="A70" s="23" t="inlineStr">
@@ -16412,9 +16856,9 @@
           <t>Clinical progression without radiological confirmation is legitimate and common near end of life; the record should show it as such rather than leaving the tumor data silent.</t>
         </is>
       </c>
-      <c r="H70" s="33" t="n"/>
-      <c r="I70" s="33" t="n"/>
-      <c r="J70" s="34" t="n"/>
+      <c r="H70" s="52" t="n"/>
+      <c r="I70" s="52" t="n"/>
+      <c r="J70" s="53" t="n"/>
     </row>
     <row r="71" ht="108" customHeight="1">
       <c r="A71" s="25" t="inlineStr">
@@ -16452,9 +16896,9 @@
           <t>Check the applicable response criteria first — under iRECIST this pattern is normal and the finding should be rejected.</t>
         </is>
       </c>
-      <c r="H71" s="33" t="n"/>
-      <c r="I71" s="33" t="n"/>
-      <c r="J71" s="34" t="n"/>
+      <c r="H71" s="52" t="n"/>
+      <c r="I71" s="52" t="n"/>
+      <c r="J71" s="53" t="n"/>
     </row>
     <row r="72" ht="108" customHeight="1">
       <c r="A72" s="23" t="inlineStr">
@@ -16492,9 +16936,9 @@
           <t>Radiotherapy for symptom palliation is a frequent benign explanation; distinguish it from a change of systemic therapy.</t>
         </is>
       </c>
-      <c r="H72" s="33" t="n"/>
-      <c r="I72" s="33" t="n"/>
-      <c r="J72" s="34" t="n"/>
+      <c r="H72" s="52" t="n"/>
+      <c r="I72" s="52" t="n"/>
+      <c r="J72" s="53" t="n"/>
     </row>
     <row r="73" ht="108" customHeight="1">
       <c r="A73" s="25" t="inlineStr">
@@ -16532,9 +16976,9 @@
           <t>The usual analytical convention is that the subject is considered to have progressed, or is censored, at the time of local therapy to a target lesion; confirm the protocol's convention with the statistician.</t>
         </is>
       </c>
-      <c r="H73" s="33" t="n"/>
-      <c r="I73" s="33" t="n"/>
-      <c r="J73" s="34" t="n"/>
+      <c r="H73" s="52" t="n"/>
+      <c r="I73" s="52" t="n"/>
+      <c r="J73" s="53" t="n"/>
     </row>
     <row r="74" ht="108" customHeight="1">
       <c r="A74" s="23" t="inlineStr">
@@ -16572,9 +17016,9 @@
           <t>Many sponsors instruct sites not to report disease progression as an adverse event; where that convention applies, the finding is also a coding issue for the safety team.</t>
         </is>
       </c>
-      <c r="H74" s="33" t="n"/>
-      <c r="I74" s="33" t="n"/>
-      <c r="J74" s="34" t="n"/>
+      <c r="H74" s="52" t="n"/>
+      <c r="I74" s="52" t="n"/>
+      <c r="J74" s="53" t="n"/>
     </row>
     <row r="75" ht="108" customHeight="1">
       <c r="A75" s="25" t="inlineStr">
@@ -16612,9 +17056,9 @@
           <t>Partial dates are a frequent cause; check whether an imputed date is being compared against a complete one.</t>
         </is>
       </c>
-      <c r="H75" s="33" t="n"/>
-      <c r="I75" s="33" t="n"/>
-      <c r="J75" s="34" t="n"/>
+      <c r="H75" s="52" t="n"/>
+      <c r="I75" s="52" t="n"/>
+      <c r="J75" s="53" t="n"/>
     </row>
     <row r="76" ht="108" customHeight="1">
       <c r="A76" s="23" t="inlineStr">
@@ -16652,9 +17096,9 @@
           <t>Marker elevation can have non-malignant causes; the site's explanation may be sufficient without a data change.</t>
         </is>
       </c>
-      <c r="H76" s="33" t="n"/>
-      <c r="I76" s="33" t="n"/>
-      <c r="J76" s="34" t="n"/>
+      <c r="H76" s="52" t="n"/>
+      <c r="I76" s="52" t="n"/>
+      <c r="J76" s="53" t="n"/>
     </row>
     <row r="77" ht="108" customHeight="1">
       <c r="A77" s="25" t="inlineStr">
@@ -16692,9 +17136,9 @@
           <t>Contrast versus non-contrast CT is the most consequential variant and is often not captured as a distinct modality; consider whether the eCRF should distinguish them.</t>
         </is>
       </c>
-      <c r="H77" s="33" t="n"/>
-      <c r="I77" s="33" t="n"/>
-      <c r="J77" s="34" t="n"/>
+      <c r="H77" s="52" t="n"/>
+      <c r="I77" s="52" t="n"/>
+      <c r="J77" s="53" t="n"/>
     </row>
     <row r="78" ht="108" customHeight="1">
       <c r="A78" s="23" t="inlineStr">
@@ -16732,9 +17176,9 @@
           <t>Brain imaging is the usual case, particularly in lung cancer and melanoma studies.</t>
         </is>
       </c>
-      <c r="H78" s="33" t="n"/>
-      <c r="I78" s="33" t="n"/>
-      <c r="J78" s="34" t="n"/>
+      <c r="H78" s="52" t="n"/>
+      <c r="I78" s="52" t="n"/>
+      <c r="J78" s="53" t="n"/>
     </row>
     <row r="79" ht="108" customHeight="1">
       <c r="A79" s="25" t="inlineStr">
@@ -16772,9 +17216,9 @@
           <t>Check for an unscheduled assessment that was not entered; a response confirmed at an unscheduled visit is a common cause.</t>
         </is>
       </c>
-      <c r="H79" s="33" t="n"/>
-      <c r="I79" s="33" t="n"/>
-      <c r="J79" s="34" t="n"/>
+      <c r="H79" s="52" t="n"/>
+      <c r="I79" s="52" t="n"/>
+      <c r="J79" s="53" t="n"/>
     </row>
     <row r="80" ht="108" customHeight="1">
       <c r="A80" s="23" t="inlineStr">
@@ -16812,9 +17256,9 @@
           <t>Early death or early withdrawal are the usual explanations and are legitimate; the finding exists to ensure the reason is captured.</t>
         </is>
       </c>
-      <c r="H80" s="33" t="n"/>
-      <c r="I80" s="33" t="n"/>
-      <c r="J80" s="34" t="n"/>
+      <c r="H80" s="52" t="n"/>
+      <c r="I80" s="52" t="n"/>
+      <c r="J80" s="53" t="n"/>
     </row>
     <row r="81" ht="108" customHeight="1">
       <c r="A81" s="25" t="inlineStr">
@@ -16852,9 +17296,9 @@
           <t>Pair with a site training action and re-check at the next data cut; the recurrence status on the linked findings will show whether the intervention worked.</t>
         </is>
       </c>
-      <c r="H81" s="33" t="n"/>
-      <c r="I81" s="33" t="n"/>
-      <c r="J81" s="34" t="n"/>
+      <c r="H81" s="52" t="n"/>
+      <c r="I81" s="52" t="n"/>
+      <c r="J81" s="53" t="n"/>
     </row>
     <row r="82" ht="108" customHeight="1">
       <c r="A82" s="23" t="inlineStr">
@@ -16892,9 +17336,9 @@
           <t>If the outstanding query is materially different in scope from this finding, disposition the finding as NEW manually and issue a distinct query.</t>
         </is>
       </c>
-      <c r="H82" s="33" t="n"/>
-      <c r="I82" s="33" t="n"/>
-      <c r="J82" s="34" t="n"/>
+      <c r="H82" s="52" t="n"/>
+      <c r="I82" s="52" t="n"/>
+      <c r="J82" s="53" t="n"/>
     </row>
     <row r="83" ht="108" customHeight="1">
       <c r="A83" s="25" t="inlineStr">
@@ -16932,9 +17376,9 @@
           <t>Read the original answer in full before re-querying — it is quoted above. Where the site confirmed the data is correct and the explanation holds, disposition this as justified so it is not raised again at the next data cut.</t>
         </is>
       </c>
-      <c r="H83" s="33" t="n"/>
-      <c r="I83" s="33" t="n"/>
-      <c r="J83" s="34" t="n"/>
+      <c r="H83" s="52" t="n"/>
+      <c r="I83" s="52" t="n"/>
+      <c r="J83" s="53" t="n"/>
     </row>
     <row r="84" ht="108" customHeight="1">
       <c r="A84" s="23" t="inlineStr">
@@ -16972,9 +17416,9 @@
           <t>Compare the audit trail of the affected field across the two data cuts; a reverted correction and a fresh error need different responses.</t>
         </is>
       </c>
-      <c r="H84" s="33" t="n"/>
-      <c r="I84" s="33" t="n"/>
-      <c r="J84" s="34" t="n"/>
+      <c r="H84" s="52" t="n"/>
+      <c r="I84" s="52" t="n"/>
+      <c r="J84" s="53" t="n"/>
     </row>
     <row r="85" ht="108" customHeight="1">
       <c r="A85" s="25" t="inlineStr">
@@ -17012,9 +17456,9 @@
           <t>Escalate through the monitoring team rather than by reissuing the query.</t>
         </is>
       </c>
-      <c r="H85" s="33" t="n"/>
-      <c r="I85" s="33" t="n"/>
-      <c r="J85" s="34" t="n"/>
+      <c r="H85" s="52" t="n"/>
+      <c r="I85" s="52" t="n"/>
+      <c r="J85" s="53" t="n"/>
     </row>
     <row r="86" ht="108" customHeight="1">
       <c r="A86" s="23" t="inlineStr">
@@ -17052,9 +17496,9 @@
           <t>Site answers are often correct but terse. Read the original answer in full before re-querying; the model flags candidates rather than making the determination.</t>
         </is>
       </c>
-      <c r="H86" s="33" t="n"/>
-      <c r="I86" s="33" t="n"/>
-      <c r="J86" s="34" t="n"/>
+      <c r="H86" s="52" t="n"/>
+      <c r="I86" s="52" t="n"/>
+      <c r="J86" s="53" t="n"/>
     </row>
     <row r="87" ht="108" customHeight="1">
       <c r="A87" s="25" t="inlineStr">
@@ -17092,9 +17536,9 @@
           <t>This is why measurement corrections should always be reviewed together with the sum and the response for the same timepoint, and for all later timepoints if the nadir moved.</t>
         </is>
       </c>
-      <c r="H87" s="33" t="n"/>
-      <c r="I87" s="33" t="n"/>
-      <c r="J87" s="34" t="n"/>
+      <c r="H87" s="52" t="n"/>
+      <c r="I87" s="52" t="n"/>
+      <c r="J87" s="53" t="n"/>
     </row>
     <row r="88" ht="108" customHeight="1">
       <c r="A88" s="23" t="inlineStr">
@@ -17132,9 +17576,9 @@
           <t>This matters most where the effusion is the sole basis for progression; where other unequivocal progression exists the finding is suppressed. Some protocols explicitly waive cytological confirmation — check the protocol before querying, and if it is waived, deactivate this rule at the AC-11 intake rather than dispositioning each occurrence.</t>
         </is>
       </c>
-      <c r="H88" s="33" t="n"/>
-      <c r="I88" s="33" t="n"/>
-      <c r="J88" s="34" t="n"/>
+      <c r="H88" s="52" t="n"/>
+      <c r="I88" s="52" t="n"/>
+      <c r="J88" s="53" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:J88"/>

--- a/docs/spec/TEA-SPEC-001_programming-specification.xlsx
+++ b/docs/spec/TEA-SPEC-001_programming-specification.xlsx
@@ -16,23 +16,24 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pipeline" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rules" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rule_Messages" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Confidence_Model" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Query_Reconciliation" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prioritisation" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Input_Contract" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Finding_Contract" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LLM_Integration" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Testing" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Extensibility" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Log" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Query_Style" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Confidence_Model" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Query_Reconciliation" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prioritisation" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Input_Contract" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Finding_Contract" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LLM_Integration" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Testing" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Extensibility" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Log" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Definitions'!$A$3:$C$50</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Rules'!$A$3:$Q$88</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Rule_Messages'!$A$3:$J$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Rules'!$A$3:$U$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Rule_Messages'!$A$3:$K$88</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -41,7 +42,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -134,6 +135,11 @@
       <sz val="8"/>
     </font>
     <font>
+      <name val="Consolas"/>
+      <color rgb="008A938B"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="004A6B8A"/>
@@ -163,6 +169,11 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="008A938B"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <color rgb="006B7770"/>
       <sz val="9"/>
     </font>
@@ -186,12 +197,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E3EDE7"/>
+        <fgColor rgb="00FBF0DC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FBF0DC"/>
+        <fgColor rgb="00E3EDE7"/>
       </patternFill>
     </fill>
     <fill>
@@ -201,12 +212,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F6F3"/>
+        <fgColor rgb="00FFF9D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF9D6"/>
+        <fgColor rgb="00F2F6F3"/>
       </patternFill>
     </fill>
   </fills>
@@ -236,7 +247,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -263,10 +274,10 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -320,44 +331,56 @@
     <xf numFmtId="9" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="9" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="9" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="9" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="20" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -369,16 +392,20 @@
     <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -388,7 +415,7 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -756,7 +783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -809,7 +836,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>1.2.0 — rule logic confirmed</t>
+          <t>1.3.0 — reviewer-lens pass applied</t>
         </is>
       </c>
     </row>
@@ -821,7 +848,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>DRAFT — rule logic settled; Rule_Messages outstanding</t>
+          <t>DRAFT — 27 rules changed at the reviewer-lens pass; confirm to freeze</t>
         </is>
       </c>
     </row>
@@ -857,7 +884,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>v1.1.1, issued 2026-08-19</t>
+          <t>v1.2.0, issued 2026-08-21</t>
         </is>
       </c>
     </row>
@@ -905,7 +932,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Rule_Messages — the query wording. Rules is complete.</t>
+          <t>The 27 rules changed at round 3 — see Review_Log and the R3 columns</t>
         </is>
       </c>
     </row>
@@ -919,35 +946,35 @@
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>•  Rules is COMPLETE. All 85 dispositioned at round 1 (70 accept, 14 discuss, 1 reject), and all 16 amended or explained rules confirmed at round 2 with no further comments.</t>
+          <t>•  Rounds 1 and 2 dispositioned all 85 rules, and round 2 confirmed every amendment. Rule_Messages was then accepted in full, and all nine open questions were answered.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>•  The rule logic, severities, modes and confidence base rates are therefore settled. Both rounds are recorded on each rule and narrated on Review_Log.</t>
+          <t>•  Round 3 is a quality pass, not a disposition: the rules and query messages were re-read through a clinical data manager's eyes and a medical monitor's eyes. 27 rules changed.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>•  Rule_Messages has NOT been reviewed. It holds the query wording that reaches a site, so it is the one remaining surface before the Step 2 gate.</t>
+          <t>•  19 query messages were rewritten (CDM lens) and 8 rule logics amended (MM lens). Every change carries its before text and the reason, on the Rules and Rule_Messages sheets and on Review_Log.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>•  The rule pack is not frozen yet. It freezes when Rule_Messages is accepted — that is the gate, and Step 3 starts behind it.</t>
+          <t>•  Query_Style is new. It states the house rules these rewrites follow, so rule 86 does not reintroduce the problems fixed in rules 1 to 85.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>•  Open_Questions still carries SQ-01 to SQ-09. SQ-08 was answered by the TE-BL-011 decision; SQ-01 and SQ-02 are covered by the rule-by-rule acceptance but have no separate recorded decision — confirm or correct them there.</t>
+          <t>•  Nothing else changed. The other 58 rules are exactly as you accepted them.</t>
         </is>
       </c>
     </row>
@@ -955,40 +982,33 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>WHAT CHANGED AT THIS REVISION</t>
+          <t>THE TWO THINGS THE PASS FOUND</t>
         </is>
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>•  Round-2 confirmations recorded against all 16 amended rules. No rule logic changed at this revision — this is a disposition record, not an edit.</t>
+          <t>•  CDM lens — nine queries told the site what the answer was ('the overall response should be PD', 'the lesion should be recorded as non-target'). That converts a check into an instruction: the site confirms rather than verifies, and if the agent's derivation is wrong the error comes back signed by the site.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="26" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>•  The Rules sheet no longer offers a reviewer input column: it is complete, and its decision columns are now read-only history.</t>
+          <t>•  MM lens — five rules turned one underlying event into many findings, or fired on data a monitor would never query. Local therapy to one target lesion raised a finding at every subsequent visit; an adverse event of progression raised a query asking for a scan the subject was too unwell to have.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="26" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>•  Review_Log gains the round-2 outcome alongside round 1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>•  Open_Questions gains a decision column, pre-filled where the two review rounds already settled the answer.</t>
+          <t>•  Both are the kind of thing that costs a review tool its credibility in the first month of use, so they are worth fixing before any code is written.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="21">
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="A27:F27"/>
@@ -1001,7 +1021,6 @@
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A29:F29"/>
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A19:F19"/>
@@ -1022,6 +1041,330 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="74" customWidth="1" min="3" max="3"/>
+    <col width="78" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Query message house rules</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>TEA-QS-001. Settled at the reviewer-lens pass and by the SQ-05 decision. Every query template follows these; a new review point is not complete until its query does.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>Example</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>State the observation, then ask one question.</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>A query with two questions comes back answering one. A query with none comes back as 'reviewed, no change'.</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>Good — 'The response recorded at Visit 4 is SD. Please confirm the response against the source imaging report.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>Never state the expected answer.</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>Naming the value turns a check into an instruction. The site confirms instead of verifying, and if the agent's derivation is wrong the error returns signed by the site. This was the single commonest fault in the first draft.</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>Not — '...the overall response should be PD.'   Instead — 'Please review the overall response against these components.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>No guideline reference in the query.</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>SQ-05. The site is being asked about their data, not about RECIST. The clause reads as a lecture and invites a guideline argument rather than a data correction. The citation belongs in element 5, which the reviewer reads.</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Not — '...which does not meet the 5 mm absolute increase required by RECIST 1.1.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>Guideline words are allowed when they name a CRF field or a recorded value.</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>'The iRECIST response field' is the name of something on the form. That is not a citation of authority and the site needs it to find the record.</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>Fine — 'The RECIST 1.1 and iRECIST responses recorded at Visit 6 are PD and iUPD.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Prefer plain description to guideline vocabulary.</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>A site coordinator may not know 'nadir'. They do know 'the smallest sum recorded on study'. Same fact, no glossary needed.</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>Not — 'a 22% increase from nadir'.   Instead — 'compared with the smallest sum recorded on study of 48 mm at Visit 3'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>Point at the source document.</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>Almost every one of these findings is resolved by looking at the imaging report. Saying so converts a query into a task.</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>'...please confirm against the source imaging report.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Never ask a site coordinator for a medical judgement.</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>Asking whether overall tumor burden increased substantially puts a clinical decision on someone who cannot make it, and produces a defensive answer. Ask for the radiology description instead and let the monitor judge.</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>Not — 'Please confirm that the overall tumor burden has increased substantially.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>Never instruct a site to delete recorded data.</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>Deleting is theirs to decide and theirs to audit. Ask them to confirm intent.</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>Not — 'please remove it from the assessment.'   Instead — 'Please confirm whether this node was intended to be recorded as disease.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>Keep the derivation out of the query.</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>The arithmetic is reviewer-facing context. A site re-checking a record does not need the agent's working, and it makes the query hard to scan.</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>Element 3 carries current-versus-expected in full; element 4 states only what is needed to find the record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>Invite the legitimate explanation where one exists.</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>Many findings have a correct answer that is not a data change. Asking the question that surfaces it saves a round trip.</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>'Please confirm what the progression assessment at this visit was based on — the target lesion measurements, a new lesion, or worsening of non-target disease.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Target 400 characters or fewer.</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>EDC query fields truncate, and long queries are skim-read. The current set runs 41 to 323 characters.</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>Measured by the build; a template over the limit fails CI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="25" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>STUDY_TEAM findings carry no query text.</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>Some findings are never issued to a site — BICR discordance, study set-up, query ageing. Their query field says so explicitly rather than leaving a template someone might send.</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>'Not applicable: this finding is for internal review and is not issued as a site query.'</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1066,9 +1409,9 @@
 # so certainty is never total. A 100% display would invite unread query issuance.</t>
         </is>
       </c>
-      <c r="B4" s="54" t="n"/>
-      <c r="C4" s="54" t="n"/>
-      <c r="D4" s="54" t="n"/>
+      <c r="B4" s="60" t="n"/>
+      <c r="C4" s="60" t="n"/>
+      <c r="D4" s="60" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
@@ -1342,7 +1685,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1407,9 +1750,9 @@
         f.status = RECURRENT</t>
         </is>
       </c>
-      <c r="B4" s="54" t="n"/>
-      <c r="C4" s="54" t="n"/>
-      <c r="D4" s="54" t="n"/>
+      <c r="B4" s="60" t="n"/>
+      <c r="C4" s="60" t="n"/>
+      <c r="D4" s="60" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -1463,7 +1806,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1504,9 +1847,9 @@
 it necessarily causes, so the reviewer fixes the baseline once instead of querying ten visits.</t>
         </is>
       </c>
-      <c r="B4" s="54" t="n"/>
-      <c r="C4" s="54" t="n"/>
-      <c r="D4" s="54" t="n"/>
+      <c r="B4" s="60" t="n"/>
+      <c r="C4" s="60" t="n"/>
+      <c r="D4" s="60" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -1529,9 +1872,9 @@
 where it does rather than having to trust the ordering.</t>
         </is>
       </c>
-      <c r="B7" s="54" t="n"/>
-      <c r="C7" s="54" t="n"/>
-      <c r="D7" s="54" t="n"/>
+      <c r="B7" s="60" t="n"/>
+      <c r="C7" s="60" t="n"/>
+      <c r="D7" s="60" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1543,7 +1886,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1606,7 +1949,7 @@
           <t>study</t>
         </is>
       </c>
-      <c r="B4" s="55" t="inlineStr">
+      <c r="B4" s="61" t="inlineStr">
         <is>
           <t>study_id</t>
         </is>
@@ -1629,7 +1972,7 @@
           <t>study</t>
         </is>
       </c>
-      <c r="B5" s="56" t="inlineStr">
+      <c r="B5" s="62" t="inlineStr">
         <is>
           <t>indication</t>
         </is>
@@ -1656,7 +1999,7 @@
           <t>study</t>
         </is>
       </c>
-      <c r="B6" s="55" t="inlineStr">
+      <c r="B6" s="61" t="inlineStr">
         <is>
           <t>guideline_version</t>
         </is>
@@ -1683,7 +2026,7 @@
           <t>protocol_config</t>
         </is>
       </c>
-      <c r="B7" s="56" t="inlineStr">
+      <c r="B7" s="62" t="inlineStr">
         <is>
           <t>(28 parameters)</t>
         </is>
@@ -1710,7 +2053,7 @@
           <t>subjects</t>
         </is>
       </c>
-      <c r="B8" s="55" t="inlineStr">
+      <c r="B8" s="61" t="inlineStr">
         <is>
           <t>subject_id, site_id, first_dose_date, discontinuation_date, death_date, has_measurable_disease_at_baseline</t>
         </is>
@@ -1733,7 +2076,7 @@
           <t>lesions</t>
         </is>
       </c>
-      <c r="B9" s="56" t="inlineStr">
+      <c r="B9" s="62" t="inlineStr">
         <is>
           <t>lesion_id, category, is_nodal, organ, location_detail, laterality, method, new_lesion_certainty, previously_irradiated</t>
         </is>
@@ -1760,7 +2103,7 @@
           <t>assessments</t>
         </is>
       </c>
-      <c r="B10" s="55" t="inlineStr">
+      <c r="B10" s="61" t="inlineStr">
         <is>
           <t>assessment_id, visit_name, visit_number, assessment_date, scan_dates, is_baseline, evaluator</t>
         </is>
@@ -1783,7 +2126,7 @@
           <t>measurements</t>
         </is>
       </c>
-      <c r="B11" s="56" t="inlineStr">
+      <c r="B11" s="62" t="inlineStr">
         <is>
           <t>assessment_id, lesion_id, value_mm, original_unit, axis_recorded, state, non_target_state, comment_text</t>
         </is>
@@ -1810,7 +2153,7 @@
           <t>reported_responses</t>
         </is>
       </c>
-      <c r="B12" s="55" t="inlineStr">
+      <c r="B12" s="61" t="inlineStr">
         <is>
           <t>target, non_target, new_lesion, overall, irecist, sum_of_diameters_reported, best_overall_response, progression_date</t>
         </is>
@@ -1837,7 +2180,7 @@
           <t>queries</t>
         </is>
       </c>
-      <c r="B13" s="56" t="inlineStr">
+      <c r="B13" s="62" t="inlineStr">
         <is>
           <t>query_id, query_text, answer_text, status, opened/answered/closed dates, tea_rule_id</t>
         </is>
@@ -1864,7 +2207,7 @@
           <t>cross_domain</t>
         </is>
       </c>
-      <c r="B14" s="55" t="inlineStr">
+      <c r="B14" s="61" t="inlineStr">
         <is>
           <t>exposure, anticancer_therapy, radiotherapy, procedures, adverse_events, lab_markers, performance_status</t>
         </is>
@@ -1891,7 +2234,7 @@
           <t>imaging_metadata</t>
         </is>
       </c>
-      <c r="B15" s="56" t="inlineStr">
+      <c r="B15" s="62" t="inlineStr">
         <is>
           <t>modality, scan_date, slice_thickness_mm, regions_imaged, contrast_used</t>
         </is>
@@ -1956,7 +2299,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2500,7 +2843,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2567,7 +2910,7 @@
           <t>Lesion organ, laterality, location text, description text, method, guideline extract</t>
         </is>
       </c>
-      <c r="D5" s="55" t="inlineStr">
+      <c r="D5" s="61" t="inlineStr">
         <is>
           <t>{is_non_measurable, category, confidence, rationale}</t>
         </is>
@@ -2589,7 +2932,7 @@
           <t>Non-target descriptions at this and the previous timepoint, target response, sum change, guideline extract</t>
         </is>
       </c>
-      <c r="D6" s="56" t="inlineStr">
+      <c r="D6" s="62" t="inlineStr">
         <is>
           <t>{supports_unequivocal, magnitude_comment, confidence, rationale}</t>
         </is>
@@ -2611,7 +2954,7 @@
           <t>Candidate finding summary; historical queries for the subject</t>
         </is>
       </c>
-      <c r="D7" s="55" t="inlineStr">
+      <c r="D7" s="61" t="inlineStr">
         <is>
           <t>{matches:[{query_id, relation, confidence}]}</t>
         </is>
@@ -2633,7 +2976,7 @@
           <t>Query text, answer text, current values of the queried fields  (NEW at review)</t>
         </is>
       </c>
-      <c r="D8" s="56" t="inlineStr">
+      <c r="D8" s="62" t="inlineStr">
         <is>
           <t>{classification, confidence, rationale, quoted_span}</t>
         </is>
@@ -2655,7 +2998,7 @@
           <t>Evidence object, rule metadata, message templates, guideline citation, indication context</t>
         </is>
       </c>
-      <c r="D9" s="55" t="inlineStr">
+      <c r="D9" s="61" t="inlineStr">
         <is>
           <t>{five narrative fields}</t>
         </is>
@@ -2677,7 +3020,7 @@
           <t>Protocol and imaging charter text  (NEW at review, AC-11)</t>
         </is>
       </c>
-      <c r="D10" s="56" t="inlineStr">
+      <c r="D10" s="62" t="inlineStr">
         <is>
           <t>{checkpoints:[{parameter, value_found, page_ref, confidence}]}</t>
         </is>
@@ -2853,9 +3196,9 @@
 log the event. The finding is still produced, with template text.</t>
         </is>
       </c>
-      <c r="B23" s="54" t="n"/>
-      <c r="C23" s="54" t="n"/>
-      <c r="D23" s="54" t="n"/>
+      <c r="B23" s="60" t="n"/>
+      <c r="C23" s="60" t="n"/>
+      <c r="D23" s="60" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2866,7 +3209,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3172,7 +3515,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3388,7 +3731,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3516,314 +3859,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="72" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="66" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>Open specification questions</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="9" t="inlineStr">
-        <is>
-          <t>For decision at the Step 2 gate. The status column records what the two review rounds already settled; the yellow columns are for the rest.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>Question</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
-        <is>
-          <t>Impact</t>
-        </is>
-      </c>
-      <c r="D3" s="10" t="inlineStr">
-        <is>
-          <t>Status after 2 rounds</t>
-        </is>
-      </c>
-      <c r="E3" s="10" t="inlineStr">
-        <is>
-          <t>Decision</t>
-        </is>
-      </c>
-      <c r="F3" s="10" t="inlineStr">
-        <is>
-          <t>Reviewer</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="23" t="inlineStr">
-        <is>
-          <t>SQ-01</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>Confirm the severity assigned to each rule against sponsor conventions. Severity drives prioritisation and the database-lock criteria.</t>
-        </is>
-      </c>
-      <c r="C4" s="37" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="D4" s="12" t="inlineStr">
-        <is>
-          <t>Covered by the rule-by-rule acceptance — every accepted row carried its severity. No separate decision recorded; confirm or correct.</t>
-        </is>
-      </c>
-      <c r="E4" s="52" t="n"/>
-      <c r="F4" s="53" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="25" t="inlineStr">
-        <is>
-          <t>SQ-02</t>
-        </is>
-      </c>
-      <c r="B5" s="22" t="inlineStr">
-        <is>
-          <t>Confirm the confidence base rate proposed for each rule (Open Item OI-02). These drive triage for every finding the agent produces.</t>
-        </is>
-      </c>
-      <c r="C5" s="57" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="D5" s="22" t="inlineStr">
-        <is>
-          <t>Covered by the rule-by-rule acceptance — every accepted row carried its base rate. No separate decision recorded; confirm or correct.</t>
-        </is>
-      </c>
-      <c r="E5" s="52" t="n"/>
-      <c r="F5" s="53" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="23" t="inlineStr">
-        <is>
-          <t>SQ-03</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>Confirm the interpretation decisions ID-01 to ID-08, particularly the too-small-to-measure convention and the treatment of reappearing lesions.</t>
-        </is>
-      </c>
-      <c r="C6" s="37" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>Six accepted at round 1. ID-05 expanded and ID-06 amended, neither re-reviewed since.</t>
-        </is>
-      </c>
-      <c r="E6" s="52" t="n"/>
-      <c r="F6" s="53" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="25" t="inlineStr">
-        <is>
-          <t>SQ-04</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>Confirm whether the three PROPOSED_OPTIONAL rules should be activated: TE-BL-016 (lesion location versus coded organ), TE-IR-008 (clinical stability documented at treatment beyond iUPD) and TE-RS-021 (cytological confirmation of an effusion driving progression).</t>
-        </is>
-      </c>
-      <c r="C7" s="27" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D7" s="22" t="inlineStr">
-        <is>
-          <t>All three accepted as rules, but acceptance is not activation. They remain off by default pending this decision.</t>
-        </is>
-      </c>
-      <c r="E7" s="52" t="n"/>
-      <c r="F7" s="53" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="23" t="inlineStr">
-        <is>
-          <t>SQ-05</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>Confirm the query text style: salutation, level of explanation, and whether the guideline reference appears in the query itself or only in the reviewer-facing tips.</t>
-        </is>
-      </c>
-      <c r="C8" s="31" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>OPEN — settle this alongside the Rule_Messages review, since it governs all 85 query texts at once.</t>
-        </is>
-      </c>
-      <c r="E8" s="52" t="n"/>
-      <c r="F8" s="53" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="25" t="inlineStr">
-        <is>
-          <t>SQ-06</t>
-        </is>
-      </c>
-      <c r="B9" s="22" t="inlineStr">
-        <is>
-          <t>Confirm tolerances: sum tolerance in mm, percentage tolerance, date tolerance for BICR comparison.</t>
-        </is>
-      </c>
-      <c r="C9" s="27" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D9" s="22" t="inlineStr">
-        <is>
-          <t>OPEN. Defaults are on the Interpretations sheet under ID-05.</t>
-        </is>
-      </c>
-      <c r="E9" s="52" t="n"/>
-      <c r="F9" s="53" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="23" t="inlineStr">
-        <is>
-          <t>SQ-07</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>Confirm whether STUDY_TEAM findings (TE-RS-020, TE-IR-010, TE-XD-012, TE-QM-004) should be a separate class in the UI, since they are never issued as site queries.</t>
-        </is>
-      </c>
-      <c r="C10" s="31" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>OPEN. TE-RS-007 joined this group at round 1 when it dropped to INFO.</t>
-        </is>
-      </c>
-      <c r="E10" s="52" t="n"/>
-      <c r="F10" s="53" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="25" t="inlineStr">
-        <is>
-          <t>SQ-08</t>
-        </is>
-      </c>
-      <c r="B11" s="22" t="inlineStr">
-        <is>
-          <t>Confirm whether the Veeva CRF collects a sum of diameters at all. If it is derived only, TE-BL-011 and TE-FU-001 do not apply and weight shifts onto TE-RS-001.</t>
-        </is>
-      </c>
-      <c r="C11" s="57" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="D11" s="22" t="inlineStr">
-        <is>
-          <t>ANSWERED at round 1. Both rules are CONDITIONAL on a site-entered sum, determined from the CRF specification at the AC-11 intake.</t>
-        </is>
-      </c>
-      <c r="E11" s="52" t="inlineStr">
-        <is>
-          <t>Accept</t>
-        </is>
-      </c>
-      <c r="F11" s="53" t="inlineStr">
-        <is>
-          <t>Daniel</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="23" t="inlineStr">
-        <is>
-          <t>SQ-09</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>Confirm the confidence threshold at which a JUSTIFIED_BY_ANSWER suppression may occur without human confirmation. Currently 0.70, and never for CRITICAL or MAJOR.</t>
-        </is>
-      </c>
-      <c r="C12" s="37" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>OPEN. TE-QM-002 was accepted at round 1, but the threshold itself has no recorded decision.</t>
-        </is>
-      </c>
-      <c r="E12" s="52" t="n"/>
-      <c r="F12" s="53" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="E4:E12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Accept,Amend,Reject,Discuss"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3843,7 +3885,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>TEA-SPEC-001 v1.2.0 — rule logic confirmed over two review rounds. Rule_Messages is the one surface still to review.</t>
+          <t>TEA-SPEC-001 v1.3.0 — everything accepted, then a reviewer-lens quality pass changed 27 rules. Those 27 are what is left to confirm.</t>
         </is>
       </c>
     </row>
@@ -4046,12 +4088,12 @@
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>27 rows</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
         <is>
-          <t>both rounds recorded</t>
+          <t>R3 changes, amber</t>
         </is>
       </c>
     </row>
@@ -4072,12 +4114,12 @@
       </c>
       <c r="D12" s="17" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>19 rows</t>
         </is>
       </c>
       <c r="E12" s="15" t="inlineStr">
         <is>
-          <t>the remaining surface</t>
+          <t>rewritten queries, amber</t>
         </is>
       </c>
     </row>
@@ -4093,14 +4135,10 @@
         </is>
       </c>
       <c r="C13" s="13" t="n"/>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D13" s="14" t="inlineStr"/>
       <c r="E13" s="15" t="inlineStr">
         <is>
-          <t>NEW — OBJ-03</t>
+          <t>OBJ-03</t>
         </is>
       </c>
     </row>
@@ -4281,32 +4319,54 @@
       </c>
       <c r="D22" s="17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>done</t>
         </is>
       </c>
       <c r="E22" s="15" t="inlineStr">
         <is>
-          <t>SQ-08 answered; 8 open</t>
+          <t>all nine answered</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
+          <t>Query_Style</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>12 house rules for query text</t>
+        </is>
+      </c>
+      <c r="C23" s="16">
+        <f>COUNTA(Query_Style!A4:A15)</f>
+        <v/>
+      </c>
+      <c r="D23" s="14" t="inlineStr"/>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>NEW — settles SQ-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
           <t>Traceability</t>
         </is>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>Plan requirement to specification to tests</t>
         </is>
       </c>
-      <c r="C23" s="16">
+      <c r="C24" s="16">
         <f>COUNTA(Traceability!A4:A23)</f>
         <v/>
       </c>
-      <c r="D23" s="14" t="inlineStr"/>
-      <c r="E23" s="15" t="inlineStr"/>
+      <c r="D24" s="14" t="inlineStr"/>
+      <c r="E24" s="15" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4333,13 +4393,420 @@
     <hyperlink ref="A20" location="Testing!A1"/>
     <hyperlink ref="A21" location="Extensibility!A1"/>
     <hyperlink ref="A22" location="Open_Questions!A1"/>
-    <hyperlink ref="A23" location="Traceability!A1"/>
+    <hyperlink ref="A23" location="Query_Style!A1"/>
+    <hyperlink ref="A24" location="Traceability!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="72" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="66" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Open specification questions — all answered</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>All nine answered on 2026-08-21. SQ-05 carries a decision rather than a plain accept, and that decision is applied across every query text and written up on Query_Style.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>Status after 2 rounds</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>Reviewer</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="23" t="inlineStr">
+        <is>
+          <t>SQ-01</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>Confirm the severity assigned to each rule against sponsor conventions. Severity drives prioritisation and the database-lock criteria.</t>
+        </is>
+      </c>
+      <c r="C4" s="40" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>Covered by the rule-by-rule acceptance — every accepted row carried its severity.</t>
+        </is>
+      </c>
+      <c r="E4" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="F4" s="24" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>SQ-02</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>Confirm the confidence base rate proposed for each rule (Open Item OI-02). These drive triage for every finding the agent produces.</t>
+        </is>
+      </c>
+      <c r="C5" s="63" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>Covered by the rule-by-rule acceptance — every accepted row carried its base rate.</t>
+        </is>
+      </c>
+      <c r="E5" s="25" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="F5" s="26" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>SQ-03</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Confirm the interpretation decisions ID-01 to ID-08, particularly the too-small-to-measure convention and the treatment of reappearing lesions.</t>
+        </is>
+      </c>
+      <c r="C6" s="40" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Six accepted at round 1. ID-05 expanded and ID-06 amended; ACCEPTED 2026-08-21, though neither amendment was separately re-read.</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="F6" s="24" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="25" t="inlineStr">
+        <is>
+          <t>SQ-04</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>Confirm whether the three PROPOSED_OPTIONAL rules should be activated: TE-BL-016 (lesion location versus coded organ), TE-IR-008 (clinical stability documented at treatment beyond iUPD) and TE-RS-021 (cytological confirmation of an effusion driving progression).</t>
+        </is>
+      </c>
+      <c r="C7" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>ANSWERED 2026-08-21. Accepted — the three PROPOSED_OPTIONAL rules stay available and off by default until a study enables them.</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="F7" s="26" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>SQ-05</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Confirm the query text style: salutation, level of explanation, and whether the guideline reference appears in the query itself or only in the reviewer-facing tips.</t>
+        </is>
+      </c>
+      <c r="C8" s="31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>ANSWERED 2026-08-21: the guideline reference appears only in the reviewer-facing tips. Applied across all 85 query texts and written up as rule 3 on Query_Style.</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
+          <t>Discuss</t>
+        </is>
+      </c>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>SQ-06</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>Confirm tolerances: sum tolerance in mm, percentage tolerance, date tolerance for BICR comparison.</t>
+        </is>
+      </c>
+      <c r="C9" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>ANSWERED 2026-08-21. Defaults on the Interpretations sheet under ID-05 accepted; confirmed per study at the AC-11 intake.</t>
+        </is>
+      </c>
+      <c r="E9" s="25" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="F9" s="26" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>SQ-07</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Confirm whether STUDY_TEAM findings (TE-RS-020, TE-IR-010, TE-XD-012, TE-QM-004) should be a separate class in the UI, since they are never issued as site queries.</t>
+        </is>
+      </c>
+      <c r="C10" s="31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>ANSWERED 2026-08-21. STUDY_TEAM findings are a separate class; their query text says so explicitly (Query_Style rule 12).</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="25" t="inlineStr">
+        <is>
+          <t>SQ-08</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>Confirm whether the Veeva CRF collects a sum of diameters at all. If it is derived only, TE-BL-011 and TE-FU-001 do not apply and weight shifts onto TE-RS-001.</t>
+        </is>
+      </c>
+      <c r="C11" s="63" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>ANSWERED at round 1 and confirmed. Both rules are CONDITIONAL on a site-entered sum, determined from the CRF specification at the AC-11 intake.</t>
+        </is>
+      </c>
+      <c r="E11" s="25" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="F11" s="26" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>SQ-09</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>Confirm the confidence threshold at which a JUSTIFIED_BY_ANSWER suppression may occur without human confirmation. Currently 0.70, and never for CRITICAL or MAJOR.</t>
+        </is>
+      </c>
+      <c r="C12" s="40" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>ANSWERED 2026-08-21. The 0.70 threshold is accepted, and CRITICAL and MAJOR findings are never suppressed on it.</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>SQ-05 as decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="40" customHeight="1">
+      <c r="A15" s="30" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>“It is enough that the guideline reference appears only in the reviewer-facing tips.”</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="30" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Nine query texts carried a guideline citation as authority; all nine were rewritten. Guideline words are kept only where they name a CRF field or a recorded value, which the site needs in order to find the record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="30" t="inlineStr">
+        <is>
+          <t>Enforced</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Query_Style rules 3 and 4, and a CI check that fails the build if a query template reintroduces a citation.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B17:F17"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4839,13 +5306,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -4859,14 +5326,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>Step 2 review — rounds 1 and 2</t>
+          <t>Step 2 review — rounds 1, 2 and 3</t>
         </is>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>Round 1 (2026-08-19) raised 15 items across 85 rules; round 2 (2026-08-21) confirmed every resolution with no further comments. The rule logic is settled. Rule_Messages is not yet reviewed.</t>
+          <t>Rounds 1 and 2 dispositioned and confirmed every rule; Rule_Messages and all nine open questions were then accepted. Round 3 is a quality pass through a data manager's and a monitor's eyes — 27 rules changed, listed on their own below.</t>
         </is>
       </c>
     </row>
@@ -5293,7 +5760,7 @@
           <t>TE-RS-011</t>
         </is>
       </c>
-      <c r="B16" s="37" t="inlineStr">
+      <c r="B16" s="40" t="inlineStr">
         <is>
           <t>Reject</t>
         </is>
@@ -5556,17 +6023,608 @@
     <row r="30" ht="44" customHeight="1">
       <c r="A30" s="30" t="inlineStr">
         <is>
+          <t>Round 3</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>A quality pass, not a disposition. 19 query messages rewritten under the CDM lens and 8 rule logics amended under the MM lens. The other 58 rules are untouched.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="44" customHeight="1">
+      <c r="A31" s="30" t="inlineStr">
+        <is>
           <t>Not re-reviewed</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>Interpretations ID-05 and ID-06 were amended at round 1 and were not looked at again in round 2. They are flagged rather than assumed accepted.</t>
-        </is>
-      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Interpretations ID-05 and ID-06 were amended at round 1 and were not looked at again. They are flagged rather than assumed accepted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="44" customHeight="1">
+      <c r="A32" s="30" t="inlineStr">
+        <is>
+          <t>Now open</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>The 27 rules changed at round 3, in the amber columns on Rules and Rule_Messages. Nothing else is outstanding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Round 3 — what the two lenses changed</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>What changed and why</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr"/>
+      <c r="E35" s="10" t="inlineStr"/>
+      <c r="F35" s="10" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="23" t="inlineStr">
+        <is>
+          <t>TE-ST-002</t>
+        </is>
+      </c>
+      <c r="B36" s="24" t="inlineStr">
+        <is>
+          <t>MM</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>Grouping on normalised location text collides two genuinely separate lesions in the same organ — two distinct liver metastases are routine. Added the size and description discriminators a monitor would apply before calling it a duplicate.</t>
+        </is>
+      </c>
+      <c r="D36" s="24" t="inlineStr"/>
+      <c r="E36" s="24" t="inlineStr"/>
+      <c r="F36" s="24" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="25" t="inlineStr">
+        <is>
+          <t>TE-ST-003</t>
+        </is>
+      </c>
+      <c r="B37" s="26" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="C37" s="22" t="inlineStr">
+        <is>
+          <t>Removed the instruction to correct the value. The query now asks the site to check the source rather than telling them which axis is wrong.</t>
+        </is>
+      </c>
+      <c r="D37" s="26" t="inlineStr"/>
+      <c r="E37" s="26" t="inlineStr"/>
+      <c r="F37" s="26" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="23" t="inlineStr">
+        <is>
+          <t>TE-BL-004</t>
+        </is>
+      </c>
+      <c r="B38" s="24" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>Removed the sentence stating what the node should have been recorded as. That is the investigator's call, and stating it invites the site to confirm rather than check.</t>
+        </is>
+      </c>
+      <c r="D38" s="24" t="inlineStr"/>
+      <c r="E38" s="24" t="inlineStr"/>
+      <c r="F38" s="24" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="25" t="inlineStr">
+        <is>
+          <t>TE-BL-005</t>
+        </is>
+      </c>
+      <c r="B39" s="26" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="C39" s="22" t="inlineStr">
+        <is>
+          <t>Removed 'please remove it from the assessment'. A query should never instruct a site to delete recorded data; it asks them to confirm intent and act on their own record.</t>
+        </is>
+      </c>
+      <c r="D39" s="26" t="inlineStr"/>
+      <c r="E39" s="26" t="inlineStr"/>
+      <c r="F39" s="26" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="23" t="inlineStr">
+        <is>
+          <t>TE-BL-007</t>
+        </is>
+      </c>
+      <c r="B40" s="24" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>Removed the guideline reference (SQ-05) and the instruction to re-classify. Asks the measurability question in plain terms instead.</t>
+        </is>
+      </c>
+      <c r="D40" s="24" t="inlineStr"/>
+      <c r="E40" s="24" t="inlineStr"/>
+      <c r="F40" s="24" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="25" t="inlineStr">
+        <is>
+          <t>TE-BL-008</t>
+        </is>
+      </c>
+      <c r="B41" s="26" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="C41" s="22" t="inlineStr">
+        <is>
+          <t>Removed the clause telling the site to record it as non-target. Asks for the evidence that decides the question, which is what the reviewer actually needs.</t>
+        </is>
+      </c>
+      <c r="D41" s="26" t="inlineStr"/>
+      <c r="E41" s="26" t="inlineStr"/>
+      <c r="F41" s="26" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="23" t="inlineStr">
+        <is>
+          <t>TE-BL-014</t>
+        </is>
+      </c>
+      <c r="B42" s="24" t="inlineStr">
+        <is>
+          <t>MM</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>A study-wide modality change — a protocol amendment, a scanner replacement — was raising a finding on every lesion in every subject. That is a study-level observation, not a per-lesion data query.</t>
+        </is>
+      </c>
+      <c r="D42" s="24" t="inlineStr"/>
+      <c r="E42" s="24" t="inlineStr"/>
+      <c r="F42" s="24" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="25" t="inlineStr">
+        <is>
+          <t>TE-FU-009</t>
+        </is>
+      </c>
+      <c r="B43" s="26" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="C43" s="22" t="inlineStr">
+        <is>
+          <t>Removed the guideline sentence (SQ-05) and the bare instruction to enter a measurement. Now allows for the case where the node genuinely was not measurable.</t>
+        </is>
+      </c>
+      <c r="D43" s="26" t="inlineStr"/>
+      <c r="E43" s="26" t="inlineStr"/>
+      <c r="F43" s="26" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="23" t="inlineStr">
+        <is>
+          <t>TE-FU-011</t>
+        </is>
+      </c>
+      <c r="B44" s="24" t="inlineStr">
+        <is>
+          <t>MM</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t>An assessment dated the same day as death is common and legitimate — the scan preceded the death that day. Firing on it produced an unanswerable query. Partial dates were also being treated as full ones.</t>
+        </is>
+      </c>
+      <c r="D44" s="24" t="inlineStr"/>
+      <c r="E44" s="24" t="inlineStr"/>
+      <c r="F44" s="24" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="25" t="inlineStr">
+        <is>
+          <t>TE-FU-014</t>
+        </is>
+      </c>
+      <c r="B45" s="26" t="inlineStr">
+        <is>
+          <t>MM</t>
+        </is>
+      </c>
+      <c r="C45" s="22" t="inlineStr">
+        <is>
+          <t>Per-lesion identical values are common in genuinely stable disease, which is why this sat at a 0.30 base rate. The pattern that actually signals copied data is every target lesion identical across visits. Narrowed to that, and the base rate rises accordingly.</t>
+        </is>
+      </c>
+      <c r="D45" s="26" t="inlineStr"/>
+      <c r="E45" s="26" t="inlineStr"/>
+      <c r="F45" s="26" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="23" t="inlineStr">
+        <is>
+          <t>TE-RS-001</t>
+        </is>
+      </c>
+      <c r="B46" s="24" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="C46" s="12" t="inlineStr">
+        <is>
+          <t>Removed the agent's derivation from the query. The percent-change arithmetic is reviewer-facing context, not something a site coordinator needs in order to re-check a record.</t>
+        </is>
+      </c>
+      <c r="D46" s="24" t="inlineStr"/>
+      <c r="E46" s="24" t="inlineStr"/>
+      <c r="F46" s="24" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="25" t="inlineStr">
+        <is>
+          <t>TE-RS-002</t>
+        </is>
+      </c>
+      <c r="B47" s="26" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="C47" s="22" t="inlineStr">
+        <is>
+          <t>Removed the guideline citation and the threshold arithmetic (SQ-05). Asks the one question that resolves the finding: what drove the PD call.</t>
+        </is>
+      </c>
+      <c r="D47" s="26" t="inlineStr"/>
+      <c r="E47" s="26" t="inlineStr"/>
+      <c r="F47" s="26" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="23" t="inlineStr">
+        <is>
+          <t>TE-RS-003</t>
+        </is>
+      </c>
+      <c r="B48" s="24" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="inlineStr">
+        <is>
+          <t>Removed the guideline citation (SQ-05) and replaced 'nadir' with 'the smallest sum recorded on study', which a site coordinator can act on without knowing the term.</t>
+        </is>
+      </c>
+      <c r="D48" s="24" t="inlineStr"/>
+      <c r="E48" s="24" t="inlineStr"/>
+      <c r="F48" s="24" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="25" t="inlineStr">
+        <is>
+          <t>TE-RS-007</t>
+        </is>
+      </c>
+      <c r="B49" s="26" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="C49" s="22" t="inlineStr">
+        <is>
+          <t>Removed 'please confirm that the overall tumor burden has increased substantially'. That is a medical judgement and does not belong in a query answered by site data staff. The query now asks only for the radiology description, which is a data request; the judgement stays with the monitor.</t>
+        </is>
+      </c>
+      <c r="D49" s="26" t="inlineStr"/>
+      <c r="E49" s="26" t="inlineStr"/>
+      <c r="F49" s="26" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="23" t="inlineStr">
+        <is>
+          <t>TE-RS-008</t>
+        </is>
+      </c>
+      <c r="B50" s="24" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="inlineStr">
+        <is>
+          <t>Removed 'the overall response should be {derived_overall}'. Naming the expected value turns a check into an instruction, and if the derivation is wrong the site confirms the error.</t>
+        </is>
+      </c>
+      <c r="D50" s="24" t="inlineStr"/>
+      <c r="E50" s="24" t="inlineStr"/>
+      <c r="F50" s="24" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="25" t="inlineStr">
+        <is>
+          <t>TE-RS-013</t>
+        </is>
+      </c>
+      <c r="B51" s="26" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="C51" s="22" t="inlineStr">
+        <is>
+          <t>Removed 'per RECIST the progression date should be {first_date}' — both a guideline citation (SQ-05) and a statement of the answer.</t>
+        </is>
+      </c>
+      <c r="D51" s="26" t="inlineStr"/>
+      <c r="E51" s="26" t="inlineStr"/>
+      <c r="F51" s="26" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="23" t="inlineStr">
+        <is>
+          <t>TE-RS-016</t>
+        </is>
+      </c>
+      <c r="B52" s="24" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="inlineStr">
+        <is>
+          <t>Removed the list of permitted response categories. The finding may equally be a missing baseline target lesion rather than a wrong response, and the original wording pointed at only one of the two.</t>
+        </is>
+      </c>
+      <c r="D52" s="24" t="inlineStr"/>
+      <c r="E52" s="24" t="inlineStr"/>
+      <c r="F52" s="24" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="25" t="inlineStr">
+        <is>
+          <t>TE-RS-020</t>
+        </is>
+      </c>
+      <c r="B53" s="26" t="inlineStr">
+        <is>
+          <t>MM</t>
+        </is>
+      </c>
+      <c r="C53" s="22" t="inlineStr">
+        <is>
+          <t>Was raising a finding per discordant assessment. A subject whose whole response history differs between investigator and BICR produced a finding at every visit. Now one finding per subject, listing the discordant timepoints, which is also how a monitor reconciles it.</t>
+        </is>
+      </c>
+      <c r="D53" s="26" t="inlineStr"/>
+      <c r="E53" s="26" t="inlineStr"/>
+      <c r="F53" s="26" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="23" t="inlineStr">
+        <is>
+          <t>TE-IR-001</t>
+        </is>
+      </c>
+      <c r="B54" s="24" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="C54" s="12" t="inlineStr">
+        <is>
+          <t>Removed the guideline explanation and the statement that iUPD should have been recorded (SQ-05). iUPD stays in the reviewer-facing tips, where the explanation belongs.</t>
+        </is>
+      </c>
+      <c r="D54" s="24" t="inlineStr"/>
+      <c r="E54" s="24" t="inlineStr"/>
+      <c r="F54" s="24" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="25" t="inlineStr">
+        <is>
+          <t>TE-IR-003</t>
+        </is>
+      </c>
+      <c r="B55" s="26" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="C55" s="22" t="inlineStr">
+        <is>
+          <t>Removed 'against the iRECIST criteria' (SQ-05). The comparison rule is in the tips.</t>
+        </is>
+      </c>
+      <c r="D55" s="26" t="inlineStr"/>
+      <c r="E55" s="26" t="inlineStr"/>
+      <c r="F55" s="26" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="23" t="inlineStr">
+        <is>
+          <t>TE-IR-004</t>
+        </is>
+      </c>
+      <c r="B56" s="24" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="C56" s="12" t="inlineStr">
+        <is>
+          <t>Removed the guideline explanation of separate new-lesion sums (SQ-05), and narrowed the query to the single factual question.</t>
+        </is>
+      </c>
+      <c r="D56" s="24" t="inlineStr"/>
+      <c r="E56" s="24" t="inlineStr"/>
+      <c r="F56" s="24" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="25" t="inlineStr">
+        <is>
+          <t>TE-IR-005</t>
+        </is>
+      </c>
+      <c r="B57" s="26" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="C57" s="22" t="inlineStr">
+        <is>
+          <t>Removed the derived-response arithmetic from the query; it remains in the reviewer-facing reason.</t>
+        </is>
+      </c>
+      <c r="D57" s="26" t="inlineStr"/>
+      <c r="E57" s="26" t="inlineStr"/>
+      <c r="F57" s="26" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="23" t="inlineStr">
+        <is>
+          <t>TE-IR-006</t>
+        </is>
+      </c>
+      <c r="B58" s="24" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="C58" s="12" t="inlineStr">
+        <is>
+          <t>Replaced the guideline citation with the study's own configured limits (SQ-05). Naming study configuration is not a guideline reference and is what the site can act on.</t>
+        </is>
+      </c>
+      <c r="D58" s="24" t="inlineStr"/>
+      <c r="E58" s="24" t="inlineStr"/>
+      <c r="F58" s="24" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="25" t="inlineStr">
+        <is>
+          <t>TE-IR-009</t>
+        </is>
+      </c>
+      <c r="B59" s="26" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="C59" s="22" t="inlineStr">
+        <is>
+          <t>Removed 'the iRECIST response would be expected to be {expected_irecist}'. The two guideline names are retained because here they are the names of CRF fields, not a citation of authority.</t>
+        </is>
+      </c>
+      <c r="D59" s="26" t="inlineStr"/>
+      <c r="E59" s="26" t="inlineStr"/>
+      <c r="F59" s="26" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="23" t="inlineStr">
+        <is>
+          <t>TE-XD-003</t>
+        </is>
+      </c>
+      <c r="B60" s="24" t="inlineStr">
+        <is>
+          <t>MM</t>
+        </is>
+      </c>
+      <c r="C60" s="12" t="inlineStr">
+        <is>
+          <t>Fires on any new systemic anticancer therapy, including protocol-permitted maintenance and supportive regimens. A monitor would not query those.</t>
+        </is>
+      </c>
+      <c r="D60" s="24" t="inlineStr"/>
+      <c r="E60" s="24" t="inlineStr"/>
+      <c r="F60" s="24" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="25" t="inlineStr">
+        <is>
+          <t>TE-XD-004</t>
+        </is>
+      </c>
+      <c r="B61" s="26" t="inlineStr">
+        <is>
+          <t>MM</t>
+        </is>
+      </c>
+      <c r="C61" s="22" t="inlineStr">
+        <is>
+          <t>One event was producing one finding per subsequent visit. A single course of radiotherapy to a target lesion in a 12-visit study raised eleven findings for one fact. Now one finding per lesion, listing the affected assessments.</t>
+        </is>
+      </c>
+      <c r="D61" s="26" t="inlineStr"/>
+      <c r="E61" s="26" t="inlineStr"/>
+      <c r="F61" s="26" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="23" t="inlineStr">
+        <is>
+          <t>TE-XD-005</t>
+        </is>
+      </c>
+      <c r="B62" s="24" t="inlineStr">
+        <is>
+          <t>MM</t>
+        </is>
+      </c>
+      <c r="C62" s="12" t="inlineStr">
+        <is>
+          <t>An adverse event of disease progression with no PD assessment is often correct: the subject deteriorated and no further imaging was possible. Querying the site for a scan that could not be done is exactly the kind of query that costs credibility.</t>
+        </is>
+      </c>
+      <c r="D62" s="24" t="inlineStr"/>
+      <c r="E62" s="24" t="inlineStr"/>
+      <c r="F62" s="24" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="11">
     <mergeCell ref="B30:F30"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="B29:F29"/>
@@ -5574,6 +6632,8 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B25:F25"/>
     <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B32:F32"/>
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="B27:F27"/>
   </mergeCells>
@@ -7932,7 +8992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R88"/>
+  <dimension ref="A1:U88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -7952,20 +9012,23 @@
     <col width="66" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="11" customWidth="1" min="17" max="17"/>
-    <col width="2" customWidth="1" min="18" max="18"/>
+    <col width="74" customWidth="1" min="18" max="18"/>
+    <col width="66" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>Rule catalog — 85 review points, 83 live — REVIEW COMPLETE</t>
+          <t>Rule catalog — 85 review points, 83 live</t>
         </is>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>Both review rounds are recorded here and no further input is needed on this sheet. R2 shows a dash where a rule was accepted outright at round 1 and never re-opened. Retired rules are greyed and keep their ids permanently.</t>
+          <t>Rounds 1 and 2 are closed history. Round 3 is a quality pass: the R3 columns show which lens found something, what changed, and the logic as it stood before. Only the amber rows need a decision. Filter on R3 lens to see the 27.</t>
         </is>
       </c>
     </row>
@@ -8052,10 +9115,29 @@
       </c>
       <c r="Q3" s="10" t="inlineStr">
         <is>
-          <t>R2 by</t>
-        </is>
-      </c>
-      <c r="R3" s="10" t="inlineStr"/>
+          <t>R3 lens</t>
+        </is>
+      </c>
+      <c r="R3" s="10" t="inlineStr">
+        <is>
+          <t>R3 change at this revision</t>
+        </is>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>Logic before R3</t>
+        </is>
+      </c>
+      <c r="T3" s="10" t="inlineStr">
+        <is>
+          <t>R3 decision</t>
+        </is>
+      </c>
+      <c r="U3" s="10" t="inlineStr">
+        <is>
+          <t>Reviewer</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="96" customHeight="1">
       <c r="A4" s="11" t="inlineStr">
@@ -8125,6 +9207,10 @@
         </is>
       </c>
       <c r="Q4" s="24" t="inlineStr"/>
+      <c r="R4" s="12" t="inlineStr"/>
+      <c r="S4" s="13" t="n"/>
+      <c r="T4" s="33" t="n"/>
+      <c r="U4" s="34" t="n"/>
     </row>
     <row r="5" ht="96" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
@@ -8162,8 +9248,8 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="H5" s="33" t="n">
-        <v>0.72</v>
+      <c r="H5" s="32" t="n">
+        <v>0.8</v>
       </c>
       <c r="I5" s="12" t="inlineStr">
         <is>
@@ -8175,7 +9261,14 @@
       <c r="L5" s="29" t="inlineStr">
         <is>
           <t>group lesions by (subject, organ, laterality, normalised location_detail)
-if group size &gt; 1 and both are TARGET or both NON_TARGET: raise finding</t>
+if group size &gt; 1 and all members share the same category:
+    if baseline values differ by &lt;= config.duplicate_size_tolerance_mm (default 2)
+       or any member has no baseline value:
+           raise finding
+guards:
+  - no finding where the descriptions carry distinguishing detail
+    (segment, lobe, station, numbering) — two separate lesions, not a duplicate
+  - no finding where baseline values differ materially: distinct lesions</t>
         </is>
       </c>
       <c r="M5" s="23" t="inlineStr">
@@ -8190,7 +9283,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q5" s="24" t="inlineStr"/>
+      <c r="Q5" s="31" t="inlineStr">
+        <is>
+          <t>MM</t>
+        </is>
+      </c>
+      <c r="R5" s="35" t="inlineStr">
+        <is>
+          <t>Grouping on normalised location text collides two genuinely separate lesions in the same organ — two distinct liver metastases are routine. Added the size and description discriminators a monitor would apply before calling it a duplicate.</t>
+        </is>
+      </c>
+      <c r="S5" s="36" t="inlineStr">
+        <is>
+          <t>group lesions by (subject, organ, laterality, normalised location_detail)
+if group size &gt; 1 and both are TARGET or both NON_TARGET: raise finding</t>
+        </is>
+      </c>
+      <c r="T5" s="33" t="n"/>
+      <c r="U5" s="34" t="n"/>
     </row>
     <row r="6" ht="96" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
@@ -8269,21 +9379,29 @@
           <t>Some CRF doesn't collect the type of size, instead the CRF directly asks sites to enter size based on the appropriate type. Consider the field name directly mentions right size type, if there's no size type selection field in the CRF.</t>
         </is>
       </c>
-      <c r="O6" s="34" t="inlineStr">
+      <c r="O6" s="37" t="inlineStr">
         <is>
           <t>AMENDED. Axis type is now resolved at ingestion in priority order rather than assumed to be a collected field: an explicit axis-type field if one exists, otherwise the axis implied by the CRF field itself as declared in the structured CRF specification, otherwise the protocol default. The rule fires only when no source establishes that a nodal measurement is a short axis.</t>
         </is>
       </c>
-      <c r="P6" s="35" t="inlineStr">
-        <is>
-          <t>Accept</t>
-        </is>
-      </c>
-      <c r="Q6" s="24" t="inlineStr">
-        <is>
-          <t>Daniel</t>
-        </is>
-      </c>
+      <c r="P6" s="38" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="Q6" s="31" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="R6" s="35" t="inlineStr">
+        <is>
+          <t>Removed the instruction to correct the value. The query now asks the site to check the source rather than telling them which axis is wrong.</t>
+        </is>
+      </c>
+      <c r="S6" s="13" t="n"/>
+      <c r="T6" s="33" t="n"/>
+      <c r="U6" s="34" t="n"/>
     </row>
     <row r="7" ht="96" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
@@ -8306,7 +9424,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E7" s="36" t="inlineStr">
+      <c r="E7" s="39" t="inlineStr">
         <is>
           <t>MINOR</t>
         </is>
@@ -8350,6 +9468,10 @@
         </is>
       </c>
       <c r="Q7" s="24" t="inlineStr"/>
+      <c r="R7" s="12" t="inlineStr"/>
+      <c r="S7" s="13" t="n"/>
+      <c r="T7" s="33" t="n"/>
+      <c r="U7" s="34" t="n"/>
     </row>
     <row r="8" ht="96" customHeight="1">
       <c r="A8" s="11" t="inlineStr">
@@ -8372,7 +9494,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E8" s="36" t="inlineStr">
+      <c r="E8" s="39" t="inlineStr">
         <is>
           <t>MINOR</t>
         </is>
@@ -8415,6 +9537,10 @@
         </is>
       </c>
       <c r="Q8" s="24" t="inlineStr"/>
+      <c r="R8" s="12" t="inlineStr"/>
+      <c r="S8" s="13" t="n"/>
+      <c r="T8" s="33" t="n"/>
+      <c r="U8" s="34" t="n"/>
     </row>
     <row r="9" ht="96" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
@@ -8437,7 +9563,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E9" s="37" t="inlineStr">
+      <c r="E9" s="40" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -8485,6 +9611,10 @@
         </is>
       </c>
       <c r="Q9" s="24" t="inlineStr"/>
+      <c r="R9" s="12" t="inlineStr"/>
+      <c r="S9" s="13" t="n"/>
+      <c r="T9" s="33" t="n"/>
+      <c r="U9" s="34" t="n"/>
     </row>
     <row r="10" ht="96" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
@@ -8507,7 +9637,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E10" s="37" t="inlineStr">
+      <c r="E10" s="40" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -8551,6 +9681,10 @@
         </is>
       </c>
       <c r="Q10" s="24" t="inlineStr"/>
+      <c r="R10" s="12" t="inlineStr"/>
+      <c r="S10" s="13" t="n"/>
+      <c r="T10" s="33" t="n"/>
+      <c r="U10" s="34" t="n"/>
     </row>
     <row r="11" ht="96" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
@@ -8573,7 +9707,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E11" s="37" t="inlineStr">
+      <c r="E11" s="40" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -8620,6 +9754,10 @@
         </is>
       </c>
       <c r="Q11" s="24" t="inlineStr"/>
+      <c r="R11" s="12" t="inlineStr"/>
+      <c r="S11" s="13" t="n"/>
+      <c r="T11" s="33" t="n"/>
+      <c r="U11" s="34" t="n"/>
     </row>
     <row r="12" ht="96" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
@@ -8642,7 +9780,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E12" s="37" t="inlineStr">
+      <c r="E12" s="40" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -8685,7 +9823,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q12" s="24" t="inlineStr"/>
+      <c r="Q12" s="31" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="R12" s="35" t="inlineStr">
+        <is>
+          <t>Removed the sentence stating what the node should have been recorded as. That is the investigator's call, and stating it invites the site to confirm rather than check.</t>
+        </is>
+      </c>
+      <c r="S12" s="13" t="n"/>
+      <c r="T12" s="33" t="n"/>
+      <c r="U12" s="34" t="n"/>
     </row>
     <row r="13" ht="96" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
@@ -8751,7 +9901,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q13" s="24" t="inlineStr"/>
+      <c r="Q13" s="31" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="R13" s="35" t="inlineStr">
+        <is>
+          <t>Removed 'please remove it from the assessment'. A query should never instruct a site to delete recorded data; it asks them to confirm intent and act on their own record.</t>
+        </is>
+      </c>
+      <c r="S13" s="13" t="n"/>
+      <c r="T13" s="33" t="n"/>
+      <c r="U13" s="34" t="n"/>
     </row>
     <row r="14" ht="96" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
@@ -8789,7 +9951,7 @@
           <t>CONDITIONAL</t>
         </is>
       </c>
-      <c r="H14" s="33" t="n">
+      <c r="H14" s="41" t="n">
         <v>0.7</v>
       </c>
       <c r="I14" s="12" t="inlineStr">
@@ -8821,6 +9983,10 @@
         </is>
       </c>
       <c r="Q14" s="24" t="inlineStr"/>
+      <c r="R14" s="12" t="inlineStr"/>
+      <c r="S14" s="13" t="n"/>
+      <c r="T14" s="33" t="n"/>
+      <c r="U14" s="34" t="n"/>
     </row>
     <row r="15" ht="96" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
@@ -8858,7 +10024,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="H15" s="33" t="n">
+      <c r="H15" s="41" t="n">
         <v>0.65</v>
       </c>
       <c r="I15" s="12" t="inlineStr">
@@ -8896,7 +10062,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q15" s="24" t="inlineStr"/>
+      <c r="Q15" s="31" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="R15" s="35" t="inlineStr">
+        <is>
+          <t>Removed the guideline reference (SQ-05) and the instruction to re-classify. Asks the measurability question in plain terms instead.</t>
+        </is>
+      </c>
+      <c r="S15" s="13" t="n"/>
+      <c r="T15" s="33" t="n"/>
+      <c r="U15" s="34" t="n"/>
     </row>
     <row r="16" ht="96" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
@@ -8934,7 +10112,7 @@
           <t>CONDITIONAL</t>
         </is>
       </c>
-      <c r="H16" s="33" t="n">
+      <c r="H16" s="41" t="n">
         <v>0.72</v>
       </c>
       <c r="I16" s="12" t="inlineStr">
@@ -8966,7 +10144,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q16" s="24" t="inlineStr"/>
+      <c r="Q16" s="31" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="R16" s="35" t="inlineStr">
+        <is>
+          <t>Removed the clause telling the site to record it as non-target. Asks for the evidence that decides the question, which is what the reviewer actually needs.</t>
+        </is>
+      </c>
+      <c r="S16" s="13" t="n"/>
+      <c r="T16" s="33" t="n"/>
+      <c r="U16" s="34" t="n"/>
     </row>
     <row r="17" ht="96" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
@@ -8989,7 +10179,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E17" s="37" t="inlineStr">
+      <c r="E17" s="40" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -9033,6 +10223,10 @@
         </is>
       </c>
       <c r="Q17" s="24" t="inlineStr"/>
+      <c r="R17" s="12" t="inlineStr"/>
+      <c r="S17" s="13" t="n"/>
+      <c r="T17" s="33" t="n"/>
+      <c r="U17" s="34" t="n"/>
     </row>
     <row r="18" ht="96" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
@@ -9103,6 +10297,10 @@
         </is>
       </c>
       <c r="Q18" s="24" t="inlineStr"/>
+      <c r="R18" s="12" t="inlineStr"/>
+      <c r="S18" s="13" t="n"/>
+      <c r="T18" s="33" t="n"/>
+      <c r="U18" s="34" t="n"/>
     </row>
     <row r="19" ht="96" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
@@ -9179,21 +10377,21 @@
           <t>In case of the CRF not collecting manual entry for the reported sum, this rule should be ignored. The LLM needs to identify study's CRF capture the information by CRF specification.</t>
         </is>
       </c>
-      <c r="O19" s="34" t="inlineStr">
+      <c r="O19" s="37" t="inlineStr">
         <is>
           <t>AMENDED, and this answers SQ-08. Status moves from ACTIVE to CONDITIONAL: the rule requires a site-entered sum field. Whether the sum is site-entered or system-derived is determined from the structured CRF specification at the AC-11 intake, and a derived sum deactivates the rule with an explicit NOT_EVALUATED in the coverage report rather than a silent pass. Applied to TE-FU-001 as well, which carries the identical condition at follow-up.</t>
         </is>
       </c>
-      <c r="P19" s="35" t="inlineStr">
-        <is>
-          <t>Accept</t>
-        </is>
-      </c>
-      <c r="Q19" s="24" t="inlineStr">
-        <is>
-          <t>Daniel</t>
-        </is>
-      </c>
+      <c r="P19" s="38" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="Q19" s="24" t="inlineStr"/>
+      <c r="R19" s="12" t="inlineStr"/>
+      <c r="S19" s="13" t="n"/>
+      <c r="T19" s="33" t="n"/>
+      <c r="U19" s="34" t="n"/>
     </row>
     <row r="20" ht="96" customHeight="1">
       <c r="A20" s="11" t="inlineStr">
@@ -9216,7 +10414,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E20" s="36" t="inlineStr">
+      <c r="E20" s="39" t="inlineStr">
         <is>
           <t>MINOR</t>
         </is>
@@ -9231,7 +10429,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="H20" s="38" t="n">
+      <c r="H20" s="42" t="n">
         <v>0.35</v>
       </c>
       <c r="I20" s="12" t="inlineStr">
@@ -9260,6 +10458,10 @@
         </is>
       </c>
       <c r="Q20" s="24" t="inlineStr"/>
+      <c r="R20" s="12" t="inlineStr"/>
+      <c r="S20" s="13" t="n"/>
+      <c r="T20" s="33" t="n"/>
+      <c r="U20" s="34" t="n"/>
     </row>
     <row r="21" ht="96" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
@@ -9325,6 +10527,10 @@
         </is>
       </c>
       <c r="Q21" s="24" t="inlineStr"/>
+      <c r="R21" s="12" t="inlineStr"/>
+      <c r="S21" s="13" t="n"/>
+      <c r="T21" s="33" t="n"/>
+      <c r="U21" s="34" t="n"/>
     </row>
     <row r="22" ht="96" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
@@ -9347,7 +10553,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E22" s="36" t="inlineStr">
+      <c r="E22" s="39" t="inlineStr">
         <is>
           <t>MINOR</t>
         </is>
@@ -9362,8 +10568,8 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="H22" s="33" t="n">
-        <v>0.55</v>
+      <c r="H22" s="41" t="n">
+        <v>0.62</v>
       </c>
       <c r="I22" s="12" t="inlineStr">
         <is>
@@ -9375,7 +10581,15 @@
       <c r="L22" s="29" t="inlineStr">
         <is>
           <t>for lesion, visits in measurements grouped by lesion:
-    if distinct method_at_visit values &gt; 1: raise finding</t>
+    if distinct method_at_visit values &gt; 1:
+        candidate = lesion
+if the same method change affects &gt;= config.method_change_study_wide_pct (default 50)
+   of lesions at the same visit:
+       raise ONE study-level finding, audience STUDY_TEAM
+else:
+       raise a per-lesion finding
+guards:
+  - no finding where the method change is recorded with a reason</t>
         </is>
       </c>
       <c r="M22" s="23" t="inlineStr">
@@ -9390,7 +10604,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q22" s="24" t="inlineStr"/>
+      <c r="Q22" s="31" t="inlineStr">
+        <is>
+          <t>MM</t>
+        </is>
+      </c>
+      <c r="R22" s="35" t="inlineStr">
+        <is>
+          <t>A study-wide modality change — a protocol amendment, a scanner replacement — was raising a finding on every lesion in every subject. That is a study-level observation, not a per-lesion data query.</t>
+        </is>
+      </c>
+      <c r="S22" s="36" t="inlineStr">
+        <is>
+          <t>for lesion, visits in measurements grouped by lesion:
+    if distinct method_at_visit values &gt; 1: raise finding</t>
+        </is>
+      </c>
+      <c r="T22" s="33" t="n"/>
+      <c r="U22" s="34" t="n"/>
     </row>
     <row r="23" ht="96" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
@@ -9413,7 +10644,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E23" s="36" t="inlineStr">
+      <c r="E23" s="39" t="inlineStr">
         <is>
           <t>MINOR</t>
         </is>
@@ -9428,7 +10659,7 @@
           <t>CONDITIONAL</t>
         </is>
       </c>
-      <c r="H23" s="33" t="n">
+      <c r="H23" s="41" t="n">
         <v>0.6</v>
       </c>
       <c r="I23" s="12" t="inlineStr">
@@ -9461,6 +10692,10 @@
         </is>
       </c>
       <c r="Q23" s="24" t="inlineStr"/>
+      <c r="R23" s="12" t="inlineStr"/>
+      <c r="S23" s="13" t="n"/>
+      <c r="T23" s="33" t="n"/>
+      <c r="U23" s="34" t="n"/>
     </row>
     <row r="24" ht="96" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
@@ -9493,12 +10728,12 @@
           <t>LLM_ADJUDICATED</t>
         </is>
       </c>
-      <c r="G24" s="39" t="inlineStr">
+      <c r="G24" s="43" t="inlineStr">
         <is>
           <t>PROPOSED_OPTIONAL</t>
         </is>
       </c>
-      <c r="H24" s="33" t="n">
+      <c r="H24" s="41" t="n">
         <v>0.55</v>
       </c>
       <c r="I24" s="12" t="inlineStr">
@@ -9527,6 +10762,10 @@
         </is>
       </c>
       <c r="Q24" s="24" t="inlineStr"/>
+      <c r="R24" s="12" t="inlineStr"/>
+      <c r="S24" s="13" t="n"/>
+      <c r="T24" s="33" t="n"/>
+      <c r="U24" s="34" t="n"/>
     </row>
     <row r="25" ht="96" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
@@ -9592,6 +10831,10 @@
         </is>
       </c>
       <c r="Q25" s="24" t="inlineStr"/>
+      <c r="R25" s="12" t="inlineStr"/>
+      <c r="S25" s="13" t="n"/>
+      <c r="T25" s="33" t="n"/>
+      <c r="U25" s="34" t="n"/>
     </row>
     <row r="26" ht="96" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
@@ -9664,21 +10907,21 @@
         </is>
       </c>
       <c r="N26" s="12" t="inlineStr"/>
-      <c r="O26" s="34" t="inlineStr">
+      <c r="O26" s="37" t="inlineStr">
         <is>
           <t>AMENDED alongside TE-BL-011, which carries the identical condition. Accepted at round 1, but the same CRF-dependency applies at follow-up and the pair must move together.</t>
         </is>
       </c>
-      <c r="P26" s="35" t="inlineStr">
-        <is>
-          <t>Accept</t>
-        </is>
-      </c>
-      <c r="Q26" s="24" t="inlineStr">
-        <is>
-          <t>Daniel</t>
-        </is>
-      </c>
+      <c r="P26" s="38" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="Q26" s="24" t="inlineStr"/>
+      <c r="R26" s="12" t="inlineStr"/>
+      <c r="S26" s="13" t="n"/>
+      <c r="T26" s="33" t="n"/>
+      <c r="U26" s="34" t="n"/>
     </row>
     <row r="27" ht="96" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
@@ -9745,6 +10988,10 @@
         </is>
       </c>
       <c r="Q27" s="24" t="inlineStr"/>
+      <c r="R27" s="12" t="inlineStr"/>
+      <c r="S27" s="13" t="n"/>
+      <c r="T27" s="33" t="n"/>
+      <c r="U27" s="34" t="n"/>
     </row>
     <row r="28" ht="96" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
@@ -9812,6 +11059,10 @@
         </is>
       </c>
       <c r="Q28" s="24" t="inlineStr"/>
+      <c r="R28" s="12" t="inlineStr"/>
+      <c r="S28" s="13" t="n"/>
+      <c r="T28" s="33" t="n"/>
+      <c r="U28" s="34" t="n"/>
     </row>
     <row r="29" ht="96" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
@@ -9834,7 +11085,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E29" s="36" t="inlineStr">
+      <c r="E29" s="39" t="inlineStr">
         <is>
           <t>MINOR</t>
         </is>
@@ -9849,7 +11100,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="H29" s="38" t="n">
+      <c r="H29" s="42" t="n">
         <v>0.45</v>
       </c>
       <c r="I29" s="12" t="inlineStr">
@@ -9881,21 +11132,21 @@
           <t>Provide the rationale insisting the proposed threshold. What material or information is referred to make this validation rule.</t>
         </is>
       </c>
-      <c r="O29" s="34" t="inlineStr">
+      <c r="O29" s="37" t="inlineStr">
         <is>
           <t>RATIONALE ADDED. These thresholds are not drawn from RECIST — the guideline sets no outlier limits. They are heuristics aimed at transcription error, and they are declared as such rather than dressed up with a citation. Proposed for calibration against the golden dataset at Step 3, where the false-positive rate can actually be measured.</t>
         </is>
       </c>
-      <c r="P29" s="35" t="inlineStr">
-        <is>
-          <t>Accept</t>
-        </is>
-      </c>
-      <c r="Q29" s="24" t="inlineStr">
-        <is>
-          <t>Daniel</t>
-        </is>
-      </c>
+      <c r="P29" s="38" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="Q29" s="24" t="inlineStr"/>
+      <c r="R29" s="12" t="inlineStr"/>
+      <c r="S29" s="13" t="n"/>
+      <c r="T29" s="33" t="n"/>
+      <c r="U29" s="34" t="n"/>
     </row>
     <row r="30" ht="96" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
@@ -9964,21 +11215,21 @@
           <t>Provide the rationale insisting the proposed threshold. What material or information is referred to make this validation rule.</t>
         </is>
       </c>
-      <c r="O30" s="34" t="inlineStr">
+      <c r="O30" s="37" t="inlineStr">
         <is>
           <t>RATIONALE ADDED. This rule carries no numeric threshold; the parameter in it is the interpretation decision ID-01, which is a protocol question rather than a guideline constant.</t>
         </is>
       </c>
-      <c r="P30" s="35" t="inlineStr">
-        <is>
-          <t>Accept</t>
-        </is>
-      </c>
-      <c r="Q30" s="24" t="inlineStr">
-        <is>
-          <t>Daniel</t>
-        </is>
-      </c>
+      <c r="P30" s="38" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="Q30" s="24" t="inlineStr"/>
+      <c r="R30" s="12" t="inlineStr"/>
+      <c r="S30" s="13" t="n"/>
+      <c r="T30" s="33" t="n"/>
+      <c r="U30" s="34" t="n"/>
     </row>
     <row r="31" ht="96" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
@@ -10001,7 +11252,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E31" s="36" t="inlineStr">
+      <c r="E31" s="39" t="inlineStr">
         <is>
           <t>MINOR</t>
         </is>
@@ -10016,7 +11267,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="H31" s="33" t="n">
+      <c r="H31" s="41" t="n">
         <v>0.7</v>
       </c>
       <c r="I31" s="12" t="inlineStr">
@@ -10045,6 +11296,10 @@
         </is>
       </c>
       <c r="Q31" s="24" t="inlineStr"/>
+      <c r="R31" s="12" t="inlineStr"/>
+      <c r="S31" s="13" t="n"/>
+      <c r="T31" s="33" t="n"/>
+      <c r="U31" s="34" t="n"/>
     </row>
     <row r="32" ht="96" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
@@ -10130,21 +11385,21 @@
           <t>The proposed condition is fine. Since a protocol may define different assessment window for particular assessment timing, consider to get information about study's individual tumor assessment window period.</t>
         </is>
       </c>
-      <c r="O32" s="34" t="inlineStr">
+      <c r="O32" s="37" t="inlineStr">
         <is>
           <t>AMENDED. The scalar interval and window are replaced by a per-visit schedule captured at the AC-11 protocol intake, so a protocol that tightens or widens the window at particular timepoints is honoured. The scalar remains as a fallback for protocols with a uniform interval.</t>
         </is>
       </c>
-      <c r="P32" s="35" t="inlineStr">
-        <is>
-          <t>Accept</t>
-        </is>
-      </c>
-      <c r="Q32" s="24" t="inlineStr">
-        <is>
-          <t>Daniel</t>
-        </is>
-      </c>
+      <c r="P32" s="38" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="Q32" s="24" t="inlineStr"/>
+      <c r="R32" s="12" t="inlineStr"/>
+      <c r="S32" s="13" t="n"/>
+      <c r="T32" s="33" t="n"/>
+      <c r="U32" s="34" t="n"/>
     </row>
     <row r="33" ht="96" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
@@ -10211,6 +11466,10 @@
         </is>
       </c>
       <c r="Q33" s="24" t="inlineStr"/>
+      <c r="R33" s="12" t="inlineStr"/>
+      <c r="S33" s="13" t="n"/>
+      <c r="T33" s="33" t="n"/>
+      <c r="U33" s="34" t="n"/>
     </row>
     <row r="34" ht="96" customHeight="1">
       <c r="A34" s="11" t="inlineStr">
@@ -10233,7 +11492,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
+      <c r="E34" s="40" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -10282,21 +11541,29 @@
           <t>The proposed condition could be applied to follow-up assessment? It's okay to check at baseline's tumor identification, but I'm not sure to check under follow-up assessment.</t>
         </is>
       </c>
-      <c r="O34" s="34" t="inlineStr">
+      <c r="O34" s="37" t="inlineStr">
         <is>
           <t>AMENDED, and the scope was the wrong way round. The rule is only meaningful at follow-up: a nodal target cannot be absent at baseline, since it was selected for having a short axis of at least 15 mm. What it catches is a node recorded as absent or zero at follow-up once it has normalised, which drops it out of the sum and produces a falsely low sum and a spurious response. The rule is now explicitly restricted to follow-up, and the too-small-to-measure state is excluded so that ID-02 handling is not flagged as an error.</t>
         </is>
       </c>
-      <c r="P34" s="35" t="inlineStr">
-        <is>
-          <t>Accept</t>
-        </is>
-      </c>
-      <c r="Q34" s="24" t="inlineStr">
-        <is>
-          <t>Daniel</t>
-        </is>
-      </c>
+      <c r="P34" s="38" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="Q34" s="31" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="R34" s="35" t="inlineStr">
+        <is>
+          <t>Removed the guideline sentence (SQ-05) and the bare instruction to enter a measurement. Now allows for the case where the node genuinely was not measurable.</t>
+        </is>
+      </c>
+      <c r="S34" s="13" t="n"/>
+      <c r="T34" s="33" t="n"/>
+      <c r="U34" s="34" t="n"/>
     </row>
     <row r="35" ht="96" customHeight="1">
       <c r="A35" s="11" t="inlineStr">
@@ -10319,7 +11586,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E35" s="36" t="inlineStr">
+      <c r="E35" s="39" t="inlineStr">
         <is>
           <t>MINOR</t>
         </is>
@@ -10362,6 +11629,10 @@
         </is>
       </c>
       <c r="Q35" s="24" t="inlineStr"/>
+      <c r="R35" s="12" t="inlineStr"/>
+      <c r="S35" s="13" t="n"/>
+      <c r="T35" s="33" t="n"/>
+      <c r="U35" s="34" t="n"/>
     </row>
     <row r="36" ht="96" customHeight="1">
       <c r="A36" s="11" t="inlineStr">
@@ -10400,7 +11671,7 @@
         </is>
       </c>
       <c r="H36" s="32" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="I36" s="12" t="inlineStr">
         <is>
@@ -10415,8 +11686,14 @@
       </c>
       <c r="L36" s="29" t="inlineStr">
         <is>
-          <t>if assessment_date &gt; death_date: raise CRITICAL
-if assessment_date &gt; discontinuation_date + config.post_treatment_followup_days: raise MAJOR</t>
+          <t>if assessment_date &gt; death_date
+   or assessment_date &gt; end_of_participation_date:
+       raise finding
+guards:
+  - no finding where assessment_date == death_date: the assessment may legitimately
+    precede death on the same day
+  - no finding where either date is partial to the point that the comparison cannot
+    be made — report NOT_EVALUATED rather than guessing</t>
         </is>
       </c>
       <c r="M36" s="23" t="inlineStr">
@@ -10431,7 +11708,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q36" s="24" t="inlineStr"/>
+      <c r="Q36" s="31" t="inlineStr">
+        <is>
+          <t>MM</t>
+        </is>
+      </c>
+      <c r="R36" s="35" t="inlineStr">
+        <is>
+          <t>An assessment dated the same day as death is common and legitimate — the scan preceded the death that day. Firing on it produced an unanswerable query. Partial dates were also being treated as full ones.</t>
+        </is>
+      </c>
+      <c r="S36" s="36" t="inlineStr">
+        <is>
+          <t>if assessment_date &gt; death_date: raise CRITICAL
+if assessment_date &gt; discontinuation_date + config.post_treatment_followup_days: raise MAJOR</t>
+        </is>
+      </c>
+      <c r="T36" s="33" t="n"/>
+      <c r="U36" s="34" t="n"/>
     </row>
     <row r="37" ht="96" customHeight="1">
       <c r="A37" s="11" t="inlineStr">
@@ -10454,7 +11748,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E37" s="36" t="inlineStr">
+      <c r="E37" s="39" t="inlineStr">
         <is>
           <t>MINOR</t>
         </is>
@@ -10498,6 +11792,10 @@
         </is>
       </c>
       <c r="Q37" s="24" t="inlineStr"/>
+      <c r="R37" s="12" t="inlineStr"/>
+      <c r="S37" s="13" t="n"/>
+      <c r="T37" s="33" t="n"/>
+      <c r="U37" s="34" t="n"/>
     </row>
     <row r="38" ht="96" customHeight="1">
       <c r="A38" s="11" t="inlineStr">
@@ -10520,7 +11818,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E38" s="36" t="inlineStr">
+      <c r="E38" s="39" t="inlineStr">
         <is>
           <t>MINOR</t>
         </is>
@@ -10535,7 +11833,7 @@
           <t>CONDITIONAL</t>
         </is>
       </c>
-      <c r="H38" s="33" t="n">
+      <c r="H38" s="41" t="n">
         <v>0.58</v>
       </c>
       <c r="I38" s="12" t="inlineStr">
@@ -10567,6 +11865,10 @@
         </is>
       </c>
       <c r="Q38" s="24" t="inlineStr"/>
+      <c r="R38" s="12" t="inlineStr"/>
+      <c r="S38" s="13" t="n"/>
+      <c r="T38" s="33" t="n"/>
+      <c r="U38" s="34" t="n"/>
     </row>
     <row r="39" ht="96" customHeight="1">
       <c r="A39" s="11" t="inlineStr">
@@ -10589,7 +11891,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E39" s="40" t="inlineStr">
+      <c r="E39" s="44" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -10604,8 +11906,8 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="H39" s="38" t="n">
-        <v>0.3</v>
+      <c r="H39" s="41" t="n">
+        <v>0.55</v>
       </c>
       <c r="I39" s="12" t="inlineStr">
         <is>
@@ -10616,8 +11918,13 @@
       <c r="K39" s="12" t="inlineStr"/>
       <c r="L39" s="29" t="inlineStr">
         <is>
-          <t>if a lesion has the identical value at &gt;= 3 consecutive assessments
-   and the lesion is &gt; config.identical_value_min_mm (default 15): raise finding</t>
+          <t>if ALL target lesions for a subject carry identical values at &gt;= 3 consecutive
+   assessments, and at least one lesion is &gt; config.identical_value_min_mm (default 15):
+       raise finding
+guards:
+  - no finding where only some lesions repeat: genuinely stable disease does this
+  - no finding where the assessments are within config.identical_min_interval_days
+    of each other (default 21), where a real repeat read is plausible</t>
         </is>
       </c>
       <c r="M39" s="23" t="inlineStr">
@@ -10632,7 +11939,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q39" s="24" t="inlineStr"/>
+      <c r="Q39" s="31" t="inlineStr">
+        <is>
+          <t>MM</t>
+        </is>
+      </c>
+      <c r="R39" s="35" t="inlineStr">
+        <is>
+          <t>Per-lesion identical values are common in genuinely stable disease, which is why this sat at a 0.30 base rate. The pattern that actually signals copied data is every target lesion identical across visits. Narrowed to that, and the base rate rises accordingly.</t>
+        </is>
+      </c>
+      <c r="S39" s="36" t="inlineStr">
+        <is>
+          <t>if a lesion has the identical value at &gt;= 3 consecutive assessments
+   and the lesion is &gt; config.identical_value_min_mm (default 15): raise finding</t>
+        </is>
+      </c>
+      <c r="T39" s="33" t="n"/>
+      <c r="U39" s="34" t="n"/>
     </row>
     <row r="40" ht="96" customHeight="1">
       <c r="A40" s="11" t="inlineStr">
@@ -10655,7 +11979,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E40" s="37" t="inlineStr">
+      <c r="E40" s="40" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -10699,7 +12023,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q40" s="24" t="inlineStr"/>
+      <c r="Q40" s="31" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="R40" s="35" t="inlineStr">
+        <is>
+          <t>Removed the agent's derivation from the query. The percent-change arithmetic is reviewer-facing context, not something a site coordinator needs in order to re-check a record.</t>
+        </is>
+      </c>
+      <c r="S40" s="13" t="n"/>
+      <c r="T40" s="33" t="n"/>
+      <c r="U40" s="34" t="n"/>
     </row>
     <row r="41" ht="96" customHeight="1">
       <c r="A41" s="11" t="inlineStr">
@@ -10722,7 +12058,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E41" s="37" t="inlineStr">
+      <c r="E41" s="40" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -10772,21 +12108,29 @@
 In addition, the 'TE-RS-002' and 'TE-RS-003' are duplicate with 'TE-RS-001'? If yes, should we keep the two rules in the rule list?</t>
         </is>
       </c>
-      <c r="O41" s="34" t="inlineStr">
+      <c r="O41" s="37" t="inlineStr">
         <is>
           <t>KEPT, with the relationship now declared explicitly. On the logic: the proposed variant uses AND, but PD requires both criteria, so 'PD not met' is pct &lt; 20 OR abs &lt; 5 — the AND form is narrower than the correct negation and would miss cases. That complete check already exists as TE-RS-001, which recomputes the response and compares. On duplication: yes, TE-RS-002 and TE-RS-003 are both subsumed by TE-RS-001 for detection. Their value is diagnostic, not detective — TE-RS-001 says the response is wrong, these say why, and the query text differs accordingly. They are now declared as cascade children of TE-RS-001, so when both fire the reviewer sees one finding carrying the specific reason, not two.</t>
         </is>
       </c>
-      <c r="P41" s="35" t="inlineStr">
-        <is>
-          <t>Accept</t>
-        </is>
-      </c>
-      <c r="Q41" s="24" t="inlineStr">
-        <is>
-          <t>Daniel</t>
-        </is>
-      </c>
+      <c r="P41" s="38" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="Q41" s="31" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="R41" s="35" t="inlineStr">
+        <is>
+          <t>Removed the guideline citation and the threshold arithmetic (SQ-05). Asks the one question that resolves the finding: what drove the PD call.</t>
+        </is>
+      </c>
+      <c r="S41" s="13" t="n"/>
+      <c r="T41" s="33" t="n"/>
+      <c r="U41" s="34" t="n"/>
     </row>
     <row r="42" ht="96" customHeight="1">
       <c r="A42" s="11" t="inlineStr">
@@ -10809,7 +12153,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E42" s="37" t="inlineStr">
+      <c r="E42" s="40" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -10861,21 +12205,29 @@
           <t>Question to this rule. Should it consider the pct_from_baseline condition? Given that the proposed condition could check incorrect data well with the 1st and 2nd line (i.e. "if reported_target_response != PD and pct_from_nadir &gt;= pd_pct and abs_from_nadir_mm &gt;= pd_abs"), if 3rd line condition isn't definitely deciding data consistency, I suggest to have rule conditions without 3rd line condition.</t>
         </is>
       </c>
-      <c r="O42" s="34" t="inlineStr">
+      <c r="O42" s="37" t="inlineStr">
         <is>
           <t>AMENDED as suggested. The baseline comparison is removed from the gate, so the rule now catches every case where progression criteria are met from nadir but progression was not reported. The baseline comparison is retained purely as a discriminator: where percent change from baseline also falls short of the threshold, the site almost certainly compared against baseline instead of nadir, and the finding carries that specific wording and a higher confidence. Where it does not, the finding is still raised with generic wording.</t>
         </is>
       </c>
-      <c r="P42" s="35" t="inlineStr">
-        <is>
-          <t>Accept</t>
-        </is>
-      </c>
-      <c r="Q42" s="24" t="inlineStr">
-        <is>
-          <t>Daniel</t>
-        </is>
-      </c>
+      <c r="P42" s="38" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="Q42" s="31" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="R42" s="35" t="inlineStr">
+        <is>
+          <t>Removed the guideline citation (SQ-05) and replaced 'nadir' with 'the smallest sum recorded on study', which a site coordinator can act on without knowing the term.</t>
+        </is>
+      </c>
+      <c r="S42" s="13" t="n"/>
+      <c r="T42" s="33" t="n"/>
+      <c r="U42" s="34" t="n"/>
     </row>
     <row r="43" ht="96" customHeight="1">
       <c r="A43" s="11" t="inlineStr">
@@ -10898,7 +12250,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E43" s="37" t="inlineStr">
+      <c r="E43" s="40" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -10944,6 +12296,10 @@
         </is>
       </c>
       <c r="Q43" s="24" t="inlineStr"/>
+      <c r="R43" s="12" t="inlineStr"/>
+      <c r="S43" s="13" t="n"/>
+      <c r="T43" s="33" t="n"/>
+      <c r="U43" s="34" t="n"/>
     </row>
     <row r="44" ht="96" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
@@ -10966,7 +12322,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E44" s="37" t="inlineStr">
+      <c r="E44" s="40" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -11010,6 +12366,10 @@
         </is>
       </c>
       <c r="Q44" s="24" t="inlineStr"/>
+      <c r="R44" s="12" t="inlineStr"/>
+      <c r="S44" s="13" t="n"/>
+      <c r="T44" s="33" t="n"/>
+      <c r="U44" s="34" t="n"/>
     </row>
     <row r="45" ht="96" customHeight="1">
       <c r="A45" s="11" t="inlineStr">
@@ -11076,6 +12436,10 @@
         </is>
       </c>
       <c r="Q45" s="24" t="inlineStr"/>
+      <c r="R45" s="12" t="inlineStr"/>
+      <c r="S45" s="13" t="n"/>
+      <c r="T45" s="33" t="n"/>
+      <c r="U45" s="34" t="n"/>
     </row>
     <row r="46" ht="96" customHeight="1">
       <c r="A46" s="11" t="inlineStr">
@@ -11098,7 +12462,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E46" s="40" t="inlineStr">
+      <c r="E46" s="44" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -11113,7 +12477,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="H46" s="38" t="n">
+      <c r="H46" s="42" t="n">
         <v>0.45</v>
       </c>
       <c r="I46" s="12" t="inlineStr">
@@ -11145,21 +12509,29 @@
           <t>This isn't decisive with entered data only. Check whether it could downgrade the severity to 'INFO'.</t>
         </is>
       </c>
-      <c r="O46" s="34" t="inlineStr">
+      <c r="O46" s="37" t="inlineStr">
         <is>
           <t>AMENDED to INFO. You are right that collected data cannot settle this — the guideline's test is a judgement about overall tumor burden that the recorded non-target states do not capture. Note the consequence, which is intended: INFO findings do not enter the default query worklist, so this becomes a study-team observation rather than a site query. The adjudicator can still escalate to MAJOR where the recorded descriptions actively contradict the reported progression.</t>
         </is>
       </c>
-      <c r="P46" s="35" t="inlineStr">
-        <is>
-          <t>Accept</t>
-        </is>
-      </c>
-      <c r="Q46" s="24" t="inlineStr">
-        <is>
-          <t>Daniel</t>
-        </is>
-      </c>
+      <c r="P46" s="38" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="Q46" s="31" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="R46" s="35" t="inlineStr">
+        <is>
+          <t>Removed 'please confirm that the overall tumor burden has increased substantially'. That is a medical judgement and does not belong in a query answered by site data staff. The query now asks only for the radiology description, which is a data request; the judgement stays with the monitor.</t>
+        </is>
+      </c>
+      <c r="S46" s="13" t="n"/>
+      <c r="T46" s="33" t="n"/>
+      <c r="U46" s="34" t="n"/>
     </row>
     <row r="47" ht="96" customHeight="1">
       <c r="A47" s="11" t="inlineStr">
@@ -11182,7 +12554,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E47" s="37" t="inlineStr">
+      <c r="E47" s="40" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -11236,21 +12608,29 @@
           <t>Is it possible to give information whether any issue in the individual response (target, non-target) and their relevant detail data (e.g. tumor size, individual lesion response) in order not to avoid duplicate query in both sides (i.e. overall response, target/non-target response)</t>
         </is>
       </c>
-      <c r="O47" s="34" t="inlineStr">
+      <c r="O47" s="37" t="inlineStr">
         <is>
           <t>AMENDED. The rule now declares its component dependencies, and the cascade grouping suppresses the separate overall-response query whenever a component finding is already open for the same assessment. Where no component finding exists, the overall-response finding is raised alone and names which component drove the expected value, so the site receives one query identifying the specific field rather than two queries about the same visit.</t>
         </is>
       </c>
-      <c r="P47" s="35" t="inlineStr">
-        <is>
-          <t>Accept</t>
-        </is>
-      </c>
-      <c r="Q47" s="24" t="inlineStr">
-        <is>
-          <t>Daniel</t>
-        </is>
-      </c>
+      <c r="P47" s="38" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="Q47" s="31" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="R47" s="35" t="inlineStr">
+        <is>
+          <t>Removed 'the overall response should be {derived_overall}'. Naming the expected value turns a check into an instruction, and if the derivation is wrong the site confirms the error.</t>
+        </is>
+      </c>
+      <c r="S47" s="13" t="n"/>
+      <c r="T47" s="33" t="n"/>
+      <c r="U47" s="34" t="n"/>
     </row>
     <row r="48" ht="96" customHeight="1">
       <c r="A48" s="11" t="inlineStr">
@@ -11317,174 +12697,178 @@
         </is>
       </c>
       <c r="Q48" s="24" t="inlineStr"/>
+      <c r="R48" s="12" t="inlineStr"/>
+      <c r="S48" s="13" t="n"/>
+      <c r="T48" s="33" t="n"/>
+      <c r="U48" s="34" t="n"/>
     </row>
     <row r="49" ht="96" customHeight="1">
-      <c r="A49" s="41" t="inlineStr">
+      <c r="A49" s="45" t="inlineStr">
         <is>
           <t>TE-RS-010</t>
         </is>
       </c>
-      <c r="B49" s="42" t="inlineStr">
+      <c r="B49" s="46" t="inlineStr">
         <is>
           <t>RS</t>
         </is>
       </c>
-      <c r="C49" s="43" t="inlineStr">
+      <c r="C49" s="47" t="inlineStr">
         <is>
           <t>New lesion recorded but overall response is not progression</t>
         </is>
       </c>
-      <c r="D49" s="42" t="inlineStr">
+      <c r="D49" s="46" t="inlineStr">
         <is>
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E49" s="42" t="inlineStr">
+      <c r="E49" s="46" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="F49" s="42" t="inlineStr">
+      <c r="F49" s="46" t="inlineStr">
         <is>
           <t>DETERMINISTIC</t>
         </is>
       </c>
-      <c r="G49" s="44" t="inlineStr">
+      <c r="G49" s="48" t="inlineStr">
         <is>
           <t>RETIRED</t>
         </is>
       </c>
-      <c r="H49" s="45" t="n">
+      <c r="H49" s="49" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="I49" s="43" t="inlineStr">
+      <c r="I49" s="47" t="inlineStr">
         <is>
           <t>A confirmed new lesion always means progression under RECIST 1.1.</t>
         </is>
       </c>
-      <c r="J49" s="43" t="inlineStr">
+      <c r="J49" s="47" t="inlineStr">
         <is>
           <t>Retired at the Step 2 review as fully subsumed by TE-RS-008 (overall response versus the component table), TE-RS-009 (flag versus recorded lesions) and TE-IR-001 (iUPD under iRECIST).</t>
         </is>
       </c>
-      <c r="K49" s="43" t="inlineStr"/>
-      <c r="L49" s="46" t="inlineStr">
+      <c r="K49" s="47" t="inlineStr"/>
+      <c r="L49" s="50" t="inlineStr">
         <is>
           <t>if new_lesion_flag == YES and reported_overall != PD: raise finding
    (under iRECIST the expected value is iUPD; see TE-IR-001)</t>
         </is>
       </c>
-      <c r="M49" s="47" t="inlineStr">
+      <c r="M49" s="51" t="inlineStr">
         <is>
           <t>Discuss</t>
         </is>
       </c>
-      <c r="N49" s="48" t="inlineStr">
+      <c r="N49" s="52" t="inlineStr">
         <is>
           <t>Check if this rule is duplicate, considering TE-RS-008.
 If duplicate rule, I suggest remove this rule, instead, add only iRECIST condition to the TE-RS-008.</t>
         </is>
       </c>
-      <c r="O49" s="48" t="inlineStr">
+      <c r="O49" s="52" t="inlineStr">
         <is>
           <t>RETIRED — you are right. TE-RS-008 derives the overall response from the reported components, and the new-lesion flag is one of those components, so a recorded new lesion with a non-PD overall response already fires TE-RS-008. The one case that is not covered — a new lesion present in the lesion table while the flag says NO — is TE-RS-009. The iRECIST expectation needs no folding in, because TE-IR-001 already requires iUPD rather than PD where iRECIST applies. The id is retained permanently and never reused, so historical findings stay interpretable.</t>
         </is>
       </c>
-      <c r="P49" s="49" t="inlineStr">
-        <is>
-          <t>Accept</t>
-        </is>
-      </c>
-      <c r="Q49" s="47" t="inlineStr">
-        <is>
-          <t>Daniel</t>
-        </is>
-      </c>
+      <c r="P49" s="53" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="Q49" s="51" t="inlineStr"/>
+      <c r="R49" s="52" t="inlineStr"/>
+      <c r="S49" s="54" t="n"/>
+      <c r="T49" s="33" t="n"/>
+      <c r="U49" s="34" t="n"/>
     </row>
     <row r="50" ht="96" customHeight="1">
-      <c r="A50" s="41" t="inlineStr">
+      <c r="A50" s="45" t="inlineStr">
         <is>
           <t>TE-RS-011</t>
         </is>
       </c>
-      <c r="B50" s="42" t="inlineStr">
+      <c r="B50" s="46" t="inlineStr">
         <is>
           <t>RS</t>
         </is>
       </c>
-      <c r="C50" s="43" t="inlineStr">
+      <c r="C50" s="47" t="inlineStr">
         <is>
           <t>New lesion in an anatomical region not imaged at baseline</t>
         </is>
       </c>
-      <c r="D50" s="42" t="inlineStr">
+      <c r="D50" s="46" t="inlineStr">
         <is>
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E50" s="42" t="inlineStr">
+      <c r="E50" s="46" t="inlineStr">
         <is>
           <t>MAJOR</t>
         </is>
       </c>
-      <c r="F50" s="42" t="inlineStr">
+      <c r="F50" s="46" t="inlineStr">
         <is>
           <t>HYBRID</t>
         </is>
       </c>
-      <c r="G50" s="44" t="inlineStr">
+      <c r="G50" s="48" t="inlineStr">
         <is>
           <t>RETIRED</t>
         </is>
       </c>
-      <c r="H50" s="45" t="n">
+      <c r="H50" s="49" t="n">
         <v>0.62</v>
       </c>
-      <c r="I50" s="43" t="inlineStr">
+      <c r="I50" s="47" t="inlineStr">
         <is>
           <t>Ensure the region-not-imaged case was considered explicitly.</t>
         </is>
       </c>
-      <c r="J50" s="43" t="inlineStr">
+      <c r="J50" s="47" t="inlineStr">
         <is>
           <t>Rejected at the Step 2 review. The premise does not hold: investigator-discretion imaging routinely covers regions absent from the baseline protocol imaging, so region coverage is not evidence of a data problem.</t>
         </is>
       </c>
-      <c r="K50" s="43" t="inlineStr">
+      <c r="K50" s="47" t="inlineStr">
         <is>
           <t>imaging_metadata.regions_imaged (or inferred from baseline lesion organs and modality)</t>
         </is>
       </c>
-      <c r="L50" s="46" t="inlineStr">
+      <c r="L50" s="50" t="inlineStr">
         <is>
           <t>if new lesion organ/region was not covered by the baseline imaging: raise finding</t>
         </is>
       </c>
-      <c r="M50" s="50" t="inlineStr">
+      <c r="M50" s="55" t="inlineStr">
         <is>
           <t>Reject</t>
         </is>
       </c>
-      <c r="N50" s="48" t="inlineStr">
+      <c r="N50" s="52" t="inlineStr">
         <is>
           <t>New lesion could be confirmed by other organ/region not covered by the baseline image, because of doing other image by investigator's discretion. Suggest not to run this rule.</t>
         </is>
       </c>
-      <c r="O50" s="48" t="inlineStr">
+      <c r="O50" s="52" t="inlineStr">
         <is>
           <t>RETIRED as rejected. Imaging performed at investigator discretion outside the baseline coverage is routine and entirely legitimate, and a new lesion found that way is a real new lesion. The rule assumed baseline coverage bounded where disease could be found, which is not how imaging is actually ordered. The id is retained permanently and never reused.</t>
         </is>
       </c>
-      <c r="P50" s="49" t="inlineStr">
-        <is>
-          <t>Accept</t>
-        </is>
-      </c>
-      <c r="Q50" s="47" t="inlineStr">
-        <is>
-          <t>Daniel</t>
-        </is>
-      </c>
+      <c r="P50" s="53" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="Q50" s="51" t="inlineStr"/>
+      <c r="R50" s="52" t="inlineStr"/>
+      <c r="S50" s="54" t="n"/>
+      <c r="T50" s="33" t="n"/>
+      <c r="U50" s="34" t="n"/>
     </row>
     <row r="51" ht="96" customHeight="1">
       <c r="A51" s="11" t="inlineStr">
@@ -11522,7 +12906,7 @@
           <t>CONDITIONAL</t>
         </is>
       </c>
-      <c r="H51" s="33" t="n">
+      <c r="H51" s="41" t="n">
         <v>0.68</v>
       </c>
       <c r="I51" s="12" t="inlineStr">
@@ -11555,6 +12939,10 @@
         </is>
       </c>
       <c r="Q51" s="24" t="inlineStr"/>
+      <c r="R51" s="12" t="inlineStr"/>
+      <c r="S51" s="13" t="n"/>
+      <c r="T51" s="33" t="n"/>
+      <c r="U51" s="34" t="n"/>
     </row>
     <row r="52" ht="96" customHeight="1">
       <c r="A52" s="11" t="inlineStr">
@@ -11627,21 +13015,29 @@
           <t>This rule should consider the case that the visit j's data has definitive rationale of PD. E.g. At the visit j, there is evidence to determine PD due to other conditions (e.g. target lesion sum mm passes 20% worsen and over minimum increase)</t>
         </is>
       </c>
-      <c r="O52" s="34" t="inlineStr">
+      <c r="O52" s="37" t="inlineStr">
         <is>
           <t>AMENDED. A guard now suppresses the finding where progression at visit j is independently established by the target or non-target criteria. Back-dating is only correct where the equivocal-then-confirmed lesion is what drove progression; where the target sum crossed the threshold at visit j in its own right, visit j is the correct progression date and the earlier equivocal observation is irrelevant to it.</t>
         </is>
       </c>
-      <c r="P52" s="35" t="inlineStr">
-        <is>
-          <t>Accept</t>
-        </is>
-      </c>
-      <c r="Q52" s="24" t="inlineStr">
-        <is>
-          <t>Daniel</t>
-        </is>
-      </c>
+      <c r="P52" s="38" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="Q52" s="31" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="R52" s="35" t="inlineStr">
+        <is>
+          <t>Removed 'per RECIST the progression date should be {first_date}' — both a guideline citation (SQ-05) and a statement of the answer.</t>
+        </is>
+      </c>
+      <c r="S52" s="13" t="n"/>
+      <c r="T52" s="33" t="n"/>
+      <c r="U52" s="34" t="n"/>
     </row>
     <row r="53" ht="96" customHeight="1">
       <c r="A53" s="11" t="inlineStr">
@@ -11664,7 +13060,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E53" s="37" t="inlineStr">
+      <c r="E53" s="40" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -11715,21 +13111,21 @@
           <t>Provide the rationale insisting the proposed threshold. What material or information is referred to make this validation rule.</t>
         </is>
       </c>
-      <c r="O53" s="34" t="inlineStr">
+      <c r="O53" s="37" t="inlineStr">
         <is>
           <t>RATIONALE ADDED, and this one does have a guideline source, unlike TE-FU-004.</t>
         </is>
       </c>
-      <c r="P53" s="35" t="inlineStr">
-        <is>
-          <t>Accept</t>
-        </is>
-      </c>
-      <c r="Q53" s="24" t="inlineStr">
-        <is>
-          <t>Daniel</t>
-        </is>
-      </c>
+      <c r="P53" s="38" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="Q53" s="24" t="inlineStr"/>
+      <c r="R53" s="12" t="inlineStr"/>
+      <c r="S53" s="13" t="n"/>
+      <c r="T53" s="33" t="n"/>
+      <c r="U53" s="34" t="n"/>
     </row>
     <row r="54" ht="96" customHeight="1">
       <c r="A54" s="11" t="inlineStr">
@@ -11752,7 +13148,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E54" s="37" t="inlineStr">
+      <c r="E54" s="40" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -11796,6 +13192,10 @@
         </is>
       </c>
       <c r="Q54" s="24" t="inlineStr"/>
+      <c r="R54" s="12" t="inlineStr"/>
+      <c r="S54" s="13" t="n"/>
+      <c r="T54" s="33" t="n"/>
+      <c r="U54" s="34" t="n"/>
     </row>
     <row r="55" ht="96" customHeight="1">
       <c r="A55" s="11" t="inlineStr">
@@ -11818,7 +13218,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E55" s="37" t="inlineStr">
+      <c r="E55" s="40" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -11861,7 +13261,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q55" s="24" t="inlineStr"/>
+      <c r="Q55" s="31" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="R55" s="35" t="inlineStr">
+        <is>
+          <t>Removed the list of permitted response categories. The finding may equally be a missing baseline target lesion rather than a wrong response, and the original wording pointed at only one of the two.</t>
+        </is>
+      </c>
+      <c r="S55" s="13" t="n"/>
+      <c r="T55" s="33" t="n"/>
+      <c r="U55" s="34" t="n"/>
     </row>
     <row r="56" ht="96" customHeight="1">
       <c r="A56" s="11" t="inlineStr">
@@ -11932,6 +13344,10 @@
         </is>
       </c>
       <c r="Q56" s="24" t="inlineStr"/>
+      <c r="R56" s="12" t="inlineStr"/>
+      <c r="S56" s="13" t="n"/>
+      <c r="T56" s="33" t="n"/>
+      <c r="U56" s="34" t="n"/>
     </row>
     <row r="57" ht="96" customHeight="1">
       <c r="A57" s="11" t="inlineStr">
@@ -11998,6 +13414,10 @@
         </is>
       </c>
       <c r="Q57" s="24" t="inlineStr"/>
+      <c r="R57" s="12" t="inlineStr"/>
+      <c r="S57" s="13" t="n"/>
+      <c r="T57" s="33" t="n"/>
+      <c r="U57" s="34" t="n"/>
     </row>
     <row r="58" ht="96" customHeight="1">
       <c r="A58" s="11" t="inlineStr">
@@ -12064,6 +13484,10 @@
         </is>
       </c>
       <c r="Q58" s="24" t="inlineStr"/>
+      <c r="R58" s="12" t="inlineStr"/>
+      <c r="S58" s="13" t="n"/>
+      <c r="T58" s="33" t="n"/>
+      <c r="U58" s="34" t="n"/>
     </row>
     <row r="59" ht="96" customHeight="1">
       <c r="A59" s="11" t="inlineStr">
@@ -12101,7 +13525,7 @@
           <t>CONDITIONAL</t>
         </is>
       </c>
-      <c r="H59" s="33" t="n">
+      <c r="H59" s="41" t="n">
         <v>0.5</v>
       </c>
       <c r="I59" s="12" t="inlineStr">
@@ -12116,25 +13540,50 @@
         </is>
       </c>
       <c r="L59" s="29" t="inlineStr">
+        <is>
+          <t>for each subject with both INVESTIGATOR and BICR streams:
+    discordant = assessments where responses differ,
+                 or progression dates differ by &gt; config.bicr_date_tolerance_days
+    if discordant is non-empty:
+        raise ONE finding per subject listing the discordant assessments
+        severity MAJOR when any difference changes best overall response or the
+                       progression date; INFO otherwise
+guards:
+  - disabled by default; enabled per study in configuration (FR-12)
+  - audience STUDY_TEAM — never issued as a site query</t>
+        </is>
+      </c>
+      <c r="M59" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="N59" s="12" t="inlineStr"/>
+      <c r="O59" s="12" t="inlineStr"/>
+      <c r="P59" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q59" s="31" t="inlineStr">
+        <is>
+          <t>MM</t>
+        </is>
+      </c>
+      <c r="R59" s="35" t="inlineStr">
+        <is>
+          <t>Was raising a finding per discordant assessment. A subject whose whole response history differs between investigator and BICR produced a finding at every visit. Now one finding per subject, listing the discordant timepoints, which is also how a monitor reconciles it.</t>
+        </is>
+      </c>
+      <c r="S59" s="36" t="inlineStr">
         <is>
           <t>for each assessment with both INVESTIGATOR and BICR responses:
     if responses differ, or progression dates differ by &gt; config.bicr_date_tolerance_days:
         raise finding (INFO by default when the difference does not cross a PD boundary)</t>
         </is>
       </c>
-      <c r="M59" s="23" t="inlineStr">
-        <is>
-          <t>Accept</t>
-        </is>
-      </c>
-      <c r="N59" s="12" t="inlineStr"/>
-      <c r="O59" s="12" t="inlineStr"/>
-      <c r="P59" s="24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q59" s="24" t="inlineStr"/>
+      <c r="T59" s="33" t="n"/>
+      <c r="U59" s="34" t="n"/>
     </row>
     <row r="60" ht="96" customHeight="1">
       <c r="A60" s="11" t="inlineStr">
@@ -12157,7 +13606,7 @@
           <t>iRECIST only</t>
         </is>
       </c>
-      <c r="E60" s="37" t="inlineStr">
+      <c r="E60" s="40" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -12201,7 +13650,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q60" s="24" t="inlineStr"/>
+      <c r="Q60" s="31" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="R60" s="35" t="inlineStr">
+        <is>
+          <t>Removed the guideline explanation and the statement that iUPD should have been recorded (SQ-05). iUPD stays in the reviewer-facing tips, where the explanation belongs.</t>
+        </is>
+      </c>
+      <c r="S60" s="13" t="n"/>
+      <c r="T60" s="33" t="n"/>
+      <c r="U60" s="34" t="n"/>
     </row>
     <row r="61" ht="96" customHeight="1">
       <c r="A61" s="11" t="inlineStr">
@@ -12224,7 +13685,7 @@
           <t>iRECIST only</t>
         </is>
       </c>
-      <c r="E61" s="37" t="inlineStr">
+      <c r="E61" s="40" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -12271,6 +13732,10 @@
         </is>
       </c>
       <c r="Q61" s="24" t="inlineStr"/>
+      <c r="R61" s="12" t="inlineStr"/>
+      <c r="S61" s="13" t="n"/>
+      <c r="T61" s="33" t="n"/>
+      <c r="U61" s="34" t="n"/>
     </row>
     <row r="62" ht="96" customHeight="1">
       <c r="A62" s="11" t="inlineStr">
@@ -12293,7 +13758,7 @@
           <t>iRECIST only</t>
         </is>
       </c>
-      <c r="E62" s="37" t="inlineStr">
+      <c r="E62" s="40" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -12342,7 +13807,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q62" s="24" t="inlineStr"/>
+      <c r="Q62" s="31" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="R62" s="35" t="inlineStr">
+        <is>
+          <t>Removed 'against the iRECIST criteria' (SQ-05). The comparison rule is in the tips.</t>
+        </is>
+      </c>
+      <c r="S62" s="13" t="n"/>
+      <c r="T62" s="33" t="n"/>
+      <c r="U62" s="34" t="n"/>
     </row>
     <row r="63" ht="96" customHeight="1">
       <c r="A63" s="11" t="inlineStr">
@@ -12365,7 +13842,7 @@
           <t>iRECIST only</t>
         </is>
       </c>
-      <c r="E63" s="37" t="inlineStr">
+      <c r="E63" s="40" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -12408,7 +13885,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q63" s="24" t="inlineStr"/>
+      <c r="Q63" s="31" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="R63" s="35" t="inlineStr">
+        <is>
+          <t>Removed the guideline explanation of separate new-lesion sums (SQ-05), and narrowed the query to the single factual question.</t>
+        </is>
+      </c>
+      <c r="S63" s="13" t="n"/>
+      <c r="T63" s="33" t="n"/>
+      <c r="U63" s="34" t="n"/>
     </row>
     <row r="64" ht="96" customHeight="1">
       <c r="A64" s="11" t="inlineStr">
@@ -12475,7 +13964,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q64" s="24" t="inlineStr"/>
+      <c r="Q64" s="31" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="R64" s="35" t="inlineStr">
+        <is>
+          <t>Removed the derived-response arithmetic from the query; it remains in the reviewer-facing reason.</t>
+        </is>
+      </c>
+      <c r="S64" s="13" t="n"/>
+      <c r="T64" s="33" t="n"/>
+      <c r="U64" s="34" t="n"/>
     </row>
     <row r="65" ht="96" customHeight="1">
       <c r="A65" s="11" t="inlineStr">
@@ -12541,7 +14042,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q65" s="24" t="inlineStr"/>
+      <c r="Q65" s="31" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="R65" s="35" t="inlineStr">
+        <is>
+          <t>Replaced the guideline citation with the study's own configured limits (SQ-05). Naming study configuration is not a guideline reference and is what the site can act on.</t>
+        </is>
+      </c>
+      <c r="S65" s="13" t="n"/>
+      <c r="T65" s="33" t="n"/>
+      <c r="U65" s="34" t="n"/>
     </row>
     <row r="66" ht="96" customHeight="1">
       <c r="A66" s="11" t="inlineStr">
@@ -12608,6 +14121,10 @@
         </is>
       </c>
       <c r="Q66" s="24" t="inlineStr"/>
+      <c r="R66" s="12" t="inlineStr"/>
+      <c r="S66" s="13" t="n"/>
+      <c r="T66" s="33" t="n"/>
+      <c r="U66" s="34" t="n"/>
     </row>
     <row r="67" ht="96" customHeight="1">
       <c r="A67" s="11" t="inlineStr">
@@ -12640,12 +14157,12 @@
           <t>HYBRID</t>
         </is>
       </c>
-      <c r="G67" s="39" t="inlineStr">
+      <c r="G67" s="43" t="inlineStr">
         <is>
           <t>PROPOSED_OPTIONAL</t>
         </is>
       </c>
-      <c r="H67" s="38" t="n">
+      <c r="H67" s="42" t="n">
         <v>0.48</v>
       </c>
       <c r="I67" s="12" t="inlineStr">
@@ -12678,6 +14195,10 @@
         </is>
       </c>
       <c r="Q67" s="24" t="inlineStr"/>
+      <c r="R67" s="12" t="inlineStr"/>
+      <c r="S67" s="13" t="n"/>
+      <c r="T67" s="33" t="n"/>
+      <c r="U67" s="34" t="n"/>
     </row>
     <row r="68" ht="96" customHeight="1">
       <c r="A68" s="11" t="inlineStr">
@@ -12743,7 +14264,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q68" s="24" t="inlineStr"/>
+      <c r="Q68" s="31" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="R68" s="35" t="inlineStr">
+        <is>
+          <t>Removed 'the iRECIST response would be expected to be {expected_irecist}'. The two guideline names are retained because here they are the names of CRF fields, not a citation of authority.</t>
+        </is>
+      </c>
+      <c r="S68" s="13" t="n"/>
+      <c r="T68" s="33" t="n"/>
+      <c r="U68" s="34" t="n"/>
     </row>
     <row r="69" ht="96" customHeight="1">
       <c r="A69" s="11" t="inlineStr">
@@ -12814,6 +14347,10 @@
         </is>
       </c>
       <c r="Q69" s="24" t="inlineStr"/>
+      <c r="R69" s="12" t="inlineStr"/>
+      <c r="S69" s="13" t="n"/>
+      <c r="T69" s="33" t="n"/>
+      <c r="U69" s="34" t="n"/>
     </row>
     <row r="70" ht="96" customHeight="1">
       <c r="A70" s="11" t="inlineStr">
@@ -12880,6 +14417,10 @@
         </is>
       </c>
       <c r="Q70" s="24" t="inlineStr"/>
+      <c r="R70" s="12" t="inlineStr"/>
+      <c r="S70" s="13" t="n"/>
+      <c r="T70" s="33" t="n"/>
+      <c r="U70" s="34" t="n"/>
     </row>
     <row r="71" ht="96" customHeight="1">
       <c r="A71" s="11" t="inlineStr">
@@ -12917,7 +14458,7 @@
           <t>CONDITIONAL</t>
         </is>
       </c>
-      <c r="H71" s="33" t="n">
+      <c r="H71" s="41" t="n">
         <v>0.62</v>
       </c>
       <c r="I71" s="12" t="inlineStr"/>
@@ -12947,6 +14488,10 @@
         </is>
       </c>
       <c r="Q71" s="24" t="inlineStr"/>
+      <c r="R71" s="12" t="inlineStr"/>
+      <c r="S71" s="13" t="n"/>
+      <c r="T71" s="33" t="n"/>
+      <c r="U71" s="34" t="n"/>
     </row>
     <row r="72" ht="96" customHeight="1">
       <c r="A72" s="11" t="inlineStr">
@@ -12984,8 +14529,8 @@
           <t>CONDITIONAL</t>
         </is>
       </c>
-      <c r="H72" s="33" t="n">
-        <v>0.7</v>
+      <c r="H72" s="32" t="n">
+        <v>0.75</v>
       </c>
       <c r="I72" s="12" t="inlineStr"/>
       <c r="J72" s="12" t="inlineStr"/>
@@ -12997,7 +14542,14 @@
       <c r="L72" s="29" t="inlineStr">
         <is>
           <t>if a new systemic anticancer therapy starts before the recorded progression date
-   (or before any recorded progression): raise finding</t>
+   (or before any recorded progression):
+       raise finding
+guards:
+  - suppress therapies listed in config.permitted_concomitant_therapies
+    (bone-modifying agents, hormonal maintenance, protocol-permitted supportive care)
+  - suppress where the therapy is local rather than systemic — that is TE-XD-004
+  - suppress where the start date is within config.therapy_date_tolerance_days
+    (default 7) of a recorded progression: date-entry noise, not a real sequence error</t>
         </is>
       </c>
       <c r="M72" s="23" t="inlineStr">
@@ -13012,7 +14564,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q72" s="24" t="inlineStr"/>
+      <c r="Q72" s="31" t="inlineStr">
+        <is>
+          <t>MM</t>
+        </is>
+      </c>
+      <c r="R72" s="35" t="inlineStr">
+        <is>
+          <t>Fires on any new systemic anticancer therapy, including protocol-permitted maintenance and supportive regimens. A monitor would not query those.</t>
+        </is>
+      </c>
+      <c r="S72" s="36" t="inlineStr">
+        <is>
+          <t>if a new systemic anticancer therapy starts before the recorded progression date
+   (or before any recorded progression): raise finding</t>
+        </is>
+      </c>
+      <c r="T72" s="33" t="n"/>
+      <c r="U72" s="34" t="n"/>
     </row>
     <row r="73" ht="96" customHeight="1">
       <c r="A73" s="11" t="inlineStr">
@@ -13051,7 +14620,7 @@
         </is>
       </c>
       <c r="H73" s="32" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="I73" s="12" t="inlineStr"/>
       <c r="J73" s="12" t="inlineStr"/>
@@ -13063,7 +14632,12 @@
       <c r="L73" s="29" t="inlineStr">
         <is>
           <t>if radiotherapy, surgery or ablation is recorded at a site matching a target lesion
-   after baseline: raise finding on all subsequent assessments of that lesion</t>
+   after baseline:
+       raise ONE finding for that lesion, listing every subsequent assessment
+       in which the lesion still contributes to the sum
+guards:
+  - suppress where the lesion was already excluded from the sum after the therapy
+  - suppress where the therapy date precedes baseline (covered by TE-BL-008)</t>
         </is>
       </c>
       <c r="M73" s="23" t="inlineStr">
@@ -13078,7 +14652,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q73" s="24" t="inlineStr"/>
+      <c r="Q73" s="31" t="inlineStr">
+        <is>
+          <t>MM</t>
+        </is>
+      </c>
+      <c r="R73" s="35" t="inlineStr">
+        <is>
+          <t>One event was producing one finding per subsequent visit. A single course of radiotherapy to a target lesion in a 12-visit study raised eleven findings for one fact. Now one finding per lesion, listing the affected assessments.</t>
+        </is>
+      </c>
+      <c r="S73" s="36" t="inlineStr">
+        <is>
+          <t>if radiotherapy, surgery or ablation is recorded at a site matching a target lesion
+   after baseline: raise finding on all subsequent assessments of that lesion</t>
+        </is>
+      </c>
+      <c r="T73" s="33" t="n"/>
+      <c r="U73" s="34" t="n"/>
     </row>
     <row r="74" ht="96" customHeight="1">
       <c r="A74" s="11" t="inlineStr">
@@ -13116,8 +14707,8 @@
           <t>CONDITIONAL</t>
         </is>
       </c>
-      <c r="H74" s="33" t="n">
-        <v>0.65</v>
+      <c r="H74" s="41" t="n">
+        <v>0.7</v>
       </c>
       <c r="I74" s="12" t="inlineStr"/>
       <c r="J74" s="12" t="inlineStr"/>
@@ -13129,7 +14720,14 @@
       <c r="L74" s="29" t="inlineStr">
         <is>
           <t>if an AE term maps to disease progression / malignant neoplasm progression
-   and no PD assessment exists within config.ae_pd_window_days (default 60): raise finding</t>
+   and no PD assessment exists within config.ae_pd_window_days (default 60):
+       raise finding
+guards:
+  - suppress where the subject died, or discontinued for clinical deterioration,
+    before the next scheduled assessment was due
+  - suppress where an assessment exists in the window but is NOT EVALUABLE with
+    a recorded reason
+  - audience STUDY_TEAM where suppressed: the endpoint still needs a decision</t>
         </is>
       </c>
       <c r="M74" s="23" t="inlineStr">
@@ -13144,7 +14742,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q74" s="24" t="inlineStr"/>
+      <c r="Q74" s="31" t="inlineStr">
+        <is>
+          <t>MM</t>
+        </is>
+      </c>
+      <c r="R74" s="35" t="inlineStr">
+        <is>
+          <t>An adverse event of disease progression with no PD assessment is often correct: the subject deteriorated and no further imaging was possible. Querying the site for a scan that could not be done is exactly the kind of query that costs credibility.</t>
+        </is>
+      </c>
+      <c r="S74" s="36" t="inlineStr">
+        <is>
+          <t>if an AE term maps to disease progression / malignant neoplasm progression
+   and no PD assessment exists within config.ae_pd_window_days (default 60): raise finding</t>
+        </is>
+      </c>
+      <c r="T74" s="33" t="n"/>
+      <c r="U74" s="34" t="n"/>
     </row>
     <row r="75" ht="96" customHeight="1">
       <c r="A75" s="11" t="inlineStr">
@@ -13167,7 +14782,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E75" s="37" t="inlineStr">
+      <c r="E75" s="40" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -13210,6 +14825,10 @@
         </is>
       </c>
       <c r="Q75" s="24" t="inlineStr"/>
+      <c r="R75" s="12" t="inlineStr"/>
+      <c r="S75" s="13" t="n"/>
+      <c r="T75" s="33" t="n"/>
+      <c r="U75" s="34" t="n"/>
     </row>
     <row r="76" ht="96" customHeight="1">
       <c r="A76" s="11" t="inlineStr">
@@ -13232,7 +14851,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E76" s="36" t="inlineStr">
+      <c r="E76" s="39" t="inlineStr">
         <is>
           <t>MINOR</t>
         </is>
@@ -13247,7 +14866,7 @@
           <t>CONDITIONAL</t>
         </is>
       </c>
-      <c r="H76" s="33" t="n">
+      <c r="H76" s="41" t="n">
         <v>0.6</v>
       </c>
       <c r="I76" s="12" t="inlineStr"/>
@@ -13276,21 +14895,21 @@
           <t>Provide the rationale insisting the proposed threshold. What material or information is referred to make this validation rule.</t>
         </is>
       </c>
-      <c r="O76" s="34" t="inlineStr">
+      <c r="O76" s="37" t="inlineStr">
         <is>
           <t>RATIONALE ADDED. The threshold is the laboratory's own upper limit of normal, not a value the agent chooses.</t>
         </is>
       </c>
-      <c r="P76" s="35" t="inlineStr">
-        <is>
-          <t>Accept</t>
-        </is>
-      </c>
-      <c r="Q76" s="24" t="inlineStr">
-        <is>
-          <t>Daniel</t>
-        </is>
-      </c>
+      <c r="P76" s="38" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="Q76" s="24" t="inlineStr"/>
+      <c r="R76" s="12" t="inlineStr"/>
+      <c r="S76" s="13" t="n"/>
+      <c r="T76" s="33" t="n"/>
+      <c r="U76" s="34" t="n"/>
     </row>
     <row r="77" ht="96" customHeight="1">
       <c r="A77" s="11" t="inlineStr">
@@ -13313,7 +14932,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E77" s="36" t="inlineStr">
+      <c r="E77" s="39" t="inlineStr">
         <is>
           <t>MINOR</t>
         </is>
@@ -13328,7 +14947,7 @@
           <t>CONDITIONAL</t>
         </is>
       </c>
-      <c r="H77" s="33" t="n">
+      <c r="H77" s="41" t="n">
         <v>0.58</v>
       </c>
       <c r="I77" s="12" t="inlineStr"/>
@@ -13356,6 +14975,10 @@
         </is>
       </c>
       <c r="Q77" s="24" t="inlineStr"/>
+      <c r="R77" s="12" t="inlineStr"/>
+      <c r="S77" s="13" t="n"/>
+      <c r="T77" s="33" t="n"/>
+      <c r="U77" s="34" t="n"/>
     </row>
     <row r="78" ht="96" customHeight="1">
       <c r="A78" s="11" t="inlineStr">
@@ -13378,7 +15001,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E78" s="36" t="inlineStr">
+      <c r="E78" s="39" t="inlineStr">
         <is>
           <t>MINOR</t>
         </is>
@@ -13393,7 +15016,7 @@
           <t>CONDITIONAL</t>
         </is>
       </c>
-      <c r="H78" s="33" t="n">
+      <c r="H78" s="41" t="n">
         <v>0.62</v>
       </c>
       <c r="I78" s="12" t="inlineStr"/>
@@ -13422,6 +15045,10 @@
         </is>
       </c>
       <c r="Q78" s="24" t="inlineStr"/>
+      <c r="R78" s="12" t="inlineStr"/>
+      <c r="S78" s="13" t="n"/>
+      <c r="T78" s="33" t="n"/>
+      <c r="U78" s="34" t="n"/>
     </row>
     <row r="79" ht="96" customHeight="1">
       <c r="A79" s="11" t="inlineStr">
@@ -13483,6 +15110,10 @@
         </is>
       </c>
       <c r="Q79" s="24" t="inlineStr"/>
+      <c r="R79" s="12" t="inlineStr"/>
+      <c r="S79" s="13" t="n"/>
+      <c r="T79" s="33" t="n"/>
+      <c r="U79" s="34" t="n"/>
     </row>
     <row r="80" ht="96" customHeight="1">
       <c r="A80" s="11" t="inlineStr">
@@ -13505,7 +15136,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E80" s="40" t="inlineStr">
+      <c r="E80" s="44" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -13520,7 +15151,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="H80" s="33" t="n">
+      <c r="H80" s="41" t="n">
         <v>0.55</v>
       </c>
       <c r="I80" s="12" t="inlineStr"/>
@@ -13545,6 +15176,10 @@
         </is>
       </c>
       <c r="Q80" s="24" t="inlineStr"/>
+      <c r="R80" s="12" t="inlineStr"/>
+      <c r="S80" s="13" t="n"/>
+      <c r="T80" s="33" t="n"/>
+      <c r="U80" s="34" t="n"/>
     </row>
     <row r="81" ht="96" customHeight="1">
       <c r="A81" s="11" t="inlineStr">
@@ -13567,7 +15202,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E81" s="36" t="inlineStr">
+      <c r="E81" s="39" t="inlineStr">
         <is>
           <t>MINOR</t>
         </is>
@@ -13582,7 +15217,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="H81" s="33" t="n">
+      <c r="H81" s="41" t="n">
         <v>0.7</v>
       </c>
       <c r="I81" s="12" t="inlineStr"/>
@@ -13608,6 +15243,10 @@
         </is>
       </c>
       <c r="Q81" s="24" t="inlineStr"/>
+      <c r="R81" s="12" t="inlineStr"/>
+      <c r="S81" s="13" t="n"/>
+      <c r="T81" s="33" t="n"/>
+      <c r="U81" s="34" t="n"/>
     </row>
     <row r="82" ht="96" customHeight="1">
       <c r="A82" s="11" t="inlineStr">
@@ -13630,7 +15269,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E82" s="40" t="inlineStr">
+      <c r="E82" s="44" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -13669,6 +15308,10 @@
         </is>
       </c>
       <c r="Q82" s="24" t="inlineStr"/>
+      <c r="R82" s="12" t="inlineStr"/>
+      <c r="S82" s="13" t="n"/>
+      <c r="T82" s="33" t="n"/>
+      <c r="U82" s="34" t="n"/>
     </row>
     <row r="83" ht="96" customHeight="1">
       <c r="A83" s="11" t="inlineStr">
@@ -13745,6 +15388,10 @@
         </is>
       </c>
       <c r="Q83" s="24" t="inlineStr"/>
+      <c r="R83" s="12" t="inlineStr"/>
+      <c r="S83" s="13" t="n"/>
+      <c r="T83" s="33" t="n"/>
+      <c r="U83" s="34" t="n"/>
     </row>
     <row r="84" ht="96" customHeight="1">
       <c r="A84" s="11" t="inlineStr">
@@ -13807,6 +15454,10 @@
         </is>
       </c>
       <c r="Q84" s="24" t="inlineStr"/>
+      <c r="R84" s="12" t="inlineStr"/>
+      <c r="S84" s="13" t="n"/>
+      <c r="T84" s="33" t="n"/>
+      <c r="U84" s="34" t="n"/>
     </row>
     <row r="85" ht="96" customHeight="1">
       <c r="A85" s="11" t="inlineStr">
@@ -13829,7 +15480,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E85" s="36" t="inlineStr">
+      <c r="E85" s="39" t="inlineStr">
         <is>
           <t>MINOR</t>
         </is>
@@ -13869,6 +15520,10 @@
         </is>
       </c>
       <c r="Q85" s="24" t="inlineStr"/>
+      <c r="R85" s="12" t="inlineStr"/>
+      <c r="S85" s="13" t="n"/>
+      <c r="T85" s="33" t="n"/>
+      <c r="U85" s="34" t="n"/>
     </row>
     <row r="86" ht="96" customHeight="1">
       <c r="A86" s="11" t="inlineStr">
@@ -13891,7 +15546,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E86" s="40" t="inlineStr">
+      <c r="E86" s="44" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -13906,7 +15561,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="H86" s="33" t="n">
+      <c r="H86" s="41" t="n">
         <v>0.55</v>
       </c>
       <c r="I86" s="12" t="inlineStr"/>
@@ -13933,6 +15588,10 @@
         </is>
       </c>
       <c r="Q86" s="24" t="inlineStr"/>
+      <c r="R86" s="12" t="inlineStr"/>
+      <c r="S86" s="13" t="n"/>
+      <c r="T86" s="33" t="n"/>
+      <c r="U86" s="34" t="n"/>
     </row>
     <row r="87" ht="96" customHeight="1">
       <c r="A87" s="11" t="inlineStr">
@@ -13955,7 +15614,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E87" s="40" t="inlineStr">
+      <c r="E87" s="44" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -13970,7 +15629,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="H87" s="33" t="n">
+      <c r="H87" s="41" t="n">
         <v>0.72</v>
       </c>
       <c r="I87" s="12" t="inlineStr"/>
@@ -13995,6 +15654,10 @@
         </is>
       </c>
       <c r="Q87" s="24" t="inlineStr"/>
+      <c r="R87" s="12" t="inlineStr"/>
+      <c r="S87" s="13" t="n"/>
+      <c r="T87" s="33" t="n"/>
+      <c r="U87" s="34" t="n"/>
     </row>
     <row r="88" ht="96" customHeight="1">
       <c r="A88" s="11" t="inlineStr">
@@ -14027,12 +15690,12 @@
           <t>HYBRID</t>
         </is>
       </c>
-      <c r="G88" s="39" t="inlineStr">
+      <c r="G88" s="43" t="inlineStr">
         <is>
           <t>PROPOSED_OPTIONAL</t>
         </is>
       </c>
-      <c r="H88" s="33" t="n">
+      <c r="H88" s="41" t="n">
         <v>0.55</v>
       </c>
       <c r="I88" s="12" t="inlineStr">
@@ -14082,13 +15745,22 @@
         </is>
       </c>
       <c r="Q88" s="24" t="inlineStr"/>
+      <c r="R88" s="12" t="inlineStr"/>
+      <c r="S88" s="13" t="n"/>
+      <c r="T88" s="33" t="n"/>
+      <c r="U88" s="34" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:Q88"/>
+  <autoFilter ref="A3:U88"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:R2"/>
-    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="A2:U2"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="T4:T88" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Accept,Amend,Reject,Discuss"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14099,19 +15771,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J88"/>
+  <dimension ref="A1:K88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
-    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="58" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
-    <col width="52" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="58" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -14124,7 +15797,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>The five elements presented for every finding. The Suggested query column is the text that reaches a site — review it as sponsor correspondence, not as documentation.</t>
+          <t>All 85 accepted 2026-08-21. 19 query texts were then rewritten at the reviewer-lens pass, following the house rules on Query_Style; the previous wording is kept beside each so the change is visible. Only the amber rows need a decision.</t>
         </is>
       </c>
     </row>
@@ -14166,17 +15839,22 @@
       </c>
       <c r="H3" s="10" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="I3" s="10" t="inlineStr">
         <is>
+          <t>Query before R3</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="inlineStr">
+        <is>
+          <t>R3 decision</t>
+        </is>
+      </c>
+      <c r="K3" s="10" t="inlineStr">
+        <is>
           <t>Reviewer</t>
-        </is>
-      </c>
-      <c r="J3" s="10" t="inlineStr">
-        <is>
-          <t>Comment</t>
         </is>
       </c>
     </row>
@@ -14206,7 +15884,7 @@
           <t>Measurements can only be interpreted against an identified lesion with a category (target/non-target/new) and location. Without it, the lesion cannot enter the sum of diameters, and the derived response may be wrong.</t>
         </is>
       </c>
-      <c r="F4" s="51" t="inlineStr">
+      <c r="F4" s="56" t="inlineStr">
         <is>
           <t>A measurement is recorded for lesion {lesion_id} at {visit} but this lesion is not present on the tumor identification form. Please confirm the lesion identification and complete the missing record, or correct the lesion number on the measurement.</t>
         </is>
@@ -14216,9 +15894,14 @@
           <t>Most often a lesion numbering typo, or a new lesion measured before it was formally recorded as new. Check whether the number matches an existing lesion at another site of disease.</t>
         </is>
       </c>
-      <c r="H4" s="52" t="n"/>
-      <c r="I4" s="52" t="n"/>
-      <c r="J4" s="53" t="n"/>
+      <c r="H4" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="inlineStr"/>
+      <c r="J4" s="33" t="n"/>
+      <c r="K4" s="34" t="n"/>
     </row>
     <row r="5" ht="108" customHeight="1">
       <c r="A5" s="25" t="inlineStr">
@@ -14246,7 +15929,7 @@
           <t>If the same lesion is recorded twice, it is counted twice in the sum of diameters, inflating tumor burden and distorting percent change and the nadir.</t>
         </is>
       </c>
-      <c r="F5" s="51" t="inlineStr">
+      <c r="F5" s="56" t="inlineStr">
         <is>
           <t>Lesions {lesion_id_a} and {lesion_id_b} appear to describe the same lesion at {organ}. Please confirm whether these are two distinct lesions; if not, please remove the duplicate and update the affected assessments.</t>
         </is>
@@ -14256,12 +15939,17 @@
           <t>Compare the baseline sizes and the size trajectory: identical or near-identical values across visits strongly suggests duplication.</t>
         </is>
       </c>
-      <c r="H5" s="52" t="n"/>
-      <c r="I5" s="52" t="n"/>
-      <c r="J5" s="53" t="n"/>
+      <c r="H5" s="25" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I5" s="22" t="inlineStr"/>
+      <c r="J5" s="33" t="n"/>
+      <c r="K5" s="34" t="n"/>
     </row>
     <row r="6" ht="108" customHeight="1">
-      <c r="A6" s="23" t="inlineStr">
+      <c r="A6" s="57" t="inlineStr">
         <is>
           <t>TE-ST-003</t>
         </is>
@@ -14286,19 +15974,28 @@
           <t>RECIST 1.1 requires the short axis for nodal lesions, at baseline and at every follow-up. Using the longest diameter overstates the nodal contribution to the sum and can mask a response or create a false progression.</t>
         </is>
       </c>
-      <c r="F6" s="51" t="inlineStr">
+      <c r="F6" s="35" t="inlineStr">
+        <is>
+          <t>Lesion {lesion_id} is recorded as a lymph node. Please confirm, against the source imaging report, which axis the measurement recorded at {visit} represents and whether the value is correct.</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>Nodal lesions were only formally distinguished from RECIST 1.0 onwards in version 1.1; sites experienced with older studies frequently record the long axis out of habit.</t>
+        </is>
+      </c>
+      <c r="H6" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I6" s="58" t="inlineStr">
         <is>
           <t>Lesion {lesion_id} is a lymph node. Please confirm the measurement recorded at {visit} is the short axis; if the longest diameter was recorded, please correct it.</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>Nodal lesions were only formally distinguished from RECIST 1.0 onwards in version 1.1; sites experienced with older studies frequently record the long axis out of habit.</t>
-        </is>
-      </c>
-      <c r="H6" s="52" t="n"/>
-      <c r="I6" s="52" t="n"/>
-      <c r="J6" s="53" t="n"/>
+      <c r="J6" s="33" t="n"/>
+      <c r="K6" s="34" t="n"/>
     </row>
     <row r="7" ht="108" customHeight="1">
       <c r="A7" s="25" t="inlineStr">
@@ -14326,7 +16023,7 @@
           <t>A centimetre value entered in a millimetre field understates a lesion tenfold, which can convert a progression into an apparent response.</t>
         </is>
       </c>
-      <c r="F7" s="51" t="inlineStr">
+      <c r="F7" s="56" t="inlineStr">
         <is>
           <t>Please confirm the unit of the measurement for lesion {lesion_id} at {visit} ({original_value} {original_unit}); the value appears inconsistent with the other measurements recorded for this subject.</t>
         </is>
@@ -14336,9 +16033,14 @@
           <t>Check the trajectory of the same lesion across visits — a tenfold step between adjacent visits is diagnostic of a unit error.</t>
         </is>
       </c>
-      <c r="H7" s="52" t="n"/>
-      <c r="I7" s="52" t="n"/>
-      <c r="J7" s="53" t="n"/>
+      <c r="H7" s="25" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I7" s="22" t="inlineStr"/>
+      <c r="J7" s="33" t="n"/>
+      <c r="K7" s="34" t="n"/>
     </row>
     <row r="8" ht="108" customHeight="1">
       <c r="A8" s="23" t="inlineStr">
@@ -14366,7 +16068,7 @@
           <t>Nadir, progression dating and best overall response all depend on chronological order. An out-of-order date can move the nadir and change the progression determination.</t>
         </is>
       </c>
-      <c r="F8" s="51" t="inlineStr">
+      <c r="F8" s="56" t="inlineStr">
         <is>
           <t>The assessment dates for {visit_a} and {visit_b} appear inconsistent with the visit sequence. Please verify the assessment dates.</t>
         </is>
@@ -14376,9 +16078,14 @@
           <t>Confirm against the scan dates in the imaging report rather than the visit date, which may reflect the clinic visit rather than the scan.</t>
         </is>
       </c>
-      <c r="H8" s="52" t="n"/>
-      <c r="I8" s="52" t="n"/>
-      <c r="J8" s="53" t="n"/>
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I8" s="12" t="inlineStr"/>
+      <c r="J8" s="33" t="n"/>
+      <c r="K8" s="34" t="n"/>
     </row>
     <row r="9" ht="108" customHeight="1">
       <c r="A9" s="25" t="inlineStr">
@@ -14406,7 +16113,7 @@
           <t>RECIST {guideline_version} permits a maximum of {max_total} target lesions in total. Additional lesions must be recorded as non-target. Including extra lesions in the sum changes the denominator for percent change and can alter the response category at every subsequent timepoint.</t>
         </is>
       </c>
-      <c r="F9" s="51" t="inlineStr">
+      <c r="F9" s="56" t="inlineStr">
         <is>
           <t>{n} target lesions are recorded at baseline for this subject, exceeding the maximum of {max_total} specified in the protocol. Please review the target lesion selection and re-classify the excess lesions as non-target, updating all affected assessments.</t>
         </is>
@@ -14416,9 +16123,14 @@
           <t>Re-selection changes the baseline sum and therefore every subsequent percent change; expect all downstream responses to require re-derivation. Prioritise this issue before reviewing any response mismatch for this subject.</t>
         </is>
       </c>
-      <c r="H9" s="52" t="n"/>
-      <c r="I9" s="52" t="n"/>
-      <c r="J9" s="53" t="n"/>
+      <c r="H9" s="25" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I9" s="22" t="inlineStr"/>
+      <c r="J9" s="33" t="n"/>
+      <c r="K9" s="34" t="n"/>
     </row>
     <row r="10" ht="108" customHeight="1">
       <c r="A10" s="23" t="inlineStr">
@@ -14446,7 +16158,7 @@
           <t>RECIST {guideline_version} limits target lesions to {max_per_organ} per organ so that the sum represents the overall disease burden rather than one organ. Over-representation of one organ biases the response assessment.</t>
         </is>
       </c>
-      <c r="F10" s="51" t="inlineStr">
+      <c r="F10" s="56" t="inlineStr">
         <is>
           <t>{n} target lesions are recorded in {organ}, exceeding the per-organ maximum of {max_per_organ}. Please re-classify the excess lesions as non-target and update the affected assessments.</t>
         </is>
@@ -14456,9 +16168,14 @@
           <t>Lymph nodes in different nodal stations are commonly all coded to a single "lymph node" organ; confirm whether the sponsor's convention treats nodal stations as separate organs before raising.</t>
         </is>
       </c>
-      <c r="H10" s="52" t="n"/>
-      <c r="I10" s="52" t="n"/>
-      <c r="J10" s="53" t="n"/>
+      <c r="H10" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I10" s="12" t="inlineStr"/>
+      <c r="J10" s="33" t="n"/>
+      <c r="K10" s="34" t="n"/>
     </row>
     <row r="11" ht="108" customHeight="1">
       <c r="A11" s="25" t="inlineStr">
@@ -14486,7 +16203,7 @@
           <t>RECIST {guideline_version} requires a non-nodal lesion to be at least {threshold} mm by {method} to be measurable and therefore eligible as a target lesion. Sub-threshold lesions are subject to unreliable measurement, and including one makes the whole sum unreliable.</t>
         </is>
       </c>
-      <c r="F11" s="51" t="inlineStr">
+      <c r="F11" s="56" t="inlineStr">
         <is>
           <t>Target lesion {lesion_id} measures {value} mm at baseline, below the {threshold} mm threshold for measurability by {method}. Please confirm the measurement, or re-classify this lesion as non-target and update the affected assessments.</t>
         </is>
@@ -14496,12 +16213,17 @@
           <t>Check the imaging slice thickness where available: a lesion must be at least twice the slice thickness to be measurable, so a 10 mm lesion on 8 mm slices is not measurable even though it meets the nominal threshold.</t>
         </is>
       </c>
-      <c r="H11" s="52" t="n"/>
-      <c r="I11" s="52" t="n"/>
-      <c r="J11" s="53" t="n"/>
+      <c r="H11" s="25" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I11" s="22" t="inlineStr"/>
+      <c r="J11" s="33" t="n"/>
+      <c r="K11" s="34" t="n"/>
     </row>
     <row r="12" ht="108" customHeight="1">
-      <c r="A12" s="23" t="inlineStr">
+      <c r="A12" s="57" t="inlineStr">
         <is>
           <t>TE-BL-004</t>
         </is>
@@ -14526,22 +16248,31 @@
           <t>RECIST 1.1 requires a short axis of at least 15 mm for a node to be measurable and selectable as a target lesion. Nodes with a short axis of 10 to under 15 mm are pathological but non-measurable and should be recorded as non-target; nodes under 10 mm are non-pathological and should not be recorded at all.</t>
         </is>
       </c>
-      <c r="F12" s="51" t="inlineStr">
+      <c r="F12" s="35" t="inlineStr">
+        <is>
+          <t>Nodal target lesion {lesion_id} has a baseline short axis of {value} mm recorded at {visit}. Please confirm against the source imaging report whether this measurement is correct, and whether this node was intended to be recorded as a target lesion.</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>This is one of the most frequent baseline errors. Verify that the recorded value is a short axis and not a longest diameter before concluding the selection was wrong.</t>
+        </is>
+      </c>
+      <c r="H12" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I12" s="58" t="inlineStr">
         <is>
           <t>Nodal target lesion {lesion_id} has a baseline short axis of {value} mm. Please confirm the measurement; a node with short axis below 15 mm should be recorded as a non-target lesion (10 to &lt;15 mm) or not recorded (&lt;10 mm).</t>
         </is>
       </c>
-      <c r="G12" s="12" t="inlineStr">
-        <is>
-          <t>This is one of the most frequent baseline errors. Verify that the recorded value is a short axis and not a longest diameter before concluding the selection was wrong.</t>
-        </is>
-      </c>
-      <c r="H12" s="52" t="n"/>
-      <c r="I12" s="52" t="n"/>
-      <c r="J12" s="53" t="n"/>
+      <c r="J12" s="33" t="n"/>
+      <c r="K12" s="34" t="n"/>
     </row>
     <row r="13" ht="108" customHeight="1">
-      <c r="A13" s="25" t="inlineStr">
+      <c r="A13" s="57" t="inlineStr">
         <is>
           <t>TE-BL-005</t>
         </is>
@@ -14566,19 +16297,28 @@
           <t>Under RECIST 1.1 a node with a short axis below 10 mm is considered non-pathological and is not recorded or followed. Recording it adds normal tissue to the disease assessment and can prevent a complete response from being assigned.</t>
         </is>
       </c>
-      <c r="F13" s="51" t="inlineStr">
+      <c r="F13" s="35" t="inlineStr">
+        <is>
+          <t>Node {lesion_id} has a baseline short axis of {value} mm recorded at {visit}. Please confirm whether this node was intended to be recorded as disease for this subject, and correct the record if it was not.</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>Where a node is clinically relevant despite being below threshold (for example biopsy-proven involvement), the site should document the rationale; consider accepting with a comment rather than a data change.</t>
+        </is>
+      </c>
+      <c r="H13" s="25" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I13" s="59" t="inlineStr">
         <is>
           <t>Node {lesion_id} has a baseline short axis of {value} mm, below the 10 mm pathological threshold. Please confirm whether this node should be recorded as disease; if not, please remove it from the assessment.</t>
         </is>
       </c>
-      <c r="G13" s="22" t="inlineStr">
-        <is>
-          <t>Where a node is clinically relevant despite being below threshold (for example biopsy-proven involvement), the site should document the rationale; consider accepting with a comment rather than a data change.</t>
-        </is>
-      </c>
-      <c r="H13" s="52" t="n"/>
-      <c r="I13" s="52" t="n"/>
-      <c r="J13" s="53" t="n"/>
+      <c r="J13" s="33" t="n"/>
+      <c r="K13" s="34" t="n"/>
     </row>
     <row r="14" ht="108" customHeight="1">
       <c r="A14" s="23" t="inlineStr">
@@ -14606,7 +16346,7 @@
           <t>RECIST 1.1 requires a lesion to be at least twice the slice thickness to be measurable; on {slice_thickness} mm slices the minimum measurable lesion is {min_size} mm. Below that, apparent size changes may be partial-volume artefacts rather than real change.</t>
         </is>
       </c>
-      <c r="F14" s="51" t="inlineStr">
+      <c r="F14" s="56" t="inlineStr">
         <is>
           <t>Target lesion {lesion_id} measures {value} mm at baseline on images with {slice_thickness} mm slice thickness. Please confirm the lesion is measurable per the imaging manual, or re-classify it as non-target.</t>
         </is>
@@ -14616,12 +16356,17 @@
           <t>Slice thickness often varies between the baseline and follow-up scans; if so, the comparison itself is compromised and merits a note to the imaging vendor.</t>
         </is>
       </c>
-      <c r="H14" s="52" t="n"/>
-      <c r="I14" s="52" t="n"/>
-      <c r="J14" s="53" t="n"/>
+      <c r="H14" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I14" s="12" t="inlineStr"/>
+      <c r="J14" s="33" t="n"/>
+      <c r="K14" s="34" t="n"/>
     </row>
     <row r="15" ht="108" customHeight="1">
-      <c r="A15" s="25" t="inlineStr">
+      <c r="A15" s="57" t="inlineStr">
         <is>
           <t>TE-BL-007</t>
         </is>
@@ -14646,22 +16391,31 @@
           <t>RECIST classifies {non_measurable_category} as non-measurable disease: it cannot be reproducibly measured in one dimension. Such disease must be recorded as non-target and assessed qualitatively. A non-measurable lesion inside the target sum makes the sum, and every percent change derived from it, unreliable.</t>
         </is>
       </c>
-      <c r="F15" s="51" t="inlineStr">
+      <c r="F15" s="35" t="inlineStr">
+        <is>
+          <t>Target lesion {lesion_id} is described as '{location_detail}'. Please confirm the lesion type, and whether this finding can be measured reproducibly in one dimension on the source imaging. If the description is incomplete, please add the detail from the imaging report.</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>Blastic bone lesions are non-measurable, but a lytic or mixed lytic-blastic lesion with an identifiable soft tissue component can be measurable on CT/MRI. Cystic metastases can be measurable, but where non-cystic lesions are available they are preferred as targets.</t>
+        </is>
+      </c>
+      <c r="H15" s="25" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I15" s="59" t="inlineStr">
         <is>
           <t>Target lesion {lesion_id} is described as "{location_detail}". This appears to represent non-measurable disease under RECIST. Please confirm the lesion selection and, if appropriate, re-classify it as a non-target lesion.</t>
         </is>
       </c>
-      <c r="G15" s="22" t="inlineStr">
-        <is>
-          <t>Blastic bone lesions are non-measurable, but a lytic or mixed lytic-blastic lesion with an identifiable soft tissue component can be measurable on CT/MRI. Cystic metastases can be measurable, but where non-cystic lesions are available they are preferred as targets.</t>
-        </is>
-      </c>
-      <c r="H15" s="52" t="n"/>
-      <c r="I15" s="52" t="n"/>
-      <c r="J15" s="53" t="n"/>
+      <c r="J15" s="33" t="n"/>
+      <c r="K15" s="34" t="n"/>
     </row>
     <row r="16" ht="108" customHeight="1">
-      <c r="A16" s="23" t="inlineStr">
+      <c r="A16" s="57" t="inlineStr">
         <is>
           <t>TE-BL-008</t>
         </is>
@@ -14686,19 +16440,28 @@
           <t>RECIST treats lesions in a previously irradiated area, or subjected to other locoregional therapy, as non-measurable unless progression of that lesion has been demonstrated since the treatment. Post-radiation change can mimic both response and progression.</t>
         </is>
       </c>
-      <c r="F16" s="51" t="inlineStr">
+      <c r="F16" s="35" t="inlineStr">
+        <is>
+          <t>Target lesion {lesion_id} is recorded within a prior radiotherapy field. Please confirm whether progression of this specific lesion has been documented since that radiotherapy, and provide the date and source document if so.</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>Also relevant for lesions treated with ablation, embolisation or surgery during the study — see TE-XD-004 for on-study local therapy.</t>
+        </is>
+      </c>
+      <c r="H16" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I16" s="58" t="inlineStr">
         <is>
           <t>Target lesion {lesion_id} is located within a prior radiotherapy field. Please confirm whether progression of this lesion has been documented since radiotherapy; if not, the lesion should be recorded as non-target.</t>
         </is>
       </c>
-      <c r="G16" s="12" t="inlineStr">
-        <is>
-          <t>Also relevant for lesions treated with ablation, embolisation or surgery during the study — see TE-XD-004 for on-study local therapy.</t>
-        </is>
-      </c>
-      <c r="H16" s="52" t="n"/>
-      <c r="I16" s="52" t="n"/>
-      <c r="J16" s="53" t="n"/>
+      <c r="J16" s="33" t="n"/>
+      <c r="K16" s="34" t="n"/>
     </row>
     <row r="17" ht="108" customHeight="1">
       <c r="A17" s="25" t="inlineStr">
@@ -14726,7 +16489,7 @@
           <t>The measurable-disease determination drives the response algorithm: subjects without measurable disease can only be assigned CR, Non-CR/Non-PD, PD or NE, never PR or SD. An inconsistency here produces a systematically wrong response for every timepoint, and may also affect eligibility.</t>
         </is>
       </c>
-      <c r="F17" s="51" t="inlineStr">
+      <c r="F17" s="56" t="inlineStr">
         <is>
           <t>Measurable disease at baseline is recorded as {flag} while {n} target lesions are entered. Please confirm the baseline disease status and correct the inconsistent record.</t>
         </is>
@@ -14736,9 +16499,14 @@
           <t>Check eligibility criteria: if the protocol requires measurable disease, this may also be an eligibility deviation requiring separate escalation.</t>
         </is>
       </c>
-      <c r="H17" s="52" t="n"/>
-      <c r="I17" s="52" t="n"/>
-      <c r="J17" s="53" t="n"/>
+      <c r="H17" s="25" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I17" s="22" t="inlineStr"/>
+      <c r="J17" s="33" t="n"/>
+      <c r="K17" s="34" t="n"/>
     </row>
     <row r="18" ht="108" customHeight="1">
       <c r="A18" s="23" t="inlineStr">
@@ -14766,7 +16534,7 @@
           <t>A baseline older than the protocol window may no longer represent the disease burden at the start of treatment, which biases every subsequent percent change. A baseline dated after first dose is not a baseline at all and would understate treatment effect.</t>
         </is>
       </c>
-      <c r="F18" s="51" t="inlineStr">
+      <c r="F18" s="56" t="inlineStr">
         <is>
           <t>The baseline tumor assessment ({baseline_date}) falls {gap} days before first dose ({first_dose_date}), outside the protocol window of {window} days. Please confirm the assessment date and whether a protocol deviation has been recorded.</t>
         </is>
@@ -14776,9 +16544,14 @@
           <t>Distinguish the scan date from the assessment or read date; the protocol window normally applies to the scan.</t>
         </is>
       </c>
-      <c r="H18" s="52" t="n"/>
-      <c r="I18" s="52" t="n"/>
-      <c r="J18" s="53" t="n"/>
+      <c r="H18" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I18" s="12" t="inlineStr"/>
+      <c r="J18" s="33" t="n"/>
+      <c r="K18" s="34" t="n"/>
     </row>
     <row r="19" ht="108" customHeight="1">
       <c r="A19" s="25" t="inlineStr">
@@ -14806,7 +16579,7 @@
           <t>The baseline sum is the reference for every partial response determination. An error of {difference} mm shifts the 30% response threshold and can change the response category at multiple timepoints. Recorded lesions: {lesion_breakdown}.</t>
         </is>
       </c>
-      <c r="F19" s="51" t="inlineStr">
+      <c r="F19" s="56" t="inlineStr">
         <is>
           <t>The baseline sum of diameters ({reported} mm) does not equal the sum of the recorded target lesion measurements ({derived} mm). Please verify the individual measurements and the sum.</t>
         </is>
@@ -14816,9 +16589,14 @@
           <t>Check first whether a nodal target was included using its longest diameter, and whether all target lesions have a baseline measurement.</t>
         </is>
       </c>
-      <c r="H19" s="52" t="n"/>
-      <c r="I19" s="52" t="n"/>
-      <c r="J19" s="53" t="n"/>
+      <c r="H19" s="25" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I19" s="22" t="inlineStr"/>
+      <c r="J19" s="33" t="n"/>
+      <c r="K19" s="34" t="n"/>
     </row>
     <row r="20" ht="108" customHeight="1">
       <c r="A20" s="23" t="inlineStr">
@@ -14846,7 +16624,7 @@
           <t>RECIST directs that target lesions be selected on the basis of size, choosing the largest lesions that are reproducibly measurable, while remaining representative of all involved organs. Selecting smaller lesions as targets while larger measurable lesions are left as non-target reduces the sensitivity of the response assessment.</t>
         </is>
       </c>
-      <c r="F20" s="51" t="inlineStr">
+      <c r="F20" s="56" t="inlineStr">
         <is>
           <t>Non-target lesion {nt_lesion_id} ({nt_value} mm) is larger than target lesion {t_lesion_id} ({t_value} mm). Please confirm the target lesion selection rationale, for example poor reproducibility of the larger lesion.</t>
         </is>
@@ -14856,9 +16634,14 @@
           <t>Reproducibility legitimately overrides size — a large but ill-defined or confluent mass is a poor target. Expect a proportion of these to be correctly explained rather than corrected.</t>
         </is>
       </c>
-      <c r="H20" s="52" t="n"/>
-      <c r="I20" s="52" t="n"/>
-      <c r="J20" s="53" t="n"/>
+      <c r="H20" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I20" s="12" t="inlineStr"/>
+      <c r="J20" s="33" t="n"/>
+      <c r="K20" s="34" t="n"/>
     </row>
     <row r="21" ht="108" customHeight="1">
       <c r="A21" s="25" t="inlineStr">
@@ -14886,7 +16669,7 @@
           <t>Without a baseline value the lesion cannot contribute to the baseline sum, so the reference for percent change is understated and partial response may be reported prematurely.</t>
         </is>
       </c>
-      <c r="F21" s="51" t="inlineStr">
+      <c r="F21" s="56" t="inlineStr">
         <is>
           <t>Target lesion {lesion_id} has no baseline measurement. Please enter the baseline measurement, or re-classify the lesion if it was not measurable at baseline.</t>
         </is>
@@ -14896,9 +16679,14 @@
           <t>A target lesion that was not evaluable at baseline should not have been selected as a target; check whether re-selection is required.</t>
         </is>
       </c>
-      <c r="H21" s="52" t="n"/>
-      <c r="I21" s="52" t="n"/>
-      <c r="J21" s="53" t="n"/>
+      <c r="H21" s="25" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I21" s="22" t="inlineStr"/>
+      <c r="J21" s="33" t="n"/>
+      <c r="K21" s="34" t="n"/>
     </row>
     <row r="22" ht="108" customHeight="1">
       <c r="A22" s="23" t="inlineStr">
@@ -14926,7 +16714,7 @@
           <t>RECIST requires the same method of assessment and the same technique at baseline and during follow-up. Different modalities measure different things — a change of modality can produce an apparent size change of the order of the response thresholds without any true biological change.</t>
         </is>
       </c>
-      <c r="F22" s="51" t="inlineStr">
+      <c r="F22" s="56" t="inlineStr">
         <is>
           <t>Lesion {lesion_id} was assessed by {method_a} at baseline and {method_b} at {visit_b}. Please confirm the modality used and whether the change was clinically necessary.</t>
         </is>
@@ -14936,9 +16724,14 @@
           <t>Where a modality change was unavoidable, the affected timepoint may need to be treated as not evaluable for that lesion rather than measured.</t>
         </is>
       </c>
-      <c r="H22" s="52" t="n"/>
-      <c r="I22" s="52" t="n"/>
-      <c r="J22" s="53" t="n"/>
+      <c r="H22" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I22" s="12" t="inlineStr"/>
+      <c r="J22" s="33" t="n"/>
+      <c r="K22" s="34" t="n"/>
     </row>
     <row r="23" ht="108" customHeight="1">
       <c r="A23" s="25" t="inlineStr">
@@ -14966,7 +16759,7 @@
           <t>An assessment is intended to be a snapshot. When component scans are widely separated, lesions measured on the later scans reflect a different point in the disease course, which distorts the sum and, at baseline, the reference for all later comparisons.</t>
         </is>
       </c>
-      <c r="F23" s="51" t="inlineStr">
+      <c r="F23" s="56" t="inlineStr">
         <is>
           <t>The scans comprising the {visit} tumor assessment span {span} days. Please confirm the scan dates and whether all scans belong to this assessment.</t>
         </is>
@@ -14976,9 +16769,14 @@
           <t>Commonly caused by brain MRI scheduled separately from body CT; confirm the imaging manual's tolerance before raising.</t>
         </is>
       </c>
-      <c r="H23" s="52" t="n"/>
-      <c r="I23" s="52" t="n"/>
-      <c r="J23" s="53" t="n"/>
+      <c r="H23" s="25" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I23" s="22" t="inlineStr"/>
+      <c r="J23" s="33" t="n"/>
+      <c r="K23" s="34" t="n"/>
     </row>
     <row r="24" ht="108" customHeight="1">
       <c r="A24" s="23" t="inlineStr">
@@ -15006,7 +16804,7 @@
           <t>Organ coding drives the per-organ target lesion limit and the interpretation of new lesions by region. A mismatch can hide a breach of the per-organ limit or misclassify a new lesion.</t>
         </is>
       </c>
-      <c r="F24" s="51" t="inlineStr">
+      <c r="F24" s="56" t="inlineStr">
         <is>
           <t>Lesion {lesion_id} is recorded at {organ} {laterality} with the description "{location_detail}". Please confirm the anatomical location and correct the coding if needed.</t>
         </is>
@@ -15016,9 +16814,14 @@
           <t>Laterality errors are the most common subtype and matter most for paired organs (lung, kidney, breast, adnexa).</t>
         </is>
       </c>
-      <c r="H24" s="52" t="n"/>
-      <c r="I24" s="52" t="n"/>
-      <c r="J24" s="53" t="n"/>
+      <c r="H24" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I24" s="12" t="inlineStr"/>
+      <c r="J24" s="33" t="n"/>
+      <c r="K24" s="34" t="n"/>
     </row>
     <row r="25" ht="108" customHeight="1">
       <c r="A25" s="25" t="inlineStr">
@@ -15046,7 +16849,7 @@
           <t>Percent change from baseline, the nadir and every response category depend on a baseline. Without it the subject cannot contribute to any efficacy endpoint.</t>
         </is>
       </c>
-      <c r="F25" s="51" t="inlineStr">
+      <c r="F25" s="56" t="inlineStr">
         <is>
           <t>No baseline tumor assessment is recorded for this subject although follow-up assessments exist. Please enter the baseline assessment or confirm why it was not performed.</t>
         </is>
@@ -15056,9 +16859,14 @@
           <t>Check whether the baseline was entered under a screening visit name that failed to map; this is frequently a data-transfer issue rather than missing data.</t>
         </is>
       </c>
-      <c r="H25" s="52" t="n"/>
-      <c r="I25" s="52" t="n"/>
-      <c r="J25" s="53" t="n"/>
+      <c r="H25" s="25" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I25" s="22" t="inlineStr"/>
+      <c r="J25" s="33" t="n"/>
+      <c r="K25" s="34" t="n"/>
     </row>
     <row r="26" ht="108" customHeight="1">
       <c r="A26" s="23" t="inlineStr">
@@ -15086,7 +16894,7 @@
           <t>The sum drives percent change from baseline (partial response) and from nadir (progression). A {difference} mm error at this timepoint changes the percent change from {reported_pct}% to {derived_pct}% and the derived response from {reported_response} to {derived_response}.</t>
         </is>
       </c>
-      <c r="F26" s="51" t="inlineStr">
+      <c r="F26" s="56" t="inlineStr">
         <is>
           <t>The sum of diameters recorded at {visit} ({reported} mm) does not match the sum of the individual target lesion measurements ({derived} mm). Please verify the individual measurements and the recorded sum.</t>
         </is>
@@ -15096,9 +16904,14 @@
           <t>Check for a lesion measured but omitted from the sum, a lesion recorded as absent but still included, and nodal lesions entered with the wrong axis.</t>
         </is>
       </c>
-      <c r="H26" s="52" t="n"/>
-      <c r="I26" s="52" t="n"/>
-      <c r="J26" s="53" t="n"/>
+      <c r="H26" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I26" s="12" t="inlineStr"/>
+      <c r="J26" s="33" t="n"/>
+      <c r="K26" s="34" t="n"/>
     </row>
     <row r="27" ht="108" customHeight="1">
       <c r="A27" s="25" t="inlineStr">
@@ -15126,7 +16939,7 @@
           <t>An unexplained missing measurement makes the sum incomplete, which forces the target response to not evaluable and can propagate into a missing timepoint for progression-free survival.</t>
         </is>
       </c>
-      <c r="F27" s="51" t="inlineStr">
+      <c r="F27" s="56" t="inlineStr">
         <is>
           <t>No measurement is recorded for target lesion {lesion_id} at {visit}. Please enter the measurement or record the reason it could not be assessed.</t>
         </is>
@@ -15136,9 +16949,14 @@
           <t>Distinguish "not evaluable" (lesion could not be assessed) from "absent" (lesion no longer visible); the two have opposite consequences for response.</t>
         </is>
       </c>
-      <c r="H27" s="52" t="n"/>
-      <c r="I27" s="52" t="n"/>
-      <c r="J27" s="53" t="n"/>
+      <c r="H27" s="25" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I27" s="22" t="inlineStr"/>
+      <c r="J27" s="33" t="n"/>
+      <c r="K27" s="34" t="n"/>
     </row>
     <row r="28" ht="108" customHeight="1">
       <c r="A28" s="23" t="inlineStr">
@@ -15166,7 +16984,7 @@
           <t>When any target lesion cannot be assessed, the sum is incomplete and the true tumor burden is unknown, so the response is not evaluable. The exception is progression: if the measured lesions alone already meet the progression threshold, progressive disease can still be assigned. Here the measured lesions sum to {partial_sum} mm against a nadir of {nadir} mm ({partial_pct}%), which does not reach the progression threshold.</t>
         </is>
       </c>
-      <c r="F28" s="51" t="inlineStr">
+      <c r="F28" s="56" t="inlineStr">
         <is>
           <t>Target lesion {lesion_id} is recorded as not evaluable at {visit} while the target lesion response is reported as {reported_response}. Please confirm; where a target lesion cannot be assessed, the target response should normally be not evaluable.</t>
         </is>
@@ -15176,9 +16994,14 @@
           <t>This is a systematic misunderstanding at many sites: a lesion that is "not seen because it resolved" should be recorded as absent, not as not evaluable.</t>
         </is>
       </c>
-      <c r="H28" s="52" t="n"/>
-      <c r="I28" s="52" t="n"/>
-      <c r="J28" s="53" t="n"/>
+      <c r="H28" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I28" s="12" t="inlineStr"/>
+      <c r="J28" s="33" t="n"/>
+      <c r="K28" s="34" t="n"/>
     </row>
     <row r="29" ht="108" customHeight="1">
       <c r="A29" s="25" t="inlineStr">
@@ -15206,7 +17029,7 @@
           <t>A change of this magnitude over {interval} days is unusual and is more often a transcription error, a unit error, or measurement of a different lesion than true biology. The change moves the sum from {prev_sum} mm to {sum} mm and the derived response from {prev_response} to {response}.</t>
         </is>
       </c>
-      <c r="F29" s="51" t="inlineStr">
+      <c r="F29" s="56" t="inlineStr">
         <is>
           <t>Lesion {lesion_id} changed from {prev_value} mm to {value} mm between {prev_visit} and {visit}. Please verify the measurement against the imaging report.</t>
         </is>
@@ -15216,9 +17039,14 @@
           <t>Genuine large changes do occur — rapid response to targeted therapy, cavitation, haemorrhage into a lesion, or coalescence of adjacent lesions. Look for a comment or a matching change in a neighbouring lesion.</t>
         </is>
       </c>
-      <c r="H29" s="52" t="n"/>
-      <c r="I29" s="52" t="n"/>
-      <c r="J29" s="53" t="n"/>
+      <c r="H29" s="25" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I29" s="22" t="inlineStr"/>
+      <c r="J29" s="33" t="n"/>
+      <c r="K29" s="34" t="n"/>
     </row>
     <row r="30" ht="108" customHeight="1">
       <c r="A30" s="23" t="inlineStr">
@@ -15246,7 +17074,7 @@
           <t>A previously resolved target lesion that reappears re-enters the sum of diameters at its measured size; it is not a new lesion, because it was present at baseline. Progression is then judged against the nadir. If it has instead been recorded as a new lesion, progression will be dated incorrectly and the sum will double-count the disease.</t>
         </is>
       </c>
-      <c r="F30" s="51" t="inlineStr">
+      <c r="F30" s="56" t="inlineStr">
         <is>
           <t>Lesion {lesion_id} was recorded as absent at {absent_visit} and is measured again at {visit}. Please confirm this is the same baseline target lesion rather than a new lesion, and that it is included in the sum of diameters.</t>
         </is>
@@ -15256,9 +17084,14 @@
           <t>Confirm the protocol's position: some protocols treat reappearance after a complete response as progression in itself. The study configuration setting is reappearance_is_progression = {reappearance_is_progression}.</t>
         </is>
       </c>
-      <c r="H30" s="52" t="n"/>
-      <c r="I30" s="52" t="n"/>
-      <c r="J30" s="53" t="n"/>
+      <c r="H30" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I30" s="12" t="inlineStr"/>
+      <c r="J30" s="33" t="n"/>
+      <c r="K30" s="34" t="n"/>
     </row>
     <row r="31" ht="108" customHeight="1">
       <c r="A31" s="25" t="inlineStr">
@@ -15286,7 +17119,7 @@
           <t>The two conventions produce different sums and different eligibility for complete response. Mixing them makes cross-subject comparison unreliable and can make a complete response unassignable for some subjects and assignable for others with identical imaging.</t>
         </is>
       </c>
-      <c r="F31" s="51" t="inlineStr">
+      <c r="F31" s="56" t="inlineStr">
         <is>
           <t>Please confirm the convention used for lesions below the limit of reliable measurement at this site, so that the records can be harmonised.</t>
         </is>
@@ -15296,9 +17129,14 @@
           <t>Agree the convention centrally and document it in the imaging manual; retrospective harmonisation is usually preferable to leaving the study mixed.</t>
         </is>
       </c>
-      <c r="H31" s="52" t="n"/>
-      <c r="I31" s="52" t="n"/>
-      <c r="J31" s="53" t="n"/>
+      <c r="H31" s="25" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I31" s="22" t="inlineStr"/>
+      <c r="J31" s="33" t="n"/>
+      <c r="K31" s="34" t="n"/>
     </row>
     <row r="32" ht="108" customHeight="1">
       <c r="A32" s="23" t="inlineStr">
@@ -15326,7 +17164,7 @@
           <t>Assessment timing determines the resolution of progression dating and, in randomised trials, the comparability of progression-free survival between arms. Systematically late assessments delay progression detection.</t>
         </is>
       </c>
-      <c r="F32" s="51" t="inlineStr">
+      <c r="F32" s="56" t="inlineStr">
         <is>
           <t>The interval between {prev_visit} and {visit} is {interval} days, outside the protocol window of {expected} ± {window} days. Please confirm the assessment date and whether a protocol deviation has been recorded.</t>
         </is>
@@ -15336,9 +17174,14 @@
           <t>Cluster by site: isolated deviations are scheduling reality, but a site with a consistent bias is a monitoring signal.</t>
         </is>
       </c>
-      <c r="H32" s="52" t="n"/>
-      <c r="I32" s="52" t="n"/>
-      <c r="J32" s="53" t="n"/>
+      <c r="H32" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I32" s="12" t="inlineStr"/>
+      <c r="J32" s="33" t="n"/>
+      <c r="K32" s="34" t="n"/>
     </row>
     <row r="33" ht="108" customHeight="1">
       <c r="A33" s="25" t="inlineStr">
@@ -15366,7 +17209,7 @@
           <t>Two or more consecutively missed assessments typically require censoring at the last evaluable assessment in progression-free survival analyses, which reduces the information contributed by this subject and can bias the estimate.</t>
         </is>
       </c>
-      <c r="F33" s="51" t="inlineStr">
+      <c r="F33" s="56" t="inlineStr">
         <is>
           <t>No tumor assessment is recorded between {prev_date} and {date} although the subject remained on treatment. Please confirm whether assessments were performed and, if so, enter the data; otherwise please record the reason.</t>
         </is>
@@ -15376,12 +17219,17 @@
           <t>Cross-check against the visit schedule and any unscheduled visits; assessments performed but entered under an unmapped visit name are a common cause.</t>
         </is>
       </c>
-      <c r="H33" s="52" t="n"/>
-      <c r="I33" s="52" t="n"/>
-      <c r="J33" s="53" t="n"/>
+      <c r="H33" s="25" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I33" s="22" t="inlineStr"/>
+      <c r="J33" s="33" t="n"/>
+      <c r="K33" s="34" t="n"/>
     </row>
     <row r="34" ht="108" customHeight="1">
-      <c r="A34" s="23" t="inlineStr">
+      <c r="A34" s="57" t="inlineStr">
         <is>
           <t>TE-FU-009</t>
         </is>
@@ -15406,19 +17254,28 @@
           <t>Under RECIST 1.1 lymph nodes always retain a measurable short axis and are never recorded as absent; they continue to contribute their short axis to the sum even when it falls below 10 mm. The sum therefore need not reach zero for a complete response — what is required is that every pathological node has a short axis below 10 mm. Recording the node as zero understates the sum by its true short axis and can produce a false partial response or complete response.</t>
         </is>
       </c>
-      <c r="F34" s="51" t="inlineStr">
+      <c r="F34" s="35" t="inlineStr">
+        <is>
+          <t>Nodal target lesion {lesion_id} is recorded as {state_or_zero} at {visit}. Please confirm whether this node was measured at this visit and, if so, record the short axis from the source imaging report. If it could not be measured, please record the reason.</t>
+        </is>
+      </c>
+      <c r="G34" s="12" t="inlineStr">
+        <is>
+          <t>This is the single most common nodal error and it usually reflects a well-intentioned attempt to make the arithmetic produce a complete response. Explain the rule to the site rather than only requesting the correction.</t>
+        </is>
+      </c>
+      <c r="H34" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I34" s="58" t="inlineStr">
         <is>
           <t>Nodal target lesion {lesion_id} is recorded as {state_or_zero} at {visit}. Lymph nodes should continue to be measured in short axis at every visit, including when they normalise. Please enter the measured short axis.</t>
         </is>
       </c>
-      <c r="G34" s="12" t="inlineStr">
-        <is>
-          <t>This is the single most common nodal error and it usually reflects a well-intentioned attempt to make the arithmetic produce a complete response. Explain the rule to the site rather than only requesting the correction.</t>
-        </is>
-      </c>
-      <c r="H34" s="52" t="n"/>
-      <c r="I34" s="52" t="n"/>
-      <c r="J34" s="53" t="n"/>
+      <c r="J34" s="33" t="n"/>
+      <c r="K34" s="34" t="n"/>
     </row>
     <row r="35" ht="108" customHeight="1">
       <c r="A35" s="25" t="inlineStr">
@@ -15446,7 +17303,7 @@
           <t>The non-target response contributes to the overall timepoint response, and unequivocal progression of non-target disease is sufficient for progression on its own. A missing non-target assessment leaves the overall response underdetermined.</t>
         </is>
       </c>
-      <c r="F35" s="51" t="inlineStr">
+      <c r="F35" s="56" t="inlineStr">
         <is>
           <t>No assessment is recorded for non-target lesion {lesion_id} at {visit}. Please record the status of this lesion.</t>
         </is>
@@ -15456,9 +17313,14 @@
           <t>Sites often assess non-target disease collectively rather than lesion by lesion; check whether the eCRF expects a per-lesion or an overall non-target response.</t>
         </is>
       </c>
-      <c r="H35" s="52" t="n"/>
-      <c r="I35" s="52" t="n"/>
-      <c r="J35" s="53" t="n"/>
+      <c r="H35" s="25" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I35" s="22" t="inlineStr"/>
+      <c r="J35" s="33" t="n"/>
+      <c r="K35" s="34" t="n"/>
     </row>
     <row r="36" ht="108" customHeight="1">
       <c r="A36" s="23" t="inlineStr">
@@ -15486,7 +17348,7 @@
           <t>An assessment dated after death or well beyond the end of follow-up indicates an error in one of the two dates. Either error affects analysis: an incorrect assessment date can move the progression date, and an incorrect death date affects survival analysis.</t>
         </is>
       </c>
-      <c r="F36" s="51" t="inlineStr">
+      <c r="F36" s="56" t="inlineStr">
         <is>
           <t>The {visit} tumor assessment is dated {date}, after the recorded {reference_event} ({reference_date}). Please verify both dates.</t>
         </is>
@@ -15496,9 +17358,14 @@
           <t>Post-treatment follow-up assessments are legitimate in many protocols; confirm the follow-up period before treating a post-discontinuation assessment as an error.</t>
         </is>
       </c>
-      <c r="H36" s="52" t="n"/>
-      <c r="I36" s="52" t="n"/>
-      <c r="J36" s="53" t="n"/>
+      <c r="H36" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I36" s="12" t="inlineStr"/>
+      <c r="J36" s="33" t="n"/>
+      <c r="K36" s="34" t="n"/>
     </row>
     <row r="37" ht="108" customHeight="1">
       <c r="A37" s="25" t="inlineStr">
@@ -15526,7 +17393,7 @@
           <t>The progression date is taken from the first assessment at which the new lesion was observed. An inconsistency between these dates produces the wrong progression date and therefore the wrong progression-free survival time.</t>
         </is>
       </c>
-      <c r="F37" s="51" t="inlineStr">
+      <c r="F37" s="56" t="inlineStr">
         <is>
           <t>New lesion {lesion_id} has an identification date of {identified_date} but is first reported at {visit} ({visit_date}). Please confirm the date the lesion was first observed.</t>
         </is>
@@ -15536,9 +17403,14 @@
           <t>Where the lesion was visible in retrospect on an earlier scan, the progression date is normally the earlier scan; this requires a documented radiology decision.</t>
         </is>
       </c>
-      <c r="H37" s="52" t="n"/>
-      <c r="I37" s="52" t="n"/>
-      <c r="J37" s="53" t="n"/>
+      <c r="H37" s="25" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I37" s="22" t="inlineStr"/>
+      <c r="J37" s="33" t="n"/>
+      <c r="K37" s="34" t="n"/>
     </row>
     <row r="38" ht="108" customHeight="1">
       <c r="A38" s="23" t="inlineStr">
@@ -15566,7 +17438,7 @@
           <t>Widely separated component scans mean that different parts of the tumor burden are measured at different times, which affects the sum and may affect the progression date.</t>
         </is>
       </c>
-      <c r="F38" s="51" t="inlineStr">
+      <c r="F38" s="56" t="inlineStr">
         <is>
           <t>The scans comprising the {visit} assessment span {span} days. Please confirm the scan dates.</t>
         </is>
@@ -15576,9 +17448,14 @@
           <t>Where the span is unavoidable, the assessment date convention (earliest scan or latest scan) should be applied consistently across the study.</t>
         </is>
       </c>
-      <c r="H38" s="52" t="n"/>
-      <c r="I38" s="52" t="n"/>
-      <c r="J38" s="53" t="n"/>
+      <c r="H38" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I38" s="12" t="inlineStr"/>
+      <c r="J38" s="33" t="n"/>
+      <c r="K38" s="34" t="n"/>
     </row>
     <row r="39" ht="108" customHeight="1">
       <c r="A39" s="25" t="inlineStr">
@@ -15606,7 +17483,7 @@
           <t>Identical measurements of a lesion of this size across several timepoints are uncommon given normal measurement variability, and may indicate that a previous value was copied rather than the lesion re-measured. If so, the sum does not reflect the current tumor burden.</t>
         </is>
       </c>
-      <c r="F39" s="51" t="inlineStr">
+      <c r="F39" s="56" t="inlineStr">
         <is>
           <t>Lesion {lesion_id} is recorded as exactly {value} mm at {visits}. Please confirm that the lesion was measured at each assessment.</t>
         </is>
@@ -15616,12 +17493,17 @@
           <t>Small and stable lesions genuinely produce repeated values; this check is deliberately informational and should be reviewed in the context of the whole subject rather than raised as a query in isolation.</t>
         </is>
       </c>
-      <c r="H39" s="52" t="n"/>
-      <c r="I39" s="52" t="n"/>
-      <c r="J39" s="53" t="n"/>
+      <c r="H39" s="25" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I39" s="22" t="inlineStr"/>
+      <c r="J39" s="33" t="n"/>
+      <c r="K39" s="34" t="n"/>
     </row>
     <row r="40" ht="108" customHeight="1">
-      <c r="A40" s="23" t="inlineStr">
+      <c r="A40" s="57" t="inlineStr">
         <is>
           <t>TE-RS-001</t>
         </is>
@@ -15646,22 +17528,31 @@
           <t>{derivation_explanation}</t>
         </is>
       </c>
-      <c r="F40" s="51" t="inlineStr">
+      <c r="F40" s="35" t="inlineStr">
+        <is>
+          <t>The target lesion response recorded at {visit} is {reported}, while the individual lesion measurements recorded for the same visit sum to {sum} mm. Please review the recorded response together with the lesion measurements against the source imaging report, and correct whichever does not match the source.</t>
+        </is>
+      </c>
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>Before querying the response, confirm the measurements themselves: a response mismatch is frequently a symptom of a measurement or sum error already flagged for this subject. Check the linked findings for this subject first.</t>
+        </is>
+      </c>
+      <c r="H40" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I40" s="58" t="inlineStr">
         <is>
           <t>The target lesion response recorded at {visit} is {reported}. Based on the recorded lesion measurements the sum of diameters is {sum} mm, a {pct_baseline}% change from baseline and a {pct_nadir}% change from the nadir of {nadir_sum} mm, which corresponds to {derived}. Please review the recorded response and the underlying measurements.</t>
         </is>
       </c>
-      <c r="G40" s="12" t="inlineStr">
-        <is>
-          <t>Before querying the response, confirm the measurements themselves: a response mismatch is frequently a symptom of a measurement or sum error already flagged for this subject. Check the linked findings for this subject first.</t>
-        </is>
-      </c>
-      <c r="H40" s="52" t="n"/>
-      <c r="I40" s="52" t="n"/>
-      <c r="J40" s="53" t="n"/>
+      <c r="J40" s="33" t="n"/>
+      <c r="K40" s="34" t="n"/>
     </row>
     <row r="41" ht="108" customHeight="1">
-      <c r="A41" s="25" t="inlineStr">
+      <c r="A41" s="57" t="inlineStr">
         <is>
           <t>TE-RS-002</t>
         </is>
@@ -15686,22 +17577,31 @@
           <t>RECIST 1.1 requires both a relative increase of at least {pd_pct}% and an absolute increase of at least {pd_abs} mm from the nadir. The absolute criterion was introduced precisely for small tumor burdens, where a 20% increase can fall within measurement variability. Here the absolute increase of {abs_nadir} mm does not reach {pd_abs} mm, so the derived response is {derived}.</t>
         </is>
       </c>
-      <c r="F41" s="51" t="inlineStr">
+      <c r="F41" s="35" t="inlineStr">
+        <is>
+          <t>Progressive disease is recorded at {visit}. The sum of diameters has increased from {nadir_sum} mm at {nadir_visit} to {sum} mm, a change of {abs_nadir} mm. Please confirm what the progression assessment at this visit was based on — the target lesion measurements, a new lesion, or worsening of non-target disease.</t>
+        </is>
+      </c>
+      <c r="G41" s="22" t="inlineStr">
+        <is>
+          <t>Confirm first whether progression was actually driven by a new lesion or by non-target progression, in which case the response is correct and this finding can be rejected. This check applies only to progression driven by the target sum.</t>
+        </is>
+      </c>
+      <c r="H41" s="25" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I41" s="59" t="inlineStr">
         <is>
           <t>Progressive disease is recorded at {visit} based on an increase from the nadir of {nadir_sum} mm to {sum} mm. This is a {pct_nadir}% increase but only {abs_nadir} mm in absolute terms, which does not meet the {pd_abs} mm absolute increase also required by RECIST 1.1. Please review the response assessment, unless progression is based on a new lesion or on unequivocal non-target progression.</t>
         </is>
       </c>
-      <c r="G41" s="22" t="inlineStr">
-        <is>
-          <t>Confirm first whether progression was actually driven by a new lesion or by non-target progression, in which case the response is correct and this finding can be rejected. This check applies only to progression driven by the target sum.</t>
-        </is>
-      </c>
-      <c r="H41" s="52" t="n"/>
-      <c r="I41" s="52" t="n"/>
-      <c r="J41" s="53" t="n"/>
+      <c r="J41" s="33" t="n"/>
+      <c r="K41" s="34" t="n"/>
     </row>
     <row r="42" ht="108" customHeight="1">
-      <c r="A42" s="23" t="inlineStr">
+      <c r="A42" s="57" t="inlineStr">
         <is>
           <t>TE-RS-003</t>
         </is>
@@ -15726,19 +17626,28 @@
           <t>Progression is assessed against the smallest sum recorded on study, including baseline, not against baseline itself. Because this subject responded before progressing, the comparison against baseline still looks favourable while the comparison against the nadir meets the progression criteria. The derived response is progressive disease.</t>
         </is>
       </c>
-      <c r="F42" s="51" t="inlineStr">
+      <c r="F42" s="35" t="inlineStr">
+        <is>
+          <t>At {visit} the sum of diameters is {sum} mm, compared with the smallest sum recorded on study of {nadir_sum} mm at {nadir_visit}. The response recorded at {visit} is {reported}. Please confirm the response assessment for this visit against the source imaging report.</t>
+        </is>
+      </c>
+      <c r="G42" s="12" t="inlineStr">
+        <is>
+          <t>This is the most consequential single error class in tumor data: it delays or entirely misses the progression date and directly biases progression-free survival. Always check the nadir visit shown above is itself a complete assessment.</t>
+        </is>
+      </c>
+      <c r="H42" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I42" s="58" t="inlineStr">
         <is>
           <t>At {visit} the sum of diameters is {sum} mm compared with a nadir of {nadir_sum} mm at {nadir_visit}, a {pct_nadir}% increase of {abs_nadir} mm, which meets the RECIST criteria for progression. The recorded response is {reported}. Please review the response assessment.</t>
         </is>
       </c>
-      <c r="G42" s="12" t="inlineStr">
-        <is>
-          <t>This is the most consequential single error class in tumor data: it delays or entirely misses the progression date and directly biases progression-free survival. Always check the nadir visit shown above is itself a complete assessment.</t>
-        </is>
-      </c>
-      <c r="H42" s="52" t="n"/>
-      <c r="I42" s="52" t="n"/>
-      <c r="J42" s="53" t="n"/>
+      <c r="J42" s="33" t="n"/>
+      <c r="K42" s="34" t="n"/>
     </row>
     <row r="43" ht="108" customHeight="1">
       <c r="A43" s="25" t="inlineStr">
@@ -15766,7 +17675,7 @@
           <t>A complete response of target lesions requires the disappearance of all non-nodal target lesions and a reduction of every pathological lymph node, whether target or non-target, to a short axis below {node_threshold} mm. A lesion that is still visible, including one recorded as too small to measure, is not a disappearance.</t>
         </is>
       </c>
-      <c r="F43" s="51" t="inlineStr">
+      <c r="F43" s="56" t="inlineStr">
         <is>
           <t>A complete response is recorded at {visit}, but {blocking_description}. Please review the response assessment and the individual lesion records.</t>
         </is>
@@ -15776,9 +17685,14 @@
           <t>Note the asymmetry that causes most of these: the sum of diameters can be very small without a complete response being appropriate, because nodes retain a short axis. Conversely, complete response does not require the sum to be zero.</t>
         </is>
       </c>
-      <c r="H43" s="52" t="n"/>
-      <c r="I43" s="52" t="n"/>
-      <c r="J43" s="53" t="n"/>
+      <c r="H43" s="25" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I43" s="22" t="inlineStr"/>
+      <c r="J43" s="33" t="n"/>
+      <c r="K43" s="34" t="n"/>
     </row>
     <row r="44" ht="108" customHeight="1">
       <c r="A44" s="23" t="inlineStr">
@@ -15806,7 +17720,7 @@
           <t>{derivation_explanation}</t>
         </is>
       </c>
-      <c r="F44" s="51" t="inlineStr">
+      <c r="F44" s="56" t="inlineStr">
         <is>
           <t>The non-target lesion response recorded at {visit} is {reported}, while the individual non-target lesion assessments ({non_target_breakdown}) correspond to {derived}. Please review.</t>
         </is>
@@ -15816,9 +17730,14 @@
           <t>A complete response of non-target disease additionally requires every pathological lymph node to be below 10 mm short axis, and where the protocol uses tumor markers, normalisation of those markers.</t>
         </is>
       </c>
-      <c r="H44" s="52" t="n"/>
-      <c r="I44" s="52" t="n"/>
-      <c r="J44" s="53" t="n"/>
+      <c r="H44" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I44" s="12" t="inlineStr"/>
+      <c r="J44" s="33" t="n"/>
+      <c r="K44" s="34" t="n"/>
     </row>
     <row r="45" ht="108" customHeight="1">
       <c r="A45" s="25" t="inlineStr">
@@ -15846,7 +17765,7 @@
           <t>A complete response requires all lymph nodes, target and non-target alike, to have reduced to a short axis below {node_threshold} mm. A node of {value} mm remains pathological, so the non-target response is Non-CR/Non-PD.</t>
         </is>
       </c>
-      <c r="F45" s="51" t="inlineStr">
+      <c r="F45" s="56" t="inlineStr">
         <is>
           <t>A complete response of non-target lesions is recorded at {visit}, but node {lesion_id} measures {value} mm in short axis. Please review the non-target response.</t>
         </is>
@@ -15856,12 +17775,17 @@
           <t>Non-target nodes are often not measured at all; where the eCRF does not capture a short axis for non-target nodes, this check depends on the radiology narrative and may need to be raised as a clarification rather than a correction.</t>
         </is>
       </c>
-      <c r="H45" s="52" t="n"/>
-      <c r="I45" s="52" t="n"/>
-      <c r="J45" s="53" t="n"/>
+      <c r="H45" s="25" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I45" s="22" t="inlineStr"/>
+      <c r="J45" s="33" t="n"/>
+      <c r="K45" s="34" t="n"/>
     </row>
     <row r="46" ht="108" customHeight="1">
-      <c r="A46" s="23" t="inlineStr">
+      <c r="A46" s="57" t="inlineStr">
         <is>
           <t>TE-RS-007</t>
         </is>
@@ -15886,22 +17810,31 @@
           <t>RECIST states that where measurable disease is present, unequivocal progression based on non-target disease alone should be an exceptional circumstance: the increase in overall tumor burden must be comparable in magnitude to the increase that would be required to declare progression for measurable disease. A modest increase in one non-target lesion is not sufficient, particularly while the target lesions are {target_response}.</t>
         </is>
       </c>
-      <c r="F46" s="51" t="inlineStr">
+      <c r="F46" s="35" t="inlineStr">
+        <is>
+          <t>Progression of non-target disease is recorded at {visit} while the target lesions are recorded as {target_response}. Please provide the radiological description supporting the non-target assessment at this visit, from the source imaging report.</t>
+        </is>
+      </c>
+      <c r="G46" s="12" t="inlineStr">
+        <is>
+          <t>Genuine cases exist — for example a marked increase in a pleural effusion or in lymphangitic disease. The question to the site is not "is this wrong" but "what supports unequivocal". Where the answer supports it, accept and record the rationale so the same finding is not re-raised.</t>
+        </is>
+      </c>
+      <c r="H46" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I46" s="58" t="inlineStr">
         <is>
           <t>Unequivocal progression of non-target disease is recorded at {visit} while the target lesions show {target_response}. Please confirm that the overall tumor burden has increased substantially, and provide the radiological description supporting unequivocal progression.</t>
         </is>
       </c>
-      <c r="G46" s="12" t="inlineStr">
-        <is>
-          <t>Genuine cases exist — for example a marked increase in a pleural effusion or in lymphangitic disease. The question to the site is not "is this wrong" but "what supports unequivocal". Where the answer supports it, accept and record the rationale so the same finding is not re-raised.</t>
-        </is>
-      </c>
-      <c r="H46" s="52" t="n"/>
-      <c r="I46" s="52" t="n"/>
-      <c r="J46" s="53" t="n"/>
+      <c r="J46" s="33" t="n"/>
+      <c r="K46" s="34" t="n"/>
     </row>
     <row r="47" ht="108" customHeight="1">
-      <c r="A47" s="25" t="inlineStr">
+      <c r="A47" s="57" t="inlineStr">
         <is>
           <t>TE-RS-008</t>
         </is>
@@ -15926,19 +17859,28 @@
           <t>{table_explanation}</t>
         </is>
       </c>
-      <c r="F47" s="51" t="inlineStr">
+      <c r="F47" s="35" t="inlineStr">
+        <is>
+          <t>The overall response recorded at {visit} is {reported_overall}, with target lesion response {target}, non-target response {non_target} and new lesions {new_lesion} recorded at the same visit. Please review the overall response against these components and correct whichever does not reflect the assessment.</t>
+        </is>
+      </c>
+      <c r="G47" s="22" t="inlineStr">
+        <is>
+          <t>The combinations most often mis-applied are: target complete response with persisting non-target disease, which is a partial response rather than a complete response; and any new lesion, which is progression regardless of the target and non-target results.</t>
+        </is>
+      </c>
+      <c r="H47" s="25" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I47" s="59" t="inlineStr">
         <is>
           <t>The overall response recorded at {visit} is {reported_overall}. Based on the recorded components — target lesion response {target}, non-target response {non_target}, new lesions {new_lesion} — the overall response should be {derived_overall}. Please review.</t>
         </is>
       </c>
-      <c r="G47" s="22" t="inlineStr">
-        <is>
-          <t>The combinations most often mis-applied are: target complete response with persisting non-target disease, which is a partial response rather than a complete response; and any new lesion, which is progression regardless of the target and non-target results.</t>
-        </is>
-      </c>
-      <c r="H47" s="52" t="n"/>
-      <c r="I47" s="52" t="n"/>
-      <c r="J47" s="53" t="n"/>
+      <c r="J47" s="33" t="n"/>
+      <c r="K47" s="34" t="n"/>
     </row>
     <row r="48" ht="108" customHeight="1">
       <c r="A48" s="23" t="inlineStr">
@@ -15966,7 +17908,7 @@
           <t>A new lesion is sufficient for progression on its own. If the indicator and the lesion records disagree, either progression has been declared without a documented lesion, or a documented new lesion has not been reflected in the response — both change the progression date.</t>
         </is>
       </c>
-      <c r="F48" s="51" t="inlineStr">
+      <c r="F48" s="56" t="inlineStr">
         <is>
           <t>The new lesion indicator at {visit} is recorded as {flag} while {lesion_situation}. Please reconcile the new lesion records with the response assessment.</t>
         </is>
@@ -15976,9 +17918,14 @@
           <t>Check whether the lesion was recorded as a new lesion at a later visit than the one where it was first seen; the progression date follows the first observation.</t>
         </is>
       </c>
-      <c r="H48" s="52" t="n"/>
-      <c r="I48" s="52" t="n"/>
-      <c r="J48" s="53" t="n"/>
+      <c r="H48" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I48" s="12" t="inlineStr"/>
+      <c r="J48" s="33" t="n"/>
+      <c r="K48" s="34" t="n"/>
     </row>
     <row r="49" ht="108" customHeight="1">
       <c r="A49" s="25" t="inlineStr">
@@ -16006,7 +17953,7 @@
           <t>Under RECIST 1.1 the appearance of any unequivocal new lesion is progression, irrespective of the target and non-target responses. {irecist_note}</t>
         </is>
       </c>
-      <c r="F49" s="51" t="inlineStr">
+      <c r="F49" s="56" t="inlineStr">
         <is>
           <t>A new lesion is recorded at {visit} while the overall response is {reported_overall}. Please confirm the new lesion and review the overall response assessment.</t>
         </is>
@@ -16016,9 +17963,14 @@
           <t>Where the finding is equivocal rather than unequivocal, the correct handling is to record it as equivocal and continue treatment, treating the timepoint as not evaluable and re-assessing at the next visit; if later confirmed, progression is dated to this visit.</t>
         </is>
       </c>
-      <c r="H49" s="52" t="n"/>
-      <c r="I49" s="52" t="n"/>
-      <c r="J49" s="53" t="n"/>
+      <c r="H49" s="25" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I49" s="22" t="inlineStr"/>
+      <c r="J49" s="33" t="n"/>
+      <c r="K49" s="34" t="n"/>
     </row>
     <row r="50" ht="108" customHeight="1">
       <c r="A50" s="23" t="inlineStr">
@@ -16046,7 +17998,7 @@
           <t>A lesion identified in a region that was not scanned at baseline is considered a new lesion, and therefore progression, because pre-existing disease at that site cannot be excluded. The point of this check is to confirm that the site made this determination deliberately rather than by default, since the alternative interpretation — that the lesion was present but unimaged — is not permitted.</t>
         </is>
       </c>
-      <c r="F50" s="51" t="inlineStr">
+      <c r="F50" s="56" t="inlineStr">
         <is>
           <t>A new lesion is recorded in {organ} at {visit}. Baseline imaging does not appear to have covered this region. Please confirm the finding represents a new lesion and that baseline imaging of this region was not performed.</t>
         </is>
@@ -16056,9 +18008,14 @@
           <t>Brain metastases are the usual case: many protocols do not require baseline brain imaging, so a first brain scan performed for symptoms yields lesions that must be treated as new. Confirm the protocol's imaging requirements before raising.</t>
         </is>
       </c>
-      <c r="H50" s="52" t="n"/>
-      <c r="I50" s="52" t="n"/>
-      <c r="J50" s="53" t="n"/>
+      <c r="H50" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I50" s="12" t="inlineStr"/>
+      <c r="J50" s="33" t="n"/>
+      <c r="K50" s="34" t="n"/>
     </row>
     <row r="51" ht="108" customHeight="1">
       <c r="A51" s="25" t="inlineStr">
@@ -16086,7 +18043,7 @@
           <t>A positive FDG-PET finding establishes a new lesion when the baseline PET was negative, or when the new site is confirmed on CT or MRI. Without either, a positive PET alone is not sufficient, because the finding may represent disease present but not FDG-avid or not imaged at baseline, or may be non-malignant uptake.</t>
         </is>
       </c>
-      <c r="F51" s="51" t="inlineStr">
+      <c r="F51" s="56" t="inlineStr">
         <is>
           <t>The new lesion recorded at {visit} in {organ} is based on FDG-PET. Please confirm whether a baseline PET was performed and negative, or whether the lesion is confirmed on CT or MRI.</t>
         </is>
@@ -16096,12 +18053,17 @@
           <t>Inflammatory and infectious uptake is common, particularly under immunotherapy; anatomical confirmation matters most in that setting.</t>
         </is>
       </c>
-      <c r="H51" s="52" t="n"/>
-      <c r="I51" s="52" t="n"/>
-      <c r="J51" s="53" t="n"/>
+      <c r="H51" s="25" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I51" s="22" t="inlineStr"/>
+      <c r="J51" s="33" t="n"/>
+      <c r="K51" s="34" t="n"/>
     </row>
     <row r="52" ht="108" customHeight="1">
-      <c r="A52" s="23" t="inlineStr">
+      <c r="A52" s="57" t="inlineStr">
         <is>
           <t>TE-RS-013</t>
         </is>
@@ -16126,19 +18088,28 @@
           <t>Where therapy continues after an equivocal finding and the finding is subsequently confirmed as a new lesion, progression is dated to the time of the initial observation, not to the confirming assessment. Using the later date overstates progression-free survival by {days_difference} days.</t>
         </is>
       </c>
-      <c r="F52" s="51" t="inlineStr">
+      <c r="F52" s="35" t="inlineStr">
+        <is>
+          <t>Lesion {lesion_id} was recorded as equivocal at {first_visit} and as confirmed at {confirm_visit}. The progression date recorded for this subject is {reported_pd_date}. Please confirm the progression date against the source imaging reports for both visits.</t>
+        </is>
+      </c>
+      <c r="G52" s="12" t="inlineStr">
+        <is>
+          <t>Under iRECIST the handling differs — the iUPD and iCPD dates are both retained and the analysis convention is protocol-specific. Check which criteria govern before applying this rule.</t>
+        </is>
+      </c>
+      <c r="H52" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I52" s="58" t="inlineStr">
         <is>
           <t>Lesion {lesion_id} was equivocal at {first_visit} and confirmed at {confirm_visit}. Please confirm the date of progression; per RECIST the progression date should be the date of the initial observation ({first_date}).</t>
         </is>
       </c>
-      <c r="G52" s="12" t="inlineStr">
-        <is>
-          <t>Under iRECIST the handling differs — the iUPD and iCPD dates are both retained and the analysis convention is protocol-specific. Check which criteria govern before applying this rule.</t>
-        </is>
-      </c>
-      <c r="H52" s="52" t="n"/>
-      <c r="I52" s="52" t="n"/>
-      <c r="J52" s="53" t="n"/>
+      <c r="J52" s="33" t="n"/>
+      <c r="K52" s="34" t="n"/>
     </row>
     <row r="53" ht="108" customHeight="1">
       <c r="A53" s="25" t="inlineStr">
@@ -16166,7 +18137,7 @@
           <t>The protocol requires confirmation of a complete or partial response by a repeat assessment performed no less than {confirm_days} days after the criteria were first met. Without confirmation the response is unconfirmed and the derived best overall response is {derived_bor}. Counting unconfirmed responses inflates the objective response rate.</t>
         </is>
       </c>
-      <c r="F53" s="51" t="inlineStr">
+      <c r="F53" s="56" t="inlineStr">
         <is>
           <t>The best overall response is recorded as {reported_bor} based on the assessment at {first_visit}. A confirmatory assessment at least {confirm_days} days later does not appear to support this response. Please review the best overall response.</t>
         </is>
@@ -16176,9 +18147,14 @@
           <t>Check whether a confirmatory scan exists but was entered as an unscheduled visit; also check the interval, since a confirmation performed too early does not satisfy the requirement.</t>
         </is>
       </c>
-      <c r="H53" s="52" t="n"/>
-      <c r="I53" s="52" t="n"/>
-      <c r="J53" s="53" t="n"/>
+      <c r="H53" s="25" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I53" s="22" t="inlineStr"/>
+      <c r="J53" s="33" t="n"/>
+      <c r="K53" s="34" t="n"/>
     </row>
     <row r="54" ht="108" customHeight="1">
       <c r="A54" s="23" t="inlineStr">
@@ -16206,7 +18182,7 @@
           <t>{bor_explanation}</t>
         </is>
       </c>
-      <c r="F54" s="51" t="inlineStr">
+      <c r="F54" s="56" t="inlineStr">
         <is>
           <t>The best overall response recorded for this subject is {reported_bor}. Based on the recorded timepoint responses ({timepoint_sequence}) and the protocol's confirmation requirement, the best overall response derives as {derived_bor}. Please review.</t>
         </is>
@@ -16216,12 +18192,17 @@
           <t>Two frequent causes: a response recorded after progression being counted, and a stable disease result assigned before the protocol's minimum duration from baseline has elapsed.</t>
         </is>
       </c>
-      <c r="H54" s="52" t="n"/>
-      <c r="I54" s="52" t="n"/>
-      <c r="J54" s="53" t="n"/>
+      <c r="H54" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I54" s="12" t="inlineStr"/>
+      <c r="J54" s="33" t="n"/>
+      <c r="K54" s="34" t="n"/>
     </row>
     <row r="55" ht="108" customHeight="1">
-      <c r="A55" s="25" t="inlineStr">
+      <c r="A55" s="57" t="inlineStr">
         <is>
           <t>TE-RS-016</t>
         </is>
@@ -16246,19 +18227,28 @@
           <t>A subject with non-measurable disease only can be assigned a complete response, Non-CR/Non-PD, progressive disease or not evaluable. Partial response and stable disease require measurable disease, since both are defined by a change in the sum of diameters. The corresponding category here is Non-CR/Non-PD.</t>
         </is>
       </c>
-      <c r="F55" s="51" t="inlineStr">
+      <c r="F55" s="35" t="inlineStr">
+        <is>
+          <t>The overall response at {visit} is recorded as {reported_overall}, and no target lesions are recorded at baseline for this subject. Please confirm the baseline lesion records and the overall response at this visit.</t>
+        </is>
+      </c>
+      <c r="G55" s="22" t="inlineStr">
+        <is>
+          <t>Check first whether target lesions were in fact selected but failed to load — a missing target lesion record produces this finding spuriously. Look for a companion structural finding on this subject.</t>
+        </is>
+      </c>
+      <c r="H55" s="25" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I55" s="59" t="inlineStr">
         <is>
           <t>The overall response at {visit} is recorded as {reported_overall} although no target lesions were identified at baseline. Please review; for subjects with non-measurable disease only, the appropriate categories are complete response, Non-CR/Non-PD, progressive disease or not evaluable.</t>
         </is>
       </c>
-      <c r="G55" s="22" t="inlineStr">
-        <is>
-          <t>Check first whether target lesions were in fact selected but failed to load — a missing target lesion record produces this finding spuriously. Look for a companion structural finding on this subject.</t>
-        </is>
-      </c>
-      <c r="H55" s="52" t="n"/>
-      <c r="I55" s="52" t="n"/>
-      <c r="J55" s="53" t="n"/>
+      <c r="J55" s="33" t="n"/>
+      <c r="K55" s="34" t="n"/>
     </row>
     <row r="56" ht="108" customHeight="1">
       <c r="A56" s="23" t="inlineStr">
@@ -16286,7 +18276,7 @@
           <t>Stable disease is meaningful only if maintained for a minimum interval defined by the protocol. An earlier assessment cannot establish stability, and counting it inflates the disease control rate.</t>
         </is>
       </c>
-      <c r="F56" s="51" t="inlineStr">
+      <c r="F56" s="56" t="inlineStr">
         <is>
           <t>Stable disease is recorded at {visit}, {days} days after baseline, which is shorter than the minimum of {min_days} days specified in the protocol. Please review the response assessment.</t>
         </is>
@@ -16296,9 +18286,14 @@
           <t>This affects best overall response rather than the timepoint response in many conventions; confirm the sponsor's derivation convention before querying the site.</t>
         </is>
       </c>
-      <c r="H56" s="52" t="n"/>
-      <c r="I56" s="52" t="n"/>
-      <c r="J56" s="53" t="n"/>
+      <c r="H56" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I56" s="12" t="inlineStr"/>
+      <c r="J56" s="33" t="n"/>
+      <c r="K56" s="34" t="n"/>
     </row>
     <row r="57" ht="108" customHeight="1">
       <c r="A57" s="25" t="inlineStr">
@@ -16326,7 +18321,7 @@
           <t>Best overall response is determined from the assessments recorded from the start of treatment until progression. Assessments after progression are retained in the data but do not contribute to the response endpoints. Including one here changes the best overall response from {derived_bor} to {reported_bor}.</t>
         </is>
       </c>
-      <c r="F57" s="51" t="inlineStr">
+      <c r="F57" s="56" t="inlineStr">
         <is>
           <t>A response of {response} is recorded at {later_visit}, after progression was recorded at {pd_visit}. Please confirm the progression date and the response assessments.</t>
         </is>
@@ -16336,9 +18331,14 @@
           <t>Where the subject continued treatment beyond progression, the later assessments are legitimate data; the issue is their use in derivation, not their existence. If iRECIST applies, progression may have been unconfirmed and the later assessments are then fully valid — check the applicable criteria.</t>
         </is>
       </c>
-      <c r="H57" s="52" t="n"/>
-      <c r="I57" s="52" t="n"/>
-      <c r="J57" s="53" t="n"/>
+      <c r="H57" s="25" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I57" s="22" t="inlineStr"/>
+      <c r="J57" s="33" t="n"/>
+      <c r="K57" s="34" t="n"/>
     </row>
     <row r="58" ht="108" customHeight="1">
       <c r="A58" s="23" t="inlineStr">
@@ -16366,7 +18366,7 @@
           <t>Progression-free survival is measured to the date of the first assessment demonstrating progression. A difference of {days_difference} days changes the event time for this subject and, aggregated across subjects, biases the survival estimate.</t>
         </is>
       </c>
-      <c r="F58" s="51" t="inlineStr">
+      <c r="F58" s="56" t="inlineStr">
         <is>
           <t>The progression date is recorded as {reported_date}, while the earliest assessment meeting progression criteria is {derived_visit} on {derived_date}. Please confirm the date of progression.</t>
         </is>
@@ -16376,9 +18376,14 @@
           <t>Distinguish radiological progression from clinical progression: if progression was determined clinically, the date may legitimately precede any imaging, and the record should say so.</t>
         </is>
       </c>
-      <c r="H58" s="52" t="n"/>
-      <c r="I58" s="52" t="n"/>
-      <c r="J58" s="53" t="n"/>
+      <c r="H58" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I58" s="12" t="inlineStr"/>
+      <c r="J58" s="33" t="n"/>
+      <c r="K58" s="34" t="n"/>
     </row>
     <row r="59" ht="108" customHeight="1">
       <c r="A59" s="25" t="inlineStr">
@@ -16406,7 +18411,7 @@
           <t>Discordance between the investigator and central review is expected at some rate, but discordance that crosses a progression boundary affects the primary endpoint where the central review is the basis of analysis, and may indicate a systematic difference in lesion selection or measurement at this site.</t>
         </is>
       </c>
-      <c r="F59" s="51" t="inlineStr">
+      <c r="F59" s="56" t="inlineStr">
         <is>
           <t>Not applicable: this finding is for internal review and reconciliation and is not normally issued as a site query.</t>
         </is>
@@ -16416,12 +18421,17 @@
           <t>Review the lesion-level data from both readers side by side. Consistent directional discordance at one site is a monitoring signal; scattered discordance is normal reader variability. Where the sponsor keeps the two streams deliberately separated, this rule should be disabled in configuration.</t>
         </is>
       </c>
-      <c r="H59" s="52" t="n"/>
-      <c r="I59" s="52" t="n"/>
-      <c r="J59" s="53" t="n"/>
+      <c r="H59" s="25" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I59" s="22" t="inlineStr"/>
+      <c r="J59" s="33" t="n"/>
+      <c r="K59" s="34" t="n"/>
     </row>
     <row r="60" ht="108" customHeight="1">
-      <c r="A60" s="23" t="inlineStr">
+      <c r="A60" s="57" t="inlineStr">
         <is>
           <t>TE-IR-001</t>
         </is>
@@ -16446,19 +18456,28 @@
           <t>Under iRECIST, the first timepoint at which RECIST 1.1 progression criteria are met is assigned unconfirmed progression (iUPD). Confirmed progression (iCPD) can only be assigned at a subsequent assessment that demonstrates further worsening. Recording confirmed progression at first occurrence removes the confirmation step that iRECIST exists to provide, and may lead to treatment being discontinued for pseudoprogression.</t>
         </is>
       </c>
-      <c r="F60" s="51" t="inlineStr">
+      <c r="F60" s="35" t="inlineStr">
+        <is>
+          <t>The iRECIST response at {visit} is recorded as {reported_irecist}. The lesion measurements at this visit show an increase against the smallest sum recorded on study ({nadir_sum} mm). Please confirm the iRECIST response recorded for this visit against the source imaging report.</t>
+        </is>
+      </c>
+      <c r="G60" s="12" t="inlineStr">
+        <is>
+          <t>The commonest cause is the site applying RECIST 1.1 habits to an iRECIST study. Where both RECIST 1.1 and iRECIST responses are collected, the RECIST 1.1 field correctly reads PD while the iRECIST field should read iUPD — the two are not in conflict.</t>
+        </is>
+      </c>
+      <c r="H60" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I60" s="58" t="inlineStr">
         <is>
           <t>RECIST 1.1 progression criteria are met at {visit} and the iRECIST response is recorded as {reported_irecist}. Under iRECIST the first occurrence of progression should be recorded as unconfirmed progression (iUPD), with confirmation at the next assessment. Please review.</t>
         </is>
       </c>
-      <c r="G60" s="12" t="inlineStr">
-        <is>
-          <t>The commonest cause is the site applying RECIST 1.1 habits to an iRECIST study. Where both RECIST 1.1 and iRECIST responses are collected, the RECIST 1.1 field correctly reads PD while the iRECIST field should read iUPD — the two are not in conflict.</t>
-        </is>
-      </c>
-      <c r="H60" s="52" t="n"/>
-      <c r="I60" s="52" t="n"/>
-      <c r="J60" s="53" t="n"/>
+      <c r="J60" s="33" t="n"/>
+      <c r="K60" s="34" t="n"/>
     </row>
     <row r="61" ht="108" customHeight="1">
       <c r="A61" s="25" t="inlineStr">
@@ -16486,7 +18505,7 @@
           <t>iRECIST requires the confirmatory assessment between {window_min} and {window_max} days after unconfirmed progression. Assessing too early risks confirming transient pseudoprogression as true progression; assessing too late leaves the subject on a potentially ineffective therapy and leaves the progression date ambiguous. Without a confirmatory assessment, progression remains unconfirmed and the subject's progression status for analysis is indeterminate.</t>
         </is>
       </c>
-      <c r="F61" s="51" t="inlineStr">
+      <c r="F61" s="56" t="inlineStr">
         <is>
           <t>Unconfirmed progression was recorded at {iupd_visit} on {iupd_date}. {confirmation_situation}. Please confirm whether a confirmatory tumor assessment was performed and enter the data, or record the reason it was not performed.</t>
         </is>
@@ -16496,12 +18515,17 @@
           <t>Where the subject discontinued treatment at unconfirmed progression, no confirmation is expected and this finding should be rejected with that reason; check the disposition data before querying.</t>
         </is>
       </c>
-      <c r="H61" s="52" t="n"/>
-      <c r="I61" s="52" t="n"/>
-      <c r="J61" s="53" t="n"/>
+      <c r="H61" s="25" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I61" s="22" t="inlineStr"/>
+      <c r="J61" s="33" t="n"/>
+      <c r="K61" s="34" t="n"/>
     </row>
     <row r="62" ht="108" customHeight="1">
-      <c r="A62" s="23" t="inlineStr">
+      <c r="A62" s="57" t="inlineStr">
         <is>
           <t>TE-IR-003</t>
         </is>
@@ -16526,22 +18550,31 @@
           <t>Confirmation of progression requires further worsening in the category that drove the unconfirmed progression: an increase of at least {target_increment} mm in the target lesion sum relative to the unconfirmed progression timepoint, further unequivocal worsening of non-target disease, an increase of at least {new_increment} mm in the sum of new measurable lesions, or the appearance of additional new lesions. A new category independently meeting RECIST 1.1 progression criteria also confirms. None of these is evident here, so the response should remain unconfirmed progression or reset according to the current burden.</t>
         </is>
       </c>
-      <c r="F62" s="51" t="inlineStr">
+      <c r="F62" s="35" t="inlineStr">
+        <is>
+          <t>Confirmed progression is recorded at {visit}. Unconfirmed progression was recorded at {iupd_visit}, driven by {driver}, and the current assessment shows {confirmation_evidence}. Please confirm the response recorded at {visit} against the source imaging report.</t>
+        </is>
+      </c>
+      <c r="G62" s="12" t="inlineStr">
+        <is>
+          <t>Note the reference point: confirmation compares against the unconfirmed progression timepoint, not against the nadir. This differs from RECIST 1.1 and is a frequent source of confusion.</t>
+        </is>
+      </c>
+      <c r="H62" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I62" s="58" t="inlineStr">
         <is>
           <t>Confirmed progression is recorded at {visit}. The unconfirmed progression at {iupd_visit} was driven by {driver}, and the current assessment shows {confirmation_evidence}. Please review the confirmation of progression against the iRECIST criteria.</t>
         </is>
       </c>
-      <c r="G62" s="12" t="inlineStr">
-        <is>
-          <t>Note the reference point: confirmation compares against the unconfirmed progression timepoint, not against the nadir. This differs from RECIST 1.1 and is a frequent source of confusion.</t>
-        </is>
-      </c>
-      <c r="H62" s="52" t="n"/>
-      <c r="I62" s="52" t="n"/>
-      <c r="J62" s="53" t="n"/>
+      <c r="J62" s="33" t="n"/>
+      <c r="K62" s="34" t="n"/>
     </row>
     <row r="63" ht="108" customHeight="1">
-      <c r="A63" s="25" t="inlineStr">
+      <c r="A63" s="57" t="inlineStr">
         <is>
           <t>TE-IR-004</t>
         </is>
@@ -16566,22 +18599,31 @@
           <t>Under iRECIST, new lesions are recorded and measured separately from the baseline target lesions, with their own sum of up to five new measurable lesions, two per organ. They are never added to the baseline target sum, because the baseline sum must remain comparable to baseline for response assessment, while the new lesion sum is used to judge confirmation of progression. Combining them corrupts both.</t>
         </is>
       </c>
-      <c r="F63" s="51" t="inlineStr">
+      <c r="F63" s="35" t="inlineStr">
+        <is>
+          <t>The sum of diameters recorded at {visit} appears to include measurements of lesions recorded as new. Please confirm which lesions are included in the sum of diameters at this visit.</t>
+        </is>
+      </c>
+      <c r="G63" s="22" t="inlineStr">
+        <is>
+          <t>Confirm the eCRF design supports separate new lesion recording; where it does not, this is a study set-up issue affecting every iRECIST subject rather than a site error.</t>
+        </is>
+      </c>
+      <c r="H63" s="25" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I63" s="59" t="inlineStr">
         <is>
           <t>The sum of diameters at {visit} appears to include the measurements of new lesions. Under iRECIST new lesions are recorded and summed separately from the baseline target lesions. Please review the sum of diameters and the new lesion records.</t>
         </is>
       </c>
-      <c r="G63" s="22" t="inlineStr">
-        <is>
-          <t>Confirm the eCRF design supports separate new lesion recording; where it does not, this is a study set-up issue affecting every iRECIST subject rather than a site error.</t>
-        </is>
-      </c>
-      <c r="H63" s="52" t="n"/>
-      <c r="I63" s="52" t="n"/>
-      <c r="J63" s="53" t="n"/>
+      <c r="J63" s="33" t="n"/>
+      <c r="K63" s="34" t="n"/>
     </row>
     <row r="64" ht="108" customHeight="1">
-      <c r="A64" s="23" t="inlineStr">
+      <c r="A64" s="57" t="inlineStr">
         <is>
           <t>TE-IR-005</t>
         </is>
@@ -16606,22 +18648,31 @@
           <t>If confirmation criteria are not met, the subject's response resets to iCR, iPR or iSD according to the current tumor burden measured against the original nadir. The nadir is not reset by the unconfirmed progression, so a later increase can again produce unconfirmed progression. This is the mechanism by which iRECIST accommodates pseudoprogression.</t>
         </is>
       </c>
-      <c r="F64" s="51" t="inlineStr">
+      <c r="F64" s="35" t="inlineStr">
+        <is>
+          <t>Unconfirmed progression was recorded at {iupd_visit} and was not confirmed at {visit}. The iRECIST response at {visit} is recorded as {reported_irecist}, with a sum of diameters of {sum} mm. Please confirm the iRECIST response recorded for this visit.</t>
+        </is>
+      </c>
+      <c r="G64" s="12" t="inlineStr">
+        <is>
+          <t>Multiple episodes of unconfirmed progression are permitted and are not an error. What is not permitted is treating the unconfirmed progression sum as the new reference.</t>
+        </is>
+      </c>
+      <c r="H64" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I64" s="58" t="inlineStr">
         <is>
           <t>Unconfirmed progression was recorded at {iupd_visit} and was not confirmed at {visit}. The response at {visit} is recorded as {reported_irecist}; based on the current sum of {sum} mm against the nadir of {nadir_sum} mm the response derives as {derived_irecist}. Please review.</t>
         </is>
       </c>
-      <c r="G64" s="12" t="inlineStr">
-        <is>
-          <t>Multiple episodes of unconfirmed progression are permitted and are not an error. What is not permitted is treating the unconfirmed progression sum as the new reference.</t>
-        </is>
-      </c>
-      <c r="H64" s="52" t="n"/>
-      <c r="I64" s="52" t="n"/>
-      <c r="J64" s="53" t="n"/>
+      <c r="J64" s="33" t="n"/>
+      <c r="K64" s="34" t="n"/>
     </row>
     <row r="65" ht="108" customHeight="1">
-      <c r="A65" s="25" t="inlineStr">
+      <c r="A65" s="57" t="inlineStr">
         <is>
           <t>TE-IR-006</t>
         </is>
@@ -16646,19 +18697,28 @@
           <t>The new lesion sum is used to judge confirmation of progression, so it must be constructed consistently. Additional new lesions beyond the limits are recorded as new non-target lesions rather than measured.</t>
         </is>
       </c>
-      <c r="F65" s="51" t="inlineStr">
+      <c r="F65" s="35" t="inlineStr">
+        <is>
+          <t>{n} new measurable lesions are recorded for this subject. This study records up to {max_total} new measurable lesions in total and {max_per_organ} per organ, with any further new lesions recorded as non-target. Please review the new lesion records.</t>
+        </is>
+      </c>
+      <c r="G65" s="22" t="inlineStr">
+        <is>
+          <t>The appearance of numerous new lesions is itself strong evidence of true progression, so this finding is usually a recording issue rather than a clinical question.</t>
+        </is>
+      </c>
+      <c r="H65" s="25" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I65" s="59" t="inlineStr">
         <is>
           <t>{n} new measurable lesions are recorded for this subject. iRECIST permits up to {max_total} new measurable lesions in total, and {max_per_organ} per organ, with any further new lesions recorded as non-target. Please review the new lesion records.</t>
         </is>
       </c>
-      <c r="G65" s="22" t="inlineStr">
-        <is>
-          <t>The appearance of numerous new lesions is itself strong evidence of true progression, so this finding is usually a recording issue rather than a clinical question.</t>
-        </is>
-      </c>
-      <c r="H65" s="52" t="n"/>
-      <c r="I65" s="52" t="n"/>
-      <c r="J65" s="53" t="n"/>
+      <c r="J65" s="33" t="n"/>
+      <c r="K65" s="34" t="n"/>
     </row>
     <row r="66" ht="108" customHeight="1">
       <c r="A66" s="23" t="inlineStr">
@@ -16686,7 +18746,7 @@
           <t>Confirmed progression is the terminal response state. Later assessments may be collected for follow-up, but assigning a non-progression response after confirmed progression is inconsistent and risks the later response being carried into the best overall response derivation.</t>
         </is>
       </c>
-      <c r="F66" s="51" t="inlineStr">
+      <c r="F66" s="56" t="inlineStr">
         <is>
           <t>Assessments after the confirmed progression at {icpd_visit} carry responses of {later_responses}. Please confirm the progression status and the response assessments recorded after it.</t>
         </is>
@@ -16696,9 +18756,14 @@
           <t>Check whether the earlier assessment was in fact unconfirmed rather than confirmed progression; a mislabelled iCPD is the more likely error.</t>
         </is>
       </c>
-      <c r="H66" s="52" t="n"/>
-      <c r="I66" s="52" t="n"/>
-      <c r="J66" s="53" t="n"/>
+      <c r="H66" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I66" s="12" t="inlineStr"/>
+      <c r="J66" s="33" t="n"/>
+      <c r="K66" s="34" t="n"/>
     </row>
     <row r="67" ht="108" customHeight="1">
       <c r="A67" s="25" t="inlineStr">
@@ -16726,7 +18791,7 @@
           <t>iRECIST permits treatment beyond unconfirmed progression only where the subject is clinically stable: no decline in performance status, no worsening of symptoms attributable to disease, and no need for intensified management. The documentation supports both subject safety and the interpretation of the subsequent assessment.</t>
         </is>
       </c>
-      <c r="F67" s="51" t="inlineStr">
+      <c r="F67" s="56" t="inlineStr">
         <is>
           <t>Treatment continued after unconfirmed progression at {iupd_visit}. Please confirm that the subject was assessed as clinically stable at that time and that this is documented.</t>
         </is>
@@ -16736,12 +18801,17 @@
           <t>This is a protocol compliance point as much as a data point; where the eCRF has no field for it, escalate to the monitoring team rather than issuing a data query.</t>
         </is>
       </c>
-      <c r="H67" s="52" t="n"/>
-      <c r="I67" s="52" t="n"/>
-      <c r="J67" s="53" t="n"/>
+      <c r="H67" s="25" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I67" s="22" t="inlineStr"/>
+      <c r="J67" s="33" t="n"/>
+      <c r="K67" s="34" t="n"/>
     </row>
     <row r="68" ht="108" customHeight="1">
-      <c r="A68" s="23" t="inlineStr">
+      <c r="A68" s="57" t="inlineStr">
         <is>
           <t>TE-IR-009</t>
         </is>
@@ -16766,19 +18836,28 @@
           <t>The iRECIST assessment is derived from the same underlying measurements as the RECIST 1.1 assessment, differing only in the treatment of progression and new lesions. Given the RECIST 1.1 result at this timepoint and the preceding response history, the iRECIST response should be {expected_irecist}.</t>
         </is>
       </c>
-      <c r="F68" s="51" t="inlineStr">
+      <c r="F68" s="35" t="inlineStr">
+        <is>
+          <t>The RECIST 1.1 and iRECIST responses recorded at {visit} are {r11_response} and {reported_irecist}. Please confirm both response fields for this visit against the source imaging report.</t>
+        </is>
+      </c>
+      <c r="G68" s="12" t="inlineStr">
+        <is>
+          <t>Where the two fields are on separate forms completed by different people, expect systematic divergence at a site; treat that as a training signal rather than a per-record query.</t>
+        </is>
+      </c>
+      <c r="H68" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I68" s="58" t="inlineStr">
         <is>
           <t>The RECIST 1.1 and iRECIST responses recorded at {visit} are {r11_response} and {reported_irecist}. Based on the response history the iRECIST response would be expected to be {expected_irecist}. Please review.</t>
         </is>
       </c>
-      <c r="G68" s="12" t="inlineStr">
-        <is>
-          <t>Where the two fields are on separate forms completed by different people, expect systematic divergence at a site; treat that as a training signal rather than a per-record query.</t>
-        </is>
-      </c>
-      <c r="H68" s="52" t="n"/>
-      <c r="I68" s="52" t="n"/>
-      <c r="J68" s="53" t="n"/>
+      <c r="J68" s="33" t="n"/>
+      <c r="K68" s="34" t="n"/>
     </row>
     <row r="69" ht="108" customHeight="1">
       <c r="A69" s="25" t="inlineStr">
@@ -16806,7 +18885,7 @@
           <t>If iRECIST is specified but not collected, pseudoprogression cannot be distinguished from true progression, and subjects may be discontinued prematurely. If iRECIST is collected but not specified in the protocol, the analysis convention is undefined. Either way the endpoint derivation is at risk across the whole study.</t>
         </is>
       </c>
-      <c r="F69" s="51" t="inlineStr">
+      <c r="F69" s="56" t="inlineStr">
         <is>
           <t>Not applicable: this is a study set-up finding for the study team rather than a site query.</t>
         </is>
@@ -16816,9 +18895,14 @@
           <t>Raise with the study data manager and the biostatistician; resolution usually requires a database change rather than data correction.</t>
         </is>
       </c>
-      <c r="H69" s="52" t="n"/>
-      <c r="I69" s="52" t="n"/>
-      <c r="J69" s="53" t="n"/>
+      <c r="H69" s="25" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I69" s="22" t="inlineStr"/>
+      <c r="J69" s="33" t="n"/>
+      <c r="K69" s="34" t="n"/>
     </row>
     <row r="70" ht="108" customHeight="1">
       <c r="A70" s="23" t="inlineStr">
@@ -16846,7 +18930,7 @@
           <t>If treatment stopped for progression, either an assessment demonstrating progression is missing from the tumor data, or the discontinuation reason is incorrect. Both affect the progression-free survival analysis: a missing progression event leads to censoring instead of an event.</t>
         </is>
       </c>
-      <c r="F70" s="51" t="inlineStr">
+      <c r="F70" s="56" t="inlineStr">
         <is>
           <t>Treatment was discontinued for {disposition_reason} on {disposition_date}, but no tumor assessment recording progression is present. Please confirm whether a tumor assessment demonstrating progression was performed, and enter the data if so; if progression was determined clinically, please confirm the basis and the date.</t>
         </is>
@@ -16856,9 +18940,14 @@
           <t>Clinical progression without radiological confirmation is legitimate and common near end of life; the record should show it as such rather than leaving the tumor data silent.</t>
         </is>
       </c>
-      <c r="H70" s="52" t="n"/>
-      <c r="I70" s="52" t="n"/>
-      <c r="J70" s="53" t="n"/>
+      <c r="H70" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I70" s="12" t="inlineStr"/>
+      <c r="J70" s="33" t="n"/>
+      <c r="K70" s="34" t="n"/>
     </row>
     <row r="71" ht="108" customHeight="1">
       <c r="A71" s="25" t="inlineStr">
@@ -16886,7 +18975,7 @@
           <t>Treatment beyond progression may be permitted by the protocol, but it must be documented, and it changes the interpretation of subsequent assessments. Where it is not permitted, this is a protocol deviation. Where the study uses iRECIST, the earlier assessment may have been unconfirmed progression rather than confirmed progression, in which case continuation is expected and the response coding needs review instead.</t>
         </is>
       </c>
-      <c r="F71" s="51" t="inlineStr">
+      <c r="F71" s="56" t="inlineStr">
         <is>
           <t>Study treatment continued for {days} days after the progression recorded at {pd_visit}. Please confirm the progression assessment and whether continuation beyond progression was approved.</t>
         </is>
@@ -16896,9 +18985,14 @@
           <t>Check the applicable response criteria first — under iRECIST this pattern is normal and the finding should be rejected.</t>
         </is>
       </c>
-      <c r="H71" s="52" t="n"/>
-      <c r="I71" s="52" t="n"/>
-      <c r="J71" s="53" t="n"/>
+      <c r="H71" s="25" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I71" s="22" t="inlineStr"/>
+      <c r="J71" s="33" t="n"/>
+      <c r="K71" s="34" t="n"/>
     </row>
     <row r="72" ht="108" customHeight="1">
       <c r="A72" s="23" t="inlineStr">
@@ -16926,7 +19020,7 @@
           <t>Starting a new anticancer therapy before recorded progression usually indicates that progression occurred but was not captured, or that treatment changed for another documented reason. In progression-free survival analyses the start of new therapy is commonly a censoring or event-defining event, so the discrepancy has direct analytical consequences, and any tumor assessment after the new therapy no longer reflects the study treatment.</t>
         </is>
       </c>
-      <c r="F72" s="51" t="inlineStr">
+      <c r="F72" s="56" t="inlineStr">
         <is>
           <t>A new anticancer therapy ({therapy}) started on {therapy_date}, before any recorded disease progression. Please confirm the reason for starting new therapy and whether a tumor assessment demonstrating progression was performed.</t>
         </is>
@@ -16936,9 +19030,14 @@
           <t>Radiotherapy for symptom palliation is a frequent benign explanation; distinguish it from a change of systemic therapy.</t>
         </is>
       </c>
-      <c r="H72" s="52" t="n"/>
-      <c r="I72" s="52" t="n"/>
-      <c r="J72" s="53" t="n"/>
+      <c r="H72" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I72" s="12" t="inlineStr"/>
+      <c r="J72" s="33" t="n"/>
+      <c r="K72" s="34" t="n"/>
     </row>
     <row r="73" ht="108" customHeight="1">
       <c r="A73" s="25" t="inlineStr">
@@ -16966,7 +19065,7 @@
           <t>Once a lesion has received locoregional therapy, its subsequent size no longer reflects the systemic treatment effect, and RECIST treats such lesions as non-measurable unless progression is demonstrated. Continuing to include it in the sum understates tumor burden and can produce a spurious partial response.</t>
         </is>
       </c>
-      <c r="F73" s="51" t="inlineStr">
+      <c r="F73" s="56" t="inlineStr">
         <is>
           <t>{procedure} was applied to {site} on {procedure_date}, which corresponds to target lesion {lesion_id}. Please confirm and clarify how this lesion has been assessed at subsequent visits.</t>
         </is>
@@ -16976,9 +19075,14 @@
           <t>The usual analytical convention is that the subject is considered to have progressed, or is censored, at the time of local therapy to a target lesion; confirm the protocol's convention with the statistician.</t>
         </is>
       </c>
-      <c r="H73" s="52" t="n"/>
-      <c r="I73" s="52" t="n"/>
-      <c r="J73" s="53" t="n"/>
+      <c r="H73" s="25" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I73" s="22" t="inlineStr"/>
+      <c r="J73" s="33" t="n"/>
+      <c r="K73" s="34" t="n"/>
     </row>
     <row r="74" ht="108" customHeight="1">
       <c r="A74" s="23" t="inlineStr">
@@ -17006,7 +19110,7 @@
           <t>An adverse event of disease progression implies a clinical determination of progression. If the tumor data does not reflect it, the progression event may be missing from the efficacy analysis, or the adverse event may have been coded inappropriately — disease progression is frequently reported as an adverse event when it should be captured as an efficacy outcome.</t>
         </is>
       </c>
-      <c r="F74" s="51" t="inlineStr">
+      <c r="F74" s="56" t="inlineStr">
         <is>
           <t>An adverse event of "{ae_term}" is recorded with onset {ae_date}. Please confirm whether disease progression was documented and whether a tumor assessment was performed at that time.</t>
         </is>
@@ -17016,9 +19120,14 @@
           <t>Many sponsors instruct sites not to report disease progression as an adverse event; where that convention applies, the finding is also a coding issue for the safety team.</t>
         </is>
       </c>
-      <c r="H74" s="52" t="n"/>
-      <c r="I74" s="52" t="n"/>
-      <c r="J74" s="53" t="n"/>
+      <c r="H74" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I74" s="12" t="inlineStr"/>
+      <c r="J74" s="33" t="n"/>
+      <c r="K74" s="34" t="n"/>
     </row>
     <row r="75" ht="108" customHeight="1">
       <c r="A75" s="25" t="inlineStr">
@@ -17046,7 +19155,7 @@
           <t>A tumor assessment or progression date after the date of death is impossible, so one of the dates is wrong. Both feed survival and progression-free survival analyses directly.</t>
         </is>
       </c>
-      <c r="F75" s="51" t="inlineStr">
+      <c r="F75" s="56" t="inlineStr">
         <is>
           <t>The date of death ({death_date}) precedes {conflicting_record} ({conflict_date}). Please verify both dates.</t>
         </is>
@@ -17056,9 +19165,14 @@
           <t>Partial dates are a frequent cause; check whether an imputed date is being compared against a complete one.</t>
         </is>
       </c>
-      <c r="H75" s="52" t="n"/>
-      <c r="I75" s="52" t="n"/>
-      <c r="J75" s="53" t="n"/>
+      <c r="H75" s="25" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I75" s="22" t="inlineStr"/>
+      <c r="J75" s="33" t="n"/>
+      <c r="K75" s="34" t="n"/>
     </row>
     <row r="76" ht="108" customHeight="1">
       <c r="A76" s="23" t="inlineStr">
@@ -17086,7 +19200,7 @@
           <t>Where the protocol includes tumor markers in the response definition, a complete response requires marker normalisation in addition to the disappearance of all lesions. A persistently elevated marker means the response is Non-CR/Non-PD.</t>
         </is>
       </c>
-      <c r="F76" s="51" t="inlineStr">
+      <c r="F76" s="56" t="inlineStr">
         <is>
           <t>A complete response is recorded at {visit} while {marker} remains above the upper limit of normal ({value} {unit}). Please review the response assessment.</t>
         </is>
@@ -17096,9 +19210,14 @@
           <t>Marker elevation can have non-malignant causes; the site's explanation may be sufficient without a data change.</t>
         </is>
       </c>
-      <c r="H76" s="52" t="n"/>
-      <c r="I76" s="52" t="n"/>
-      <c r="J76" s="53" t="n"/>
+      <c r="H76" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I76" s="12" t="inlineStr"/>
+      <c r="J76" s="33" t="n"/>
+      <c r="K76" s="34" t="n"/>
     </row>
     <row r="77" ht="108" customHeight="1">
       <c r="A77" s="25" t="inlineStr">
@@ -17126,7 +19245,7 @@
           <t>Modalities differ in sensitivity and in measurement reproducibility. Using a modality outside the protocol makes the measurement non-comparable with the rest of the subject's data and with other subjects.</t>
         </is>
       </c>
-      <c r="F77" s="51" t="inlineStr">
+      <c r="F77" s="56" t="inlineStr">
         <is>
           <t>Lesion {lesion_id} was assessed by {method} at {visit}, which is not among the modalities specified in the protocol. Please confirm the modality used.</t>
         </is>
@@ -17136,9 +19255,14 @@
           <t>Contrast versus non-contrast CT is the most consequential variant and is often not captured as a distinct modality; consider whether the eCRF should distinguish them.</t>
         </is>
       </c>
-      <c r="H77" s="52" t="n"/>
-      <c r="I77" s="52" t="n"/>
-      <c r="J77" s="53" t="n"/>
+      <c r="H77" s="25" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I77" s="22" t="inlineStr"/>
+      <c r="J77" s="33" t="n"/>
+      <c r="K77" s="34" t="n"/>
     </row>
     <row r="78" ht="108" customHeight="1">
       <c r="A78" s="23" t="inlineStr">
@@ -17166,7 +19290,7 @@
           <t>Disease in an unimaged region cannot be assessed, and a lesion later found there must be treated as a new lesion. Missing required imaging therefore both reduces the reliability of the current response and risks a spurious progression later.</t>
         </is>
       </c>
-      <c r="F78" s="51" t="inlineStr">
+      <c r="F78" s="56" t="inlineStr">
         <is>
           <t>No assessment of {required_region} is recorded at {visit} although the protocol requires it. Please confirm whether the imaging was performed and enter the results.</t>
         </is>
@@ -17176,9 +19300,14 @@
           <t>Brain imaging is the usual case, particularly in lung cancer and melanoma studies.</t>
         </is>
       </c>
-      <c r="H78" s="52" t="n"/>
-      <c r="I78" s="52" t="n"/>
-      <c r="J78" s="53" t="n"/>
+      <c r="H78" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I78" s="12" t="inlineStr"/>
+      <c r="J78" s="33" t="n"/>
+      <c r="K78" s="34" t="n"/>
     </row>
     <row r="79" ht="108" customHeight="1">
       <c r="A79" s="25" t="inlineStr">
@@ -17206,7 +19335,7 @@
           <t>The best overall response cannot be better than any response actually recorded at a timepoint. This indicates either a missing timepoint assessment or an incorrect best overall response.</t>
         </is>
       </c>
-      <c r="F79" s="51" t="inlineStr">
+      <c r="F79" s="56" t="inlineStr">
         <is>
           <t>The best overall response is recorded as {reported_bor}, but the best response recorded at any timepoint is {best_timepoint}. Please review.</t>
         </is>
@@ -17216,9 +19345,14 @@
           <t>Check for an unscheduled assessment that was not entered; a response confirmed at an unscheduled visit is a common cause.</t>
         </is>
       </c>
-      <c r="H79" s="52" t="n"/>
-      <c r="I79" s="52" t="n"/>
-      <c r="J79" s="53" t="n"/>
+      <c r="H79" s="25" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I79" s="22" t="inlineStr"/>
+      <c r="J79" s="33" t="n"/>
+      <c r="K79" s="34" t="n"/>
     </row>
     <row r="80" ht="108" customHeight="1">
       <c r="A80" s="23" t="inlineStr">
@@ -17246,7 +19380,7 @@
           <t>A treated subject with no post-baseline assessment is not evaluable for response and is censored at randomisation or treatment start in progression-free survival, which reduces the power of the analysis. The reason should be documented.</t>
         </is>
       </c>
-      <c r="F80" s="51" t="inlineStr">
+      <c r="F80" s="56" t="inlineStr">
         <is>
           <t>No post-baseline tumor assessment is recorded for this subject. Please confirm whether an assessment was performed, and record the reason if it was not.</t>
         </is>
@@ -17256,9 +19390,14 @@
           <t>Early death or early withdrawal are the usual explanations and are legitimate; the finding exists to ensure the reason is captured.</t>
         </is>
       </c>
-      <c r="H80" s="52" t="n"/>
-      <c r="I80" s="52" t="n"/>
-      <c r="J80" s="53" t="n"/>
+      <c r="H80" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I80" s="12" t="inlineStr"/>
+      <c r="J80" s="33" t="n"/>
+      <c r="K80" s="34" t="n"/>
     </row>
     <row r="81" ht="108" customHeight="1">
       <c r="A81" s="25" t="inlineStr">
@@ -17286,7 +19425,7 @@
           <t>A concentration of the same issue at one site usually reflects a training or process gap rather than isolated errors. Addressing it at the site level resolves the whole cluster and prevents recurrence, whereas issuing individual queries treats the symptom.</t>
         </is>
       </c>
-      <c r="F81" s="51" t="inlineStr">
+      <c r="F81" s="56" t="inlineStr">
         <is>
           <t>Not applicable: this finding is directed to the monitoring team rather than to the site as a data query.</t>
         </is>
@@ -17296,9 +19435,14 @@
           <t>Pair with a site training action and re-check at the next data cut; the recurrence status on the linked findings will show whether the intervention worked.</t>
         </is>
       </c>
-      <c r="H81" s="52" t="n"/>
-      <c r="I81" s="52" t="n"/>
-      <c r="J81" s="53" t="n"/>
+      <c r="H81" s="25" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I81" s="22" t="inlineStr"/>
+      <c r="J81" s="33" t="n"/>
+      <c r="K81" s="34" t="n"/>
     </row>
     <row r="82" ht="108" customHeight="1">
       <c r="A82" s="23" t="inlineStr">
@@ -17326,7 +19470,7 @@
           <t>Re-issuing a query that is already outstanding creates duplicate work at the site and confuses the audit trail. The finding is retained and linked, but is suppressed from the default worklist until the query is answered.</t>
         </is>
       </c>
-      <c r="F82" s="51" t="inlineStr">
+      <c r="F82" s="56" t="inlineStr">
         <is>
           <t>Not applicable: no new query is required.</t>
         </is>
@@ -17336,9 +19480,14 @@
           <t>If the outstanding query is materially different in scope from this finding, disposition the finding as NEW manually and issue a distinct query.</t>
         </is>
       </c>
-      <c r="H82" s="52" t="n"/>
-      <c r="I82" s="52" t="n"/>
-      <c r="J82" s="53" t="n"/>
+      <c r="H82" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I82" s="12" t="inlineStr"/>
+      <c r="J82" s="33" t="n"/>
+      <c r="K82" s="34" t="n"/>
     </row>
     <row r="83" ht="108" customHeight="1">
       <c r="A83" s="25" t="inlineStr">
@@ -17366,7 +19515,7 @@
           <t>The query was resolved without the data being corrected. The site's answer does not explain why the current values are correct, so the issue survives into the locked database. Where an answer does justify the data, this finding is suppressed instead and the justification is recorded against the record.</t>
         </is>
       </c>
-      <c r="F83" s="51" t="inlineStr">
+      <c r="F83" s="56" t="inlineStr">
         <is>
           <t>Query {query_id} regarding {issue_summary} was answered on {resolution_date}, but the data still shows {current_state}. Please clarify: if the data is correct as entered, please explain the basis; otherwise please make the correction.</t>
         </is>
@@ -17376,9 +19525,14 @@
           <t>Read the original answer in full before re-querying — it is quoted above. Where the site confirmed the data is correct and the explanation holds, disposition this as justified so it is not raised again at the next data cut.</t>
         </is>
       </c>
-      <c r="H83" s="52" t="n"/>
-      <c r="I83" s="52" t="n"/>
-      <c r="J83" s="53" t="n"/>
+      <c r="H83" s="25" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I83" s="22" t="inlineStr"/>
+      <c r="J83" s="33" t="n"/>
+      <c r="K83" s="34" t="n"/>
     </row>
     <row r="84" ht="108" customHeight="1">
       <c r="A84" s="23" t="inlineStr">
@@ -17406,7 +19560,7 @@
           <t>A recurrence usually means either that a data correction was reverted, or that a subsequent data entry reintroduced the same error. Both are worth understanding, because the same cause is likely to affect other records.</t>
         </is>
       </c>
-      <c r="F84" s="51" t="inlineStr">
+      <c r="F84" s="56" t="inlineStr">
         <is>
           <t>This issue was previously raised and resolved on {previous_resolution_date}, and is present again in the current data. Please confirm the current value and clarify the reason for the change.</t>
         </is>
@@ -17416,9 +19570,14 @@
           <t>Compare the audit trail of the affected field across the two data cuts; a reverted correction and a fresh error need different responses.</t>
         </is>
       </c>
-      <c r="H84" s="52" t="n"/>
-      <c r="I84" s="52" t="n"/>
-      <c r="J84" s="53" t="n"/>
+      <c r="H84" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I84" s="12" t="inlineStr"/>
+      <c r="J84" s="33" t="n"/>
+      <c r="K84" s="34" t="n"/>
     </row>
     <row r="85" ht="108" customHeight="1">
       <c r="A85" s="25" t="inlineStr">
@@ -17446,7 +19605,7 @@
           <t>Endpoint-critical data cannot be locked while the query is outstanding, and late resolution compresses the timeline before database lock. Ageing queries on response data are a leading cause of lock delay.</t>
         </is>
       </c>
-      <c r="F85" s="51" t="inlineStr">
+      <c r="F85" s="56" t="inlineStr">
         <is>
           <t>Not applicable: this finding is for the study team's query management rather than a new site query.</t>
         </is>
@@ -17456,9 +19615,14 @@
           <t>Escalate through the monitoring team rather than by reissuing the query.</t>
         </is>
       </c>
-      <c r="H85" s="52" t="n"/>
-      <c r="I85" s="52" t="n"/>
-      <c r="J85" s="53" t="n"/>
+      <c r="H85" s="25" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I85" s="22" t="inlineStr"/>
+      <c r="J85" s="33" t="n"/>
+      <c r="K85" s="34" t="n"/>
     </row>
     <row r="86" ht="108" customHeight="1">
       <c r="A86" s="23" t="inlineStr">
@@ -17486,7 +19650,7 @@
           <t>An unresponsive answer that is nonetheless accepted closes the query without resolving the underlying data question, so the issue survives into the locked database.</t>
         </is>
       </c>
-      <c r="F86" s="51" t="inlineStr">
+      <c r="F86" s="56" t="inlineStr">
         <is>
           <t>Thank you for the response to query {query_id}. The original question concerned {query_summary}; could you please also confirm {outstanding_point}?</t>
         </is>
@@ -17496,9 +19660,14 @@
           <t>Site answers are often correct but terse. Read the original answer in full before re-querying; the model flags candidates rather than making the determination.</t>
         </is>
       </c>
-      <c r="H86" s="52" t="n"/>
-      <c r="I86" s="52" t="n"/>
-      <c r="J86" s="53" t="n"/>
+      <c r="H86" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I86" s="12" t="inlineStr"/>
+      <c r="J86" s="33" t="n"/>
+      <c r="K86" s="34" t="n"/>
     </row>
     <row r="87" ht="108" customHeight="1">
       <c r="A87" s="25" t="inlineStr">
@@ -17526,7 +19695,7 @@
           <t>Corrections made in isolation frequently break a dependent value — most often a lesion measurement corrected without the sum or the response being updated. The correction should be applied consistently across the dependent fields.</t>
         </is>
       </c>
-      <c r="F87" s="51" t="inlineStr">
+      <c r="F87" s="56" t="inlineStr">
         <is>
           <t>Following the correction to {field} at {visit}, {new_issue_summary}. Please review the related fields so the assessment is internally consistent.</t>
         </is>
@@ -17536,9 +19705,14 @@
           <t>This is why measurement corrections should always be reviewed together with the sum and the response for the same timepoint, and for all later timepoints if the nadir moved.</t>
         </is>
       </c>
-      <c r="H87" s="52" t="n"/>
-      <c r="I87" s="52" t="n"/>
-      <c r="J87" s="53" t="n"/>
+      <c r="H87" s="25" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I87" s="22" t="inlineStr"/>
+      <c r="J87" s="33" t="n"/>
+      <c r="K87" s="34" t="n"/>
     </row>
     <row r="88" ht="108" customHeight="1">
       <c r="A88" s="23" t="inlineStr">
@@ -17566,7 +19740,7 @@
           <t>RECIST 1.1 requires that an effusion appearing or worsening during treatment be confirmed cytologically before it is taken as evidence of progression, where the measurable disease is responding or stable. Effusions arise from causes unrelated to tumor progression, including the treatment itself and intercurrent illness. An unconfirmed effusion is a recognised source of spurious progression, which censors the subject early and shortens progression-free survival.</t>
         </is>
       </c>
-      <c r="F88" s="51" t="inlineStr">
+      <c r="F88" s="56" t="inlineStr">
         <is>
           <t>Progressive disease is recorded at {visit}, supported by {effusion_description}, while target lesions show {target_response_derived}. Please confirm whether cytological assessment of the effusion was performed and record the result. If cytology was not performed, please confirm the basis on which progression was assessed.</t>
         </is>
@@ -17576,18 +19750,23 @@
           <t>This matters most where the effusion is the sole basis for progression; where other unequivocal progression exists the finding is suppressed. Some protocols explicitly waive cytological confirmation — check the protocol before querying, and if it is waived, deactivate this rule at the AC-11 intake rather than dispositioning each occurrence.</t>
         </is>
       </c>
-      <c r="H88" s="52" t="n"/>
-      <c r="I88" s="52" t="n"/>
-      <c r="J88" s="53" t="n"/>
+      <c r="H88" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I88" s="12" t="inlineStr"/>
+      <c r="J88" s="33" t="n"/>
+      <c r="K88" s="34" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J88"/>
+  <autoFilter ref="A3:K88"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="H4:H88" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J4:J88" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Accept,Amend,Reject,Discuss"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/spec/TEA-SPEC-001_programming-specification.xlsx
+++ b/docs/spec/TEA-SPEC-001_programming-specification.xlsx
@@ -16,24 +16,25 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pipeline" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rules" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rule_Messages" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Query_Style" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Confidence_Model" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Query_Reconciliation" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prioritisation" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Input_Contract" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Finding_Contract" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LLM_Integration" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Testing" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Extensibility" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Log" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Approval" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Query_Style" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Confidence_Model" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Query_Reconciliation" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prioritisation" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Input_Contract" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Finding_Contract" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LLM_Integration" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Testing" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Extensibility" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Log" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Definitions'!$A$3:$C$50</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Rules'!$A$3:$U$88</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Rule_Messages'!$A$3:$K$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Rule_Messages'!$A$3:$J$88</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -178,7 +179,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -208,11 +209,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EFF1EE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF9D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -247,7 +243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -331,12 +327,6 @@
     <xf numFmtId="9" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -396,7 +386,10 @@
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -836,7 +829,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>1.3.0 — reviewer-lens pass applied</t>
+          <t>2.0.0 — APPROVED</t>
         </is>
       </c>
     </row>
@@ -848,7 +841,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>DRAFT — 27 rules changed at the reviewer-lens pass; confirm to freeze</t>
+          <t>APPROVED for implementation — rule pack FROZEN at 2.0.0</t>
         </is>
       </c>
     </row>
@@ -884,7 +877,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>v1.2.0, issued 2026-08-21</t>
+          <t>v1.3.0, issued 2026-08-21</t>
         </is>
       </c>
     </row>
@@ -908,7 +901,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>85 review points across 7 families — 83 live, 2 retired</t>
+          <t>85 review points, 83 live, 2 retired — frozen; changes now need change control</t>
         </is>
       </c>
     </row>
@@ -927,54 +920,54 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Review needed</t>
+          <t>Approved by</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>The 27 rules changed at round 3 — see Review_Log and the R3 columns</t>
+          <t>Daniel — 2026-08-21, reasonableness review (see Approval)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>WHERE THE REVIEW STANDS</t>
+          <t>APPROVED — WHAT THAT MEANS</t>
         </is>
       </c>
     </row>
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>•  Rounds 1 and 2 dispositioned all 85 rules, and round 2 confirmed every amendment. Rule_Messages was then accepted in full, and all nine open questions were answered.</t>
+          <t>•  The rule pack is frozen at 2.0.0. From here a rule change is not an edit: it needs a change-control entry, a version bump, and an impact assessment on findings already issued.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>•  Round 3 is a quality pass, not a disposition: the rules and query messages were re-read through a clinical data manager's eyes and a medical monitor's eyes. 27 rules changed.</t>
+          <t>•  Step 2 is closed. Step 3 begins — the prototype run on a curated dummy dataset with a signed-off expected finding list.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>•  19 query messages were rewritten (CDM lens) and 8 rule logics amended (MM lens). Every change carries its before text and the reason, on the Rules and Rule_Messages sheets and on Review_Log.</t>
+          <t>•  The approval was given as a reasonableness review. The reviewer's own words: all the changes look reasonable, the detail was not individually confirmed. The Approval sheet records that exactly, because an approval record should say what happened.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>•  Query_Style is new. It states the house rules these rewrites follow, so rule 86 does not reintroduce the problems fixed in rules 1 to 85.</t>
+          <t>•  That is a workable basis, and Step 3 is what makes it so: the golden dataset tests all 83 live rules against known expected findings, which confirms the detail by evidence rather than by reading. Anything the reasonableness review missed should surface there.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>•  Nothing else changed. The other 58 rules are exactly as you accepted them.</t>
+          <t>•  Two items were approved by the blanket statement rather than marked individually — TE-XD-005, and the 19 rewritten query messages. They are flagged on the Approval sheet, not smoothed over.</t>
         </is>
       </c>
     </row>
@@ -982,28 +975,28 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>THE TWO THINGS THE PASS FOUND</t>
+          <t>WHAT TO WATCH AT STEP 3</t>
         </is>
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>•  CDM lens — nine queries told the site what the answer was ('the overall response should be PD', 'the lesion should be recorded as non-target'). That converts a check into an instruction: the site confirms rather than verifies, and if the agent's derivation is wrong the error comes back signed by the site.</t>
+          <t>•  The 8 rules whose logic changed at round 3 have no test history at all. They are the first place a seeded-case failure would show up.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="26" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>•  MM lens — five rules turned one underlying event into many findings, or fired on data a monitor would never query. Local therapy to one target lesion raised a finding at every subsequent visit; an adverse event of progression raised a query asking for a scan the subject was too unwell to have.</t>
+          <t>•  The 27 confidence base rates below 0.75 are estimates, not measurements. Step 3 calibration is what turns them into numbers worth trusting.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="26" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>•  Both are the kind of thing that costs a review tool its credibility in the first month of use, so they are worth fixing before any code is written.</t>
+          <t>•  Interpretations ID-05 and ID-06 were amended and never separately re-read. ID-06 changed where baseline comes from, which every derivation depends on — worth a deliberate look at the first prototype output.</t>
         </is>
       </c>
     </row>
@@ -1041,6 +1034,340 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="56" customWidth="1" min="2" max="2"/>
+    <col width="92" customWidth="1" min="3" max="3"/>
+    <col width="4" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Step 2 gate — approval record</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>What was approved, by whom, on what basis, and what was not individually confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="58" customHeight="1">
+      <c r="A3" s="30" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>TEA-SPEC-001 Programming Specification, version 2.0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="58" customHeight="1">
+      <c r="A4" s="30" t="inlineStr">
+        <is>
+          <t>Rule pack</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>2.0.0 — FROZEN. Subsequent changes require change control, a version bump and an impact assessment on findings already issued.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="30" t="inlineStr">
+        <is>
+          <t>Approved by</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Daniel, 2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="30" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Reasonableness review. In the reviewer's words: “All the change looks reasonable. I haven’t confirmed all the detail, but good to final.”</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="30" t="inlineStr">
+        <is>
+          <t>Not claimed</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>This is not a line-by-line confirmation of all 85 rules, their logic, their confidence base rates or their query wording. It is recorded as what it is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="30" t="inlineStr">
+        <is>
+          <t>Mitigation</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Step 3 tests all 83 live rules against a curated dataset with a signed-off expected finding list, and measures confidence calibration against reviewer acceptance. Detail not confirmed by reading is confirmed there by evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Review history</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Round</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>85 rules, 8 interpretation decisions</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>70 accept, 14 discuss, 1 reject. 12 rules amended, 2 retired. ID-05 expanded, ID-06 amended.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B13" s="26" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>The 16 rules amended or explained at round 1</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>All confirmed Accept, no comments. Rule logic settled.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>Messages</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>85 query message sets, 9 open questions</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>All 85 accepted. All 9 questions answered; SQ-05 decided that the guideline reference appears only in the reviewer-facing tips.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>Reviewer-lens quality pass — CDM and MM</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>27 rules changed: 19 query texts rewritten, 8 rule logics amended.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>The 27 round-3 changes</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>Approved. 26 marked individually; TE-XD-005 and the 19 Rule_Messages rewrites covered by the blanket approval only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Approved by the blanket statement, not marked individually</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>What changed</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Why it is flagged</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="23" t="inlineStr">
+        <is>
+          <t>TE-XD-005</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>Guarded so it no longer queries a site for a scan the subject was too unwell to have.</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>26 of the 27 round-3 rows carry an individual Accept; this one does not. Almost certainly a missed row rather than a held decision, but the record says so rather than assuming.</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="25" t="inlineStr">
+        <is>
+          <t>Rule_Messages</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>19 query texts rewritten to remove guideline citations and statements of the expected answer.</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>The same changes are visible and marked on the Rules sheet, so this is duplication rather than a gap. Flagged for completeness.</t>
+        </is>
+      </c>
+      <c r="D21" s="26" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="23" t="inlineStr">
+        <is>
+          <t>ID-05, ID-06</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>Amended at round 1; accepted under SQ-03 without being separately re-read.</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>ID-06 changed where baseline comes from, and every derivation depends on baseline. Worth a deliberate look at the first prototype output.</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B6:D6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1359,7 +1686,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1409,9 +1736,9 @@
 # so certainty is never total. A 100% display would invite unread query issuance.</t>
         </is>
       </c>
-      <c r="B4" s="60" t="n"/>
-      <c r="C4" s="60" t="n"/>
-      <c r="D4" s="60" t="n"/>
+      <c r="B4" s="59" t="n"/>
+      <c r="C4" s="59" t="n"/>
+      <c r="D4" s="59" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
@@ -1685,7 +2012,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1750,9 +2077,9 @@
         f.status = RECURRENT</t>
         </is>
       </c>
-      <c r="B4" s="60" t="n"/>
-      <c r="C4" s="60" t="n"/>
-      <c r="D4" s="60" t="n"/>
+      <c r="B4" s="59" t="n"/>
+      <c r="C4" s="59" t="n"/>
+      <c r="D4" s="59" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -1806,7 +2133,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1847,9 +2174,9 @@
 it necessarily causes, so the reviewer fixes the baseline once instead of querying ten visits.</t>
         </is>
       </c>
-      <c r="B4" s="60" t="n"/>
-      <c r="C4" s="60" t="n"/>
-      <c r="D4" s="60" t="n"/>
+      <c r="B4" s="59" t="n"/>
+      <c r="C4" s="59" t="n"/>
+      <c r="D4" s="59" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -1872,9 +2199,9 @@
 where it does rather than having to trust the ordering.</t>
         </is>
       </c>
-      <c r="B7" s="60" t="n"/>
-      <c r="C7" s="60" t="n"/>
-      <c r="D7" s="60" t="n"/>
+      <c r="B7" s="59" t="n"/>
+      <c r="C7" s="59" t="n"/>
+      <c r="D7" s="59" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1886,7 +2213,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1949,7 +2276,7 @@
           <t>study</t>
         </is>
       </c>
-      <c r="B4" s="61" t="inlineStr">
+      <c r="B4" s="60" t="inlineStr">
         <is>
           <t>study_id</t>
         </is>
@@ -1972,7 +2299,7 @@
           <t>study</t>
         </is>
       </c>
-      <c r="B5" s="62" t="inlineStr">
+      <c r="B5" s="61" t="inlineStr">
         <is>
           <t>indication</t>
         </is>
@@ -1999,7 +2326,7 @@
           <t>study</t>
         </is>
       </c>
-      <c r="B6" s="61" t="inlineStr">
+      <c r="B6" s="60" t="inlineStr">
         <is>
           <t>guideline_version</t>
         </is>
@@ -2026,7 +2353,7 @@
           <t>protocol_config</t>
         </is>
       </c>
-      <c r="B7" s="62" t="inlineStr">
+      <c r="B7" s="61" t="inlineStr">
         <is>
           <t>(28 parameters)</t>
         </is>
@@ -2053,7 +2380,7 @@
           <t>subjects</t>
         </is>
       </c>
-      <c r="B8" s="61" t="inlineStr">
+      <c r="B8" s="60" t="inlineStr">
         <is>
           <t>subject_id, site_id, first_dose_date, discontinuation_date, death_date, has_measurable_disease_at_baseline</t>
         </is>
@@ -2076,7 +2403,7 @@
           <t>lesions</t>
         </is>
       </c>
-      <c r="B9" s="62" t="inlineStr">
+      <c r="B9" s="61" t="inlineStr">
         <is>
           <t>lesion_id, category, is_nodal, organ, location_detail, laterality, method, new_lesion_certainty, previously_irradiated</t>
         </is>
@@ -2103,7 +2430,7 @@
           <t>assessments</t>
         </is>
       </c>
-      <c r="B10" s="61" t="inlineStr">
+      <c r="B10" s="60" t="inlineStr">
         <is>
           <t>assessment_id, visit_name, visit_number, assessment_date, scan_dates, is_baseline, evaluator</t>
         </is>
@@ -2126,7 +2453,7 @@
           <t>measurements</t>
         </is>
       </c>
-      <c r="B11" s="62" t="inlineStr">
+      <c r="B11" s="61" t="inlineStr">
         <is>
           <t>assessment_id, lesion_id, value_mm, original_unit, axis_recorded, state, non_target_state, comment_text</t>
         </is>
@@ -2153,7 +2480,7 @@
           <t>reported_responses</t>
         </is>
       </c>
-      <c r="B12" s="61" t="inlineStr">
+      <c r="B12" s="60" t="inlineStr">
         <is>
           <t>target, non_target, new_lesion, overall, irecist, sum_of_diameters_reported, best_overall_response, progression_date</t>
         </is>
@@ -2180,7 +2507,7 @@
           <t>queries</t>
         </is>
       </c>
-      <c r="B13" s="62" t="inlineStr">
+      <c r="B13" s="61" t="inlineStr">
         <is>
           <t>query_id, query_text, answer_text, status, opened/answered/closed dates, tea_rule_id</t>
         </is>
@@ -2207,7 +2534,7 @@
           <t>cross_domain</t>
         </is>
       </c>
-      <c r="B14" s="61" t="inlineStr">
+      <c r="B14" s="60" t="inlineStr">
         <is>
           <t>exposure, anticancer_therapy, radiotherapy, procedures, adverse_events, lab_markers, performance_status</t>
         </is>
@@ -2234,7 +2561,7 @@
           <t>imaging_metadata</t>
         </is>
       </c>
-      <c r="B15" s="62" t="inlineStr">
+      <c r="B15" s="61" t="inlineStr">
         <is>
           <t>modality, scan_date, slice_thickness_mm, regions_imaged, contrast_used</t>
         </is>
@@ -2299,7 +2626,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2843,7 +3170,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2910,7 +3237,7 @@
           <t>Lesion organ, laterality, location text, description text, method, guideline extract</t>
         </is>
       </c>
-      <c r="D5" s="61" t="inlineStr">
+      <c r="D5" s="60" t="inlineStr">
         <is>
           <t>{is_non_measurable, category, confidence, rationale}</t>
         </is>
@@ -2932,7 +3259,7 @@
           <t>Non-target descriptions at this and the previous timepoint, target response, sum change, guideline extract</t>
         </is>
       </c>
-      <c r="D6" s="62" t="inlineStr">
+      <c r="D6" s="61" t="inlineStr">
         <is>
           <t>{supports_unequivocal, magnitude_comment, confidence, rationale}</t>
         </is>
@@ -2954,7 +3281,7 @@
           <t>Candidate finding summary; historical queries for the subject</t>
         </is>
       </c>
-      <c r="D7" s="61" t="inlineStr">
+      <c r="D7" s="60" t="inlineStr">
         <is>
           <t>{matches:[{query_id, relation, confidence}]}</t>
         </is>
@@ -2976,7 +3303,7 @@
           <t>Query text, answer text, current values of the queried fields  (NEW at review)</t>
         </is>
       </c>
-      <c r="D8" s="62" t="inlineStr">
+      <c r="D8" s="61" t="inlineStr">
         <is>
           <t>{classification, confidence, rationale, quoted_span}</t>
         </is>
@@ -2998,7 +3325,7 @@
           <t>Evidence object, rule metadata, message templates, guideline citation, indication context</t>
         </is>
       </c>
-      <c r="D9" s="61" t="inlineStr">
+      <c r="D9" s="60" t="inlineStr">
         <is>
           <t>{five narrative fields}</t>
         </is>
@@ -3020,7 +3347,7 @@
           <t>Protocol and imaging charter text  (NEW at review, AC-11)</t>
         </is>
       </c>
-      <c r="D10" s="62" t="inlineStr">
+      <c r="D10" s="61" t="inlineStr">
         <is>
           <t>{checkpoints:[{parameter, value_found, page_ref, confidence}]}</t>
         </is>
@@ -3196,9 +3523,9 @@
 log the event. The finding is still produced, with template text.</t>
         </is>
       </c>
-      <c r="B23" s="60" t="n"/>
-      <c r="C23" s="60" t="n"/>
-      <c r="D23" s="60" t="n"/>
+      <c r="B23" s="59" t="n"/>
+      <c r="C23" s="59" t="n"/>
+      <c r="D23" s="59" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3209,7 +3536,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3515,7 +3842,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3731,141 +4058,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="108" customWidth="1" min="2" max="2"/>
-    <col width="2" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>Extensibility procedures</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="9" t="inlineStr">
-        <is>
-          <t>How the system absorbs new requirements without engine changes (NFR-02).</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>Procedure</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="18" t="inlineStr">
-        <is>
-          <t>Adding a review point</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>1. Add a row to the Rules sheet with a new permanent id, guideline basis, severity, mode, confidence base rate, logic and required fields.  2. Add the five message templates to Rule_Messages.  3. Add the same entry to rule-catalog.yaml.  4. Implement the rule module with the same id as a pure function of (canonical model, derived values, config).  5. Add positive, negative and guard fixtures.  6. Bump the rule pack MINOR version.  7. Run the golden dataset and the drift check; acknowledge any change in expected findings.</t>
-        </is>
-      </c>
-      <c r="C4" s="24" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="20" t="inlineStr">
-        <is>
-          <t>Amending a rule</t>
-        </is>
-      </c>
-      <c r="B5" s="22" t="inlineStr">
-        <is>
-          <t>Never edit logic silently. Change the row, bump the rule pack MINOR or MAJOR, record the rule id in the change history, and run an impact assessment on findings already issued if MAJOR.</t>
-        </is>
-      </c>
-      <c r="C5" s="26" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>Adding a guideline</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>Add a profile to Guideline_Profiles with its parameter defaults. Add derivation variants only where the algorithm genuinely differs; otherwise parameterise. Tag rules with the versions they apply to. Bump MAJOR if any existing rule's behaviour changes.</t>
-        </is>
-      </c>
-      <c r="C6" s="24" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="20" t="inlineStr">
-        <is>
-          <t>Adding a source system</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>Implement an adapter producing the canonical input contract. No other layer changes.</t>
-        </is>
-      </c>
-      <c r="C7" s="26" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="18" t="inlineStr">
-        <is>
-          <t>Adding an LLM provider</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>Implement the adapter interface, declare its capability matrix, run the conformance suite, record results in the validation package.</t>
-        </is>
-      </c>
-      <c r="C8" s="24" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="20" t="inlineStr">
-        <is>
-          <t>Retiring a rule</t>
-        </is>
-      </c>
-      <c r="B9" s="22" t="inlineStr">
-        <is>
-          <t>Mark status RETIRED; keep the id permanently so historical findings remain interpretable. Never reuse an id.</t>
-        </is>
-      </c>
-      <c r="C9" s="26" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3885,7 +4084,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>TEA-SPEC-001 v1.3.0 — everything accepted, then a reviewer-lens quality pass changed 27 rules. Those 27 are what is left to confirm.</t>
+          <t>TEA-SPEC-001 v2.0.0 — APPROVED 2026-08-21, rule pack frozen. Step 2 is closed; Step 3 is the prototype run.</t>
         </is>
       </c>
     </row>
@@ -4088,12 +4287,12 @@
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
-          <t>27 rows</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
         <is>
-          <t>R3 changes, amber</t>
+          <t>3 rounds + gate</t>
         </is>
       </c>
     </row>
@@ -4114,12 +4313,12 @@
       </c>
       <c r="D12" s="17" t="inlineStr">
         <is>
-          <t>19 rows</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E12" s="15" t="inlineStr">
         <is>
-          <t>rewritten queries, amber</t>
+          <t>19 rewritten at R3</t>
         </is>
       </c>
     </row>
@@ -4346,27 +4545,50 @@
       <c r="D23" s="14" t="inlineStr"/>
       <c r="E23" s="15" t="inlineStr">
         <is>
-          <t>NEW — settles SQ-05</t>
+          <t>settles SQ-05</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
+          <t>Approval</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>Gate record: basis, history, what was not confirmed</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="n"/>
+      <c r="D24" s="17" t="inlineStr">
+        <is>
+          <t>read this</t>
+        </is>
+      </c>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>2 items flagged</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
           <t>Traceability</t>
         </is>
       </c>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>Plan requirement to specification to tests</t>
         </is>
       </c>
-      <c r="C24" s="16">
+      <c r="C25" s="16">
         <f>COUNTA(Traceability!A4:A23)</f>
         <v/>
       </c>
-      <c r="D24" s="14" t="inlineStr"/>
-      <c r="E24" s="15" t="inlineStr"/>
+      <c r="D25" s="14" t="inlineStr"/>
+      <c r="E25" s="15" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4394,13 +4616,142 @@
     <hyperlink ref="A21" location="Extensibility!A1"/>
     <hyperlink ref="A22" location="Open_Questions!A1"/>
     <hyperlink ref="A23" location="Query_Style!A1"/>
-    <hyperlink ref="A24" location="Traceability!A1"/>
+    <hyperlink ref="A24" location="Approval!A1"/>
+    <hyperlink ref="A25" location="Traceability!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="108" customWidth="1" min="2" max="2"/>
+    <col width="2" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Extensibility procedures</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>How the system absorbs new requirements without engine changes (NFR-02).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>Adding a review point</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>1. Add a row to the Rules sheet with a new permanent id, guideline basis, severity, mode, confidence base rate, logic and required fields.  2. Add the five message templates to Rule_Messages.  3. Add the same entry to rule-catalog.yaml.  4. Implement the rule module with the same id as a pure function of (canonical model, derived values, config).  5. Add positive, negative and guard fixtures.  6. Bump the rule pack MINOR version.  7. Run the golden dataset and the drift check; acknowledge any change in expected findings.</t>
+        </is>
+      </c>
+      <c r="C4" s="24" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>Amending a rule</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>Never edit logic silently. Change the row, bump the rule pack MINOR or MAJOR, record the rule id in the change history, and run an impact assessment on findings already issued if MAJOR.</t>
+        </is>
+      </c>
+      <c r="C5" s="26" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>Adding a guideline</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Add a profile to Guideline_Profiles with its parameter defaults. Add derivation variants only where the algorithm genuinely differs; otherwise parameterise. Tag rules with the versions they apply to. Bump MAJOR if any existing rule's behaviour changes.</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>Adding a source system</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>Implement an adapter producing the canonical input contract. No other layer changes.</t>
+        </is>
+      </c>
+      <c r="C7" s="26" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>Adding an LLM provider</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Implement the adapter interface, declare its capability matrix, run the conformance suite, record results in the validation package.</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>Retiring a rule</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>Mark status RETIRED; keep the id permanently so historical findings remain interpretable. Never reuse an id.</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4474,7 +4825,7 @@
           <t>Confirm the severity assigned to each rule against sponsor conventions. Severity drives prioritisation and the database-lock criteria.</t>
         </is>
       </c>
-      <c r="C4" s="40" t="inlineStr">
+      <c r="C4" s="38" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -4506,7 +4857,7 @@
           <t>Confirm the confidence base rate proposed for each rule (Open Item OI-02). These drive triage for every finding the agent produces.</t>
         </is>
       </c>
-      <c r="C5" s="63" t="inlineStr">
+      <c r="C5" s="62" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -4538,7 +4889,7 @@
           <t>Confirm the interpretation decisions ID-01 to ID-08, particularly the too-small-to-measure convention and the treatment of reappearing lesions.</t>
         </is>
       </c>
-      <c r="C6" s="40" t="inlineStr">
+      <c r="C6" s="38" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -4698,7 +5049,7 @@
           <t>Confirm whether the Veeva CRF collects a sum of diameters at all. If it is derived only, TE-BL-011 and TE-FU-001 do not apply and weight shifts onto TE-RS-001.</t>
         </is>
       </c>
-      <c r="C11" s="63" t="inlineStr">
+      <c r="C11" s="62" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -4730,7 +5081,7 @@
           <t>Confirm the confidence threshold at which a JUSTIFIED_BY_ANSWER suppression may occur without human confirmation. Currently 0.70, and never for CRITICAL or MAJOR.</t>
         </is>
       </c>
-      <c r="C12" s="40" t="inlineStr">
+      <c r="C12" s="38" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -4806,7 +5157,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5306,7 +5657,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5760,7 +6111,7 @@
           <t>TE-RS-011</t>
         </is>
       </c>
-      <c r="B16" s="40" t="inlineStr">
+      <c r="B16" s="38" t="inlineStr">
         <is>
           <t>Reject</t>
         </is>
@@ -9015,7 +9366,7 @@
     <col width="74" customWidth="1" min="18" max="18"/>
     <col width="66" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="42" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -9028,7 +9379,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>Rounds 1 and 2 are closed history. Round 3 is a quality pass: the R3 columns show which lens found something, what changed, and the logic as it stood before. Only the amber rows need a decision. Filter on R3 lens to see the 27.</t>
+          <t>APPROVED and frozen at rule pack 2.0.0. Every column here is closed history: three review rounds and the gate approval. Filter on R3 lens to see the 27 rules the reviewer-lens pass changed.</t>
         </is>
       </c>
     </row>
@@ -9135,7 +9486,7 @@
       </c>
       <c r="U3" s="10" t="inlineStr">
         <is>
-          <t>Reviewer</t>
+          <t>Approval basis</t>
         </is>
       </c>
     </row>
@@ -9209,8 +9560,8 @@
       <c r="Q4" s="24" t="inlineStr"/>
       <c r="R4" s="12" t="inlineStr"/>
       <c r="S4" s="13" t="n"/>
-      <c r="T4" s="33" t="n"/>
-      <c r="U4" s="34" t="n"/>
+      <c r="T4" s="24" t="inlineStr"/>
+      <c r="U4" s="12" t="inlineStr"/>
     </row>
     <row r="5" ht="96" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
@@ -9288,19 +9639,27 @@
           <t>MM</t>
         </is>
       </c>
-      <c r="R5" s="35" t="inlineStr">
+      <c r="R5" s="33" t="inlineStr">
         <is>
           <t>Grouping on normalised location text collides two genuinely separate lesions in the same organ — two distinct liver metastases are routine. Added the size and description discriminators a monitor would apply before calling it a duplicate.</t>
         </is>
       </c>
-      <c r="S5" s="36" t="inlineStr">
+      <c r="S5" s="34" t="inlineStr">
         <is>
           <t>group lesions by (subject, organ, laterality, normalised location_detail)
 if group size &gt; 1 and both are TARGET or both NON_TARGET: raise finding</t>
         </is>
       </c>
-      <c r="T5" s="33" t="n"/>
-      <c r="U5" s="34" t="n"/>
+      <c r="T5" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="U5" s="12" t="inlineStr">
+        <is>
+          <t>Marked individually</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="96" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
@@ -9379,12 +9738,12 @@
           <t>Some CRF doesn't collect the type of size, instead the CRF directly asks sites to enter size based on the appropriate type. Consider the field name directly mentions right size type, if there's no size type selection field in the CRF.</t>
         </is>
       </c>
-      <c r="O6" s="37" t="inlineStr">
+      <c r="O6" s="35" t="inlineStr">
         <is>
           <t>AMENDED. Axis type is now resolved at ingestion in priority order rather than assumed to be a collected field: an explicit axis-type field if one exists, otherwise the axis implied by the CRF field itself as declared in the structured CRF specification, otherwise the protocol default. The rule fires only when no source establishes that a nodal measurement is a short axis.</t>
         </is>
       </c>
-      <c r="P6" s="38" t="inlineStr">
+      <c r="P6" s="36" t="inlineStr">
         <is>
           <t>Accept</t>
         </is>
@@ -9394,14 +9753,22 @@
           <t>CDM</t>
         </is>
       </c>
-      <c r="R6" s="35" t="inlineStr">
+      <c r="R6" s="33" t="inlineStr">
         <is>
           <t>Removed the instruction to correct the value. The query now asks the site to check the source rather than telling them which axis is wrong.</t>
         </is>
       </c>
       <c r="S6" s="13" t="n"/>
-      <c r="T6" s="33" t="n"/>
-      <c r="U6" s="34" t="n"/>
+      <c r="T6" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="U6" s="12" t="inlineStr">
+        <is>
+          <t>Marked individually</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="96" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
@@ -9424,7 +9791,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E7" s="39" t="inlineStr">
+      <c r="E7" s="37" t="inlineStr">
         <is>
           <t>MINOR</t>
         </is>
@@ -9470,8 +9837,8 @@
       <c r="Q7" s="24" t="inlineStr"/>
       <c r="R7" s="12" t="inlineStr"/>
       <c r="S7" s="13" t="n"/>
-      <c r="T7" s="33" t="n"/>
-      <c r="U7" s="34" t="n"/>
+      <c r="T7" s="24" t="inlineStr"/>
+      <c r="U7" s="12" t="inlineStr"/>
     </row>
     <row r="8" ht="96" customHeight="1">
       <c r="A8" s="11" t="inlineStr">
@@ -9494,7 +9861,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E8" s="39" t="inlineStr">
+      <c r="E8" s="37" t="inlineStr">
         <is>
           <t>MINOR</t>
         </is>
@@ -9539,8 +9906,8 @@
       <c r="Q8" s="24" t="inlineStr"/>
       <c r="R8" s="12" t="inlineStr"/>
       <c r="S8" s="13" t="n"/>
-      <c r="T8" s="33" t="n"/>
-      <c r="U8" s="34" t="n"/>
+      <c r="T8" s="24" t="inlineStr"/>
+      <c r="U8" s="12" t="inlineStr"/>
     </row>
     <row r="9" ht="96" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
@@ -9563,7 +9930,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E9" s="40" t="inlineStr">
+      <c r="E9" s="38" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -9613,8 +9980,8 @@
       <c r="Q9" s="24" t="inlineStr"/>
       <c r="R9" s="12" t="inlineStr"/>
       <c r="S9" s="13" t="n"/>
-      <c r="T9" s="33" t="n"/>
-      <c r="U9" s="34" t="n"/>
+      <c r="T9" s="24" t="inlineStr"/>
+      <c r="U9" s="12" t="inlineStr"/>
     </row>
     <row r="10" ht="96" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
@@ -9637,7 +10004,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E10" s="40" t="inlineStr">
+      <c r="E10" s="38" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -9683,8 +10050,8 @@
       <c r="Q10" s="24" t="inlineStr"/>
       <c r="R10" s="12" t="inlineStr"/>
       <c r="S10" s="13" t="n"/>
-      <c r="T10" s="33" t="n"/>
-      <c r="U10" s="34" t="n"/>
+      <c r="T10" s="24" t="inlineStr"/>
+      <c r="U10" s="12" t="inlineStr"/>
     </row>
     <row r="11" ht="96" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
@@ -9707,7 +10074,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E11" s="40" t="inlineStr">
+      <c r="E11" s="38" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -9756,8 +10123,8 @@
       <c r="Q11" s="24" t="inlineStr"/>
       <c r="R11" s="12" t="inlineStr"/>
       <c r="S11" s="13" t="n"/>
-      <c r="T11" s="33" t="n"/>
-      <c r="U11" s="34" t="n"/>
+      <c r="T11" s="24" t="inlineStr"/>
+      <c r="U11" s="12" t="inlineStr"/>
     </row>
     <row r="12" ht="96" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
@@ -9780,7 +10147,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E12" s="40" t="inlineStr">
+      <c r="E12" s="38" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -9828,14 +10195,22 @@
           <t>CDM</t>
         </is>
       </c>
-      <c r="R12" s="35" t="inlineStr">
+      <c r="R12" s="33" t="inlineStr">
         <is>
           <t>Removed the sentence stating what the node should have been recorded as. That is the investigator's call, and stating it invites the site to confirm rather than check.</t>
         </is>
       </c>
       <c r="S12" s="13" t="n"/>
-      <c r="T12" s="33" t="n"/>
-      <c r="U12" s="34" t="n"/>
+      <c r="T12" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="U12" s="12" t="inlineStr">
+        <is>
+          <t>Marked individually</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="96" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
@@ -9906,14 +10281,22 @@
           <t>CDM</t>
         </is>
       </c>
-      <c r="R13" s="35" t="inlineStr">
+      <c r="R13" s="33" t="inlineStr">
         <is>
           <t>Removed 'please remove it from the assessment'. A query should never instruct a site to delete recorded data; it asks them to confirm intent and act on their own record.</t>
         </is>
       </c>
       <c r="S13" s="13" t="n"/>
-      <c r="T13" s="33" t="n"/>
-      <c r="U13" s="34" t="n"/>
+      <c r="T13" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="U13" s="12" t="inlineStr">
+        <is>
+          <t>Marked individually</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="96" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
@@ -9951,7 +10334,7 @@
           <t>CONDITIONAL</t>
         </is>
       </c>
-      <c r="H14" s="41" t="n">
+      <c r="H14" s="39" t="n">
         <v>0.7</v>
       </c>
       <c r="I14" s="12" t="inlineStr">
@@ -9985,8 +10368,8 @@
       <c r="Q14" s="24" t="inlineStr"/>
       <c r="R14" s="12" t="inlineStr"/>
       <c r="S14" s="13" t="n"/>
-      <c r="T14" s="33" t="n"/>
-      <c r="U14" s="34" t="n"/>
+      <c r="T14" s="24" t="inlineStr"/>
+      <c r="U14" s="12" t="inlineStr"/>
     </row>
     <row r="15" ht="96" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
@@ -10024,7 +10407,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="H15" s="41" t="n">
+      <c r="H15" s="39" t="n">
         <v>0.65</v>
       </c>
       <c r="I15" s="12" t="inlineStr">
@@ -10067,14 +10450,22 @@
           <t>CDM</t>
         </is>
       </c>
-      <c r="R15" s="35" t="inlineStr">
+      <c r="R15" s="33" t="inlineStr">
         <is>
           <t>Removed the guideline reference (SQ-05) and the instruction to re-classify. Asks the measurability question in plain terms instead.</t>
         </is>
       </c>
       <c r="S15" s="13" t="n"/>
-      <c r="T15" s="33" t="n"/>
-      <c r="U15" s="34" t="n"/>
+      <c r="T15" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="U15" s="12" t="inlineStr">
+        <is>
+          <t>Marked individually</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="96" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
@@ -10112,7 +10503,7 @@
           <t>CONDITIONAL</t>
         </is>
       </c>
-      <c r="H16" s="41" t="n">
+      <c r="H16" s="39" t="n">
         <v>0.72</v>
       </c>
       <c r="I16" s="12" t="inlineStr">
@@ -10149,14 +10540,22 @@
           <t>CDM</t>
         </is>
       </c>
-      <c r="R16" s="35" t="inlineStr">
+      <c r="R16" s="33" t="inlineStr">
         <is>
           <t>Removed the clause telling the site to record it as non-target. Asks for the evidence that decides the question, which is what the reviewer actually needs.</t>
         </is>
       </c>
       <c r="S16" s="13" t="n"/>
-      <c r="T16" s="33" t="n"/>
-      <c r="U16" s="34" t="n"/>
+      <c r="T16" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="U16" s="12" t="inlineStr">
+        <is>
+          <t>Marked individually</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="96" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
@@ -10179,7 +10578,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E17" s="40" t="inlineStr">
+      <c r="E17" s="38" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -10225,8 +10624,8 @@
       <c r="Q17" s="24" t="inlineStr"/>
       <c r="R17" s="12" t="inlineStr"/>
       <c r="S17" s="13" t="n"/>
-      <c r="T17" s="33" t="n"/>
-      <c r="U17" s="34" t="n"/>
+      <c r="T17" s="24" t="inlineStr"/>
+      <c r="U17" s="12" t="inlineStr"/>
     </row>
     <row r="18" ht="96" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
@@ -10299,8 +10698,8 @@
       <c r="Q18" s="24" t="inlineStr"/>
       <c r="R18" s="12" t="inlineStr"/>
       <c r="S18" s="13" t="n"/>
-      <c r="T18" s="33" t="n"/>
-      <c r="U18" s="34" t="n"/>
+      <c r="T18" s="24" t="inlineStr"/>
+      <c r="U18" s="12" t="inlineStr"/>
     </row>
     <row r="19" ht="96" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
@@ -10377,12 +10776,12 @@
           <t>In case of the CRF not collecting manual entry for the reported sum, this rule should be ignored. The LLM needs to identify study's CRF capture the information by CRF specification.</t>
         </is>
       </c>
-      <c r="O19" s="37" t="inlineStr">
+      <c r="O19" s="35" t="inlineStr">
         <is>
           <t>AMENDED, and this answers SQ-08. Status moves from ACTIVE to CONDITIONAL: the rule requires a site-entered sum field. Whether the sum is site-entered or system-derived is determined from the structured CRF specification at the AC-11 intake, and a derived sum deactivates the rule with an explicit NOT_EVALUATED in the coverage report rather than a silent pass. Applied to TE-FU-001 as well, which carries the identical condition at follow-up.</t>
         </is>
       </c>
-      <c r="P19" s="38" t="inlineStr">
+      <c r="P19" s="36" t="inlineStr">
         <is>
           <t>Accept</t>
         </is>
@@ -10390,8 +10789,8 @@
       <c r="Q19" s="24" t="inlineStr"/>
       <c r="R19" s="12" t="inlineStr"/>
       <c r="S19" s="13" t="n"/>
-      <c r="T19" s="33" t="n"/>
-      <c r="U19" s="34" t="n"/>
+      <c r="T19" s="24" t="inlineStr"/>
+      <c r="U19" s="12" t="inlineStr"/>
     </row>
     <row r="20" ht="96" customHeight="1">
       <c r="A20" s="11" t="inlineStr">
@@ -10414,7 +10813,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E20" s="39" t="inlineStr">
+      <c r="E20" s="37" t="inlineStr">
         <is>
           <t>MINOR</t>
         </is>
@@ -10429,7 +10828,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="H20" s="42" t="n">
+      <c r="H20" s="40" t="n">
         <v>0.35</v>
       </c>
       <c r="I20" s="12" t="inlineStr">
@@ -10460,8 +10859,8 @@
       <c r="Q20" s="24" t="inlineStr"/>
       <c r="R20" s="12" t="inlineStr"/>
       <c r="S20" s="13" t="n"/>
-      <c r="T20" s="33" t="n"/>
-      <c r="U20" s="34" t="n"/>
+      <c r="T20" s="24" t="inlineStr"/>
+      <c r="U20" s="12" t="inlineStr"/>
     </row>
     <row r="21" ht="96" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
@@ -10529,8 +10928,8 @@
       <c r="Q21" s="24" t="inlineStr"/>
       <c r="R21" s="12" t="inlineStr"/>
       <c r="S21" s="13" t="n"/>
-      <c r="T21" s="33" t="n"/>
-      <c r="U21" s="34" t="n"/>
+      <c r="T21" s="24" t="inlineStr"/>
+      <c r="U21" s="12" t="inlineStr"/>
     </row>
     <row r="22" ht="96" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
@@ -10553,7 +10952,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E22" s="39" t="inlineStr">
+      <c r="E22" s="37" t="inlineStr">
         <is>
           <t>MINOR</t>
         </is>
@@ -10568,7 +10967,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="H22" s="41" t="n">
+      <c r="H22" s="39" t="n">
         <v>0.62</v>
       </c>
       <c r="I22" s="12" t="inlineStr">
@@ -10609,19 +11008,27 @@
           <t>MM</t>
         </is>
       </c>
-      <c r="R22" s="35" t="inlineStr">
+      <c r="R22" s="33" t="inlineStr">
         <is>
           <t>A study-wide modality change — a protocol amendment, a scanner replacement — was raising a finding on every lesion in every subject. That is a study-level observation, not a per-lesion data query.</t>
         </is>
       </c>
-      <c r="S22" s="36" t="inlineStr">
+      <c r="S22" s="34" t="inlineStr">
         <is>
           <t>for lesion, visits in measurements grouped by lesion:
     if distinct method_at_visit values &gt; 1: raise finding</t>
         </is>
       </c>
-      <c r="T22" s="33" t="n"/>
-      <c r="U22" s="34" t="n"/>
+      <c r="T22" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="U22" s="12" t="inlineStr">
+        <is>
+          <t>Marked individually</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="96" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
@@ -10644,7 +11051,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E23" s="39" t="inlineStr">
+      <c r="E23" s="37" t="inlineStr">
         <is>
           <t>MINOR</t>
         </is>
@@ -10659,7 +11066,7 @@
           <t>CONDITIONAL</t>
         </is>
       </c>
-      <c r="H23" s="41" t="n">
+      <c r="H23" s="39" t="n">
         <v>0.6</v>
       </c>
       <c r="I23" s="12" t="inlineStr">
@@ -10694,8 +11101,8 @@
       <c r="Q23" s="24" t="inlineStr"/>
       <c r="R23" s="12" t="inlineStr"/>
       <c r="S23" s="13" t="n"/>
-      <c r="T23" s="33" t="n"/>
-      <c r="U23" s="34" t="n"/>
+      <c r="T23" s="24" t="inlineStr"/>
+      <c r="U23" s="12" t="inlineStr"/>
     </row>
     <row r="24" ht="96" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
@@ -10728,12 +11135,12 @@
           <t>LLM_ADJUDICATED</t>
         </is>
       </c>
-      <c r="G24" s="43" t="inlineStr">
+      <c r="G24" s="41" t="inlineStr">
         <is>
           <t>PROPOSED_OPTIONAL</t>
         </is>
       </c>
-      <c r="H24" s="41" t="n">
+      <c r="H24" s="39" t="n">
         <v>0.55</v>
       </c>
       <c r="I24" s="12" t="inlineStr">
@@ -10764,8 +11171,8 @@
       <c r="Q24" s="24" t="inlineStr"/>
       <c r="R24" s="12" t="inlineStr"/>
       <c r="S24" s="13" t="n"/>
-      <c r="T24" s="33" t="n"/>
-      <c r="U24" s="34" t="n"/>
+      <c r="T24" s="24" t="inlineStr"/>
+      <c r="U24" s="12" t="inlineStr"/>
     </row>
     <row r="25" ht="96" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
@@ -10833,8 +11240,8 @@
       <c r="Q25" s="24" t="inlineStr"/>
       <c r="R25" s="12" t="inlineStr"/>
       <c r="S25" s="13" t="n"/>
-      <c r="T25" s="33" t="n"/>
-      <c r="U25" s="34" t="n"/>
+      <c r="T25" s="24" t="inlineStr"/>
+      <c r="U25" s="12" t="inlineStr"/>
     </row>
     <row r="26" ht="96" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
@@ -10907,12 +11314,12 @@
         </is>
       </c>
       <c r="N26" s="12" t="inlineStr"/>
-      <c r="O26" s="37" t="inlineStr">
+      <c r="O26" s="35" t="inlineStr">
         <is>
           <t>AMENDED alongside TE-BL-011, which carries the identical condition. Accepted at round 1, but the same CRF-dependency applies at follow-up and the pair must move together.</t>
         </is>
       </c>
-      <c r="P26" s="38" t="inlineStr">
+      <c r="P26" s="36" t="inlineStr">
         <is>
           <t>Accept</t>
         </is>
@@ -10920,8 +11327,8 @@
       <c r="Q26" s="24" t="inlineStr"/>
       <c r="R26" s="12" t="inlineStr"/>
       <c r="S26" s="13" t="n"/>
-      <c r="T26" s="33" t="n"/>
-      <c r="U26" s="34" t="n"/>
+      <c r="T26" s="24" t="inlineStr"/>
+      <c r="U26" s="12" t="inlineStr"/>
     </row>
     <row r="27" ht="96" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
@@ -10990,8 +11397,8 @@
       <c r="Q27" s="24" t="inlineStr"/>
       <c r="R27" s="12" t="inlineStr"/>
       <c r="S27" s="13" t="n"/>
-      <c r="T27" s="33" t="n"/>
-      <c r="U27" s="34" t="n"/>
+      <c r="T27" s="24" t="inlineStr"/>
+      <c r="U27" s="12" t="inlineStr"/>
     </row>
     <row r="28" ht="96" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
@@ -11061,8 +11468,8 @@
       <c r="Q28" s="24" t="inlineStr"/>
       <c r="R28" s="12" t="inlineStr"/>
       <c r="S28" s="13" t="n"/>
-      <c r="T28" s="33" t="n"/>
-      <c r="U28" s="34" t="n"/>
+      <c r="T28" s="24" t="inlineStr"/>
+      <c r="U28" s="12" t="inlineStr"/>
     </row>
     <row r="29" ht="96" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
@@ -11085,7 +11492,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E29" s="39" t="inlineStr">
+      <c r="E29" s="37" t="inlineStr">
         <is>
           <t>MINOR</t>
         </is>
@@ -11100,7 +11507,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="H29" s="42" t="n">
+      <c r="H29" s="40" t="n">
         <v>0.45</v>
       </c>
       <c r="I29" s="12" t="inlineStr">
@@ -11132,12 +11539,12 @@
           <t>Provide the rationale insisting the proposed threshold. What material or information is referred to make this validation rule.</t>
         </is>
       </c>
-      <c r="O29" s="37" t="inlineStr">
+      <c r="O29" s="35" t="inlineStr">
         <is>
           <t>RATIONALE ADDED. These thresholds are not drawn from RECIST — the guideline sets no outlier limits. They are heuristics aimed at transcription error, and they are declared as such rather than dressed up with a citation. Proposed for calibration against the golden dataset at Step 3, where the false-positive rate can actually be measured.</t>
         </is>
       </c>
-      <c r="P29" s="38" t="inlineStr">
+      <c r="P29" s="36" t="inlineStr">
         <is>
           <t>Accept</t>
         </is>
@@ -11145,8 +11552,8 @@
       <c r="Q29" s="24" t="inlineStr"/>
       <c r="R29" s="12" t="inlineStr"/>
       <c r="S29" s="13" t="n"/>
-      <c r="T29" s="33" t="n"/>
-      <c r="U29" s="34" t="n"/>
+      <c r="T29" s="24" t="inlineStr"/>
+      <c r="U29" s="12" t="inlineStr"/>
     </row>
     <row r="30" ht="96" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
@@ -11215,12 +11622,12 @@
           <t>Provide the rationale insisting the proposed threshold. What material or information is referred to make this validation rule.</t>
         </is>
       </c>
-      <c r="O30" s="37" t="inlineStr">
+      <c r="O30" s="35" t="inlineStr">
         <is>
           <t>RATIONALE ADDED. This rule carries no numeric threshold; the parameter in it is the interpretation decision ID-01, which is a protocol question rather than a guideline constant.</t>
         </is>
       </c>
-      <c r="P30" s="38" t="inlineStr">
+      <c r="P30" s="36" t="inlineStr">
         <is>
           <t>Accept</t>
         </is>
@@ -11228,8 +11635,8 @@
       <c r="Q30" s="24" t="inlineStr"/>
       <c r="R30" s="12" t="inlineStr"/>
       <c r="S30" s="13" t="n"/>
-      <c r="T30" s="33" t="n"/>
-      <c r="U30" s="34" t="n"/>
+      <c r="T30" s="24" t="inlineStr"/>
+      <c r="U30" s="12" t="inlineStr"/>
     </row>
     <row r="31" ht="96" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
@@ -11252,7 +11659,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E31" s="39" t="inlineStr">
+      <c r="E31" s="37" t="inlineStr">
         <is>
           <t>MINOR</t>
         </is>
@@ -11267,7 +11674,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="H31" s="41" t="n">
+      <c r="H31" s="39" t="n">
         <v>0.7</v>
       </c>
       <c r="I31" s="12" t="inlineStr">
@@ -11298,8 +11705,8 @@
       <c r="Q31" s="24" t="inlineStr"/>
       <c r="R31" s="12" t="inlineStr"/>
       <c r="S31" s="13" t="n"/>
-      <c r="T31" s="33" t="n"/>
-      <c r="U31" s="34" t="n"/>
+      <c r="T31" s="24" t="inlineStr"/>
+      <c r="U31" s="12" t="inlineStr"/>
     </row>
     <row r="32" ht="96" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
@@ -11385,12 +11792,12 @@
           <t>The proposed condition is fine. Since a protocol may define different assessment window for particular assessment timing, consider to get information about study's individual tumor assessment window period.</t>
         </is>
       </c>
-      <c r="O32" s="37" t="inlineStr">
+      <c r="O32" s="35" t="inlineStr">
         <is>
           <t>AMENDED. The scalar interval and window are replaced by a per-visit schedule captured at the AC-11 protocol intake, so a protocol that tightens or widens the window at particular timepoints is honoured. The scalar remains as a fallback for protocols with a uniform interval.</t>
         </is>
       </c>
-      <c r="P32" s="38" t="inlineStr">
+      <c r="P32" s="36" t="inlineStr">
         <is>
           <t>Accept</t>
         </is>
@@ -11398,8 +11805,8 @@
       <c r="Q32" s="24" t="inlineStr"/>
       <c r="R32" s="12" t="inlineStr"/>
       <c r="S32" s="13" t="n"/>
-      <c r="T32" s="33" t="n"/>
-      <c r="U32" s="34" t="n"/>
+      <c r="T32" s="24" t="inlineStr"/>
+      <c r="U32" s="12" t="inlineStr"/>
     </row>
     <row r="33" ht="96" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
@@ -11468,8 +11875,8 @@
       <c r="Q33" s="24" t="inlineStr"/>
       <c r="R33" s="12" t="inlineStr"/>
       <c r="S33" s="13" t="n"/>
-      <c r="T33" s="33" t="n"/>
-      <c r="U33" s="34" t="n"/>
+      <c r="T33" s="24" t="inlineStr"/>
+      <c r="U33" s="12" t="inlineStr"/>
     </row>
     <row r="34" ht="96" customHeight="1">
       <c r="A34" s="11" t="inlineStr">
@@ -11492,7 +11899,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E34" s="40" t="inlineStr">
+      <c r="E34" s="38" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -11541,12 +11948,12 @@
           <t>The proposed condition could be applied to follow-up assessment? It's okay to check at baseline's tumor identification, but I'm not sure to check under follow-up assessment.</t>
         </is>
       </c>
-      <c r="O34" s="37" t="inlineStr">
+      <c r="O34" s="35" t="inlineStr">
         <is>
           <t>AMENDED, and the scope was the wrong way round. The rule is only meaningful at follow-up: a nodal target cannot be absent at baseline, since it was selected for having a short axis of at least 15 mm. What it catches is a node recorded as absent or zero at follow-up once it has normalised, which drops it out of the sum and produces a falsely low sum and a spurious response. The rule is now explicitly restricted to follow-up, and the too-small-to-measure state is excluded so that ID-02 handling is not flagged as an error.</t>
         </is>
       </c>
-      <c r="P34" s="38" t="inlineStr">
+      <c r="P34" s="36" t="inlineStr">
         <is>
           <t>Accept</t>
         </is>
@@ -11556,14 +11963,22 @@
           <t>CDM</t>
         </is>
       </c>
-      <c r="R34" s="35" t="inlineStr">
+      <c r="R34" s="33" t="inlineStr">
         <is>
           <t>Removed the guideline sentence (SQ-05) and the bare instruction to enter a measurement. Now allows for the case where the node genuinely was not measurable.</t>
         </is>
       </c>
       <c r="S34" s="13" t="n"/>
-      <c r="T34" s="33" t="n"/>
-      <c r="U34" s="34" t="n"/>
+      <c r="T34" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="U34" s="12" t="inlineStr">
+        <is>
+          <t>Marked individually</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="96" customHeight="1">
       <c r="A35" s="11" t="inlineStr">
@@ -11586,7 +12001,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E35" s="39" t="inlineStr">
+      <c r="E35" s="37" t="inlineStr">
         <is>
           <t>MINOR</t>
         </is>
@@ -11631,8 +12046,8 @@
       <c r="Q35" s="24" t="inlineStr"/>
       <c r="R35" s="12" t="inlineStr"/>
       <c r="S35" s="13" t="n"/>
-      <c r="T35" s="33" t="n"/>
-      <c r="U35" s="34" t="n"/>
+      <c r="T35" s="24" t="inlineStr"/>
+      <c r="U35" s="12" t="inlineStr"/>
     </row>
     <row r="36" ht="96" customHeight="1">
       <c r="A36" s="11" t="inlineStr">
@@ -11713,19 +12128,27 @@
           <t>MM</t>
         </is>
       </c>
-      <c r="R36" s="35" t="inlineStr">
+      <c r="R36" s="33" t="inlineStr">
         <is>
           <t>An assessment dated the same day as death is common and legitimate — the scan preceded the death that day. Firing on it produced an unanswerable query. Partial dates were also being treated as full ones.</t>
         </is>
       </c>
-      <c r="S36" s="36" t="inlineStr">
+      <c r="S36" s="34" t="inlineStr">
         <is>
           <t>if assessment_date &gt; death_date: raise CRITICAL
 if assessment_date &gt; discontinuation_date + config.post_treatment_followup_days: raise MAJOR</t>
         </is>
       </c>
-      <c r="T36" s="33" t="n"/>
-      <c r="U36" s="34" t="n"/>
+      <c r="T36" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="U36" s="12" t="inlineStr">
+        <is>
+          <t>Marked individually</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="96" customHeight="1">
       <c r="A37" s="11" t="inlineStr">
@@ -11748,7 +12171,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E37" s="39" t="inlineStr">
+      <c r="E37" s="37" t="inlineStr">
         <is>
           <t>MINOR</t>
         </is>
@@ -11794,8 +12217,8 @@
       <c r="Q37" s="24" t="inlineStr"/>
       <c r="R37" s="12" t="inlineStr"/>
       <c r="S37" s="13" t="n"/>
-      <c r="T37" s="33" t="n"/>
-      <c r="U37" s="34" t="n"/>
+      <c r="T37" s="24" t="inlineStr"/>
+      <c r="U37" s="12" t="inlineStr"/>
     </row>
     <row r="38" ht="96" customHeight="1">
       <c r="A38" s="11" t="inlineStr">
@@ -11818,7 +12241,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E38" s="39" t="inlineStr">
+      <c r="E38" s="37" t="inlineStr">
         <is>
           <t>MINOR</t>
         </is>
@@ -11833,7 +12256,7 @@
           <t>CONDITIONAL</t>
         </is>
       </c>
-      <c r="H38" s="41" t="n">
+      <c r="H38" s="39" t="n">
         <v>0.58</v>
       </c>
       <c r="I38" s="12" t="inlineStr">
@@ -11867,8 +12290,8 @@
       <c r="Q38" s="24" t="inlineStr"/>
       <c r="R38" s="12" t="inlineStr"/>
       <c r="S38" s="13" t="n"/>
-      <c r="T38" s="33" t="n"/>
-      <c r="U38" s="34" t="n"/>
+      <c r="T38" s="24" t="inlineStr"/>
+      <c r="U38" s="12" t="inlineStr"/>
     </row>
     <row r="39" ht="96" customHeight="1">
       <c r="A39" s="11" t="inlineStr">
@@ -11891,7 +12314,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E39" s="44" t="inlineStr">
+      <c r="E39" s="42" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -11906,7 +12329,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="H39" s="41" t="n">
+      <c r="H39" s="39" t="n">
         <v>0.55</v>
       </c>
       <c r="I39" s="12" t="inlineStr">
@@ -11944,19 +12367,27 @@
           <t>MM</t>
         </is>
       </c>
-      <c r="R39" s="35" t="inlineStr">
+      <c r="R39" s="33" t="inlineStr">
         <is>
           <t>Per-lesion identical values are common in genuinely stable disease, which is why this sat at a 0.30 base rate. The pattern that actually signals copied data is every target lesion identical across visits. Narrowed to that, and the base rate rises accordingly.</t>
         </is>
       </c>
-      <c r="S39" s="36" t="inlineStr">
+      <c r="S39" s="34" t="inlineStr">
         <is>
           <t>if a lesion has the identical value at &gt;= 3 consecutive assessments
    and the lesion is &gt; config.identical_value_min_mm (default 15): raise finding</t>
         </is>
       </c>
-      <c r="T39" s="33" t="n"/>
-      <c r="U39" s="34" t="n"/>
+      <c r="T39" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="U39" s="12" t="inlineStr">
+        <is>
+          <t>Marked individually</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="96" customHeight="1">
       <c r="A40" s="11" t="inlineStr">
@@ -11979,7 +12410,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E40" s="40" t="inlineStr">
+      <c r="E40" s="38" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -12028,14 +12459,22 @@
           <t>CDM</t>
         </is>
       </c>
-      <c r="R40" s="35" t="inlineStr">
+      <c r="R40" s="33" t="inlineStr">
         <is>
           <t>Removed the agent's derivation from the query. The percent-change arithmetic is reviewer-facing context, not something a site coordinator needs in order to re-check a record.</t>
         </is>
       </c>
       <c r="S40" s="13" t="n"/>
-      <c r="T40" s="33" t="n"/>
-      <c r="U40" s="34" t="n"/>
+      <c r="T40" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="U40" s="12" t="inlineStr">
+        <is>
+          <t>Marked individually</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="96" customHeight="1">
       <c r="A41" s="11" t="inlineStr">
@@ -12058,7 +12497,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E41" s="40" t="inlineStr">
+      <c r="E41" s="38" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -12108,12 +12547,12 @@
 In addition, the 'TE-RS-002' and 'TE-RS-003' are duplicate with 'TE-RS-001'? If yes, should we keep the two rules in the rule list?</t>
         </is>
       </c>
-      <c r="O41" s="37" t="inlineStr">
+      <c r="O41" s="35" t="inlineStr">
         <is>
           <t>KEPT, with the relationship now declared explicitly. On the logic: the proposed variant uses AND, but PD requires both criteria, so 'PD not met' is pct &lt; 20 OR abs &lt; 5 — the AND form is narrower than the correct negation and would miss cases. That complete check already exists as TE-RS-001, which recomputes the response and compares. On duplication: yes, TE-RS-002 and TE-RS-003 are both subsumed by TE-RS-001 for detection. Their value is diagnostic, not detective — TE-RS-001 says the response is wrong, these say why, and the query text differs accordingly. They are now declared as cascade children of TE-RS-001, so when both fire the reviewer sees one finding carrying the specific reason, not two.</t>
         </is>
       </c>
-      <c r="P41" s="38" t="inlineStr">
+      <c r="P41" s="36" t="inlineStr">
         <is>
           <t>Accept</t>
         </is>
@@ -12123,14 +12562,22 @@
           <t>CDM</t>
         </is>
       </c>
-      <c r="R41" s="35" t="inlineStr">
+      <c r="R41" s="33" t="inlineStr">
         <is>
           <t>Removed the guideline citation and the threshold arithmetic (SQ-05). Asks the one question that resolves the finding: what drove the PD call.</t>
         </is>
       </c>
       <c r="S41" s="13" t="n"/>
-      <c r="T41" s="33" t="n"/>
-      <c r="U41" s="34" t="n"/>
+      <c r="T41" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="U41" s="12" t="inlineStr">
+        <is>
+          <t>Marked individually</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="96" customHeight="1">
       <c r="A42" s="11" t="inlineStr">
@@ -12153,7 +12600,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E42" s="40" t="inlineStr">
+      <c r="E42" s="38" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -12205,12 +12652,12 @@
           <t>Question to this rule. Should it consider the pct_from_baseline condition? Given that the proposed condition could check incorrect data well with the 1st and 2nd line (i.e. "if reported_target_response != PD and pct_from_nadir &gt;= pd_pct and abs_from_nadir_mm &gt;= pd_abs"), if 3rd line condition isn't definitely deciding data consistency, I suggest to have rule conditions without 3rd line condition.</t>
         </is>
       </c>
-      <c r="O42" s="37" t="inlineStr">
+      <c r="O42" s="35" t="inlineStr">
         <is>
           <t>AMENDED as suggested. The baseline comparison is removed from the gate, so the rule now catches every case where progression criteria are met from nadir but progression was not reported. The baseline comparison is retained purely as a discriminator: where percent change from baseline also falls short of the threshold, the site almost certainly compared against baseline instead of nadir, and the finding carries that specific wording and a higher confidence. Where it does not, the finding is still raised with generic wording.</t>
         </is>
       </c>
-      <c r="P42" s="38" t="inlineStr">
+      <c r="P42" s="36" t="inlineStr">
         <is>
           <t>Accept</t>
         </is>
@@ -12220,14 +12667,22 @@
           <t>CDM</t>
         </is>
       </c>
-      <c r="R42" s="35" t="inlineStr">
+      <c r="R42" s="33" t="inlineStr">
         <is>
           <t>Removed the guideline citation (SQ-05) and replaced 'nadir' with 'the smallest sum recorded on study', which a site coordinator can act on without knowing the term.</t>
         </is>
       </c>
       <c r="S42" s="13" t="n"/>
-      <c r="T42" s="33" t="n"/>
-      <c r="U42" s="34" t="n"/>
+      <c r="T42" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="U42" s="12" t="inlineStr">
+        <is>
+          <t>Marked individually</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="96" customHeight="1">
       <c r="A43" s="11" t="inlineStr">
@@ -12250,7 +12705,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E43" s="40" t="inlineStr">
+      <c r="E43" s="38" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -12298,8 +12753,8 @@
       <c r="Q43" s="24" t="inlineStr"/>
       <c r="R43" s="12" t="inlineStr"/>
       <c r="S43" s="13" t="n"/>
-      <c r="T43" s="33" t="n"/>
-      <c r="U43" s="34" t="n"/>
+      <c r="T43" s="24" t="inlineStr"/>
+      <c r="U43" s="12" t="inlineStr"/>
     </row>
     <row r="44" ht="96" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
@@ -12322,7 +12777,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E44" s="40" t="inlineStr">
+      <c r="E44" s="38" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -12368,8 +12823,8 @@
       <c r="Q44" s="24" t="inlineStr"/>
       <c r="R44" s="12" t="inlineStr"/>
       <c r="S44" s="13" t="n"/>
-      <c r="T44" s="33" t="n"/>
-      <c r="U44" s="34" t="n"/>
+      <c r="T44" s="24" t="inlineStr"/>
+      <c r="U44" s="12" t="inlineStr"/>
     </row>
     <row r="45" ht="96" customHeight="1">
       <c r="A45" s="11" t="inlineStr">
@@ -12438,8 +12893,8 @@
       <c r="Q45" s="24" t="inlineStr"/>
       <c r="R45" s="12" t="inlineStr"/>
       <c r="S45" s="13" t="n"/>
-      <c r="T45" s="33" t="n"/>
-      <c r="U45" s="34" t="n"/>
+      <c r="T45" s="24" t="inlineStr"/>
+      <c r="U45" s="12" t="inlineStr"/>
     </row>
     <row r="46" ht="96" customHeight="1">
       <c r="A46" s="11" t="inlineStr">
@@ -12462,7 +12917,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E46" s="44" t="inlineStr">
+      <c r="E46" s="42" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -12477,7 +12932,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="H46" s="42" t="n">
+      <c r="H46" s="40" t="n">
         <v>0.45</v>
       </c>
       <c r="I46" s="12" t="inlineStr">
@@ -12509,12 +12964,12 @@
           <t>This isn't decisive with entered data only. Check whether it could downgrade the severity to 'INFO'.</t>
         </is>
       </c>
-      <c r="O46" s="37" t="inlineStr">
+      <c r="O46" s="35" t="inlineStr">
         <is>
           <t>AMENDED to INFO. You are right that collected data cannot settle this — the guideline's test is a judgement about overall tumor burden that the recorded non-target states do not capture. Note the consequence, which is intended: INFO findings do not enter the default query worklist, so this becomes a study-team observation rather than a site query. The adjudicator can still escalate to MAJOR where the recorded descriptions actively contradict the reported progression.</t>
         </is>
       </c>
-      <c r="P46" s="38" t="inlineStr">
+      <c r="P46" s="36" t="inlineStr">
         <is>
           <t>Accept</t>
         </is>
@@ -12524,14 +12979,22 @@
           <t>CDM</t>
         </is>
       </c>
-      <c r="R46" s="35" t="inlineStr">
+      <c r="R46" s="33" t="inlineStr">
         <is>
           <t>Removed 'please confirm that the overall tumor burden has increased substantially'. That is a medical judgement and does not belong in a query answered by site data staff. The query now asks only for the radiology description, which is a data request; the judgement stays with the monitor.</t>
         </is>
       </c>
       <c r="S46" s="13" t="n"/>
-      <c r="T46" s="33" t="n"/>
-      <c r="U46" s="34" t="n"/>
+      <c r="T46" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="U46" s="12" t="inlineStr">
+        <is>
+          <t>Marked individually</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="96" customHeight="1">
       <c r="A47" s="11" t="inlineStr">
@@ -12554,7 +13017,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E47" s="40" t="inlineStr">
+      <c r="E47" s="38" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -12608,12 +13071,12 @@
           <t>Is it possible to give information whether any issue in the individual response (target, non-target) and their relevant detail data (e.g. tumor size, individual lesion response) in order not to avoid duplicate query in both sides (i.e. overall response, target/non-target response)</t>
         </is>
       </c>
-      <c r="O47" s="37" t="inlineStr">
+      <c r="O47" s="35" t="inlineStr">
         <is>
           <t>AMENDED. The rule now declares its component dependencies, and the cascade grouping suppresses the separate overall-response query whenever a component finding is already open for the same assessment. Where no component finding exists, the overall-response finding is raised alone and names which component drove the expected value, so the site receives one query identifying the specific field rather than two queries about the same visit.</t>
         </is>
       </c>
-      <c r="P47" s="38" t="inlineStr">
+      <c r="P47" s="36" t="inlineStr">
         <is>
           <t>Accept</t>
         </is>
@@ -12623,14 +13086,22 @@
           <t>CDM</t>
         </is>
       </c>
-      <c r="R47" s="35" t="inlineStr">
+      <c r="R47" s="33" t="inlineStr">
         <is>
           <t>Removed 'the overall response should be {derived_overall}'. Naming the expected value turns a check into an instruction, and if the derivation is wrong the site confirms the error.</t>
         </is>
       </c>
       <c r="S47" s="13" t="n"/>
-      <c r="T47" s="33" t="n"/>
-      <c r="U47" s="34" t="n"/>
+      <c r="T47" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="U47" s="12" t="inlineStr">
+        <is>
+          <t>Marked individually</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="96" customHeight="1">
       <c r="A48" s="11" t="inlineStr">
@@ -12699,176 +13170,176 @@
       <c r="Q48" s="24" t="inlineStr"/>
       <c r="R48" s="12" t="inlineStr"/>
       <c r="S48" s="13" t="n"/>
-      <c r="T48" s="33" t="n"/>
-      <c r="U48" s="34" t="n"/>
+      <c r="T48" s="24" t="inlineStr"/>
+      <c r="U48" s="12" t="inlineStr"/>
     </row>
     <row r="49" ht="96" customHeight="1">
-      <c r="A49" s="45" t="inlineStr">
+      <c r="A49" s="43" t="inlineStr">
         <is>
           <t>TE-RS-010</t>
         </is>
       </c>
-      <c r="B49" s="46" t="inlineStr">
+      <c r="B49" s="44" t="inlineStr">
         <is>
           <t>RS</t>
         </is>
       </c>
-      <c r="C49" s="47" t="inlineStr">
+      <c r="C49" s="45" t="inlineStr">
         <is>
           <t>New lesion recorded but overall response is not progression</t>
         </is>
       </c>
-      <c r="D49" s="46" t="inlineStr">
+      <c r="D49" s="44" t="inlineStr">
         <is>
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E49" s="46" t="inlineStr">
+      <c r="E49" s="44" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="F49" s="46" t="inlineStr">
+      <c r="F49" s="44" t="inlineStr">
         <is>
           <t>DETERMINISTIC</t>
         </is>
       </c>
-      <c r="G49" s="48" t="inlineStr">
+      <c r="G49" s="46" t="inlineStr">
         <is>
           <t>RETIRED</t>
         </is>
       </c>
-      <c r="H49" s="49" t="n">
+      <c r="H49" s="47" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="I49" s="47" t="inlineStr">
+      <c r="I49" s="45" t="inlineStr">
         <is>
           <t>A confirmed new lesion always means progression under RECIST 1.1.</t>
         </is>
       </c>
-      <c r="J49" s="47" t="inlineStr">
+      <c r="J49" s="45" t="inlineStr">
         <is>
           <t>Retired at the Step 2 review as fully subsumed by TE-RS-008 (overall response versus the component table), TE-RS-009 (flag versus recorded lesions) and TE-IR-001 (iUPD under iRECIST).</t>
         </is>
       </c>
-      <c r="K49" s="47" t="inlineStr"/>
-      <c r="L49" s="50" t="inlineStr">
+      <c r="K49" s="45" t="inlineStr"/>
+      <c r="L49" s="48" t="inlineStr">
         <is>
           <t>if new_lesion_flag == YES and reported_overall != PD: raise finding
    (under iRECIST the expected value is iUPD; see TE-IR-001)</t>
         </is>
       </c>
-      <c r="M49" s="51" t="inlineStr">
+      <c r="M49" s="49" t="inlineStr">
         <is>
           <t>Discuss</t>
         </is>
       </c>
-      <c r="N49" s="52" t="inlineStr">
+      <c r="N49" s="50" t="inlineStr">
         <is>
           <t>Check if this rule is duplicate, considering TE-RS-008.
 If duplicate rule, I suggest remove this rule, instead, add only iRECIST condition to the TE-RS-008.</t>
         </is>
       </c>
-      <c r="O49" s="52" t="inlineStr">
+      <c r="O49" s="50" t="inlineStr">
         <is>
           <t>RETIRED — you are right. TE-RS-008 derives the overall response from the reported components, and the new-lesion flag is one of those components, so a recorded new lesion with a non-PD overall response already fires TE-RS-008. The one case that is not covered — a new lesion present in the lesion table while the flag says NO — is TE-RS-009. The iRECIST expectation needs no folding in, because TE-IR-001 already requires iUPD rather than PD where iRECIST applies. The id is retained permanently and never reused, so historical findings stay interpretable.</t>
         </is>
       </c>
-      <c r="P49" s="53" t="inlineStr">
-        <is>
-          <t>Accept</t>
-        </is>
-      </c>
-      <c r="Q49" s="51" t="inlineStr"/>
-      <c r="R49" s="52" t="inlineStr"/>
-      <c r="S49" s="54" t="n"/>
-      <c r="T49" s="33" t="n"/>
-      <c r="U49" s="34" t="n"/>
+      <c r="P49" s="51" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="Q49" s="49" t="inlineStr"/>
+      <c r="R49" s="50" t="inlineStr"/>
+      <c r="S49" s="52" t="n"/>
+      <c r="T49" s="49" t="inlineStr"/>
+      <c r="U49" s="50" t="inlineStr"/>
     </row>
     <row r="50" ht="96" customHeight="1">
-      <c r="A50" s="45" t="inlineStr">
+      <c r="A50" s="43" t="inlineStr">
         <is>
           <t>TE-RS-011</t>
         </is>
       </c>
-      <c r="B50" s="46" t="inlineStr">
+      <c r="B50" s="44" t="inlineStr">
         <is>
           <t>RS</t>
         </is>
       </c>
-      <c r="C50" s="47" t="inlineStr">
+      <c r="C50" s="45" t="inlineStr">
         <is>
           <t>New lesion in an anatomical region not imaged at baseline</t>
         </is>
       </c>
-      <c r="D50" s="46" t="inlineStr">
+      <c r="D50" s="44" t="inlineStr">
         <is>
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E50" s="46" t="inlineStr">
+      <c r="E50" s="44" t="inlineStr">
         <is>
           <t>MAJOR</t>
         </is>
       </c>
-      <c r="F50" s="46" t="inlineStr">
+      <c r="F50" s="44" t="inlineStr">
         <is>
           <t>HYBRID</t>
         </is>
       </c>
-      <c r="G50" s="48" t="inlineStr">
+      <c r="G50" s="46" t="inlineStr">
         <is>
           <t>RETIRED</t>
         </is>
       </c>
-      <c r="H50" s="49" t="n">
+      <c r="H50" s="47" t="n">
         <v>0.62</v>
       </c>
-      <c r="I50" s="47" t="inlineStr">
+      <c r="I50" s="45" t="inlineStr">
         <is>
           <t>Ensure the region-not-imaged case was considered explicitly.</t>
         </is>
       </c>
-      <c r="J50" s="47" t="inlineStr">
+      <c r="J50" s="45" t="inlineStr">
         <is>
           <t>Rejected at the Step 2 review. The premise does not hold: investigator-discretion imaging routinely covers regions absent from the baseline protocol imaging, so region coverage is not evidence of a data problem.</t>
         </is>
       </c>
-      <c r="K50" s="47" t="inlineStr">
+      <c r="K50" s="45" t="inlineStr">
         <is>
           <t>imaging_metadata.regions_imaged (or inferred from baseline lesion organs and modality)</t>
         </is>
       </c>
-      <c r="L50" s="50" t="inlineStr">
+      <c r="L50" s="48" t="inlineStr">
         <is>
           <t>if new lesion organ/region was not covered by the baseline imaging: raise finding</t>
         </is>
       </c>
-      <c r="M50" s="55" t="inlineStr">
+      <c r="M50" s="53" t="inlineStr">
         <is>
           <t>Reject</t>
         </is>
       </c>
-      <c r="N50" s="52" t="inlineStr">
+      <c r="N50" s="50" t="inlineStr">
         <is>
           <t>New lesion could be confirmed by other organ/region not covered by the baseline image, because of doing other image by investigator's discretion. Suggest not to run this rule.</t>
         </is>
       </c>
-      <c r="O50" s="52" t="inlineStr">
+      <c r="O50" s="50" t="inlineStr">
         <is>
           <t>RETIRED as rejected. Imaging performed at investigator discretion outside the baseline coverage is routine and entirely legitimate, and a new lesion found that way is a real new lesion. The rule assumed baseline coverage bounded where disease could be found, which is not how imaging is actually ordered. The id is retained permanently and never reused.</t>
         </is>
       </c>
-      <c r="P50" s="53" t="inlineStr">
-        <is>
-          <t>Accept</t>
-        </is>
-      </c>
-      <c r="Q50" s="51" t="inlineStr"/>
-      <c r="R50" s="52" t="inlineStr"/>
-      <c r="S50" s="54" t="n"/>
-      <c r="T50" s="33" t="n"/>
-      <c r="U50" s="34" t="n"/>
+      <c r="P50" s="51" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="Q50" s="49" t="inlineStr"/>
+      <c r="R50" s="50" t="inlineStr"/>
+      <c r="S50" s="52" t="n"/>
+      <c r="T50" s="49" t="inlineStr"/>
+      <c r="U50" s="50" t="inlineStr"/>
     </row>
     <row r="51" ht="96" customHeight="1">
       <c r="A51" s="11" t="inlineStr">
@@ -12906,7 +13377,7 @@
           <t>CONDITIONAL</t>
         </is>
       </c>
-      <c r="H51" s="41" t="n">
+      <c r="H51" s="39" t="n">
         <v>0.68</v>
       </c>
       <c r="I51" s="12" t="inlineStr">
@@ -12941,8 +13412,8 @@
       <c r="Q51" s="24" t="inlineStr"/>
       <c r="R51" s="12" t="inlineStr"/>
       <c r="S51" s="13" t="n"/>
-      <c r="T51" s="33" t="n"/>
-      <c r="U51" s="34" t="n"/>
+      <c r="T51" s="24" t="inlineStr"/>
+      <c r="U51" s="12" t="inlineStr"/>
     </row>
     <row r="52" ht="96" customHeight="1">
       <c r="A52" s="11" t="inlineStr">
@@ -13015,12 +13486,12 @@
           <t>This rule should consider the case that the visit j's data has definitive rationale of PD. E.g. At the visit j, there is evidence to determine PD due to other conditions (e.g. target lesion sum mm passes 20% worsen and over minimum increase)</t>
         </is>
       </c>
-      <c r="O52" s="37" t="inlineStr">
+      <c r="O52" s="35" t="inlineStr">
         <is>
           <t>AMENDED. A guard now suppresses the finding where progression at visit j is independently established by the target or non-target criteria. Back-dating is only correct where the equivocal-then-confirmed lesion is what drove progression; where the target sum crossed the threshold at visit j in its own right, visit j is the correct progression date and the earlier equivocal observation is irrelevant to it.</t>
         </is>
       </c>
-      <c r="P52" s="38" t="inlineStr">
+      <c r="P52" s="36" t="inlineStr">
         <is>
           <t>Accept</t>
         </is>
@@ -13030,14 +13501,22 @@
           <t>CDM</t>
         </is>
       </c>
-      <c r="R52" s="35" t="inlineStr">
+      <c r="R52" s="33" t="inlineStr">
         <is>
           <t>Removed 'per RECIST the progression date should be {first_date}' — both a guideline citation (SQ-05) and a statement of the answer.</t>
         </is>
       </c>
       <c r="S52" s="13" t="n"/>
-      <c r="T52" s="33" t="n"/>
-      <c r="U52" s="34" t="n"/>
+      <c r="T52" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="U52" s="12" t="inlineStr">
+        <is>
+          <t>Marked individually</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="96" customHeight="1">
       <c r="A53" s="11" t="inlineStr">
@@ -13060,7 +13539,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E53" s="40" t="inlineStr">
+      <c r="E53" s="38" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -13111,12 +13590,12 @@
           <t>Provide the rationale insisting the proposed threshold. What material or information is referred to make this validation rule.</t>
         </is>
       </c>
-      <c r="O53" s="37" t="inlineStr">
+      <c r="O53" s="35" t="inlineStr">
         <is>
           <t>RATIONALE ADDED, and this one does have a guideline source, unlike TE-FU-004.</t>
         </is>
       </c>
-      <c r="P53" s="38" t="inlineStr">
+      <c r="P53" s="36" t="inlineStr">
         <is>
           <t>Accept</t>
         </is>
@@ -13124,8 +13603,8 @@
       <c r="Q53" s="24" t="inlineStr"/>
       <c r="R53" s="12" t="inlineStr"/>
       <c r="S53" s="13" t="n"/>
-      <c r="T53" s="33" t="n"/>
-      <c r="U53" s="34" t="n"/>
+      <c r="T53" s="24" t="inlineStr"/>
+      <c r="U53" s="12" t="inlineStr"/>
     </row>
     <row r="54" ht="96" customHeight="1">
       <c r="A54" s="11" t="inlineStr">
@@ -13148,7 +13627,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E54" s="40" t="inlineStr">
+      <c r="E54" s="38" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -13194,8 +13673,8 @@
       <c r="Q54" s="24" t="inlineStr"/>
       <c r="R54" s="12" t="inlineStr"/>
       <c r="S54" s="13" t="n"/>
-      <c r="T54" s="33" t="n"/>
-      <c r="U54" s="34" t="n"/>
+      <c r="T54" s="24" t="inlineStr"/>
+      <c r="U54" s="12" t="inlineStr"/>
     </row>
     <row r="55" ht="96" customHeight="1">
       <c r="A55" s="11" t="inlineStr">
@@ -13218,7 +13697,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E55" s="40" t="inlineStr">
+      <c r="E55" s="38" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -13266,14 +13745,22 @@
           <t>CDM</t>
         </is>
       </c>
-      <c r="R55" s="35" t="inlineStr">
+      <c r="R55" s="33" t="inlineStr">
         <is>
           <t>Removed the list of permitted response categories. The finding may equally be a missing baseline target lesion rather than a wrong response, and the original wording pointed at only one of the two.</t>
         </is>
       </c>
       <c r="S55" s="13" t="n"/>
-      <c r="T55" s="33" t="n"/>
-      <c r="U55" s="34" t="n"/>
+      <c r="T55" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="U55" s="12" t="inlineStr">
+        <is>
+          <t>Marked individually</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="96" customHeight="1">
       <c r="A56" s="11" t="inlineStr">
@@ -13346,8 +13833,8 @@
       <c r="Q56" s="24" t="inlineStr"/>
       <c r="R56" s="12" t="inlineStr"/>
       <c r="S56" s="13" t="n"/>
-      <c r="T56" s="33" t="n"/>
-      <c r="U56" s="34" t="n"/>
+      <c r="T56" s="24" t="inlineStr"/>
+      <c r="U56" s="12" t="inlineStr"/>
     </row>
     <row r="57" ht="96" customHeight="1">
       <c r="A57" s="11" t="inlineStr">
@@ -13416,8 +13903,8 @@
       <c r="Q57" s="24" t="inlineStr"/>
       <c r="R57" s="12" t="inlineStr"/>
       <c r="S57" s="13" t="n"/>
-      <c r="T57" s="33" t="n"/>
-      <c r="U57" s="34" t="n"/>
+      <c r="T57" s="24" t="inlineStr"/>
+      <c r="U57" s="12" t="inlineStr"/>
     </row>
     <row r="58" ht="96" customHeight="1">
       <c r="A58" s="11" t="inlineStr">
@@ -13486,8 +13973,8 @@
       <c r="Q58" s="24" t="inlineStr"/>
       <c r="R58" s="12" t="inlineStr"/>
       <c r="S58" s="13" t="n"/>
-      <c r="T58" s="33" t="n"/>
-      <c r="U58" s="34" t="n"/>
+      <c r="T58" s="24" t="inlineStr"/>
+      <c r="U58" s="12" t="inlineStr"/>
     </row>
     <row r="59" ht="96" customHeight="1">
       <c r="A59" s="11" t="inlineStr">
@@ -13525,7 +14012,7 @@
           <t>CONDITIONAL</t>
         </is>
       </c>
-      <c r="H59" s="41" t="n">
+      <c r="H59" s="39" t="n">
         <v>0.5</v>
       </c>
       <c r="I59" s="12" t="inlineStr">
@@ -13570,20 +14057,28 @@
           <t>MM</t>
         </is>
       </c>
-      <c r="R59" s="35" t="inlineStr">
+      <c r="R59" s="33" t="inlineStr">
         <is>
           <t>Was raising a finding per discordant assessment. A subject whose whole response history differs between investigator and BICR produced a finding at every visit. Now one finding per subject, listing the discordant timepoints, which is also how a monitor reconciles it.</t>
         </is>
       </c>
-      <c r="S59" s="36" t="inlineStr">
+      <c r="S59" s="34" t="inlineStr">
         <is>
           <t>for each assessment with both INVESTIGATOR and BICR responses:
     if responses differ, or progression dates differ by &gt; config.bicr_date_tolerance_days:
         raise finding (INFO by default when the difference does not cross a PD boundary)</t>
         </is>
       </c>
-      <c r="T59" s="33" t="n"/>
-      <c r="U59" s="34" t="n"/>
+      <c r="T59" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="U59" s="12" t="inlineStr">
+        <is>
+          <t>Marked individually</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="96" customHeight="1">
       <c r="A60" s="11" t="inlineStr">
@@ -13606,7 +14101,7 @@
           <t>iRECIST only</t>
         </is>
       </c>
-      <c r="E60" s="40" t="inlineStr">
+      <c r="E60" s="38" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -13655,14 +14150,22 @@
           <t>CDM</t>
         </is>
       </c>
-      <c r="R60" s="35" t="inlineStr">
+      <c r="R60" s="33" t="inlineStr">
         <is>
           <t>Removed the guideline explanation and the statement that iUPD should have been recorded (SQ-05). iUPD stays in the reviewer-facing tips, where the explanation belongs.</t>
         </is>
       </c>
       <c r="S60" s="13" t="n"/>
-      <c r="T60" s="33" t="n"/>
-      <c r="U60" s="34" t="n"/>
+      <c r="T60" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="U60" s="12" t="inlineStr">
+        <is>
+          <t>Marked individually</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="96" customHeight="1">
       <c r="A61" s="11" t="inlineStr">
@@ -13685,7 +14188,7 @@
           <t>iRECIST only</t>
         </is>
       </c>
-      <c r="E61" s="40" t="inlineStr">
+      <c r="E61" s="38" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -13734,8 +14237,8 @@
       <c r="Q61" s="24" t="inlineStr"/>
       <c r="R61" s="12" t="inlineStr"/>
       <c r="S61" s="13" t="n"/>
-      <c r="T61" s="33" t="n"/>
-      <c r="U61" s="34" t="n"/>
+      <c r="T61" s="24" t="inlineStr"/>
+      <c r="U61" s="12" t="inlineStr"/>
     </row>
     <row r="62" ht="96" customHeight="1">
       <c r="A62" s="11" t="inlineStr">
@@ -13758,7 +14261,7 @@
           <t>iRECIST only</t>
         </is>
       </c>
-      <c r="E62" s="40" t="inlineStr">
+      <c r="E62" s="38" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -13812,14 +14315,22 @@
           <t>CDM</t>
         </is>
       </c>
-      <c r="R62" s="35" t="inlineStr">
+      <c r="R62" s="33" t="inlineStr">
         <is>
           <t>Removed 'against the iRECIST criteria' (SQ-05). The comparison rule is in the tips.</t>
         </is>
       </c>
       <c r="S62" s="13" t="n"/>
-      <c r="T62" s="33" t="n"/>
-      <c r="U62" s="34" t="n"/>
+      <c r="T62" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="U62" s="12" t="inlineStr">
+        <is>
+          <t>Marked individually</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="96" customHeight="1">
       <c r="A63" s="11" t="inlineStr">
@@ -13842,7 +14353,7 @@
           <t>iRECIST only</t>
         </is>
       </c>
-      <c r="E63" s="40" t="inlineStr">
+      <c r="E63" s="38" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -13890,14 +14401,22 @@
           <t>CDM</t>
         </is>
       </c>
-      <c r="R63" s="35" t="inlineStr">
+      <c r="R63" s="33" t="inlineStr">
         <is>
           <t>Removed the guideline explanation of separate new-lesion sums (SQ-05), and narrowed the query to the single factual question.</t>
         </is>
       </c>
       <c r="S63" s="13" t="n"/>
-      <c r="T63" s="33" t="n"/>
-      <c r="U63" s="34" t="n"/>
+      <c r="T63" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="U63" s="12" t="inlineStr">
+        <is>
+          <t>Marked individually</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="96" customHeight="1">
       <c r="A64" s="11" t="inlineStr">
@@ -13969,14 +14488,22 @@
           <t>CDM</t>
         </is>
       </c>
-      <c r="R64" s="35" t="inlineStr">
+      <c r="R64" s="33" t="inlineStr">
         <is>
           <t>Removed the derived-response arithmetic from the query; it remains in the reviewer-facing reason.</t>
         </is>
       </c>
       <c r="S64" s="13" t="n"/>
-      <c r="T64" s="33" t="n"/>
-      <c r="U64" s="34" t="n"/>
+      <c r="T64" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="U64" s="12" t="inlineStr">
+        <is>
+          <t>Marked individually</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="96" customHeight="1">
       <c r="A65" s="11" t="inlineStr">
@@ -14047,14 +14574,22 @@
           <t>CDM</t>
         </is>
       </c>
-      <c r="R65" s="35" t="inlineStr">
+      <c r="R65" s="33" t="inlineStr">
         <is>
           <t>Replaced the guideline citation with the study's own configured limits (SQ-05). Naming study configuration is not a guideline reference and is what the site can act on.</t>
         </is>
       </c>
       <c r="S65" s="13" t="n"/>
-      <c r="T65" s="33" t="n"/>
-      <c r="U65" s="34" t="n"/>
+      <c r="T65" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="U65" s="12" t="inlineStr">
+        <is>
+          <t>Marked individually</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="96" customHeight="1">
       <c r="A66" s="11" t="inlineStr">
@@ -14123,8 +14658,8 @@
       <c r="Q66" s="24" t="inlineStr"/>
       <c r="R66" s="12" t="inlineStr"/>
       <c r="S66" s="13" t="n"/>
-      <c r="T66" s="33" t="n"/>
-      <c r="U66" s="34" t="n"/>
+      <c r="T66" s="24" t="inlineStr"/>
+      <c r="U66" s="12" t="inlineStr"/>
     </row>
     <row r="67" ht="96" customHeight="1">
       <c r="A67" s="11" t="inlineStr">
@@ -14157,12 +14692,12 @@
           <t>HYBRID</t>
         </is>
       </c>
-      <c r="G67" s="43" t="inlineStr">
+      <c r="G67" s="41" t="inlineStr">
         <is>
           <t>PROPOSED_OPTIONAL</t>
         </is>
       </c>
-      <c r="H67" s="42" t="n">
+      <c r="H67" s="40" t="n">
         <v>0.48</v>
       </c>
       <c r="I67" s="12" t="inlineStr">
@@ -14197,8 +14732,8 @@
       <c r="Q67" s="24" t="inlineStr"/>
       <c r="R67" s="12" t="inlineStr"/>
       <c r="S67" s="13" t="n"/>
-      <c r="T67" s="33" t="n"/>
-      <c r="U67" s="34" t="n"/>
+      <c r="T67" s="24" t="inlineStr"/>
+      <c r="U67" s="12" t="inlineStr"/>
     </row>
     <row r="68" ht="96" customHeight="1">
       <c r="A68" s="11" t="inlineStr">
@@ -14269,14 +14804,22 @@
           <t>CDM</t>
         </is>
       </c>
-      <c r="R68" s="35" t="inlineStr">
+      <c r="R68" s="33" t="inlineStr">
         <is>
           <t>Removed 'the iRECIST response would be expected to be {expected_irecist}'. The two guideline names are retained because here they are the names of CRF fields, not a citation of authority.</t>
         </is>
       </c>
       <c r="S68" s="13" t="n"/>
-      <c r="T68" s="33" t="n"/>
-      <c r="U68" s="34" t="n"/>
+      <c r="T68" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="U68" s="12" t="inlineStr">
+        <is>
+          <t>Marked individually</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="96" customHeight="1">
       <c r="A69" s="11" t="inlineStr">
@@ -14349,8 +14892,8 @@
       <c r="Q69" s="24" t="inlineStr"/>
       <c r="R69" s="12" t="inlineStr"/>
       <c r="S69" s="13" t="n"/>
-      <c r="T69" s="33" t="n"/>
-      <c r="U69" s="34" t="n"/>
+      <c r="T69" s="24" t="inlineStr"/>
+      <c r="U69" s="12" t="inlineStr"/>
     </row>
     <row r="70" ht="96" customHeight="1">
       <c r="A70" s="11" t="inlineStr">
@@ -14419,8 +14962,8 @@
       <c r="Q70" s="24" t="inlineStr"/>
       <c r="R70" s="12" t="inlineStr"/>
       <c r="S70" s="13" t="n"/>
-      <c r="T70" s="33" t="n"/>
-      <c r="U70" s="34" t="n"/>
+      <c r="T70" s="24" t="inlineStr"/>
+      <c r="U70" s="12" t="inlineStr"/>
     </row>
     <row r="71" ht="96" customHeight="1">
       <c r="A71" s="11" t="inlineStr">
@@ -14458,7 +15001,7 @@
           <t>CONDITIONAL</t>
         </is>
       </c>
-      <c r="H71" s="41" t="n">
+      <c r="H71" s="39" t="n">
         <v>0.62</v>
       </c>
       <c r="I71" s="12" t="inlineStr"/>
@@ -14490,8 +15033,8 @@
       <c r="Q71" s="24" t="inlineStr"/>
       <c r="R71" s="12" t="inlineStr"/>
       <c r="S71" s="13" t="n"/>
-      <c r="T71" s="33" t="n"/>
-      <c r="U71" s="34" t="n"/>
+      <c r="T71" s="24" t="inlineStr"/>
+      <c r="U71" s="12" t="inlineStr"/>
     </row>
     <row r="72" ht="96" customHeight="1">
       <c r="A72" s="11" t="inlineStr">
@@ -14569,19 +15112,27 @@
           <t>MM</t>
         </is>
       </c>
-      <c r="R72" s="35" t="inlineStr">
+      <c r="R72" s="33" t="inlineStr">
         <is>
           <t>Fires on any new systemic anticancer therapy, including protocol-permitted maintenance and supportive regimens. A monitor would not query those.</t>
         </is>
       </c>
-      <c r="S72" s="36" t="inlineStr">
+      <c r="S72" s="34" t="inlineStr">
         <is>
           <t>if a new systemic anticancer therapy starts before the recorded progression date
    (or before any recorded progression): raise finding</t>
         </is>
       </c>
-      <c r="T72" s="33" t="n"/>
-      <c r="U72" s="34" t="n"/>
+      <c r="T72" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="U72" s="12" t="inlineStr">
+        <is>
+          <t>Marked individually</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="96" customHeight="1">
       <c r="A73" s="11" t="inlineStr">
@@ -14657,19 +15208,27 @@
           <t>MM</t>
         </is>
       </c>
-      <c r="R73" s="35" t="inlineStr">
+      <c r="R73" s="33" t="inlineStr">
         <is>
           <t>One event was producing one finding per subsequent visit. A single course of radiotherapy to a target lesion in a 12-visit study raised eleven findings for one fact. Now one finding per lesion, listing the affected assessments.</t>
         </is>
       </c>
-      <c r="S73" s="36" t="inlineStr">
+      <c r="S73" s="34" t="inlineStr">
         <is>
           <t>if radiotherapy, surgery or ablation is recorded at a site matching a target lesion
    after baseline: raise finding on all subsequent assessments of that lesion</t>
         </is>
       </c>
-      <c r="T73" s="33" t="n"/>
-      <c r="U73" s="34" t="n"/>
+      <c r="T73" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="U73" s="12" t="inlineStr">
+        <is>
+          <t>Marked individually</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="96" customHeight="1">
       <c r="A74" s="11" t="inlineStr">
@@ -14707,7 +15266,7 @@
           <t>CONDITIONAL</t>
         </is>
       </c>
-      <c r="H74" s="41" t="n">
+      <c r="H74" s="39" t="n">
         <v>0.7</v>
       </c>
       <c r="I74" s="12" t="inlineStr"/>
@@ -14747,19 +15306,27 @@
           <t>MM</t>
         </is>
       </c>
-      <c r="R74" s="35" t="inlineStr">
+      <c r="R74" s="33" t="inlineStr">
         <is>
           <t>An adverse event of disease progression with no PD assessment is often correct: the subject deteriorated and no further imaging was possible. Querying the site for a scan that could not be done is exactly the kind of query that costs credibility.</t>
         </is>
       </c>
-      <c r="S74" s="36" t="inlineStr">
+      <c r="S74" s="34" t="inlineStr">
         <is>
           <t>if an AE term maps to disease progression / malignant neoplasm progression
    and no PD assessment exists within config.ae_pd_window_days (default 60): raise finding</t>
         </is>
       </c>
-      <c r="T74" s="33" t="n"/>
-      <c r="U74" s="34" t="n"/>
+      <c r="T74" s="23" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="U74" s="54" t="inlineStr">
+        <is>
+          <t>Blanket approval only - not marked individually</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="96" customHeight="1">
       <c r="A75" s="11" t="inlineStr">
@@ -14782,7 +15349,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E75" s="40" t="inlineStr">
+      <c r="E75" s="38" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
@@ -14827,8 +15394,8 @@
       <c r="Q75" s="24" t="inlineStr"/>
       <c r="R75" s="12" t="inlineStr"/>
       <c r="S75" s="13" t="n"/>
-      <c r="T75" s="33" t="n"/>
-      <c r="U75" s="34" t="n"/>
+      <c r="T75" s="24" t="inlineStr"/>
+      <c r="U75" s="12" t="inlineStr"/>
     </row>
     <row r="76" ht="96" customHeight="1">
       <c r="A76" s="11" t="inlineStr">
@@ -14851,7 +15418,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E76" s="39" t="inlineStr">
+      <c r="E76" s="37" t="inlineStr">
         <is>
           <t>MINOR</t>
         </is>
@@ -14866,7 +15433,7 @@
           <t>CONDITIONAL</t>
         </is>
       </c>
-      <c r="H76" s="41" t="n">
+      <c r="H76" s="39" t="n">
         <v>0.6</v>
       </c>
       <c r="I76" s="12" t="inlineStr"/>
@@ -14895,12 +15462,12 @@
           <t>Provide the rationale insisting the proposed threshold. What material or information is referred to make this validation rule.</t>
         </is>
       </c>
-      <c r="O76" s="37" t="inlineStr">
+      <c r="O76" s="35" t="inlineStr">
         <is>
           <t>RATIONALE ADDED. The threshold is the laboratory's own upper limit of normal, not a value the agent chooses.</t>
         </is>
       </c>
-      <c r="P76" s="38" t="inlineStr">
+      <c r="P76" s="36" t="inlineStr">
         <is>
           <t>Accept</t>
         </is>
@@ -14908,8 +15475,8 @@
       <c r="Q76" s="24" t="inlineStr"/>
       <c r="R76" s="12" t="inlineStr"/>
       <c r="S76" s="13" t="n"/>
-      <c r="T76" s="33" t="n"/>
-      <c r="U76" s="34" t="n"/>
+      <c r="T76" s="24" t="inlineStr"/>
+      <c r="U76" s="12" t="inlineStr"/>
     </row>
     <row r="77" ht="96" customHeight="1">
       <c r="A77" s="11" t="inlineStr">
@@ -14932,7 +15499,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E77" s="39" t="inlineStr">
+      <c r="E77" s="37" t="inlineStr">
         <is>
           <t>MINOR</t>
         </is>
@@ -14947,7 +15514,7 @@
           <t>CONDITIONAL</t>
         </is>
       </c>
-      <c r="H77" s="41" t="n">
+      <c r="H77" s="39" t="n">
         <v>0.58</v>
       </c>
       <c r="I77" s="12" t="inlineStr"/>
@@ -14977,8 +15544,8 @@
       <c r="Q77" s="24" t="inlineStr"/>
       <c r="R77" s="12" t="inlineStr"/>
       <c r="S77" s="13" t="n"/>
-      <c r="T77" s="33" t="n"/>
-      <c r="U77" s="34" t="n"/>
+      <c r="T77" s="24" t="inlineStr"/>
+      <c r="U77" s="12" t="inlineStr"/>
     </row>
     <row r="78" ht="96" customHeight="1">
       <c r="A78" s="11" t="inlineStr">
@@ -15001,7 +15568,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E78" s="39" t="inlineStr">
+      <c r="E78" s="37" t="inlineStr">
         <is>
           <t>MINOR</t>
         </is>
@@ -15016,7 +15583,7 @@
           <t>CONDITIONAL</t>
         </is>
       </c>
-      <c r="H78" s="41" t="n">
+      <c r="H78" s="39" t="n">
         <v>0.62</v>
       </c>
       <c r="I78" s="12" t="inlineStr"/>
@@ -15047,8 +15614,8 @@
       <c r="Q78" s="24" t="inlineStr"/>
       <c r="R78" s="12" t="inlineStr"/>
       <c r="S78" s="13" t="n"/>
-      <c r="T78" s="33" t="n"/>
-      <c r="U78" s="34" t="n"/>
+      <c r="T78" s="24" t="inlineStr"/>
+      <c r="U78" s="12" t="inlineStr"/>
     </row>
     <row r="79" ht="96" customHeight="1">
       <c r="A79" s="11" t="inlineStr">
@@ -15112,8 +15679,8 @@
       <c r="Q79" s="24" t="inlineStr"/>
       <c r="R79" s="12" t="inlineStr"/>
       <c r="S79" s="13" t="n"/>
-      <c r="T79" s="33" t="n"/>
-      <c r="U79" s="34" t="n"/>
+      <c r="T79" s="24" t="inlineStr"/>
+      <c r="U79" s="12" t="inlineStr"/>
     </row>
     <row r="80" ht="96" customHeight="1">
       <c r="A80" s="11" t="inlineStr">
@@ -15136,7 +15703,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E80" s="44" t="inlineStr">
+      <c r="E80" s="42" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -15151,7 +15718,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="H80" s="41" t="n">
+      <c r="H80" s="39" t="n">
         <v>0.55</v>
       </c>
       <c r="I80" s="12" t="inlineStr"/>
@@ -15178,8 +15745,8 @@
       <c r="Q80" s="24" t="inlineStr"/>
       <c r="R80" s="12" t="inlineStr"/>
       <c r="S80" s="13" t="n"/>
-      <c r="T80" s="33" t="n"/>
-      <c r="U80" s="34" t="n"/>
+      <c r="T80" s="24" t="inlineStr"/>
+      <c r="U80" s="12" t="inlineStr"/>
     </row>
     <row r="81" ht="96" customHeight="1">
       <c r="A81" s="11" t="inlineStr">
@@ -15202,7 +15769,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E81" s="39" t="inlineStr">
+      <c r="E81" s="37" t="inlineStr">
         <is>
           <t>MINOR</t>
         </is>
@@ -15217,7 +15784,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="H81" s="41" t="n">
+      <c r="H81" s="39" t="n">
         <v>0.7</v>
       </c>
       <c r="I81" s="12" t="inlineStr"/>
@@ -15245,8 +15812,8 @@
       <c r="Q81" s="24" t="inlineStr"/>
       <c r="R81" s="12" t="inlineStr"/>
       <c r="S81" s="13" t="n"/>
-      <c r="T81" s="33" t="n"/>
-      <c r="U81" s="34" t="n"/>
+      <c r="T81" s="24" t="inlineStr"/>
+      <c r="U81" s="12" t="inlineStr"/>
     </row>
     <row r="82" ht="96" customHeight="1">
       <c r="A82" s="11" t="inlineStr">
@@ -15269,7 +15836,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E82" s="44" t="inlineStr">
+      <c r="E82" s="42" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -15310,8 +15877,8 @@
       <c r="Q82" s="24" t="inlineStr"/>
       <c r="R82" s="12" t="inlineStr"/>
       <c r="S82" s="13" t="n"/>
-      <c r="T82" s="33" t="n"/>
-      <c r="U82" s="34" t="n"/>
+      <c r="T82" s="24" t="inlineStr"/>
+      <c r="U82" s="12" t="inlineStr"/>
     </row>
     <row r="83" ht="96" customHeight="1">
       <c r="A83" s="11" t="inlineStr">
@@ -15390,8 +15957,8 @@
       <c r="Q83" s="24" t="inlineStr"/>
       <c r="R83" s="12" t="inlineStr"/>
       <c r="S83" s="13" t="n"/>
-      <c r="T83" s="33" t="n"/>
-      <c r="U83" s="34" t="n"/>
+      <c r="T83" s="24" t="inlineStr"/>
+      <c r="U83" s="12" t="inlineStr"/>
     </row>
     <row r="84" ht="96" customHeight="1">
       <c r="A84" s="11" t="inlineStr">
@@ -15456,8 +16023,8 @@
       <c r="Q84" s="24" t="inlineStr"/>
       <c r="R84" s="12" t="inlineStr"/>
       <c r="S84" s="13" t="n"/>
-      <c r="T84" s="33" t="n"/>
-      <c r="U84" s="34" t="n"/>
+      <c r="T84" s="24" t="inlineStr"/>
+      <c r="U84" s="12" t="inlineStr"/>
     </row>
     <row r="85" ht="96" customHeight="1">
       <c r="A85" s="11" t="inlineStr">
@@ -15480,7 +16047,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E85" s="39" t="inlineStr">
+      <c r="E85" s="37" t="inlineStr">
         <is>
           <t>MINOR</t>
         </is>
@@ -15522,8 +16089,8 @@
       <c r="Q85" s="24" t="inlineStr"/>
       <c r="R85" s="12" t="inlineStr"/>
       <c r="S85" s="13" t="n"/>
-      <c r="T85" s="33" t="n"/>
-      <c r="U85" s="34" t="n"/>
+      <c r="T85" s="24" t="inlineStr"/>
+      <c r="U85" s="12" t="inlineStr"/>
     </row>
     <row r="86" ht="96" customHeight="1">
       <c r="A86" s="11" t="inlineStr">
@@ -15546,7 +16113,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E86" s="44" t="inlineStr">
+      <c r="E86" s="42" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -15561,7 +16128,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="H86" s="41" t="n">
+      <c r="H86" s="39" t="n">
         <v>0.55</v>
       </c>
       <c r="I86" s="12" t="inlineStr"/>
@@ -15590,8 +16157,8 @@
       <c r="Q86" s="24" t="inlineStr"/>
       <c r="R86" s="12" t="inlineStr"/>
       <c r="S86" s="13" t="n"/>
-      <c r="T86" s="33" t="n"/>
-      <c r="U86" s="34" t="n"/>
+      <c r="T86" s="24" t="inlineStr"/>
+      <c r="U86" s="12" t="inlineStr"/>
     </row>
     <row r="87" ht="96" customHeight="1">
       <c r="A87" s="11" t="inlineStr">
@@ -15614,7 +16181,7 @@
           <t>RECIST 1.1 + iRECIST</t>
         </is>
       </c>
-      <c r="E87" s="44" t="inlineStr">
+      <c r="E87" s="42" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -15629,7 +16196,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="H87" s="41" t="n">
+      <c r="H87" s="39" t="n">
         <v>0.72</v>
       </c>
       <c r="I87" s="12" t="inlineStr"/>
@@ -15656,8 +16223,8 @@
       <c r="Q87" s="24" t="inlineStr"/>
       <c r="R87" s="12" t="inlineStr"/>
       <c r="S87" s="13" t="n"/>
-      <c r="T87" s="33" t="n"/>
-      <c r="U87" s="34" t="n"/>
+      <c r="T87" s="24" t="inlineStr"/>
+      <c r="U87" s="12" t="inlineStr"/>
     </row>
     <row r="88" ht="96" customHeight="1">
       <c r="A88" s="11" t="inlineStr">
@@ -15690,12 +16257,12 @@
           <t>HYBRID</t>
         </is>
       </c>
-      <c r="G88" s="43" t="inlineStr">
+      <c r="G88" s="41" t="inlineStr">
         <is>
           <t>PROPOSED_OPTIONAL</t>
         </is>
       </c>
-      <c r="H88" s="41" t="n">
+      <c r="H88" s="39" t="n">
         <v>0.55</v>
       </c>
       <c r="I88" s="12" t="inlineStr">
@@ -15747,8 +16314,8 @@
       <c r="Q88" s="24" t="inlineStr"/>
       <c r="R88" s="12" t="inlineStr"/>
       <c r="S88" s="13" t="n"/>
-      <c r="T88" s="33" t="n"/>
-      <c r="U88" s="34" t="n"/>
+      <c r="T88" s="24" t="inlineStr"/>
+      <c r="U88" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:U88"/>
@@ -15756,11 +16323,6 @@
     <mergeCell ref="A1:U1"/>
     <mergeCell ref="A2:U2"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="T4:T88" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Accept,Amend,Reject,Discuss"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15771,7 +16333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K88"/>
+  <dimension ref="A1:J88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -15783,8 +16345,7 @@
     <col width="48" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="58" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="44" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -15797,7 +16358,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>All 85 accepted 2026-08-21. 19 query texts were then rewritten at the reviewer-lens pass, following the house rules on Query_Style; the previous wording is kept beside each so the change is visible. Only the amber rows need a decision.</t>
+          <t>All 85 accepted 2026-08-21, and the 19 rewritten at the reviewer-lens pass approved at the gate. The previous wording is kept beside each rewrite so the change stays visible. Frozen at rule pack 2.0.0.</t>
         </is>
       </c>
     </row>
@@ -15849,12 +16410,7 @@
       </c>
       <c r="J3" s="10" t="inlineStr">
         <is>
-          <t>R3 decision</t>
-        </is>
-      </c>
-      <c r="K3" s="10" t="inlineStr">
-        <is>
-          <t>Reviewer</t>
+          <t>R3 approval</t>
         </is>
       </c>
     </row>
@@ -15884,7 +16440,7 @@
           <t>Measurements can only be interpreted against an identified lesion with a category (target/non-target/new) and location. Without it, the lesion cannot enter the sum of diameters, and the derived response may be wrong.</t>
         </is>
       </c>
-      <c r="F4" s="56" t="inlineStr">
+      <c r="F4" s="55" t="inlineStr">
         <is>
           <t>A measurement is recorded for lesion {lesion_id} at {visit} but this lesion is not present on the tumor identification form. Please confirm the lesion identification and complete the missing record, or correct the lesion number on the measurement.</t>
         </is>
@@ -15900,8 +16456,7 @@
         </is>
       </c>
       <c r="I4" s="12" t="inlineStr"/>
-      <c r="J4" s="33" t="n"/>
-      <c r="K4" s="34" t="n"/>
+      <c r="J4" s="12" t="inlineStr"/>
     </row>
     <row r="5" ht="108" customHeight="1">
       <c r="A5" s="25" t="inlineStr">
@@ -15929,7 +16484,7 @@
           <t>If the same lesion is recorded twice, it is counted twice in the sum of diameters, inflating tumor burden and distorting percent change and the nadir.</t>
         </is>
       </c>
-      <c r="F5" s="56" t="inlineStr">
+      <c r="F5" s="55" t="inlineStr">
         <is>
           <t>Lesions {lesion_id_a} and {lesion_id_b} appear to describe the same lesion at {organ}. Please confirm whether these are two distinct lesions; if not, please remove the duplicate and update the affected assessments.</t>
         </is>
@@ -15945,11 +16500,10 @@
         </is>
       </c>
       <c r="I5" s="22" t="inlineStr"/>
-      <c r="J5" s="33" t="n"/>
-      <c r="K5" s="34" t="n"/>
+      <c r="J5" s="22" t="inlineStr"/>
     </row>
     <row r="6" ht="108" customHeight="1">
-      <c r="A6" s="57" t="inlineStr">
+      <c r="A6" s="56" t="inlineStr">
         <is>
           <t>TE-ST-003</t>
         </is>
@@ -15974,7 +16528,7 @@
           <t>RECIST 1.1 requires the short axis for nodal lesions, at baseline and at every follow-up. Using the longest diameter overstates the nodal contribution to the sum and can mask a response or create a false progression.</t>
         </is>
       </c>
-      <c r="F6" s="35" t="inlineStr">
+      <c r="F6" s="33" t="inlineStr">
         <is>
           <t>Lesion {lesion_id} is recorded as a lymph node. Please confirm, against the source imaging report, which axis the measurement recorded at {visit} represents and whether the value is correct.</t>
         </is>
@@ -15989,13 +16543,16 @@
           <t>Accept</t>
         </is>
       </c>
-      <c r="I6" s="58" t="inlineStr">
+      <c r="I6" s="57" t="inlineStr">
         <is>
           <t>Lesion {lesion_id} is a lymph node. Please confirm the measurement recorded at {visit} is the short axis; if the longest diameter was recorded, please correct it.</t>
         </is>
       </c>
-      <c r="J6" s="33" t="n"/>
-      <c r="K6" s="34" t="n"/>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>Accepted at the gate under the blanket approval; the same change is marked individually on the Rules sheet.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="108" customHeight="1">
       <c r="A7" s="25" t="inlineStr">
@@ -16023,7 +16580,7 @@
           <t>A centimetre value entered in a millimetre field understates a lesion tenfold, which can convert a progression into an apparent response.</t>
         </is>
       </c>
-      <c r="F7" s="56" t="inlineStr">
+      <c r="F7" s="55" t="inlineStr">
         <is>
           <t>Please confirm the unit of the measurement for lesion {lesion_id} at {visit} ({original_value} {original_unit}); the value appears inconsistent with the other measurements recorded for this subject.</t>
         </is>
@@ -16039,8 +16596,7 @@
         </is>
       </c>
       <c r="I7" s="22" t="inlineStr"/>
-      <c r="J7" s="33" t="n"/>
-      <c r="K7" s="34" t="n"/>
+      <c r="J7" s="22" t="inlineStr"/>
     </row>
     <row r="8" ht="108" customHeight="1">
       <c r="A8" s="23" t="inlineStr">
@@ -16068,7 +16624,7 @@
           <t>Nadir, progression dating and best overall response all depend on chronological order. An out-of-order date can move the nadir and change the progression determination.</t>
         </is>
       </c>
-      <c r="F8" s="56" t="inlineStr">
+      <c r="F8" s="55" t="inlineStr">
         <is>
           <t>The assessment dates for {visit_a} and {visit_b} appear inconsistent with the visit sequence. Please verify the assessment dates.</t>
         </is>
@@ -16084,8 +16640,7 @@
         </is>
       </c>
       <c r="I8" s="12" t="inlineStr"/>
-      <c r="J8" s="33" t="n"/>
-      <c r="K8" s="34" t="n"/>
+      <c r="J8" s="12" t="inlineStr"/>
     </row>
     <row r="9" ht="108" customHeight="1">
       <c r="A9" s="25" t="inlineStr">
@@ -16113,7 +16668,7 @@
           <t>RECIST {guideline_version} permits a maximum of {max_total} target lesions in total. Additional lesions must be recorded as non-target. Including extra lesions in the sum changes the denominator for percent change and can alter the response category at every subsequent timepoint.</t>
         </is>
       </c>
-      <c r="F9" s="56" t="inlineStr">
+      <c r="F9" s="55" t="inlineStr">
         <is>
           <t>{n} target lesions are recorded at baseline for this subject, exceeding the maximum of {max_total} specified in the protocol. Please review the target lesion selection and re-classify the excess lesions as non-target, updating all affected assessments.</t>
         </is>
@@ -16129,8 +16684,7 @@
         </is>
       </c>
       <c r="I9" s="22" t="inlineStr"/>
-      <c r="J9" s="33" t="n"/>
-      <c r="K9" s="34" t="n"/>
+      <c r="J9" s="22" t="inlineStr"/>
     </row>
     <row r="10" ht="108" customHeight="1">
       <c r="A10" s="23" t="inlineStr">
@@ -16158,7 +16712,7 @@
           <t>RECIST {guideline_version} limits target lesions to {max_per_organ} per organ so that the sum represents the overall disease burden rather than one organ. Over-representation of one organ biases the response assessment.</t>
         </is>
       </c>
-      <c r="F10" s="56" t="inlineStr">
+      <c r="F10" s="55" t="inlineStr">
         <is>
           <t>{n} target lesions are recorded in {organ}, exceeding the per-organ maximum of {max_per_organ}. Please re-classify the excess lesions as non-target and update the affected assessments.</t>
         </is>
@@ -16174,8 +16728,7 @@
         </is>
       </c>
       <c r="I10" s="12" t="inlineStr"/>
-      <c r="J10" s="33" t="n"/>
-      <c r="K10" s="34" t="n"/>
+      <c r="J10" s="12" t="inlineStr"/>
     </row>
     <row r="11" ht="108" customHeight="1">
       <c r="A11" s="25" t="inlineStr">
@@ -16203,7 +16756,7 @@
           <t>RECIST {guideline_version} requires a non-nodal lesion to be at least {threshold} mm by {method} to be measurable and therefore eligible as a target lesion. Sub-threshold lesions are subject to unreliable measurement, and including one makes the whole sum unreliable.</t>
         </is>
       </c>
-      <c r="F11" s="56" t="inlineStr">
+      <c r="F11" s="55" t="inlineStr">
         <is>
           <t>Target lesion {lesion_id} measures {value} mm at baseline, below the {threshold} mm threshold for measurability by {method}. Please confirm the measurement, or re-classify this lesion as non-target and update the affected assessments.</t>
         </is>
@@ -16219,11 +16772,10 @@
         </is>
       </c>
       <c r="I11" s="22" t="inlineStr"/>
-      <c r="J11" s="33" t="n"/>
-      <c r="K11" s="34" t="n"/>
+      <c r="J11" s="22" t="inlineStr"/>
     </row>
     <row r="12" ht="108" customHeight="1">
-      <c r="A12" s="57" t="inlineStr">
+      <c r="A12" s="56" t="inlineStr">
         <is>
           <t>TE-BL-004</t>
         </is>
@@ -16248,7 +16800,7 @@
           <t>RECIST 1.1 requires a short axis of at least 15 mm for a node to be measurable and selectable as a target lesion. Nodes with a short axis of 10 to under 15 mm are pathological but non-measurable and should be recorded as non-target; nodes under 10 mm are non-pathological and should not be recorded at all.</t>
         </is>
       </c>
-      <c r="F12" s="35" t="inlineStr">
+      <c r="F12" s="33" t="inlineStr">
         <is>
           <t>Nodal target lesion {lesion_id} has a baseline short axis of {value} mm recorded at {visit}. Please confirm against the source imaging report whether this measurement is correct, and whether this node was intended to be recorded as a target lesion.</t>
         </is>
@@ -16263,16 +16815,19 @@
           <t>Accept</t>
         </is>
       </c>
-      <c r="I12" s="58" t="inlineStr">
+      <c r="I12" s="57" t="inlineStr">
         <is>
           <t>Nodal target lesion {lesion_id} has a baseline short axis of {value} mm. Please confirm the measurement; a node with short axis below 15 mm should be recorded as a non-target lesion (10 to &lt;15 mm) or not recorded (&lt;10 mm).</t>
         </is>
       </c>
-      <c r="J12" s="33" t="n"/>
-      <c r="K12" s="34" t="n"/>
+      <c r="J12" s="12" t="inlineStr">
+        <is>
+          <t>Accepted at the gate under the blanket approval; the same change is marked individually on the Rules sheet.</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="108" customHeight="1">
-      <c r="A13" s="57" t="inlineStr">
+      <c r="A13" s="56" t="inlineStr">
         <is>
           <t>TE-BL-005</t>
         </is>
@@ -16297,7 +16852,7 @@
           <t>Under RECIST 1.1 a node with a short axis below 10 mm is considered non-pathological and is not recorded or followed. Recording it adds normal tissue to the disease assessment and can prevent a complete response from being assigned.</t>
         </is>
       </c>
-      <c r="F13" s="35" t="inlineStr">
+      <c r="F13" s="33" t="inlineStr">
         <is>
           <t>Node {lesion_id} has a baseline short axis of {value} mm recorded at {visit}. Please confirm whether this node was intended to be recorded as disease for this subject, and correct the record if it was not.</t>
         </is>
@@ -16312,13 +16867,16 @@
           <t>Accept</t>
         </is>
       </c>
-      <c r="I13" s="59" t="inlineStr">
+      <c r="I13" s="58" t="inlineStr">
         <is>
           <t>Node {lesion_id} has a baseline short axis of {value} mm, below the 10 mm pathological threshold. Please confirm whether this node should be recorded as disease; if not, please remove it from the assessment.</t>
         </is>
       </c>
-      <c r="J13" s="33" t="n"/>
-      <c r="K13" s="34" t="n"/>
+      <c r="J13" s="22" t="inlineStr">
+        <is>
+          <t>Accepted at the gate under the blanket approval; the same change is marked individually on the Rules sheet.</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="108" customHeight="1">
       <c r="A14" s="23" t="inlineStr">
@@ -16346,7 +16904,7 @@
           <t>RECIST 1.1 requires a lesion to be at least twice the slice thickness to be measurable; on {slice_thickness} mm slices the minimum measurable lesion is {min_size} mm. Below that, apparent size changes may be partial-volume artefacts rather than real change.</t>
         </is>
       </c>
-      <c r="F14" s="56" t="inlineStr">
+      <c r="F14" s="55" t="inlineStr">
         <is>
           <t>Target lesion {lesion_id} measures {value} mm at baseline on images with {slice_thickness} mm slice thickness. Please confirm the lesion is measurable per the imaging manual, or re-classify it as non-target.</t>
         </is>
@@ -16362,11 +16920,10 @@
         </is>
       </c>
       <c r="I14" s="12" t="inlineStr"/>
-      <c r="J14" s="33" t="n"/>
-      <c r="K14" s="34" t="n"/>
+      <c r="J14" s="12" t="inlineStr"/>
     </row>
     <row r="15" ht="108" customHeight="1">
-      <c r="A15" s="57" t="inlineStr">
+      <c r="A15" s="56" t="inlineStr">
         <is>
           <t>TE-BL-007</t>
         </is>
@@ -16391,7 +16948,7 @@
           <t>RECIST classifies {non_measurable_category} as non-measurable disease: it cannot be reproducibly measured in one dimension. Such disease must be recorded as non-target and assessed qualitatively. A non-measurable lesion inside the target sum makes the sum, and every percent change derived from it, unreliable.</t>
         </is>
       </c>
-      <c r="F15" s="35" t="inlineStr">
+      <c r="F15" s="33" t="inlineStr">
         <is>
           <t>Target lesion {lesion_id} is described as '{location_detail}'. Please confirm the lesion type, and whether this finding can be measured reproducibly in one dimension on the source imaging. If the description is incomplete, please add the detail from the imaging report.</t>
         </is>
@@ -16406,16 +16963,19 @@
           <t>Accept</t>
         </is>
       </c>
-      <c r="I15" s="59" t="inlineStr">
+      <c r="I15" s="58" t="inlineStr">
         <is>
           <t>Target lesion {lesion_id} is described as "{location_detail}". This appears to represent non-measurable disease under RECIST. Please confirm the lesion selection and, if appropriate, re-classify it as a non-target lesion.</t>
         </is>
       </c>
-      <c r="J15" s="33" t="n"/>
-      <c r="K15" s="34" t="n"/>
+      <c r="J15" s="22" t="inlineStr">
+        <is>
+          <t>Accepted at the gate under the blanket approval; the same change is marked individually on the Rules sheet.</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="108" customHeight="1">
-      <c r="A16" s="57" t="inlineStr">
+      <c r="A16" s="56" t="inlineStr">
         <is>
           <t>TE-BL-008</t>
         </is>
@@ -16440,7 +17000,7 @@
           <t>RECIST treats lesions in a previously irradiated area, or subjected to other locoregional therapy, as non-measurable unless progression of that lesion has been demonstrated since the treatment. Post-radiation change can mimic both response and progression.</t>
         </is>
       </c>
-      <c r="F16" s="35" t="inlineStr">
+      <c r="F16" s="33" t="inlineStr">
         <is>
           <t>Target lesion {lesion_id} is recorded within a prior radiotherapy field. Please confirm whether progression of this specific lesion has been documented since that radiotherapy, and provide the date and source document if so.</t>
         </is>
@@ -16455,13 +17015,16 @@
           <t>Accept</t>
         </is>
       </c>
-      <c r="I16" s="58" t="inlineStr">
+      <c r="I16" s="57" t="inlineStr">
         <is>
           <t>Target lesion {lesion_id} is located within a prior radiotherapy field. Please confirm whether progression of this lesion has been documented since radiotherapy; if not, the lesion should be recorded as non-target.</t>
         </is>
       </c>
-      <c r="J16" s="33" t="n"/>
-      <c r="K16" s="34" t="n"/>
+      <c r="J16" s="12" t="inlineStr">
+        <is>
+          <t>Accepted at the gate under the blanket approval; the same change is marked individually on the Rules sheet.</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="108" customHeight="1">
       <c r="A17" s="25" t="inlineStr">
@@ -16489,7 +17052,7 @@
           <t>The measurable-disease determination drives the response algorithm: subjects without measurable disease can only be assigned CR, Non-CR/Non-PD, PD or NE, never PR or SD. An inconsistency here produces a systematically wrong response for every timepoint, and may also affect eligibility.</t>
         </is>
       </c>
-      <c r="F17" s="56" t="inlineStr">
+      <c r="F17" s="55" t="inlineStr">
         <is>
           <t>Measurable disease at baseline is recorded as {flag} while {n} target lesions are entered. Please confirm the baseline disease status and correct the inconsistent record.</t>
         </is>
@@ -16505,8 +17068,7 @@
         </is>
       </c>
       <c r="I17" s="22" t="inlineStr"/>
-      <c r="J17" s="33" t="n"/>
-      <c r="K17" s="34" t="n"/>
+      <c r="J17" s="22" t="inlineStr"/>
     </row>
     <row r="18" ht="108" customHeight="1">
       <c r="A18" s="23" t="inlineStr">
@@ -16534,7 +17096,7 @@
           <t>A baseline older than the protocol window may no longer represent the disease burden at the start of treatment, which biases every subsequent percent change. A baseline dated after first dose is not a baseline at all and would understate treatment effect.</t>
         </is>
       </c>
-      <c r="F18" s="56" t="inlineStr">
+      <c r="F18" s="55" t="inlineStr">
         <is>
           <t>The baseline tumor assessment ({baseline_date}) falls {gap} days before first dose ({first_dose_date}), outside the protocol window of {window} days. Please confirm the assessment date and whether a protocol deviation has been recorded.</t>
         </is>
@@ -16550,8 +17112,7 @@
         </is>
       </c>
       <c r="I18" s="12" t="inlineStr"/>
-      <c r="J18" s="33" t="n"/>
-      <c r="K18" s="34" t="n"/>
+      <c r="J18" s="12" t="inlineStr"/>
     </row>
     <row r="19" ht="108" customHeight="1">
       <c r="A19" s="25" t="inlineStr">
@@ -16579,7 +17140,7 @@
           <t>The baseline sum is the reference for every partial response determination. An error of {difference} mm shifts the 30% response threshold and can change the response category at multiple timepoints. Recorded lesions: {lesion_breakdown}.</t>
         </is>
       </c>
-      <c r="F19" s="56" t="inlineStr">
+      <c r="F19" s="55" t="inlineStr">
         <is>
           <t>The baseline sum of diameters ({reported} mm) does not equal the sum of the recorded target lesion measurements ({derived} mm). Please verify the individual measurements and the sum.</t>
         </is>
@@ -16595,8 +17156,7 @@
         </is>
       </c>
       <c r="I19" s="22" t="inlineStr"/>
-      <c r="J19" s="33" t="n"/>
-      <c r="K19" s="34" t="n"/>
+      <c r="J19" s="22" t="inlineStr"/>
     </row>
     <row r="20" ht="108" customHeight="1">
       <c r="A20" s="23" t="inlineStr">
@@ -16624,7 +17184,7 @@
           <t>RECIST directs that target lesions be selected on the basis of size, choosing the largest lesions that are reproducibly measurable, while remaining representative of all involved organs. Selecting smaller lesions as targets while larger measurable lesions are left as non-target reduces the sensitivity of the response assessment.</t>
         </is>
       </c>
-      <c r="F20" s="56" t="inlineStr">
+      <c r="F20" s="55" t="inlineStr">
         <is>
           <t>Non-target lesion {nt_lesion_id} ({nt_value} mm) is larger than target lesion {t_lesion_id} ({t_value} mm). Please confirm the target lesion selection rationale, for example poor reproducibility of the larger lesion.</t>
         </is>
@@ -16640,8 +17200,7 @@
         </is>
       </c>
       <c r="I20" s="12" t="inlineStr"/>
-      <c r="J20" s="33" t="n"/>
-      <c r="K20" s="34" t="n"/>
+      <c r="J20" s="12" t="inlineStr"/>
     </row>
     <row r="21" ht="108" customHeight="1">
       <c r="A21" s="25" t="inlineStr">
@@ -16669,7 +17228,7 @@
           <t>Without a baseline value the lesion cannot contribute to the baseline sum, so the reference for percent change is understated and partial response may be reported prematurely.</t>
         </is>
       </c>
-      <c r="F21" s="56" t="inlineStr">
+      <c r="F21" s="55" t="inlineStr">
         <is>
           <t>Target lesion {lesion_id} has no baseline measurement. Please enter the baseline measurement, or re-classify the lesion if it was not measurable at baseline.</t>
         </is>
@@ -16685,8 +17244,7 @@
         </is>
       </c>
       <c r="I21" s="22" t="inlineStr"/>
-      <c r="J21" s="33" t="n"/>
-      <c r="K21" s="34" t="n"/>
+      <c r="J21" s="22" t="inlineStr"/>
     </row>
     <row r="22" ht="108" customHeight="1">
       <c r="A22" s="23" t="inlineStr">
@@ -16714,7 +17272,7 @@
           <t>RECIST requires the same method of assessment and the same technique at baseline and during follow-up. Different modalities measure different things — a change of modality can produce an apparent size change of the order of the response thresholds without any true biological change.</t>
         </is>
       </c>
-      <c r="F22" s="56" t="inlineStr">
+      <c r="F22" s="55" t="inlineStr">
         <is>
           <t>Lesion {lesion_id} was assessed by {method_a} at baseline and {method_b} at {visit_b}. Please confirm the modality used and whether the change was clinically necessary.</t>
         </is>
@@ -16730,8 +17288,7 @@
         </is>
       </c>
       <c r="I22" s="12" t="inlineStr"/>
-      <c r="J22" s="33" t="n"/>
-      <c r="K22" s="34" t="n"/>
+      <c r="J22" s="12" t="inlineStr"/>
     </row>
     <row r="23" ht="108" customHeight="1">
       <c r="A23" s="25" t="inlineStr">
@@ -16759,7 +17316,7 @@
           <t>An assessment is intended to be a snapshot. When component scans are widely separated, lesions measured on the later scans reflect a different point in the disease course, which distorts the sum and, at baseline, the reference for all later comparisons.</t>
         </is>
       </c>
-      <c r="F23" s="56" t="inlineStr">
+      <c r="F23" s="55" t="inlineStr">
         <is>
           <t>The scans comprising the {visit} tumor assessment span {span} days. Please confirm the scan dates and whether all scans belong to this assessment.</t>
         </is>
@@ -16775,8 +17332,7 @@
         </is>
       </c>
       <c r="I23" s="22" t="inlineStr"/>
-      <c r="J23" s="33" t="n"/>
-      <c r="K23" s="34" t="n"/>
+      <c r="J23" s="22" t="inlineStr"/>
     </row>
     <row r="24" ht="108" customHeight="1">
       <c r="A24" s="23" t="inlineStr">
@@ -16804,7 +17360,7 @@
           <t>Organ coding drives the per-organ target lesion limit and the interpretation of new lesions by region. A mismatch can hide a breach of the per-organ limit or misclassify a new lesion.</t>
         </is>
       </c>
-      <c r="F24" s="56" t="inlineStr">
+      <c r="F24" s="55" t="inlineStr">
         <is>
           <t>Lesion {lesion_id} is recorded at {organ} {laterality} with the description "{location_detail}". Please confirm the anatomical location and correct the coding if needed.</t>
         </is>
@@ -16820,8 +17376,7 @@
         </is>
       </c>
       <c r="I24" s="12" t="inlineStr"/>
-      <c r="J24" s="33" t="n"/>
-      <c r="K24" s="34" t="n"/>
+      <c r="J24" s="12" t="inlineStr"/>
     </row>
     <row r="25" ht="108" customHeight="1">
       <c r="A25" s="25" t="inlineStr">
@@ -16849,7 +17404,7 @@
           <t>Percent change from baseline, the nadir and every response category depend on a baseline. Without it the subject cannot contribute to any efficacy endpoint.</t>
         </is>
       </c>
-      <c r="F25" s="56" t="inlineStr">
+      <c r="F25" s="55" t="inlineStr">
         <is>
           <t>No baseline tumor assessment is recorded for this subject although follow-up assessments exist. Please enter the baseline assessment or confirm why it was not performed.</t>
         </is>
@@ -16865,8 +17420,7 @@
         </is>
       </c>
       <c r="I25" s="22" t="inlineStr"/>
-      <c r="J25" s="33" t="n"/>
-      <c r="K25" s="34" t="n"/>
+      <c r="J25" s="22" t="inlineStr"/>
     </row>
     <row r="26" ht="108" customHeight="1">
       <c r="A26" s="23" t="inlineStr">
@@ -16894,7 +17448,7 @@
           <t>The sum drives percent change from baseline (partial response) and from nadir (progression). A {difference} mm error at this timepoint changes the percent change from {reported_pct}% to {derived_pct}% and the derived response from {reported_response} to {derived_response}.</t>
         </is>
       </c>
-      <c r="F26" s="56" t="inlineStr">
+      <c r="F26" s="55" t="inlineStr">
         <is>
           <t>The sum of diameters recorded at {visit} ({reported} mm) does not match the sum of the individual target lesion measurements ({derived} mm). Please verify the individual measurements and the recorded sum.</t>
         </is>
@@ -16910,8 +17464,7 @@
         </is>
       </c>
       <c r="I26" s="12" t="inlineStr"/>
-      <c r="J26" s="33" t="n"/>
-      <c r="K26" s="34" t="n"/>
+      <c r="J26" s="12" t="inlineStr"/>
     </row>
     <row r="27" ht="108" customHeight="1">
       <c r="A27" s="25" t="inlineStr">
@@ -16939,7 +17492,7 @@
           <t>An unexplained missing measurement makes the sum incomplete, which forces the target response to not evaluable and can propagate into a missing timepoint for progression-free survival.</t>
         </is>
       </c>
-      <c r="F27" s="56" t="inlineStr">
+      <c r="F27" s="55" t="inlineStr">
         <is>
           <t>No measurement is recorded for target lesion {lesion_id} at {visit}. Please enter the measurement or record the reason it could not be assessed.</t>
         </is>
@@ -16955,8 +17508,7 @@
         </is>
       </c>
       <c r="I27" s="22" t="inlineStr"/>
-      <c r="J27" s="33" t="n"/>
-      <c r="K27" s="34" t="n"/>
+      <c r="J27" s="22" t="inlineStr"/>
     </row>
     <row r="28" ht="108" customHeight="1">
       <c r="A28" s="23" t="inlineStr">
@@ -16984,7 +17536,7 @@
           <t>When any target lesion cannot be assessed, the sum is incomplete and the true tumor burden is unknown, so the response is not evaluable. The exception is progression: if the measured lesions alone already meet the progression threshold, progressive disease can still be assigned. Here the measured lesions sum to {partial_sum} mm against a nadir of {nadir} mm ({partial_pct}%), which does not reach the progression threshold.</t>
         </is>
       </c>
-      <c r="F28" s="56" t="inlineStr">
+      <c r="F28" s="55" t="inlineStr">
         <is>
           <t>Target lesion {lesion_id} is recorded as not evaluable at {visit} while the target lesion response is reported as {reported_response}. Please confirm; where a target lesion cannot be assessed, the target response should normally be not evaluable.</t>
         </is>
@@ -17000,8 +17552,7 @@
         </is>
       </c>
       <c r="I28" s="12" t="inlineStr"/>
-      <c r="J28" s="33" t="n"/>
-      <c r="K28" s="34" t="n"/>
+      <c r="J28" s="12" t="inlineStr"/>
     </row>
     <row r="29" ht="108" customHeight="1">
       <c r="A29" s="25" t="inlineStr">
@@ -17029,7 +17580,7 @@
           <t>A change of this magnitude over {interval} days is unusual and is more often a transcription error, a unit error, or measurement of a different lesion than true biology. The change moves the sum from {prev_sum} mm to {sum} mm and the derived response from {prev_response} to {response}.</t>
         </is>
       </c>
-      <c r="F29" s="56" t="inlineStr">
+      <c r="F29" s="55" t="inlineStr">
         <is>
           <t>Lesion {lesion_id} changed from {prev_value} mm to {value} mm between {prev_visit} and {visit}. Please verify the measurement against the imaging report.</t>
         </is>
@@ -17045,8 +17596,7 @@
         </is>
       </c>
       <c r="I29" s="22" t="inlineStr"/>
-      <c r="J29" s="33" t="n"/>
-      <c r="K29" s="34" t="n"/>
+      <c r="J29" s="22" t="inlineStr"/>
     </row>
     <row r="30" ht="108" customHeight="1">
       <c r="A30" s="23" t="inlineStr">
@@ -17074,7 +17624,7 @@
           <t>A previously resolved target lesion that reappears re-enters the sum of diameters at its measured size; it is not a new lesion, because it was present at baseline. Progression is then judged against the nadir. If it has instead been recorded as a new lesion, progression will be dated incorrectly and the sum will double-count the disease.</t>
         </is>
       </c>
-      <c r="F30" s="56" t="inlineStr">
+      <c r="F30" s="55" t="inlineStr">
         <is>
           <t>Lesion {lesion_id} was recorded as absent at {absent_visit} and is measured again at {visit}. Please confirm this is the same baseline target lesion rather than a new lesion, and that it is included in the sum of diameters.</t>
         </is>
@@ -17090,8 +17640,7 @@
         </is>
       </c>
       <c r="I30" s="12" t="inlineStr"/>
-      <c r="J30" s="33" t="n"/>
-      <c r="K30" s="34" t="n"/>
+      <c r="J30" s="12" t="inlineStr"/>
     </row>
     <row r="31" ht="108" customHeight="1">
       <c r="A31" s="25" t="inlineStr">
@@ -17119,7 +17668,7 @@
           <t>The two conventions produce different sums and different eligibility for complete response. Mixing them makes cross-subject comparison unreliable and can make a complete response unassignable for some subjects and assignable for others with identical imaging.</t>
         </is>
       </c>
-      <c r="F31" s="56" t="inlineStr">
+      <c r="F31" s="55" t="inlineStr">
         <is>
           <t>Please confirm the convention used for lesions below the limit of reliable measurement at this site, so that the records can be harmonised.</t>
         </is>
@@ -17135,8 +17684,7 @@
         </is>
       </c>
       <c r="I31" s="22" t="inlineStr"/>
-      <c r="J31" s="33" t="n"/>
-      <c r="K31" s="34" t="n"/>
+      <c r="J31" s="22" t="inlineStr"/>
     </row>
     <row r="32" ht="108" customHeight="1">
       <c r="A32" s="23" t="inlineStr">
@@ -17164,7 +17712,7 @@
           <t>Assessment timing determines the resolution of progression dating and, in randomised trials, the comparability of progression-free survival between arms. Systematically late assessments delay progression detection.</t>
         </is>
       </c>
-      <c r="F32" s="56" t="inlineStr">
+      <c r="F32" s="55" t="inlineStr">
         <is>
           <t>The interval between {prev_visit} and {visit} is {interval} days, outside the protocol window of {expected} ± {window} days. Please confirm the assessment date and whether a protocol deviation has been recorded.</t>
         </is>
@@ -17180,8 +17728,7 @@
         </is>
       </c>
       <c r="I32" s="12" t="inlineStr"/>
-      <c r="J32" s="33" t="n"/>
-      <c r="K32" s="34" t="n"/>
+      <c r="J32" s="12" t="inlineStr"/>
     </row>
     <row r="33" ht="108" customHeight="1">
       <c r="A33" s="25" t="inlineStr">
@@ -17209,7 +17756,7 @@
           <t>Two or more consecutively missed assessments typically require censoring at the last evaluable assessment in progression-free survival analyses, which reduces the information contributed by this subject and can bias the estimate.</t>
         </is>
       </c>
-      <c r="F33" s="56" t="inlineStr">
+      <c r="F33" s="55" t="inlineStr">
         <is>
           <t>No tumor assessment is recorded between {prev_date} and {date} although the subject remained on treatment. Please confirm whether assessments were performed and, if so, enter the data; otherwise please record the reason.</t>
         </is>
@@ -17225,11 +17772,10 @@
         </is>
       </c>
       <c r="I33" s="22" t="inlineStr"/>
-      <c r="J33" s="33" t="n"/>
-      <c r="K33" s="34" t="n"/>
+      <c r="J33" s="22" t="inlineStr"/>
     </row>
     <row r="34" ht="108" customHeight="1">
-      <c r="A34" s="57" t="inlineStr">
+      <c r="A34" s="56" t="inlineStr">
         <is>
           <t>TE-FU-009</t>
         </is>
@@ -17254,7 +17800,7 @@
           <t>Under RECIST 1.1 lymph nodes always retain a measurable short axis and are never recorded as absent; they continue to contribute their short axis to the sum even when it falls below 10 mm. The sum therefore need not reach zero for a complete response — what is required is that every pathological node has a short axis below 10 mm. Recording the node as zero understates the sum by its true short axis and can produce a false partial response or complete response.</t>
         </is>
       </c>
-      <c r="F34" s="35" t="inlineStr">
+      <c r="F34" s="33" t="inlineStr">
         <is>
           <t>Nodal target lesion {lesion_id} is recorded as {state_or_zero} at {visit}. Please confirm whether this node was measured at this visit and, if so, record the short axis from the source imaging report. If it could not be measured, please record the reason.</t>
         </is>
@@ -17269,13 +17815,16 @@
           <t>Accept</t>
         </is>
       </c>
-      <c r="I34" s="58" t="inlineStr">
+      <c r="I34" s="57" t="inlineStr">
         <is>
           <t>Nodal target lesion {lesion_id} is recorded as {state_or_zero} at {visit}. Lymph nodes should continue to be measured in short axis at every visit, including when they normalise. Please enter the measured short axis.</t>
         </is>
       </c>
-      <c r="J34" s="33" t="n"/>
-      <c r="K34" s="34" t="n"/>
+      <c r="J34" s="12" t="inlineStr">
+        <is>
+          <t>Accepted at the gate under the blanket approval; the same change is marked individually on the Rules sheet.</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="108" customHeight="1">
       <c r="A35" s="25" t="inlineStr">
@@ -17303,7 +17852,7 @@
           <t>The non-target response contributes to the overall timepoint response, and unequivocal progression of non-target disease is sufficient for progression on its own. A missing non-target assessment leaves the overall response underdetermined.</t>
         </is>
       </c>
-      <c r="F35" s="56" t="inlineStr">
+      <c r="F35" s="55" t="inlineStr">
         <is>
           <t>No assessment is recorded for non-target lesion {lesion_id} at {visit}. Please record the status of this lesion.</t>
         </is>
@@ -17319,8 +17868,7 @@
         </is>
       </c>
       <c r="I35" s="22" t="inlineStr"/>
-      <c r="J35" s="33" t="n"/>
-      <c r="K35" s="34" t="n"/>
+      <c r="J35" s="22" t="inlineStr"/>
     </row>
     <row r="36" ht="108" customHeight="1">
       <c r="A36" s="23" t="inlineStr">
@@ -17348,7 +17896,7 @@
           <t>An assessment dated after death or well beyond the end of follow-up indicates an error in one of the two dates. Either error affects analysis: an incorrect assessment date can move the progression date, and an incorrect death date affects survival analysis.</t>
         </is>
       </c>
-      <c r="F36" s="56" t="inlineStr">
+      <c r="F36" s="55" t="inlineStr">
         <is>
           <t>The {visit} tumor assessment is dated {date}, after the recorded {reference_event} ({reference_date}). Please verify both dates.</t>
         </is>
@@ -17364,8 +17912,7 @@
         </is>
       </c>
       <c r="I36" s="12" t="inlineStr"/>
-      <c r="J36" s="33" t="n"/>
-      <c r="K36" s="34" t="n"/>
+      <c r="J36" s="12" t="inlineStr"/>
     </row>
     <row r="37" ht="108" customHeight="1">
       <c r="A37" s="25" t="inlineStr">
@@ -17393,7 +17940,7 @@
           <t>The progression date is taken from the first assessment at which the new lesion was observed. An inconsistency between these dates produces the wrong progression date and therefore the wrong progression-free survival time.</t>
         </is>
       </c>
-      <c r="F37" s="56" t="inlineStr">
+      <c r="F37" s="55" t="inlineStr">
         <is>
           <t>New lesion {lesion_id} has an identification date of {identified_date} but is first reported at {visit} ({visit_date}). Please confirm the date the lesion was first observed.</t>
         </is>
@@ -17409,8 +17956,7 @@
         </is>
       </c>
       <c r="I37" s="22" t="inlineStr"/>
-      <c r="J37" s="33" t="n"/>
-      <c r="K37" s="34" t="n"/>
+      <c r="J37" s="22" t="inlineStr"/>
     </row>
     <row r="38" ht="108" customHeight="1">
       <c r="A38" s="23" t="inlineStr">
@@ -17438,7 +17984,7 @@
           <t>Widely separated component scans mean that different parts of the tumor burden are measured at different times, which affects the sum and may affect the progression date.</t>
         </is>
       </c>
-      <c r="F38" s="56" t="inlineStr">
+      <c r="F38" s="55" t="inlineStr">
         <is>
           <t>The scans comprising the {visit} assessment span {span} days. Please confirm the scan dates.</t>
         </is>
@@ -17454,8 +18000,7 @@
         </is>
       </c>
       <c r="I38" s="12" t="inlineStr"/>
-      <c r="J38" s="33" t="n"/>
-      <c r="K38" s="34" t="n"/>
+      <c r="J38" s="12" t="inlineStr"/>
     </row>
     <row r="39" ht="108" customHeight="1">
       <c r="A39" s="25" t="inlineStr">
@@ -17483,7 +18028,7 @@
           <t>Identical measurements of a lesion of this size across several timepoints are uncommon given normal measurement variability, and may indicate that a previous value was copied rather than the lesion re-measured. If so, the sum does not reflect the current tumor burden.</t>
         </is>
       </c>
-      <c r="F39" s="56" t="inlineStr">
+      <c r="F39" s="55" t="inlineStr">
         <is>
           <t>Lesion {lesion_id} is recorded as exactly {value} mm at {visits}. Please confirm that the lesion was measured at each assessment.</t>
         </is>
@@ -17499,11 +18044,10 @@
         </is>
       </c>
       <c r="I39" s="22" t="inlineStr"/>
-      <c r="J39" s="33" t="n"/>
-      <c r="K39" s="34" t="n"/>
+      <c r="J39" s="22" t="inlineStr"/>
     </row>
     <row r="40" ht="108" customHeight="1">
-      <c r="A40" s="57" t="inlineStr">
+      <c r="A40" s="56" t="inlineStr">
         <is>
           <t>TE-RS-001</t>
         </is>
@@ -17528,7 +18072,7 @@
           <t>{derivation_explanation}</t>
         </is>
       </c>
-      <c r="F40" s="35" t="inlineStr">
+      <c r="F40" s="33" t="inlineStr">
         <is>
           <t>The target lesion response recorded at {visit} is {reported}, while the individual lesion measurements recorded for the same visit sum to {sum} mm. Please review the recorded response together with the lesion measurements against the source imaging report, and correct whichever does not match the source.</t>
         </is>
@@ -17543,16 +18087,19 @@
           <t>Accept</t>
         </is>
       </c>
-      <c r="I40" s="58" t="inlineStr">
+      <c r="I40" s="57" t="inlineStr">
         <is>
           <t>The target lesion response recorded at {visit} is {reported}. Based on the recorded lesion measurements the sum of diameters is {sum} mm, a {pct_baseline}% change from baseline and a {pct_nadir}% change from the nadir of {nadir_sum} mm, which corresponds to {derived}. Please review the recorded response and the underlying measurements.</t>
         </is>
       </c>
-      <c r="J40" s="33" t="n"/>
-      <c r="K40" s="34" t="n"/>
+      <c r="J40" s="12" t="inlineStr">
+        <is>
+          <t>Accepted at the gate under the blanket approval; the same change is marked individually on the Rules sheet.</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="108" customHeight="1">
-      <c r="A41" s="57" t="inlineStr">
+      <c r="A41" s="56" t="inlineStr">
         <is>
           <t>TE-RS-002</t>
         </is>
@@ -17577,7 +18124,7 @@
           <t>RECIST 1.1 requires both a relative increase of at least {pd_pct}% and an absolute increase of at least {pd_abs} mm from the nadir. The absolute criterion was introduced precisely for small tumor burdens, where a 20% increase can fall within measurement variability. Here the absolute increase of {abs_nadir} mm does not reach {pd_abs} mm, so the derived response is {derived}.</t>
         </is>
       </c>
-      <c r="F41" s="35" t="inlineStr">
+      <c r="F41" s="33" t="inlineStr">
         <is>
           <t>Progressive disease is recorded at {visit}. The sum of diameters has increased from {nadir_sum} mm at {nadir_visit} to {sum} mm, a change of {abs_nadir} mm. Please confirm what the progression assessment at this visit was based on — the target lesion measurements, a new lesion, or worsening of non-target disease.</t>
         </is>
@@ -17592,16 +18139,19 @@
           <t>Accept</t>
         </is>
       </c>
-      <c r="I41" s="59" t="inlineStr">
+      <c r="I41" s="58" t="inlineStr">
         <is>
           <t>Progressive disease is recorded at {visit} based on an increase from the nadir of {nadir_sum} mm to {sum} mm. This is a {pct_nadir}% increase but only {abs_nadir} mm in absolute terms, which does not meet the {pd_abs} mm absolute increase also required by RECIST 1.1. Please review the response assessment, unless progression is based on a new lesion or on unequivocal non-target progression.</t>
         </is>
       </c>
-      <c r="J41" s="33" t="n"/>
-      <c r="K41" s="34" t="n"/>
+      <c r="J41" s="22" t="inlineStr">
+        <is>
+          <t>Accepted at the gate under the blanket approval; the same change is marked individually on the Rules sheet.</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="108" customHeight="1">
-      <c r="A42" s="57" t="inlineStr">
+      <c r="A42" s="56" t="inlineStr">
         <is>
           <t>TE-RS-003</t>
         </is>
@@ -17626,7 +18176,7 @@
           <t>Progression is assessed against the smallest sum recorded on study, including baseline, not against baseline itself. Because this subject responded before progressing, the comparison against baseline still looks favourable while the comparison against the nadir meets the progression criteria. The derived response is progressive disease.</t>
         </is>
       </c>
-      <c r="F42" s="35" t="inlineStr">
+      <c r="F42" s="33" t="inlineStr">
         <is>
           <t>At {visit} the sum of diameters is {sum} mm, compared with the smallest sum recorded on study of {nadir_sum} mm at {nadir_visit}. The response recorded at {visit} is {reported}. Please confirm the response assessment for this visit against the source imaging report.</t>
         </is>
@@ -17641,13 +18191,16 @@
           <t>Accept</t>
         </is>
       </c>
-      <c r="I42" s="58" t="inlineStr">
+      <c r="I42" s="57" t="inlineStr">
         <is>
           <t>At {visit} the sum of diameters is {sum} mm compared with a nadir of {nadir_sum} mm at {nadir_visit}, a {pct_nadir}% increase of {abs_nadir} mm, which meets the RECIST criteria for progression. The recorded response is {reported}. Please review the response assessment.</t>
         </is>
       </c>
-      <c r="J42" s="33" t="n"/>
-      <c r="K42" s="34" t="n"/>
+      <c r="J42" s="12" t="inlineStr">
+        <is>
+          <t>Accepted at the gate under the blanket approval; the same change is marked individually on the Rules sheet.</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="108" customHeight="1">
       <c r="A43" s="25" t="inlineStr">
@@ -17675,7 +18228,7 @@
           <t>A complete response of target lesions requires the disappearance of all non-nodal target lesions and a reduction of every pathological lymph node, whether target or non-target, to a short axis below {node_threshold} mm. A lesion that is still visible, including one recorded as too small to measure, is not a disappearance.</t>
         </is>
       </c>
-      <c r="F43" s="56" t="inlineStr">
+      <c r="F43" s="55" t="inlineStr">
         <is>
           <t>A complete response is recorded at {visit}, but {blocking_description}. Please review the response assessment and the individual lesion records.</t>
         </is>
@@ -17691,8 +18244,7 @@
         </is>
       </c>
       <c r="I43" s="22" t="inlineStr"/>
-      <c r="J43" s="33" t="n"/>
-      <c r="K43" s="34" t="n"/>
+      <c r="J43" s="22" t="inlineStr"/>
     </row>
     <row r="44" ht="108" customHeight="1">
       <c r="A44" s="23" t="inlineStr">
@@ -17720,7 +18272,7 @@
           <t>{derivation_explanation}</t>
         </is>
       </c>
-      <c r="F44" s="56" t="inlineStr">
+      <c r="F44" s="55" t="inlineStr">
         <is>
           <t>The non-target lesion response recorded at {visit} is {reported}, while the individual non-target lesion assessments ({non_target_breakdown}) correspond to {derived}. Please review.</t>
         </is>
@@ -17736,8 +18288,7 @@
         </is>
       </c>
       <c r="I44" s="12" t="inlineStr"/>
-      <c r="J44" s="33" t="n"/>
-      <c r="K44" s="34" t="n"/>
+      <c r="J44" s="12" t="inlineStr"/>
     </row>
     <row r="45" ht="108" customHeight="1">
       <c r="A45" s="25" t="inlineStr">
@@ -17765,7 +18316,7 @@
           <t>A complete response requires all lymph nodes, target and non-target alike, to have reduced to a short axis below {node_threshold} mm. A node of {value} mm remains pathological, so the non-target response is Non-CR/Non-PD.</t>
         </is>
       </c>
-      <c r="F45" s="56" t="inlineStr">
+      <c r="F45" s="55" t="inlineStr">
         <is>
           <t>A complete response of non-target lesions is recorded at {visit}, but node {lesion_id} measures {value} mm in short axis. Please review the non-target response.</t>
         </is>
@@ -17781,11 +18332,10 @@
         </is>
       </c>
       <c r="I45" s="22" t="inlineStr"/>
-      <c r="J45" s="33" t="n"/>
-      <c r="K45" s="34" t="n"/>
+      <c r="J45" s="22" t="inlineStr"/>
     </row>
     <row r="46" ht="108" customHeight="1">
-      <c r="A46" s="57" t="inlineStr">
+      <c r="A46" s="56" t="inlineStr">
         <is>
           <t>TE-RS-007</t>
         </is>
@@ -17810,7 +18360,7 @@
           <t>RECIST states that where measurable disease is present, unequivocal progression based on non-target disease alone should be an exceptional circumstance: the increase in overall tumor burden must be comparable in magnitude to the increase that would be required to declare progression for measurable disease. A modest increase in one non-target lesion is not sufficient, particularly while the target lesions are {target_response}.</t>
         </is>
       </c>
-      <c r="F46" s="35" t="inlineStr">
+      <c r="F46" s="33" t="inlineStr">
         <is>
           <t>Progression of non-target disease is recorded at {visit} while the target lesions are recorded as {target_response}. Please provide the radiological description supporting the non-target assessment at this visit, from the source imaging report.</t>
         </is>
@@ -17825,16 +18375,19 @@
           <t>Accept</t>
         </is>
       </c>
-      <c r="I46" s="58" t="inlineStr">
+      <c r="I46" s="57" t="inlineStr">
         <is>
           <t>Unequivocal progression of non-target disease is recorded at {visit} while the target lesions show {target_response}. Please confirm that the overall tumor burden has increased substantially, and provide the radiological description supporting unequivocal progression.</t>
         </is>
       </c>
-      <c r="J46" s="33" t="n"/>
-      <c r="K46" s="34" t="n"/>
+      <c r="J46" s="12" t="inlineStr">
+        <is>
+          <t>Accepted at the gate under the blanket approval; the same change is marked individually on the Rules sheet.</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="108" customHeight="1">
-      <c r="A47" s="57" t="inlineStr">
+      <c r="A47" s="56" t="inlineStr">
         <is>
           <t>TE-RS-008</t>
         </is>
@@ -17859,7 +18412,7 @@
           <t>{table_explanation}</t>
         </is>
       </c>
-      <c r="F47" s="35" t="inlineStr">
+      <c r="F47" s="33" t="inlineStr">
         <is>
           <t>The overall response recorded at {visit} is {reported_overall}, with target lesion response {target}, non-target response {non_target} and new lesions {new_lesion} recorded at the same visit. Please review the overall response against these components and correct whichever does not reflect the assessment.</t>
         </is>
@@ -17874,13 +18427,16 @@
           <t>Accept</t>
         </is>
       </c>
-      <c r="I47" s="59" t="inlineStr">
+      <c r="I47" s="58" t="inlineStr">
         <is>
           <t>The overall response recorded at {visit} is {reported_overall}. Based on the recorded components — target lesion response {target}, non-target response {non_target}, new lesions {new_lesion} — the overall response should be {derived_overall}. Please review.</t>
         </is>
       </c>
-      <c r="J47" s="33" t="n"/>
-      <c r="K47" s="34" t="n"/>
+      <c r="J47" s="22" t="inlineStr">
+        <is>
+          <t>Accepted at the gate under the blanket approval; the same change is marked individually on the Rules sheet.</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="108" customHeight="1">
       <c r="A48" s="23" t="inlineStr">
@@ -17908,7 +18464,7 @@
           <t>A new lesion is sufficient for progression on its own. If the indicator and the lesion records disagree, either progression has been declared without a documented lesion, or a documented new lesion has not been reflected in the response — both change the progression date.</t>
         </is>
       </c>
-      <c r="F48" s="56" t="inlineStr">
+      <c r="F48" s="55" t="inlineStr">
         <is>
           <t>The new lesion indicator at {visit} is recorded as {flag} while {lesion_situation}. Please reconcile the new lesion records with the response assessment.</t>
         </is>
@@ -17924,8 +18480,7 @@
         </is>
       </c>
       <c r="I48" s="12" t="inlineStr"/>
-      <c r="J48" s="33" t="n"/>
-      <c r="K48" s="34" t="n"/>
+      <c r="J48" s="12" t="inlineStr"/>
     </row>
     <row r="49" ht="108" customHeight="1">
       <c r="A49" s="25" t="inlineStr">
@@ -17953,7 +18508,7 @@
           <t>Under RECIST 1.1 the appearance of any unequivocal new lesion is progression, irrespective of the target and non-target responses. {irecist_note}</t>
         </is>
       </c>
-      <c r="F49" s="56" t="inlineStr">
+      <c r="F49" s="55" t="inlineStr">
         <is>
           <t>A new lesion is recorded at {visit} while the overall response is {reported_overall}. Please confirm the new lesion and review the overall response assessment.</t>
         </is>
@@ -17969,8 +18524,7 @@
         </is>
       </c>
       <c r="I49" s="22" t="inlineStr"/>
-      <c r="J49" s="33" t="n"/>
-      <c r="K49" s="34" t="n"/>
+      <c r="J49" s="22" t="inlineStr"/>
     </row>
     <row r="50" ht="108" customHeight="1">
       <c r="A50" s="23" t="inlineStr">
@@ -17998,7 +18552,7 @@
           <t>A lesion identified in a region that was not scanned at baseline is considered a new lesion, and therefore progression, because pre-existing disease at that site cannot be excluded. The point of this check is to confirm that the site made this determination deliberately rather than by default, since the alternative interpretation — that the lesion was present but unimaged — is not permitted.</t>
         </is>
       </c>
-      <c r="F50" s="56" t="inlineStr">
+      <c r="F50" s="55" t="inlineStr">
         <is>
           <t>A new lesion is recorded in {organ} at {visit}. Baseline imaging does not appear to have covered this region. Please confirm the finding represents a new lesion and that baseline imaging of this region was not performed.</t>
         </is>
@@ -18014,8 +18568,7 @@
         </is>
       </c>
       <c r="I50" s="12" t="inlineStr"/>
-      <c r="J50" s="33" t="n"/>
-      <c r="K50" s="34" t="n"/>
+      <c r="J50" s="12" t="inlineStr"/>
     </row>
     <row r="51" ht="108" customHeight="1">
       <c r="A51" s="25" t="inlineStr">
@@ -18043,7 +18596,7 @@
           <t>A positive FDG-PET finding establishes a new lesion when the baseline PET was negative, or when the new site is confirmed on CT or MRI. Without either, a positive PET alone is not sufficient, because the finding may represent disease present but not FDG-avid or not imaged at baseline, or may be non-malignant uptake.</t>
         </is>
       </c>
-      <c r="F51" s="56" t="inlineStr">
+      <c r="F51" s="55" t="inlineStr">
         <is>
           <t>The new lesion recorded at {visit} in {organ} is based on FDG-PET. Please confirm whether a baseline PET was performed and negative, or whether the lesion is confirmed on CT or MRI.</t>
         </is>
@@ -18059,11 +18612,10 @@
         </is>
       </c>
       <c r="I51" s="22" t="inlineStr"/>
-      <c r="J51" s="33" t="n"/>
-      <c r="K51" s="34" t="n"/>
+      <c r="J51" s="22" t="inlineStr"/>
     </row>
     <row r="52" ht="108" customHeight="1">
-      <c r="A52" s="57" t="inlineStr">
+      <c r="A52" s="56" t="inlineStr">
         <is>
           <t>TE-RS-013</t>
         </is>
@@ -18088,7 +18640,7 @@
           <t>Where therapy continues after an equivocal finding and the finding is subsequently confirmed as a new lesion, progression is dated to the time of the initial observation, not to the confirming assessment. Using the later date overstates progression-free survival by {days_difference} days.</t>
         </is>
       </c>
-      <c r="F52" s="35" t="inlineStr">
+      <c r="F52" s="33" t="inlineStr">
         <is>
           <t>Lesion {lesion_id} was recorded as equivocal at {first_visit} and as confirmed at {confirm_visit}. The progression date recorded for this subject is {reported_pd_date}. Please confirm the progression date against the source imaging reports for both visits.</t>
         </is>
@@ -18103,13 +18655,16 @@
           <t>Accept</t>
         </is>
       </c>
-      <c r="I52" s="58" t="inlineStr">
+      <c r="I52" s="57" t="inlineStr">
         <is>
           <t>Lesion {lesion_id} was equivocal at {first_visit} and confirmed at {confirm_visit}. Please confirm the date of progression; per RECIST the progression date should be the date of the initial observation ({first_date}).</t>
         </is>
       </c>
-      <c r="J52" s="33" t="n"/>
-      <c r="K52" s="34" t="n"/>
+      <c r="J52" s="12" t="inlineStr">
+        <is>
+          <t>Accepted at the gate under the blanket approval; the same change is marked individually on the Rules sheet.</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="108" customHeight="1">
       <c r="A53" s="25" t="inlineStr">
@@ -18137,7 +18692,7 @@
           <t>The protocol requires confirmation of a complete or partial response by a repeat assessment performed no less than {confirm_days} days after the criteria were first met. Without confirmation the response is unconfirmed and the derived best overall response is {derived_bor}. Counting unconfirmed responses inflates the objective response rate.</t>
         </is>
       </c>
-      <c r="F53" s="56" t="inlineStr">
+      <c r="F53" s="55" t="inlineStr">
         <is>
           <t>The best overall response is recorded as {reported_bor} based on the assessment at {first_visit}. A confirmatory assessment at least {confirm_days} days later does not appear to support this response. Please review the best overall response.</t>
         </is>
@@ -18153,8 +18708,7 @@
         </is>
       </c>
       <c r="I53" s="22" t="inlineStr"/>
-      <c r="J53" s="33" t="n"/>
-      <c r="K53" s="34" t="n"/>
+      <c r="J53" s="22" t="inlineStr"/>
     </row>
     <row r="54" ht="108" customHeight="1">
       <c r="A54" s="23" t="inlineStr">
@@ -18182,7 +18736,7 @@
           <t>{bor_explanation}</t>
         </is>
       </c>
-      <c r="F54" s="56" t="inlineStr">
+      <c r="F54" s="55" t="inlineStr">
         <is>
           <t>The best overall response recorded for this subject is {reported_bor}. Based on the recorded timepoint responses ({timepoint_sequence}) and the protocol's confirmation requirement, the best overall response derives as {derived_bor}. Please review.</t>
         </is>
@@ -18198,11 +18752,10 @@
         </is>
       </c>
       <c r="I54" s="12" t="inlineStr"/>
-      <c r="J54" s="33" t="n"/>
-      <c r="K54" s="34" t="n"/>
+      <c r="J54" s="12" t="inlineStr"/>
     </row>
     <row r="55" ht="108" customHeight="1">
-      <c r="A55" s="57" t="inlineStr">
+      <c r="A55" s="56" t="inlineStr">
         <is>
           <t>TE-RS-016</t>
         </is>
@@ -18227,7 +18780,7 @@
           <t>A subject with non-measurable disease only can be assigned a complete response, Non-CR/Non-PD, progressive disease or not evaluable. Partial response and stable disease require measurable disease, since both are defined by a change in the sum of diameters. The corresponding category here is Non-CR/Non-PD.</t>
         </is>
       </c>
-      <c r="F55" s="35" t="inlineStr">
+      <c r="F55" s="33" t="inlineStr">
         <is>
           <t>The overall response at {visit} is recorded as {reported_overall}, and no target lesions are recorded at baseline for this subject. Please confirm the baseline lesion records and the overall response at this visit.</t>
         </is>
@@ -18242,13 +18795,16 @@
           <t>Accept</t>
         </is>
       </c>
-      <c r="I55" s="59" t="inlineStr">
+      <c r="I55" s="58" t="inlineStr">
         <is>
           <t>The overall response at {visit} is recorded as {reported_overall} although no target lesions were identified at baseline. Please review; for subjects with non-measurable disease only, the appropriate categories are complete response, Non-CR/Non-PD, progressive disease or not evaluable.</t>
         </is>
       </c>
-      <c r="J55" s="33" t="n"/>
-      <c r="K55" s="34" t="n"/>
+      <c r="J55" s="22" t="inlineStr">
+        <is>
+          <t>Accepted at the gate under the blanket approval; the same change is marked individually on the Rules sheet.</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="108" customHeight="1">
       <c r="A56" s="23" t="inlineStr">
@@ -18276,7 +18832,7 @@
           <t>Stable disease is meaningful only if maintained for a minimum interval defined by the protocol. An earlier assessment cannot establish stability, and counting it inflates the disease control rate.</t>
         </is>
       </c>
-      <c r="F56" s="56" t="inlineStr">
+      <c r="F56" s="55" t="inlineStr">
         <is>
           <t>Stable disease is recorded at {visit}, {days} days after baseline, which is shorter than the minimum of {min_days} days specified in the protocol. Please review the response assessment.</t>
         </is>
@@ -18292,8 +18848,7 @@
         </is>
       </c>
       <c r="I56" s="12" t="inlineStr"/>
-      <c r="J56" s="33" t="n"/>
-      <c r="K56" s="34" t="n"/>
+      <c r="J56" s="12" t="inlineStr"/>
     </row>
     <row r="57" ht="108" customHeight="1">
       <c r="A57" s="25" t="inlineStr">
@@ -18321,7 +18876,7 @@
           <t>Best overall response is determined from the assessments recorded from the start of treatment until progression. Assessments after progression are retained in the data but do not contribute to the response endpoints. Including one here changes the best overall response from {derived_bor} to {reported_bor}.</t>
         </is>
       </c>
-      <c r="F57" s="56" t="inlineStr">
+      <c r="F57" s="55" t="inlineStr">
         <is>
           <t>A response of {response} is recorded at {later_visit}, after progression was recorded at {pd_visit}. Please confirm the progression date and the response assessments.</t>
         </is>
@@ -18337,8 +18892,7 @@
         </is>
       </c>
       <c r="I57" s="22" t="inlineStr"/>
-      <c r="J57" s="33" t="n"/>
-      <c r="K57" s="34" t="n"/>
+      <c r="J57" s="22" t="inlineStr"/>
     </row>
     <row r="58" ht="108" customHeight="1">
       <c r="A58" s="23" t="inlineStr">
@@ -18366,7 +18920,7 @@
           <t>Progression-free survival is measured to the date of the first assessment demonstrating progression. A difference of {days_difference} days changes the event time for this subject and, aggregated across subjects, biases the survival estimate.</t>
         </is>
       </c>
-      <c r="F58" s="56" t="inlineStr">
+      <c r="F58" s="55" t="inlineStr">
         <is>
           <t>The progression date is recorded as {reported_date}, while the earliest assessment meeting progression criteria is {derived_visit} on {derived_date}. Please confirm the date of progression.</t>
         </is>
@@ -18382,8 +18936,7 @@
         </is>
       </c>
       <c r="I58" s="12" t="inlineStr"/>
-      <c r="J58" s="33" t="n"/>
-      <c r="K58" s="34" t="n"/>
+      <c r="J58" s="12" t="inlineStr"/>
     </row>
     <row r="59" ht="108" customHeight="1">
       <c r="A59" s="25" t="inlineStr">
@@ -18411,7 +18964,7 @@
           <t>Discordance between the investigator and central review is expected at some rate, but discordance that crosses a progression boundary affects the primary endpoint where the central review is the basis of analysis, and may indicate a systematic difference in lesion selection or measurement at this site.</t>
         </is>
       </c>
-      <c r="F59" s="56" t="inlineStr">
+      <c r="F59" s="55" t="inlineStr">
         <is>
           <t>Not applicable: this finding is for internal review and reconciliation and is not normally issued as a site query.</t>
         </is>
@@ -18427,11 +18980,10 @@
         </is>
       </c>
       <c r="I59" s="22" t="inlineStr"/>
-      <c r="J59" s="33" t="n"/>
-      <c r="K59" s="34" t="n"/>
+      <c r="J59" s="22" t="inlineStr"/>
     </row>
     <row r="60" ht="108" customHeight="1">
-      <c r="A60" s="57" t="inlineStr">
+      <c r="A60" s="56" t="inlineStr">
         <is>
           <t>TE-IR-001</t>
         </is>
@@ -18456,7 +19008,7 @@
           <t>Under iRECIST, the first timepoint at which RECIST 1.1 progression criteria are met is assigned unconfirmed progression (iUPD). Confirmed progression (iCPD) can only be assigned at a subsequent assessment that demonstrates further worsening. Recording confirmed progression at first occurrence removes the confirmation step that iRECIST exists to provide, and may lead to treatment being discontinued for pseudoprogression.</t>
         </is>
       </c>
-      <c r="F60" s="35" t="inlineStr">
+      <c r="F60" s="33" t="inlineStr">
         <is>
           <t>The iRECIST response at {visit} is recorded as {reported_irecist}. The lesion measurements at this visit show an increase against the smallest sum recorded on study ({nadir_sum} mm). Please confirm the iRECIST response recorded for this visit against the source imaging report.</t>
         </is>
@@ -18471,13 +19023,16 @@
           <t>Accept</t>
         </is>
       </c>
-      <c r="I60" s="58" t="inlineStr">
+      <c r="I60" s="57" t="inlineStr">
         <is>
           <t>RECIST 1.1 progression criteria are met at {visit} and the iRECIST response is recorded as {reported_irecist}. Under iRECIST the first occurrence of progression should be recorded as unconfirmed progression (iUPD), with confirmation at the next assessment. Please review.</t>
         </is>
       </c>
-      <c r="J60" s="33" t="n"/>
-      <c r="K60" s="34" t="n"/>
+      <c r="J60" s="12" t="inlineStr">
+        <is>
+          <t>Accepted at the gate under the blanket approval; the same change is marked individually on the Rules sheet.</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="108" customHeight="1">
       <c r="A61" s="25" t="inlineStr">
@@ -18505,7 +19060,7 @@
           <t>iRECIST requires the confirmatory assessment between {window_min} and {window_max} days after unconfirmed progression. Assessing too early risks confirming transient pseudoprogression as true progression; assessing too late leaves the subject on a potentially ineffective therapy and leaves the progression date ambiguous. Without a confirmatory assessment, progression remains unconfirmed and the subject's progression status for analysis is indeterminate.</t>
         </is>
       </c>
-      <c r="F61" s="56" t="inlineStr">
+      <c r="F61" s="55" t="inlineStr">
         <is>
           <t>Unconfirmed progression was recorded at {iupd_visit} on {iupd_date}. {confirmation_situation}. Please confirm whether a confirmatory tumor assessment was performed and enter the data, or record the reason it was not performed.</t>
         </is>
@@ -18521,11 +19076,10 @@
         </is>
       </c>
       <c r="I61" s="22" t="inlineStr"/>
-      <c r="J61" s="33" t="n"/>
-      <c r="K61" s="34" t="n"/>
+      <c r="J61" s="22" t="inlineStr"/>
     </row>
     <row r="62" ht="108" customHeight="1">
-      <c r="A62" s="57" t="inlineStr">
+      <c r="A62" s="56" t="inlineStr">
         <is>
           <t>TE-IR-003</t>
         </is>
@@ -18550,7 +19104,7 @@
           <t>Confirmation of progression requires further worsening in the category that drove the unconfirmed progression: an increase of at least {target_increment} mm in the target lesion sum relative to the unconfirmed progression timepoint, further unequivocal worsening of non-target disease, an increase of at least {new_increment} mm in the sum of new measurable lesions, or the appearance of additional new lesions. A new category independently meeting RECIST 1.1 progression criteria also confirms. None of these is evident here, so the response should remain unconfirmed progression or reset according to the current burden.</t>
         </is>
       </c>
-      <c r="F62" s="35" t="inlineStr">
+      <c r="F62" s="33" t="inlineStr">
         <is>
           <t>Confirmed progression is recorded at {visit}. Unconfirmed progression was recorded at {iupd_visit}, driven by {driver}, and the current assessment shows {confirmation_evidence}. Please confirm the response recorded at {visit} against the source imaging report.</t>
         </is>
@@ -18565,16 +19119,19 @@
           <t>Accept</t>
         </is>
       </c>
-      <c r="I62" s="58" t="inlineStr">
+      <c r="I62" s="57" t="inlineStr">
         <is>
           <t>Confirmed progression is recorded at {visit}. The unconfirmed progression at {iupd_visit} was driven by {driver}, and the current assessment shows {confirmation_evidence}. Please review the confirmation of progression against the iRECIST criteria.</t>
         </is>
       </c>
-      <c r="J62" s="33" t="n"/>
-      <c r="K62" s="34" t="n"/>
+      <c r="J62" s="12" t="inlineStr">
+        <is>
+          <t>Accepted at the gate under the blanket approval; the same change is marked individually on the Rules sheet.</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="108" customHeight="1">
-      <c r="A63" s="57" t="inlineStr">
+      <c r="A63" s="56" t="inlineStr">
         <is>
           <t>TE-IR-004</t>
         </is>
@@ -18599,7 +19156,7 @@
           <t>Under iRECIST, new lesions are recorded and measured separately from the baseline target lesions, with their own sum of up to five new measurable lesions, two per organ. They are never added to the baseline target sum, because the baseline sum must remain comparable to baseline for response assessment, while the new lesion sum is used to judge confirmation of progression. Combining them corrupts both.</t>
         </is>
       </c>
-      <c r="F63" s="35" t="inlineStr">
+      <c r="F63" s="33" t="inlineStr">
         <is>
           <t>The sum of diameters recorded at {visit} appears to include measurements of lesions recorded as new. Please confirm which lesions are included in the sum of diameters at this visit.</t>
         </is>
@@ -18614,16 +19171,19 @@
           <t>Accept</t>
         </is>
       </c>
-      <c r="I63" s="59" t="inlineStr">
+      <c r="I63" s="58" t="inlineStr">
         <is>
           <t>The sum of diameters at {visit} appears to include the measurements of new lesions. Under iRECIST new lesions are recorded and summed separately from the baseline target lesions. Please review the sum of diameters and the new lesion records.</t>
         </is>
       </c>
-      <c r="J63" s="33" t="n"/>
-      <c r="K63" s="34" t="n"/>
+      <c r="J63" s="22" t="inlineStr">
+        <is>
+          <t>Accepted at the gate under the blanket approval; the same change is marked individually on the Rules sheet.</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="108" customHeight="1">
-      <c r="A64" s="57" t="inlineStr">
+      <c r="A64" s="56" t="inlineStr">
         <is>
           <t>TE-IR-005</t>
         </is>
@@ -18648,7 +19208,7 @@
           <t>If confirmation criteria are not met, the subject's response resets to iCR, iPR or iSD according to the current tumor burden measured against the original nadir. The nadir is not reset by the unconfirmed progression, so a later increase can again produce unconfirmed progression. This is the mechanism by which iRECIST accommodates pseudoprogression.</t>
         </is>
       </c>
-      <c r="F64" s="35" t="inlineStr">
+      <c r="F64" s="33" t="inlineStr">
         <is>
           <t>Unconfirmed progression was recorded at {iupd_visit} and was not confirmed at {visit}. The iRECIST response at {visit} is recorded as {reported_irecist}, with a sum of diameters of {sum} mm. Please confirm the iRECIST response recorded for this visit.</t>
         </is>
@@ -18663,16 +19223,19 @@
           <t>Accept</t>
         </is>
       </c>
-      <c r="I64" s="58" t="inlineStr">
+      <c r="I64" s="57" t="inlineStr">
         <is>
           <t>Unconfirmed progression was recorded at {iupd_visit} and was not confirmed at {visit}. The response at {visit} is recorded as {reported_irecist}; based on the current sum of {sum} mm against the nadir of {nadir_sum} mm the response derives as {derived_irecist}. Please review.</t>
         </is>
       </c>
-      <c r="J64" s="33" t="n"/>
-      <c r="K64" s="34" t="n"/>
+      <c r="J64" s="12" t="inlineStr">
+        <is>
+          <t>Accepted at the gate under the blanket approval; the same change is marked individually on the Rules sheet.</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="108" customHeight="1">
-      <c r="A65" s="57" t="inlineStr">
+      <c r="A65" s="56" t="inlineStr">
         <is>
           <t>TE-IR-006</t>
         </is>
@@ -18697,7 +19260,7 @@
           <t>The new lesion sum is used to judge confirmation of progression, so it must be constructed consistently. Additional new lesions beyond the limits are recorded as new non-target lesions rather than measured.</t>
         </is>
       </c>
-      <c r="F65" s="35" t="inlineStr">
+      <c r="F65" s="33" t="inlineStr">
         <is>
           <t>{n} new measurable lesions are recorded for this subject. This study records up to {max_total} new measurable lesions in total and {max_per_organ} per organ, with any further new lesions recorded as non-target. Please review the new lesion records.</t>
         </is>
@@ -18712,13 +19275,16 @@
           <t>Accept</t>
         </is>
       </c>
-      <c r="I65" s="59" t="inlineStr">
+      <c r="I65" s="58" t="inlineStr">
         <is>
           <t>{n} new measurable lesions are recorded for this subject. iRECIST permits up to {max_total} new measurable lesions in total, and {max_per_organ} per organ, with any further new lesions recorded as non-target. Please review the new lesion records.</t>
         </is>
       </c>
-      <c r="J65" s="33" t="n"/>
-      <c r="K65" s="34" t="n"/>
+      <c r="J65" s="22" t="inlineStr">
+        <is>
+          <t>Accepted at the gate under the blanket approval; the same change is marked individually on the Rules sheet.</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="108" customHeight="1">
       <c r="A66" s="23" t="inlineStr">
@@ -18746,7 +19312,7 @@
           <t>Confirmed progression is the terminal response state. Later assessments may be collected for follow-up, but assigning a non-progression response after confirmed progression is inconsistent and risks the later response being carried into the best overall response derivation.</t>
         </is>
       </c>
-      <c r="F66" s="56" t="inlineStr">
+      <c r="F66" s="55" t="inlineStr">
         <is>
           <t>Assessments after the confirmed progression at {icpd_visit} carry responses of {later_responses}. Please confirm the progression status and the response assessments recorded after it.</t>
         </is>
@@ -18762,8 +19328,7 @@
         </is>
       </c>
       <c r="I66" s="12" t="inlineStr"/>
-      <c r="J66" s="33" t="n"/>
-      <c r="K66" s="34" t="n"/>
+      <c r="J66" s="12" t="inlineStr"/>
     </row>
     <row r="67" ht="108" customHeight="1">
       <c r="A67" s="25" t="inlineStr">
@@ -18791,7 +19356,7 @@
           <t>iRECIST permits treatment beyond unconfirmed progression only where the subject is clinically stable: no decline in performance status, no worsening of symptoms attributable to disease, and no need for intensified management. The documentation supports both subject safety and the interpretation of the subsequent assessment.</t>
         </is>
       </c>
-      <c r="F67" s="56" t="inlineStr">
+      <c r="F67" s="55" t="inlineStr">
         <is>
           <t>Treatment continued after unconfirmed progression at {iupd_visit}. Please confirm that the subject was assessed as clinically stable at that time and that this is documented.</t>
         </is>
@@ -18807,11 +19372,10 @@
         </is>
       </c>
       <c r="I67" s="22" t="inlineStr"/>
-      <c r="J67" s="33" t="n"/>
-      <c r="K67" s="34" t="n"/>
+      <c r="J67" s="22" t="inlineStr"/>
     </row>
     <row r="68" ht="108" customHeight="1">
-      <c r="A68" s="57" t="inlineStr">
+      <c r="A68" s="56" t="inlineStr">
         <is>
           <t>TE-IR-009</t>
         </is>
@@ -18836,7 +19400,7 @@
           <t>The iRECIST assessment is derived from the same underlying measurements as the RECIST 1.1 assessment, differing only in the treatment of progression and new lesions. Given the RECIST 1.1 result at this timepoint and the preceding response history, the iRECIST response should be {expected_irecist}.</t>
         </is>
       </c>
-      <c r="F68" s="35" t="inlineStr">
+      <c r="F68" s="33" t="inlineStr">
         <is>
           <t>The RECIST 1.1 and iRECIST responses recorded at {visit} are {r11_response} and {reported_irecist}. Please confirm both response fields for this visit against the source imaging report.</t>
         </is>
@@ -18851,13 +19415,16 @@
           <t>Accept</t>
         </is>
       </c>
-      <c r="I68" s="58" t="inlineStr">
+      <c r="I68" s="57" t="inlineStr">
         <is>
           <t>The RECIST 1.1 and iRECIST responses recorded at {visit} are {r11_response} and {reported_irecist}. Based on the response history the iRECIST response would be expected to be {expected_irecist}. Please review.</t>
         </is>
       </c>
-      <c r="J68" s="33" t="n"/>
-      <c r="K68" s="34" t="n"/>
+      <c r="J68" s="12" t="inlineStr">
+        <is>
+          <t>Accepted at the gate under the blanket approval; the same change is marked individually on the Rules sheet.</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="108" customHeight="1">
       <c r="A69" s="25" t="inlineStr">
@@ -18885,7 +19452,7 @@
           <t>If iRECIST is specified but not collected, pseudoprogression cannot be distinguished from true progression, and subjects may be discontinued prematurely. If iRECIST is collected but not specified in the protocol, the analysis convention is undefined. Either way the endpoint derivation is at risk across the whole study.</t>
         </is>
       </c>
-      <c r="F69" s="56" t="inlineStr">
+      <c r="F69" s="55" t="inlineStr">
         <is>
           <t>Not applicable: this is a study set-up finding for the study team rather than a site query.</t>
         </is>
@@ -18901,8 +19468,7 @@
         </is>
       </c>
       <c r="I69" s="22" t="inlineStr"/>
-      <c r="J69" s="33" t="n"/>
-      <c r="K69" s="34" t="n"/>
+      <c r="J69" s="22" t="inlineStr"/>
     </row>
     <row r="70" ht="108" customHeight="1">
       <c r="A70" s="23" t="inlineStr">
@@ -18930,7 +19496,7 @@
           <t>If treatment stopped for progression, either an assessment demonstrating progression is missing from the tumor data, or the discontinuation reason is incorrect. Both affect the progression-free survival analysis: a missing progression event leads to censoring instead of an event.</t>
         </is>
       </c>
-      <c r="F70" s="56" t="inlineStr">
+      <c r="F70" s="55" t="inlineStr">
         <is>
           <t>Treatment was discontinued for {disposition_reason} on {disposition_date}, but no tumor assessment recording progression is present. Please confirm whether a tumor assessment demonstrating progression was performed, and enter the data if so; if progression was determined clinically, please confirm the basis and the date.</t>
         </is>
@@ -18946,8 +19512,7 @@
         </is>
       </c>
       <c r="I70" s="12" t="inlineStr"/>
-      <c r="J70" s="33" t="n"/>
-      <c r="K70" s="34" t="n"/>
+      <c r="J70" s="12" t="inlineStr"/>
     </row>
     <row r="71" ht="108" customHeight="1">
       <c r="A71" s="25" t="inlineStr">
@@ -18975,7 +19540,7 @@
           <t>Treatment beyond progression may be permitted by the protocol, but it must be documented, and it changes the interpretation of subsequent assessments. Where it is not permitted, this is a protocol deviation. Where the study uses iRECIST, the earlier assessment may have been unconfirmed progression rather than confirmed progression, in which case continuation is expected and the response coding needs review instead.</t>
         </is>
       </c>
-      <c r="F71" s="56" t="inlineStr">
+      <c r="F71" s="55" t="inlineStr">
         <is>
           <t>Study treatment continued for {days} days after the progression recorded at {pd_visit}. Please confirm the progression assessment and whether continuation beyond progression was approved.</t>
         </is>
@@ -18991,8 +19556,7 @@
         </is>
       </c>
       <c r="I71" s="22" t="inlineStr"/>
-      <c r="J71" s="33" t="n"/>
-      <c r="K71" s="34" t="n"/>
+      <c r="J71" s="22" t="inlineStr"/>
     </row>
     <row r="72" ht="108" customHeight="1">
       <c r="A72" s="23" t="inlineStr">
@@ -19020,7 +19584,7 @@
           <t>Starting a new anticancer therapy before recorded progression usually indicates that progression occurred but was not captured, or that treatment changed for another documented reason. In progression-free survival analyses the start of new therapy is commonly a censoring or event-defining event, so the discrepancy has direct analytical consequences, and any tumor assessment after the new therapy no longer reflects the study treatment.</t>
         </is>
       </c>
-      <c r="F72" s="56" t="inlineStr">
+      <c r="F72" s="55" t="inlineStr">
         <is>
           <t>A new anticancer therapy ({therapy}) started on {therapy_date}, before any recorded disease progression. Please confirm the reason for starting new therapy and whether a tumor assessment demonstrating progression was performed.</t>
         </is>
@@ -19036,8 +19600,7 @@
         </is>
       </c>
       <c r="I72" s="12" t="inlineStr"/>
-      <c r="J72" s="33" t="n"/>
-      <c r="K72" s="34" t="n"/>
+      <c r="J72" s="12" t="inlineStr"/>
     </row>
     <row r="73" ht="108" customHeight="1">
       <c r="A73" s="25" t="inlineStr">
@@ -19065,7 +19628,7 @@
           <t>Once a lesion has received locoregional therapy, its subsequent size no longer reflects the systemic treatment effect, and RECIST treats such lesions as non-measurable unless progression is demonstrated. Continuing to include it in the sum understates tumor burden and can produce a spurious partial response.</t>
         </is>
       </c>
-      <c r="F73" s="56" t="inlineStr">
+      <c r="F73" s="55" t="inlineStr">
         <is>
           <t>{procedure} was applied to {site} on {procedure_date}, which corresponds to target lesion {lesion_id}. Please confirm and clarify how this lesion has been assessed at subsequent visits.</t>
         </is>
@@ -19081,8 +19644,7 @@
         </is>
       </c>
       <c r="I73" s="22" t="inlineStr"/>
-      <c r="J73" s="33" t="n"/>
-      <c r="K73" s="34" t="n"/>
+      <c r="J73" s="22" t="inlineStr"/>
     </row>
     <row r="74" ht="108" customHeight="1">
       <c r="A74" s="23" t="inlineStr">
@@ -19110,7 +19672,7 @@
           <t>An adverse event of disease progression implies a clinical determination of progression. If the tumor data does not reflect it, the progression event may be missing from the efficacy analysis, or the adverse event may have been coded inappropriately — disease progression is frequently reported as an adverse event when it should be captured as an efficacy outcome.</t>
         </is>
       </c>
-      <c r="F74" s="56" t="inlineStr">
+      <c r="F74" s="55" t="inlineStr">
         <is>
           <t>An adverse event of "{ae_term}" is recorded with onset {ae_date}. Please confirm whether disease progression was documented and whether a tumor assessment was performed at that time.</t>
         </is>
@@ -19126,8 +19688,7 @@
         </is>
       </c>
       <c r="I74" s="12" t="inlineStr"/>
-      <c r="J74" s="33" t="n"/>
-      <c r="K74" s="34" t="n"/>
+      <c r="J74" s="12" t="inlineStr"/>
     </row>
     <row r="75" ht="108" customHeight="1">
       <c r="A75" s="25" t="inlineStr">
@@ -19155,7 +19716,7 @@
           <t>A tumor assessment or progression date after the date of death is impossible, so one of the dates is wrong. Both feed survival and progression-free survival analyses directly.</t>
         </is>
       </c>
-      <c r="F75" s="56" t="inlineStr">
+      <c r="F75" s="55" t="inlineStr">
         <is>
           <t>The date of death ({death_date}) precedes {conflicting_record} ({conflict_date}). Please verify both dates.</t>
         </is>
@@ -19171,8 +19732,7 @@
         </is>
       </c>
       <c r="I75" s="22" t="inlineStr"/>
-      <c r="J75" s="33" t="n"/>
-      <c r="K75" s="34" t="n"/>
+      <c r="J75" s="22" t="inlineStr"/>
     </row>
     <row r="76" ht="108" customHeight="1">
       <c r="A76" s="23" t="inlineStr">
@@ -19200,7 +19760,7 @@
           <t>Where the protocol includes tumor markers in the response definition, a complete response requires marker normalisation in addition to the disappearance of all lesions. A persistently elevated marker means the response is Non-CR/Non-PD.</t>
         </is>
       </c>
-      <c r="F76" s="56" t="inlineStr">
+      <c r="F76" s="55" t="inlineStr">
         <is>
           <t>A complete response is recorded at {visit} while {marker} remains above the upper limit of normal ({value} {unit}). Please review the response assessment.</t>
         </is>
@@ -19216,8 +19776,7 @@
         </is>
       </c>
       <c r="I76" s="12" t="inlineStr"/>
-      <c r="J76" s="33" t="n"/>
-      <c r="K76" s="34" t="n"/>
+      <c r="J76" s="12" t="inlineStr"/>
     </row>
     <row r="77" ht="108" customHeight="1">
       <c r="A77" s="25" t="inlineStr">
@@ -19245,7 +19804,7 @@
           <t>Modalities differ in sensitivity and in measurement reproducibility. Using a modality outside the protocol makes the measurement non-comparable with the rest of the subject's data and with other subjects.</t>
         </is>
       </c>
-      <c r="F77" s="56" t="inlineStr">
+      <c r="F77" s="55" t="inlineStr">
         <is>
           <t>Lesion {lesion_id} was assessed by {method} at {visit}, which is not among the modalities specified in the protocol. Please confirm the modality used.</t>
         </is>
@@ -19261,8 +19820,7 @@
         </is>
       </c>
       <c r="I77" s="22" t="inlineStr"/>
-      <c r="J77" s="33" t="n"/>
-      <c r="K77" s="34" t="n"/>
+      <c r="J77" s="22" t="inlineStr"/>
     </row>
     <row r="78" ht="108" customHeight="1">
       <c r="A78" s="23" t="inlineStr">
@@ -19290,7 +19848,7 @@
           <t>Disease in an unimaged region cannot be assessed, and a lesion later found there must be treated as a new lesion. Missing required imaging therefore both reduces the reliability of the current response and risks a spurious progression later.</t>
         </is>
       </c>
-      <c r="F78" s="56" t="inlineStr">
+      <c r="F78" s="55" t="inlineStr">
         <is>
           <t>No assessment of {required_region} is recorded at {visit} although the protocol requires it. Please confirm whether the imaging was performed and enter the results.</t>
         </is>
@@ -19306,8 +19864,7 @@
         </is>
       </c>
       <c r="I78" s="12" t="inlineStr"/>
-      <c r="J78" s="33" t="n"/>
-      <c r="K78" s="34" t="n"/>
+      <c r="J78" s="12" t="inlineStr"/>
     </row>
     <row r="79" ht="108" customHeight="1">
       <c r="A79" s="25" t="inlineStr">
@@ -19335,7 +19892,7 @@
           <t>The best overall response cannot be better than any response actually recorded at a timepoint. This indicates either a missing timepoint assessment or an incorrect best overall response.</t>
         </is>
       </c>
-      <c r="F79" s="56" t="inlineStr">
+      <c r="F79" s="55" t="inlineStr">
         <is>
           <t>The best overall response is recorded as {reported_bor}, but the best response recorded at any timepoint is {best_timepoint}. Please review.</t>
         </is>
@@ -19351,8 +19908,7 @@
         </is>
       </c>
       <c r="I79" s="22" t="inlineStr"/>
-      <c r="J79" s="33" t="n"/>
-      <c r="K79" s="34" t="n"/>
+      <c r="J79" s="22" t="inlineStr"/>
     </row>
     <row r="80" ht="108" customHeight="1">
       <c r="A80" s="23" t="inlineStr">
@@ -19380,7 +19936,7 @@
           <t>A treated subject with no post-baseline assessment is not evaluable for response and is censored at randomisation or treatment start in progression-free survival, which reduces the power of the analysis. The reason should be documented.</t>
         </is>
       </c>
-      <c r="F80" s="56" t="inlineStr">
+      <c r="F80" s="55" t="inlineStr">
         <is>
           <t>No post-baseline tumor assessment is recorded for this subject. Please confirm whether an assessment was performed, and record the reason if it was not.</t>
         </is>
@@ -19396,8 +19952,7 @@
         </is>
       </c>
       <c r="I80" s="12" t="inlineStr"/>
-      <c r="J80" s="33" t="n"/>
-      <c r="K80" s="34" t="n"/>
+      <c r="J80" s="12" t="inlineStr"/>
     </row>
     <row r="81" ht="108" customHeight="1">
       <c r="A81" s="25" t="inlineStr">
@@ -19425,7 +19980,7 @@
           <t>A concentration of the same issue at one site usually reflects a training or process gap rather than isolated errors. Addressing it at the site level resolves the whole cluster and prevents recurrence, whereas issuing individual queries treats the symptom.</t>
         </is>
       </c>
-      <c r="F81" s="56" t="inlineStr">
+      <c r="F81" s="55" t="inlineStr">
         <is>
           <t>Not applicable: this finding is directed to the monitoring team rather than to the site as a data query.</t>
         </is>
@@ -19441,8 +19996,7 @@
         </is>
       </c>
       <c r="I81" s="22" t="inlineStr"/>
-      <c r="J81" s="33" t="n"/>
-      <c r="K81" s="34" t="n"/>
+      <c r="J81" s="22" t="inlineStr"/>
     </row>
     <row r="82" ht="108" customHeight="1">
       <c r="A82" s="23" t="inlineStr">
@@ -19470,7 +20024,7 @@
           <t>Re-issuing a query that is already outstanding creates duplicate work at the site and confuses the audit trail. The finding is retained and linked, but is suppressed from the default worklist until the query is answered.</t>
         </is>
       </c>
-      <c r="F82" s="56" t="inlineStr">
+      <c r="F82" s="55" t="inlineStr">
         <is>
           <t>Not applicable: no new query is required.</t>
         </is>
@@ -19486,8 +20040,7 @@
         </is>
       </c>
       <c r="I82" s="12" t="inlineStr"/>
-      <c r="J82" s="33" t="n"/>
-      <c r="K82" s="34" t="n"/>
+      <c r="J82" s="12" t="inlineStr"/>
     </row>
     <row r="83" ht="108" customHeight="1">
       <c r="A83" s="25" t="inlineStr">
@@ -19515,7 +20068,7 @@
           <t>The query was resolved without the data being corrected. The site's answer does not explain why the current values are correct, so the issue survives into the locked database. Where an answer does justify the data, this finding is suppressed instead and the justification is recorded against the record.</t>
         </is>
       </c>
-      <c r="F83" s="56" t="inlineStr">
+      <c r="F83" s="55" t="inlineStr">
         <is>
           <t>Query {query_id} regarding {issue_summary} was answered on {resolution_date}, but the data still shows {current_state}. Please clarify: if the data is correct as entered, please explain the basis; otherwise please make the correction.</t>
         </is>
@@ -19531,8 +20084,7 @@
         </is>
       </c>
       <c r="I83" s="22" t="inlineStr"/>
-      <c r="J83" s="33" t="n"/>
-      <c r="K83" s="34" t="n"/>
+      <c r="J83" s="22" t="inlineStr"/>
     </row>
     <row r="84" ht="108" customHeight="1">
       <c r="A84" s="23" t="inlineStr">
@@ -19560,7 +20112,7 @@
           <t>A recurrence usually means either that a data correction was reverted, or that a subsequent data entry reintroduced the same error. Both are worth understanding, because the same cause is likely to affect other records.</t>
         </is>
       </c>
-      <c r="F84" s="56" t="inlineStr">
+      <c r="F84" s="55" t="inlineStr">
         <is>
           <t>This issue was previously raised and resolved on {previous_resolution_date}, and is present again in the current data. Please confirm the current value and clarify the reason for the change.</t>
         </is>
@@ -19576,8 +20128,7 @@
         </is>
       </c>
       <c r="I84" s="12" t="inlineStr"/>
-      <c r="J84" s="33" t="n"/>
-      <c r="K84" s="34" t="n"/>
+      <c r="J84" s="12" t="inlineStr"/>
     </row>
     <row r="85" ht="108" customHeight="1">
       <c r="A85" s="25" t="inlineStr">
@@ -19605,7 +20156,7 @@
           <t>Endpoint-critical data cannot be locked while the query is outstanding, and late resolution compresses the timeline before database lock. Ageing queries on response data are a leading cause of lock delay.</t>
         </is>
       </c>
-      <c r="F85" s="56" t="inlineStr">
+      <c r="F85" s="55" t="inlineStr">
         <is>
           <t>Not applicable: this finding is for the study team's query management rather than a new site query.</t>
         </is>
@@ -19621,8 +20172,7 @@
         </is>
       </c>
       <c r="I85" s="22" t="inlineStr"/>
-      <c r="J85" s="33" t="n"/>
-      <c r="K85" s="34" t="n"/>
+      <c r="J85" s="22" t="inlineStr"/>
     </row>
     <row r="86" ht="108" customHeight="1">
       <c r="A86" s="23" t="inlineStr">
@@ -19650,7 +20200,7 @@
           <t>An unresponsive answer that is nonetheless accepted closes the query without resolving the underlying data question, so the issue survives into the locked database.</t>
         </is>
       </c>
-      <c r="F86" s="56" t="inlineStr">
+      <c r="F86" s="55" t="inlineStr">
         <is>
           <t>Thank you for the response to query {query_id}. The original question concerned {query_summary}; could you please also confirm {outstanding_point}?</t>
         </is>
@@ -19666,8 +20216,7 @@
         </is>
       </c>
       <c r="I86" s="12" t="inlineStr"/>
-      <c r="J86" s="33" t="n"/>
-      <c r="K86" s="34" t="n"/>
+      <c r="J86" s="12" t="inlineStr"/>
     </row>
     <row r="87" ht="108" customHeight="1">
       <c r="A87" s="25" t="inlineStr">
@@ -19695,7 +20244,7 @@
           <t>Corrections made in isolation frequently break a dependent value — most often a lesion measurement corrected without the sum or the response being updated. The correction should be applied consistently across the dependent fields.</t>
         </is>
       </c>
-      <c r="F87" s="56" t="inlineStr">
+      <c r="F87" s="55" t="inlineStr">
         <is>
           <t>Following the correction to {field} at {visit}, {new_issue_summary}. Please review the related fields so the assessment is internally consistent.</t>
         </is>
@@ -19711,8 +20260,7 @@
         </is>
       </c>
       <c r="I87" s="22" t="inlineStr"/>
-      <c r="J87" s="33" t="n"/>
-      <c r="K87" s="34" t="n"/>
+      <c r="J87" s="22" t="inlineStr"/>
     </row>
     <row r="88" ht="108" customHeight="1">
       <c r="A88" s="23" t="inlineStr">
@@ -19740,7 +20288,7 @@
           <t>RECIST 1.1 requires that an effusion appearing or worsening during treatment be confirmed cytologically before it is taken as evidence of progression, where the measurable disease is responding or stable. Effusions arise from causes unrelated to tumor progression, including the treatment itself and intercurrent illness. An unconfirmed effusion is a recognised source of spurious progression, which censors the subject early and shortens progression-free survival.</t>
         </is>
       </c>
-      <c r="F88" s="56" t="inlineStr">
+      <c r="F88" s="55" t="inlineStr">
         <is>
           <t>Progressive disease is recorded at {visit}, supported by {effusion_description}, while target lesions show {target_response_derived}. Please confirm whether cytological assessment of the effusion was performed and record the result. If cytology was not performed, please confirm the basis on which progression was assessed.</t>
         </is>
@@ -19756,20 +20304,14 @@
         </is>
       </c>
       <c r="I88" s="12" t="inlineStr"/>
-      <c r="J88" s="33" t="n"/>
-      <c r="K88" s="34" t="n"/>
+      <c r="J88" s="12" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:K88"/>
+  <autoFilter ref="A3:J88"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="J4:J88" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Accept,Amend,Reject,Discuss"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/spec/TEA-SPEC-001_programming-specification.xlsx
+++ b/docs/spec/TEA-SPEC-001_programming-specification.xlsx
@@ -776,7 +776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -829,7 +829,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>2.0.0 — APPROVED</t>
+          <t>2.1.0 — APPROVED, amended under change control</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>APPROVED for implementation — rule pack FROZEN at 2.0.0</t>
+          <t>APPROVED — single-model amendment 2026-08-22. Rule pack UNCHANGED at 2.0.0.</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -877,7 +877,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>v1.3.0, issued 2026-08-21</t>
+          <t>v2.0.0, issued 2026-08-21</t>
         </is>
       </c>
     </row>
@@ -896,34 +896,46 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Rule catalog</t>
+          <t>Language model</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>85 review points, 83 live, 2 retired — frozen; changes now need change control</t>
+          <t>Company-hosted GLM v5.2 only — no external or commercial LLM service</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Machine-readable catalog</t>
+          <t>Rule catalog</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>docs/spec/rule-catalog.yaml — maintained separately, drift-checked in CI</t>
+          <t>85 review points, 83 live, 2 retired — frozen; changes now need change control</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
+          <t>Machine-readable catalog</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>docs/spec/rule-catalog.yaml — maintained separately, drift-checked in CI</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
           <t>Approved by</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Daniel — 2026-08-21, reasonableness review (see Approval)</t>
         </is>
@@ -932,71 +944,64 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>APPROVED — WHAT THAT MEANS</t>
+          <t>v2.1.0 — SINGLE-MODEL AMENDMENT</t>
         </is>
       </c>
     </row>
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>•  The rule pack is frozen at 2.0.0. From here a rule change is not an edit: it needs a change-control entry, a version bump, and an impact assessment on findings already issued.</t>
+          <t>•  The agent runs on the company-hosted GLM v5.2 and nothing else. Commercial and externally hosted LLM services are out of scope.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>•  Step 2 is closed. Step 3 begins — the prototype run on a curated dummy dataset with a signed-off expected finding list.</t>
+          <t>•  The rule pack is NOT affected. No rule references a provider, so the 2.0.0 freeze holds and no rule change control is triggered. Rules, Rule_Messages, Derivations and the catalog are byte-for-byte what was approved on 21 August.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>•  The approval was given as a reasonableness review. The reviewer's own words: all the changes look reasonable, the detail was not individually confirmed. The Approval sheet records that exactly, because an approval record should say what happened.</t>
+          <t>•  What changed: LLM_Integration (two adapters instead of four), Testing (verdict identity replaces cross-provider conformance), and guardrail G-06 (redaction, now much lighter).</t>
         </is>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>•  That is a workable basis, and Step 3 is what makes it so: the golden dataset tests all 83 live rules against known expected findings, which confirms the detail by evidence rather than by reading. Anything the reasonableness review missed should surface there.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>•  Two items were approved by the blanket statement rather than marked individually — TE-XD-005, and the 19 rewritten query messages. They are flagged on the Approval sheet, not smoothed over.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="26" customHeight="1"/>
+          <t>•  Cross-provider conformance is replaced rather than deleted, and this is the part worth reading. It was the mechanism proving a model cannot change a verdict. With one model that comparison proves nothing, so it moves to GLM v5.2 against the deterministic-only reference — same guarantee, still enforced on every commit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1"/>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>WHAT THE APPROVAL STILL RESTS ON</t>
+        </is>
+      </c>
+    </row>
     <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>WHAT TO WATCH AT STEP 3</t>
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>•  Approved 21 August as a reasonableness review — see the Approval sheet. That basis is unchanged by this amendment.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>•  The 8 rules whose logic changed at round 3 have no test history at all. They are the first place a seeded-case failure would show up.</t>
+          <t>•  Step 3 remains where the rule detail gets confirmed by evidence: the golden dataset runs in deterministic-only mode, so it tests the rules without the model in the way at all.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="26" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>•  The 27 confidence base rates below 0.75 are estimates, not measurements. Step 3 calibration is what turns them into numbers worth trusting.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="26" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>•  Interpretations ID-05 and ID-06 were amended and never separately re-read. ID-06 changed where baseline comes from, which every derivation depends on — worth a deliberate look at the first prototype output.</t>
+          <t>•  The GLM v5.2 capability assumptions are NOT verified. The 32k prompt budget and the structured-output behaviour were assumed at OQ-03 against a generic gateway and were never checked against v5.2. That check is now a Step 5 task in its own right, not a formality.</t>
         </is>
       </c>
     </row>
@@ -1014,8 +1019,8 @@
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="A20:F20"/>
+    <mergeCell ref="B17:F17"/>
     <mergeCell ref="B13:F13"/>
-    <mergeCell ref="A28:F28"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="B9:F9"/>
@@ -3176,7 +3181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3188,7 +3193,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>LLM integration contract</t>
+          <t>Model integration contract</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3486,7 @@
       </c>
       <c r="C19" s="22" t="inlineStr">
         <is>
-          <t>Subject identifiers pseudonymised and free text scrubbed before any external call, per the study egress policy. The mapping stays inside the trust boundary.</t>
+          <t>AMENDED v2.1.0. No data leaves the company network, so redaction is no longer an egress control. Subject identifiers are still pseudonymised in the prompt — not to protect against exfiltration, but so the model cannot anchor on a subject identifier as if it carried meaning.</t>
         </is>
       </c>
       <c r="D19" s="26" t="inlineStr"/>
@@ -3507,14 +3512,77 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
+          <t>Adapters (amended v2.1.0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>Adapter</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="23" t="inlineStr">
+        <is>
+          <t>GLM v5.2</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>The only model</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>Company-hosted, reached through the internal gateway. Transport, structured-output support and context limit are configuration confirmed against the actual deployment before Step 5 — they are not asserted here, because they were never verified against v5.2.</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="25" t="inlineStr">
+        <is>
+          <t>Null</t>
+        </is>
+      </c>
+      <c r="B25" s="26" t="inlineStr">
+        <is>
+          <t>Verdict reference</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>Runs every LLM task through its deterministic template. Not a degraded mode but the definition of correct: GLM output is compared against it on every commit, and any difference in a deterministic verdict is a build failure.</t>
+        </is>
+      </c>
+      <c r="D25" s="26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
           <t>Capability negotiation</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="130" customHeight="1">
-      <c r="A23" s="29" t="inlineStr">
-        <is>
-          <t>strategy = select(adapter.capabilities, task.requirements)
+    <row r="28" ht="130" customHeight="1">
+      <c r="A28" s="29" t="inlineStr">
+        <is>
+          <t>strategy = select(glm_adapter.capabilities, task.requirements)
+  # capabilities are read from the deployed GLM v5.2 configuration,
+  # confirmed at Step 5 rather than assumed here
   CONSTRAINED_JSON_SCHEMA -&gt; constrained decoding, single call
   JSON_MODE               -&gt; JSON mode + schema validation
   otherwise               -&gt; prompt-enforced JSON + schema validation
@@ -3523,14 +3591,14 @@
 log the event. The finding is still produced, with template text.</t>
         </is>
       </c>
-      <c r="B23" s="59" t="n"/>
-      <c r="C23" s="59" t="n"/>
-      <c r="D23" s="59" t="n"/>
+      <c r="B28" s="59" t="n"/>
+      <c r="C28" s="59" t="n"/>
+      <c r="D28" s="59" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A28:D28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3848,7 +3916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3985,66 +4053,83 @@
     <row r="10">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>Provider conformance</t>
+          <t>Verdict identity</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>The same fixtures through every configured adapter. Deterministic verdicts must be identical; narratives scored against a rubric.</t>
+          <t>AMENDED v2.1.0. The same fixtures run through GLM v5.2 and through the deterministic-only reference. Every deterministic verdict must be identical; only narrative and adjudication may differ. This replaces cross-provider conformance and preserves the same guarantee — that the model cannot change a verdict.</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>Per adapter and model version</t>
+          <t>Every commit</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="20" t="inlineStr">
         <is>
-          <t>Injection tests</t>
+          <t>GLM capability verification</t>
         </is>
       </c>
       <c r="B11" s="22" t="inlineStr">
         <is>
-          <t>Fixtures containing instruction-like site text in query answers and comments. Behaviour must be unchanged and the text flagged.</t>
+          <t>Confirm the deployed v5.2 against what the adapter assumes: structured-output mode, context limit, latency under load. The OQ-03 assumptions were made against a generic gateway and never checked against this model.</t>
         </is>
       </c>
       <c r="C11" s="26" t="inlineStr">
         <is>
-          <t>Every commit</t>
+          <t>Before Step 5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="18" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Injection tests</t>
         </is>
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>Synthetic study at the NFR-03 scale.</t>
+          <t>Fixtures containing instruction-like site text in query answers and comments. Behaviour must be unchanged and the text flagged.</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Every commit</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="20" t="inlineStr">
         <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>Synthetic study at the NFR-03 scale.</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
           <t>User acceptance</t>
         </is>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>Reviewer tasks on a de-identified real study.</t>
         </is>
       </c>
-      <c r="C13" s="26" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>Step 6</t>
         </is>
@@ -4476,7 +4561,7 @@
         </is>
       </c>
       <c r="C20" s="16">
-        <f>COUNTA(Testing!A4:A13)</f>
+        <f>COUNTA(Testing!A4:A14)</f>
         <v/>
       </c>
       <c r="D20" s="14" t="inlineStr"/>
@@ -4719,12 +4804,12 @@
     <row r="8">
       <c r="A8" s="18" t="inlineStr">
         <is>
-          <t>Adding an LLM provider</t>
+          <t>Changing the model</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>Implement the adapter interface, declare its capability matrix, run the conformance suite, record results in the validation package.</t>
+          <t>The adapter interface is retained precisely so this stays cheap. Implement the adapter, declare its capability matrix, run the verdict-identity suite against the deterministic-only reference, record results in the validation package. Out of scope for release 1, which is GLM v5.2 only.</t>
         </is>
       </c>
       <c r="C8" s="24" t="inlineStr"/>

--- a/docs/spec/TEA-SPEC-001_programming-specification.xlsx
+++ b/docs/spec/TEA-SPEC-001_programming-specification.xlsx
@@ -17,24 +17,26 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rules" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rule_Messages" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Approval" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Query_Style" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Confidence_Model" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Query_Reconciliation" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prioritisation" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Input_Contract" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Finding_Contract" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LLM_Integration" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Testing" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Extensibility" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Log" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GLM_Verification" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Query_Style" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Confidence_Model" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Query_Reconciliation" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prioritisation" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Input_Contract" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Finding_Contract" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LLM_Integration" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Testing" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Extensibility" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Log" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Definitions'!$A$3:$C$50</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Rules'!$A$3:$U$88</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Rule_Messages'!$A$3:$J$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'GLM_Verification'!$A$3:$F$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -179,7 +181,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -216,6 +218,11 @@
         <fgColor rgb="00F2F6F3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF9D6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -243,7 +250,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -400,6 +407,12 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -829,7 +842,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>2.1.0 — APPROVED, amended under change control</t>
+          <t>2.2.0 — APPROVED, GLM verification checklist added</t>
         </is>
       </c>
     </row>
@@ -877,7 +890,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>v2.0.0, issued 2026-08-21</t>
+          <t>v2.1.0, issued 2026-08-22</t>
         </is>
       </c>
     </row>
@@ -1373,6 +1386,618 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="56" customWidth="1" min="2" max="2"/>
+    <col width="96" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>GLM v5.2 — what to confirm before Step 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>TEA-GLM-001. The OQ-03 assumptions were made against a generic gateway and were never checked against this model. Each row says what breaks if the answer differs from what we assumed, so the list can be triaged rather than worked end to end.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>What to confirm</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Why it matters — what breaks if the answer differs</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>Assumed today</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>Answer</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>Confirmed by</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="23" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>Which structured-output modes the endpoint supports: JSON schema with constrained decoding, JSON mode, or prompt-enforced JSON only.</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>Selects the adapter strategy. Prompt-only means more schema failures, more repair calls, and more findings falling back to template narratives. Verdicts are unaffected — they are deterministic code — so this costs narrative quality, not correctness.</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>JSON mode, no reliable constrained decoding</t>
+        </is>
+      </c>
+      <c r="E4" s="59" t="n"/>
+      <c r="F4" s="59" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>Whether the endpoint is OpenAI-compatible or GLM-native.</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>OQ-03 assumed OpenAI-compatible. If it is native, the adapter is different work and the estimate for Step 5 changes.</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>OpenAI-compatible internal gateway</t>
+        </is>
+      </c>
+      <c r="E5" s="59" t="n"/>
+      <c r="F5" s="59" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>What the endpoint returns when output violates the requested schema — a typed error, or best-effort text.</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Decides the repair loop. A typed error can be retried precisely; best-effort text has to be detected by validation, which is slower and occasionally wrong.</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Schema validation catches it; one repair call, then template fallback</t>
+        </is>
+      </c>
+      <c r="E6" s="59" t="n"/>
+      <c r="F6" s="59" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="25" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>Maximum input context in tokens, and maximum output tokens, as configured on this deployment — not the model's theoretical maximum.</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>NFR-05. The 32k figure is carried forward from OQ-03 and has never been verified. Deployments are routinely configured below the model's ceiling.</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>32k prompt budget</t>
+        </is>
+      </c>
+      <c r="E7" s="59" t="n"/>
+      <c r="F7" s="59" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="60" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="B8" s="33" t="inlineStr">
+        <is>
+          <t>Whether a full protocol plus imaging charter fits in one call — and if not, what the intended pattern is.</t>
+        </is>
+      </c>
+      <c r="C8" s="33" t="inlineStr">
+        <is>
+          <t>THE ONE THAT MATTERS MOST. P-INTAKE-PROTOCOL (AC-11) takes the protocol and imaging charter as input. An oncology protocol runs 100-200 pages, very roughly 60k-150k tokens, before the charter. If input context is anywhere near 32k this prompt cannot work as specified, and AC-11 needs section-targeted retrieval or chunking. That is a design change, not a configuration value, and it is better found now than at Step 5.</t>
+        </is>
+      </c>
+      <c r="D8" s="33" t="inlineStr">
+        <is>
+          <t>Assumed to fit — never checked, and probably wrong</t>
+        </is>
+      </c>
+      <c r="E8" s="59" t="n"/>
+      <c r="F8" s="59" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>Which tokenizer the deployment uses.</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>G-07 requires the adapter to enforce the budget and record truncation explicitly. If the adapter counts tokens differently from the model, it truncates at the wrong place — cutting evidence it believed it had kept.</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E9" s="59" t="n"/>
+      <c r="F9" s="59" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>What happens when input exceeds the context limit: hard error, or silent truncation.</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>G-07 states truncation is explicit and recorded, never silent. Silent server-side truncation would breach that guardrail without any local signal, and the finding would be built on evidence that was quietly dropped.</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>Hard error assumed</t>
+        </is>
+      </c>
+      <c r="E10" s="59" t="n"/>
+      <c r="F10" s="59" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="25" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>Whether temperature 0 is honoured, and whether a seed parameter is exposed.</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>G-05. Verdicts do not depend on this — they are computed in code — so it is narrative reproducibility, which matters for validation evidence rather than for correctness. Worth knowing, not worth blocking on.</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>temperature 0 honoured; seed where supported</t>
+        </is>
+      </c>
+      <c r="E11" s="59" t="n"/>
+      <c r="F11" s="59" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>Empirically: does an identical request return identical output across repeated calls?</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>Test this rather than take the documentation's word. Non-reproducible narrative is acceptable; it just has to be known, so validation does not assert reproducibility it cannot demonstrate.</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>Assumed reproducible at temperature 0</t>
+        </is>
+      </c>
+      <c r="E12" s="59" t="n"/>
+      <c r="F12" s="59" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="25" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>Whether the response reports an exact build or version identifier, or only a family name such as 'glm'.</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>GxP-critical. Every run carries a provenance stamp naming what produced it. If the endpoint reports only a family name, the stamp cannot identify what actually answered, and a historical run cannot be honestly reproduced.</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>An exact version identifier is recorded</t>
+        </is>
+      </c>
+      <c r="E13" s="59" t="n"/>
+      <c r="F13" s="59" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Whether the deployed version is pinned, or upgraded in place by the platform team.</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>RSK-16. An in-place upgrade changes narratives with no version change to detect it, which breaks the REG-05 impact assessment on findings already issued.</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>Pinned per study</t>
+        </is>
+      </c>
+      <c r="E14" s="59" t="n"/>
+      <c r="F14" s="59" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="25" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>Whether the platform team will notify before upgrading, and with what notice.</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>The practical half of RSK-16. Without notice there is no chance to re-run the verdict-identity suite before the change reaches a live study.</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>Not agreed</t>
+        </is>
+      </c>
+      <c r="E15" s="59" t="n"/>
+      <c r="F15" s="59" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>Rate limit and permitted concurrency for this application.</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>Sizing. A 500-subject run producing several hundred findings makes one narrative call per finding plus adjudications. Serially at two seconds each that is over ten minutes; concurrency is what makes run times practical. NFR-03's five-minute target is stated for the deterministic run — the model adds to it.</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E16" s="59" t="n"/>
+      <c r="F16" s="59" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="25" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>Latency, p50 and p95, at roughly 4k and at full-budget prompts.</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>Same sizing question, and it sets the timeout above which AC-08 falls back to a template.</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E17" s="59" t="n"/>
+      <c r="F17" s="59" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="23" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>What the gateway returns under overload or maintenance: 429, timeout, partial response.</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>NFR-09 requires an outage to degrade the run to deterministic-only rather than fail it. The adapter has to recognise the failure to do that, and a partial response is the hardest case.</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>Recognisable failure, clean fallback</t>
+        </is>
+      </c>
+      <c r="E18" s="59" t="n"/>
+      <c r="F18" s="59" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="25" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>Whether the gateway logs or retains prompts and completions, and for how long.</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>Prompts carry subject data. Even on-premise, retention has record-keeping implications, and REG-07's privacy record should describe what is actually kept rather than assume nothing is.</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E19" s="59" t="n"/>
+      <c r="F19" s="59" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="23" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>Whether usage is used for training or fine-tuning.</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>If yes, subject data enters a model and that needs an explicit decision rather than a default. Internal platforms sometimes do this by default.</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>Assumed not</t>
+        </is>
+      </c>
+      <c r="E20" s="59" t="n"/>
+      <c r="F20" s="59" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="25" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>Where the model runs physically, and who administers it.</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>REG-07's privacy record now describes an architecture rather than gating a release. It should describe the real one.</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>Company network, internally administered</t>
+        </is>
+      </c>
+      <c r="E21" s="59" t="n"/>
+      <c r="F21" s="59" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="23" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>Whether the platform team holds documented version control and change management for the model.</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>REG-02 and REG-05. The agent's own validation package can only be as good as what it depends on, and the model is now a dependency with no second source.</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>Not confirmed</t>
+        </is>
+      </c>
+      <c r="E22" s="59" t="n"/>
+      <c r="F22" s="59" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="25" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>Whether qualification evidence for the hosting can be supplied, and a support path for defects.</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>Needed for the validation package, and for knowing who to call when a narrative goes wrong in a live study.</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>Not confirmed</t>
+        </is>
+      </c>
+      <c r="E23" s="59" t="n"/>
+      <c r="F23" s="59" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>How to read this list</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="30" t="inlineStr">
+        <is>
+          <t>Blocking</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>B2 alone. If the protocol does not fit in one call, AC-11 needs redesigning and that is Step 5 scope, not configuration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="30" t="inlineStr">
+        <is>
+          <t>Materially affects the build</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>A1, A2, B1, B3, B4, D1, E1 — adapter strategy, budget enforcement, provenance honesty and run sizing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="30" t="inlineStr">
+        <is>
+          <t>Good to know, not blocking</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>C1, C2, E2, E3 — narrative quality and reproducibility. Verdicts do not depend on any of them, because verdicts are not produced by the model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="30" t="inlineStr">
+        <is>
+          <t>Needed for the validation package</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>D2, D3, F1, F2, F3, G1, G2 — mostly answerable by the platform team in one conversation.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:F23"/>
+  <mergeCells count="6">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B27:F27"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1691,7 +2316,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1741,9 +2366,9 @@
 # so certainty is never total. A 100% display would invite unread query issuance.</t>
         </is>
       </c>
-      <c r="B4" s="59" t="n"/>
-      <c r="C4" s="59" t="n"/>
-      <c r="D4" s="59" t="n"/>
+      <c r="B4" s="61" t="n"/>
+      <c r="C4" s="61" t="n"/>
+      <c r="D4" s="61" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
@@ -2017,7 +2642,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2082,9 +2707,9 @@
         f.status = RECURRENT</t>
         </is>
       </c>
-      <c r="B4" s="59" t="n"/>
-      <c r="C4" s="59" t="n"/>
-      <c r="D4" s="59" t="n"/>
+      <c r="B4" s="61" t="n"/>
+      <c r="C4" s="61" t="n"/>
+      <c r="D4" s="61" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -2138,7 +2763,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2179,9 +2804,9 @@
 it necessarily causes, so the reviewer fixes the baseline once instead of querying ten visits.</t>
         </is>
       </c>
-      <c r="B4" s="59" t="n"/>
-      <c r="C4" s="59" t="n"/>
-      <c r="D4" s="59" t="n"/>
+      <c r="B4" s="61" t="n"/>
+      <c r="C4" s="61" t="n"/>
+      <c r="D4" s="61" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -2204,9 +2829,9 @@
 where it does rather than having to trust the ordering.</t>
         </is>
       </c>
-      <c r="B7" s="59" t="n"/>
-      <c r="C7" s="59" t="n"/>
-      <c r="D7" s="59" t="n"/>
+      <c r="B7" s="61" t="n"/>
+      <c r="C7" s="61" t="n"/>
+      <c r="D7" s="61" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2218,7 +2843,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2281,7 +2906,7 @@
           <t>study</t>
         </is>
       </c>
-      <c r="B4" s="60" t="inlineStr">
+      <c r="B4" s="62" t="inlineStr">
         <is>
           <t>study_id</t>
         </is>
@@ -2304,7 +2929,7 @@
           <t>study</t>
         </is>
       </c>
-      <c r="B5" s="61" t="inlineStr">
+      <c r="B5" s="63" t="inlineStr">
         <is>
           <t>indication</t>
         </is>
@@ -2331,7 +2956,7 @@
           <t>study</t>
         </is>
       </c>
-      <c r="B6" s="60" t="inlineStr">
+      <c r="B6" s="62" t="inlineStr">
         <is>
           <t>guideline_version</t>
         </is>
@@ -2358,7 +2983,7 @@
           <t>protocol_config</t>
         </is>
       </c>
-      <c r="B7" s="61" t="inlineStr">
+      <c r="B7" s="63" t="inlineStr">
         <is>
           <t>(28 parameters)</t>
         </is>
@@ -2385,7 +3010,7 @@
           <t>subjects</t>
         </is>
       </c>
-      <c r="B8" s="60" t="inlineStr">
+      <c r="B8" s="62" t="inlineStr">
         <is>
           <t>subject_id, site_id, first_dose_date, discontinuation_date, death_date, has_measurable_disease_at_baseline</t>
         </is>
@@ -2408,7 +3033,7 @@
           <t>lesions</t>
         </is>
       </c>
-      <c r="B9" s="61" t="inlineStr">
+      <c r="B9" s="63" t="inlineStr">
         <is>
           <t>lesion_id, category, is_nodal, organ, location_detail, laterality, method, new_lesion_certainty, previously_irradiated</t>
         </is>
@@ -2435,7 +3060,7 @@
           <t>assessments</t>
         </is>
       </c>
-      <c r="B10" s="60" t="inlineStr">
+      <c r="B10" s="62" t="inlineStr">
         <is>
           <t>assessment_id, visit_name, visit_number, assessment_date, scan_dates, is_baseline, evaluator</t>
         </is>
@@ -2458,7 +3083,7 @@
           <t>measurements</t>
         </is>
       </c>
-      <c r="B11" s="61" t="inlineStr">
+      <c r="B11" s="63" t="inlineStr">
         <is>
           <t>assessment_id, lesion_id, value_mm, original_unit, axis_recorded, state, non_target_state, comment_text</t>
         </is>
@@ -2485,7 +3110,7 @@
           <t>reported_responses</t>
         </is>
       </c>
-      <c r="B12" s="60" t="inlineStr">
+      <c r="B12" s="62" t="inlineStr">
         <is>
           <t>target, non_target, new_lesion, overall, irecist, sum_of_diameters_reported, best_overall_response, progression_date</t>
         </is>
@@ -2512,7 +3137,7 @@
           <t>queries</t>
         </is>
       </c>
-      <c r="B13" s="61" t="inlineStr">
+      <c r="B13" s="63" t="inlineStr">
         <is>
           <t>query_id, query_text, answer_text, status, opened/answered/closed dates, tea_rule_id</t>
         </is>
@@ -2539,7 +3164,7 @@
           <t>cross_domain</t>
         </is>
       </c>
-      <c r="B14" s="60" t="inlineStr">
+      <c r="B14" s="62" t="inlineStr">
         <is>
           <t>exposure, anticancer_therapy, radiotherapy, procedures, adverse_events, lab_markers, performance_status</t>
         </is>
@@ -2566,7 +3191,7 @@
           <t>imaging_metadata</t>
         </is>
       </c>
-      <c r="B15" s="61" t="inlineStr">
+      <c r="B15" s="63" t="inlineStr">
         <is>
           <t>modality, scan_date, slice_thickness_mm, regions_imaged, contrast_used</t>
         </is>
@@ -2631,7 +3256,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3175,7 +3800,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3242,7 +3867,7 @@
           <t>Lesion organ, laterality, location text, description text, method, guideline extract</t>
         </is>
       </c>
-      <c r="D5" s="60" t="inlineStr">
+      <c r="D5" s="62" t="inlineStr">
         <is>
           <t>{is_non_measurable, category, confidence, rationale}</t>
         </is>
@@ -3264,7 +3889,7 @@
           <t>Non-target descriptions at this and the previous timepoint, target response, sum change, guideline extract</t>
         </is>
       </c>
-      <c r="D6" s="61" t="inlineStr">
+      <c r="D6" s="63" t="inlineStr">
         <is>
           <t>{supports_unequivocal, magnitude_comment, confidence, rationale}</t>
         </is>
@@ -3286,7 +3911,7 @@
           <t>Candidate finding summary; historical queries for the subject</t>
         </is>
       </c>
-      <c r="D7" s="60" t="inlineStr">
+      <c r="D7" s="62" t="inlineStr">
         <is>
           <t>{matches:[{query_id, relation, confidence}]}</t>
         </is>
@@ -3308,7 +3933,7 @@
           <t>Query text, answer text, current values of the queried fields  (NEW at review)</t>
         </is>
       </c>
-      <c r="D8" s="61" t="inlineStr">
+      <c r="D8" s="63" t="inlineStr">
         <is>
           <t>{classification, confidence, rationale, quoted_span}</t>
         </is>
@@ -3330,7 +3955,7 @@
           <t>Evidence object, rule metadata, message templates, guideline citation, indication context</t>
         </is>
       </c>
-      <c r="D9" s="60" t="inlineStr">
+      <c r="D9" s="62" t="inlineStr">
         <is>
           <t>{five narrative fields}</t>
         </is>
@@ -3352,7 +3977,7 @@
           <t>Protocol and imaging charter text  (NEW at review, AC-11)</t>
         </is>
       </c>
-      <c r="D10" s="61" t="inlineStr">
+      <c r="D10" s="63" t="inlineStr">
         <is>
           <t>{checkpoints:[{parameter, value_found, page_ref, confidence}]}</t>
         </is>
@@ -3591,9 +4216,9 @@
 log the event. The finding is still produced, with template text.</t>
         </is>
       </c>
-      <c r="B28" s="59" t="n"/>
-      <c r="C28" s="59" t="n"/>
-      <c r="D28" s="59" t="n"/>
+      <c r="B28" s="61" t="n"/>
+      <c r="C28" s="61" t="n"/>
+      <c r="D28" s="61" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3604,7 +4229,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3910,246 +4535,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="100" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>Test strategy</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>Level</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
-        <is>
-          <t>Gate</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="18" t="inlineStr">
-        <is>
-          <t>Unit — derivations</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>Every function on the Derivations sheet, with boundary fixtures at every threshold: 30% PR, 20%/5 mm PD, 10 mm and 15 mm nodal, 5 mm iCPD increment, confirmation interval boundaries.</t>
-        </is>
-      </c>
-      <c r="C4" s="24" t="inlineStr">
-        <is>
-          <t>Every commit</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="20" t="inlineStr">
-        <is>
-          <t>Unit — rules</t>
-        </is>
-      </c>
-      <c r="B5" s="22" t="inlineStr">
-        <is>
-          <t>Each rule requires at least one positive and one negative fixture; CI fails if either is missing. Rules with false-positive guards require a guard fixture.</t>
-        </is>
-      </c>
-      <c r="C5" s="26" t="inlineStr">
-        <is>
-          <t>Every commit</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>Worked examples</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>Published RECIST 1.1 and iRECIST worked examples encoded as fixtures; must reproduce exactly.</t>
-        </is>
-      </c>
-      <c r="C6" s="24" t="inlineStr">
-        <is>
-          <t>Every commit</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="20" t="inlineStr">
-        <is>
-          <t>Golden dataset</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>Curated study with a signed-off expected finding list. Any difference must be acknowledged in the rule pack change history before merge.</t>
-        </is>
-      </c>
-      <c r="C7" s="26" t="inlineStr">
-        <is>
-          <t>Every commit</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="18" t="inlineStr">
-        <is>
-          <t>Catalog drift check</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>rule-catalog.yaml compared against the Rules sheet of this workbook and against implemented rule modules. Fails on any mismatch of id, severity, mode, status or confidence base rate.</t>
-        </is>
-      </c>
-      <c r="C8" s="24" t="inlineStr">
-        <is>
-          <t>Every commit</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="20" t="inlineStr">
-        <is>
-          <t>Confidence calibration</t>
-        </is>
-      </c>
-      <c r="B9" s="22" t="inlineStr">
-        <is>
-          <t>Predicted confidence versus observed acceptance per band; mean absolute error target 0.10.</t>
-        </is>
-      </c>
-      <c r="C9" s="26" t="inlineStr">
-        <is>
-          <t>Step 3, then per release</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="18" t="inlineStr">
-        <is>
-          <t>Verdict identity</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>AMENDED v2.1.0. The same fixtures run through GLM v5.2 and through the deterministic-only reference. Every deterministic verdict must be identical; only narrative and adjudication may differ. This replaces cross-provider conformance and preserves the same guarantee — that the model cannot change a verdict.</t>
-        </is>
-      </c>
-      <c r="C10" s="24" t="inlineStr">
-        <is>
-          <t>Every commit</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="20" t="inlineStr">
-        <is>
-          <t>GLM capability verification</t>
-        </is>
-      </c>
-      <c r="B11" s="22" t="inlineStr">
-        <is>
-          <t>Confirm the deployed v5.2 against what the adapter assumes: structured-output mode, context limit, latency under load. The OQ-03 assumptions were made against a generic gateway and never checked against this model.</t>
-        </is>
-      </c>
-      <c r="C11" s="26" t="inlineStr">
-        <is>
-          <t>Before Step 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="18" t="inlineStr">
-        <is>
-          <t>Injection tests</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>Fixtures containing instruction-like site text in query answers and comments. Behaviour must be unchanged and the text flagged.</t>
-        </is>
-      </c>
-      <c r="C12" s="24" t="inlineStr">
-        <is>
-          <t>Every commit</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="20" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="B13" s="22" t="inlineStr">
-        <is>
-          <t>Synthetic study at the NFR-03 scale.</t>
-        </is>
-      </c>
-      <c r="C13" s="26" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="18" t="inlineStr">
-        <is>
-          <t>User acceptance</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>Reviewer tasks on a de-identified real study.</t>
-        </is>
-      </c>
-      <c r="C14" s="24" t="inlineStr">
-        <is>
-          <t>Step 6</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4637,43 +5029,69 @@
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>GLM_Verification</t>
         </is>
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>Gate record: basis, history, what was not confirmed</t>
-        </is>
-      </c>
-      <c r="C24" s="13" t="n"/>
+          <t>What to confirm about GLM v5.2 before Step 5</t>
+        </is>
+      </c>
+      <c r="C24" s="16">
+        <f>COUNTA(GLM_Verification!A4:A23)</f>
+        <v/>
+      </c>
       <c r="D24" s="17" t="inlineStr">
         <is>
-          <t>read this</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E24" s="15" t="inlineStr">
         <is>
-          <t>2 items flagged</t>
+          <t>B2 is blocking</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
+          <t>Approval</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>Gate record: basis, history, what was not confirmed</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="n"/>
+      <c r="D25" s="17" t="inlineStr">
+        <is>
+          <t>read this</t>
+        </is>
+      </c>
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>2 items flagged</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
           <t>Traceability</t>
         </is>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>Plan requirement to specification to tests</t>
         </is>
       </c>
-      <c r="C25" s="16">
+      <c r="C26" s="16">
         <f>COUNTA(Traceability!A4:A23)</f>
         <v/>
       </c>
-      <c r="D25" s="14" t="inlineStr"/>
-      <c r="E25" s="15" t="inlineStr"/>
+      <c r="D26" s="14" t="inlineStr"/>
+      <c r="E26" s="15" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4701,14 +5119,248 @@
     <hyperlink ref="A21" location="Extensibility!A1"/>
     <hyperlink ref="A22" location="Open_Questions!A1"/>
     <hyperlink ref="A23" location="Query_Style!A1"/>
-    <hyperlink ref="A24" location="Approval!A1"/>
-    <hyperlink ref="A25" location="Traceability!A1"/>
+    <hyperlink ref="A24" location="GLM_Verification!A1"/>
+    <hyperlink ref="A25" location="Approval!A1"/>
+    <hyperlink ref="A26" location="Traceability!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Test strategy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Level</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>Unit — derivations</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>Every function on the Derivations sheet, with boundary fixtures at every threshold: 30% PR, 20%/5 mm PD, 10 mm and 15 mm nodal, 5 mm iCPD increment, confirmation interval boundaries.</t>
+        </is>
+      </c>
+      <c r="C4" s="24" t="inlineStr">
+        <is>
+          <t>Every commit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>Unit — rules</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>Each rule requires at least one positive and one negative fixture; CI fails if either is missing. Rules with false-positive guards require a guard fixture.</t>
+        </is>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
+        <is>
+          <t>Every commit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>Worked examples</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Published RECIST 1.1 and iRECIST worked examples encoded as fixtures; must reproduce exactly.</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
+        <is>
+          <t>Every commit</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>Golden dataset</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>Curated study with a signed-off expected finding list. Any difference must be acknowledged in the rule pack change history before merge.</t>
+        </is>
+      </c>
+      <c r="C7" s="26" t="inlineStr">
+        <is>
+          <t>Every commit</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>Catalog drift check</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>rule-catalog.yaml compared against the Rules sheet of this workbook and against implemented rule modules. Fails on any mismatch of id, severity, mode, status or confidence base rate.</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t>Every commit</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>Confidence calibration</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>Predicted confidence versus observed acceptance per band; mean absolute error target 0.10.</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>Step 3, then per release</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>Verdict identity</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>AMENDED v2.1.0. The same fixtures run through GLM v5.2 and through the deterministic-only reference. Every deterministic verdict must be identical; only narrative and adjudication may differ. This replaces cross-provider conformance and preserves the same guarantee — that the model cannot change a verdict.</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>Every commit</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>GLM capability verification</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>Confirm the deployed v5.2 against what the adapter assumes: structured-output mode, context limit, latency under load. The OQ-03 assumptions were made against a generic gateway and never checked against this model.</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t>Before Step 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>Injection tests</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>Fixtures containing instruction-like site text in query answers and comments. Behaviour must be unchanged and the text flagged.</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>Every commit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>Synthetic study at the NFR-03 scale.</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>User acceptance</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Reviewer tasks on a de-identified real study.</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>Step 6</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4836,7 +5488,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4942,7 +5594,7 @@
           <t>Confirm the confidence base rate proposed for each rule (Open Item OI-02). These drive triage for every finding the agent produces.</t>
         </is>
       </c>
-      <c r="C5" s="62" t="inlineStr">
+      <c r="C5" s="64" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -5134,7 +5786,7 @@
           <t>Confirm whether the Veeva CRF collects a sum of diameters at all. If it is derived only, TE-BL-011 and TE-FU-001 do not apply and weight shifts onto TE-RS-001.</t>
         </is>
       </c>
-      <c r="C11" s="62" t="inlineStr">
+      <c r="C11" s="64" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -5242,7 +5894,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5742,7 +6394,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/docs/spec/TEA-SPEC-001_programming-specification.xlsx
+++ b/docs/spec/TEA-SPEC-001_programming-specification.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>2.2.0 — APPROVED, GLM verification checklist added</t>
+          <t>2.3.0 — APPROVED, protocol extract mitigation</t>
         </is>
       </c>
     </row>
@@ -890,7 +890,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>v2.1.0, issued 2026-08-22</t>
+          <t>v2.2.0, issued 2026-08-22</t>
         </is>
       </c>
     </row>
@@ -1386,15 +1386,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="56" customWidth="1" min="2" max="2"/>
-    <col width="96" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="76" customWidth="1" min="2" max="2"/>
+    <col width="56" customWidth="1" min="3" max="3"/>
+    <col width="2" customWidth="1" min="4" max="4"/>
+    <col width="2" customWidth="1" min="5" max="5"/>
+    <col width="2" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -1923,56 +1923,534 @@
       <c r="E23" s="59" t="n"/>
       <c r="F23" s="59" t="n"/>
     </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Protocol extract — the accepted mitigation for B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="30" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>B2 cannot be tested at this stage and is carried as a future checkpoint. If the context limit turns out to be binding, the protocol is condensed before AC-11 sees it — prepared separately with the internal LLM, or by hand — so AC-11 reads a bounded extract rather than the full document.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="30" t="inlineStr">
+        <is>
+          <t>Why this is a good answer</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>It removes the dependency rather than working around it. The extract is bounded and predictable in size, a human can read what the agent will read before it runs, and the run provenance can hash the extract so the configuration is traceable to an exact input.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="30" t="inlineStr">
+        <is>
+          <t>The risk it introduces</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>One, and it is worse than the problem it solves if left unhandled. A truncation error is loud. A missing parameter is silent: AC-11 proposes the guideline default, the user confirms a plausible-looking checkpoint, and the study runs on a threshold the protocol never specified. Nobody sees it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="30" t="inlineStr">
+        <is>
+          <t>So the extract is assembled against a list</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Not summarised freely. The parameters AC-11 needs are known in advance and are listed below, with the section that normally carries each. Condensing to a list is a checkable task; condensing to a summary is not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="54" customHeight="1">
+      <c r="A29" s="30" t="inlineStr">
+        <is>
+          <t>And AC-11 must say what it could not find</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>NEW REQUIREMENT. Every checkpoint must carry its provenance — found in the document with a location, or defaulted because it was not found — and the two must be visually distinct at the intake screen. A parameter that was defaulted is the one a human most needs to look at, and today it looks identical to one the protocol stated explicitly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>What must survive the condensation</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Parameter AC-11 must resolve</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>Normally carried in</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr"/>
+      <c r="E32" s="10" t="inlineStr"/>
+      <c r="F32" s="10" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="23" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>Guideline version — RECIST 1.1, or RECIST 1.1 with iRECIST</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>Efficacy assessments section</t>
+        </is>
+      </c>
+      <c r="D33" s="24" t="inlineStr"/>
+      <c r="E33" s="24" t="inlineStr"/>
+      <c r="F33" s="24" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>Maximum target lesions, total and per organ</t>
+        </is>
+      </c>
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t>Tumor assessment section</t>
+        </is>
+      </c>
+      <c r="D34" s="26" t="inlineStr"/>
+      <c r="E34" s="26" t="inlineStr"/>
+      <c r="F34" s="26" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="23" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>Measurability thresholds — non-nodal, nodal short axis, chest X-ray, clinical exam</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>Tumor assessment section; imaging charter</t>
+        </is>
+      </c>
+      <c r="D35" s="24" t="inlineStr"/>
+      <c r="E35" s="24" t="inlineStr"/>
+      <c r="F35" s="24" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="inlineStr">
+        <is>
+          <t>Progression thresholds — relative percent and absolute millimetres</t>
+        </is>
+      </c>
+      <c r="C36" s="22" t="inlineStr">
+        <is>
+          <t>Tumor assessment section</t>
+        </is>
+      </c>
+      <c r="D36" s="26" t="inlineStr"/>
+      <c r="E36" s="26" t="inlineStr"/>
+      <c r="F36" s="26" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="23" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>Partial response threshold — percent decrease</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>Tumor assessment section</t>
+        </is>
+      </c>
+      <c r="D37" s="24" t="inlineStr"/>
+      <c r="E37" s="24" t="inlineStr"/>
+      <c r="F37" s="24" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="25" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="B38" s="22" t="inlineStr">
+        <is>
+          <t>Whether response requires confirmation, and the minimum interval</t>
+        </is>
+      </c>
+      <c r="C38" s="22" t="inlineStr">
+        <is>
+          <t>Efficacy assessments; statistical section</t>
+        </is>
+      </c>
+      <c r="D38" s="26" t="inlineStr"/>
+      <c r="E38" s="26" t="inlineStr"/>
+      <c r="F38" s="26" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="23" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>Minimum duration for stable disease</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>Statistical section — endpoint definitions</t>
+        </is>
+      </c>
+      <c r="D39" s="24" t="inlineStr"/>
+      <c r="E39" s="24" t="inlineStr"/>
+      <c r="F39" s="24" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="25" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="B40" s="22" t="inlineStr">
+        <is>
+          <t>Assessment schedule per visit, with the permitted window each side</t>
+        </is>
+      </c>
+      <c r="C40" s="22" t="inlineStr">
+        <is>
+          <t>Schedule of assessments table</t>
+        </is>
+      </c>
+      <c r="D40" s="26" t="inlineStr"/>
+      <c r="E40" s="26" t="inlineStr"/>
+      <c r="F40" s="26" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="23" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>iRECIST confirmation window, where iRECIST applies</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>Efficacy assessments section</t>
+        </is>
+      </c>
+      <c r="D41" s="24" t="inlineStr"/>
+      <c r="E41" s="24" t="inlineStr"/>
+      <c r="F41" s="24" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="25" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="B42" s="22" t="inlineStr">
+        <is>
+          <t>New measurable lesion limits under iRECIST, total and per organ</t>
+        </is>
+      </c>
+      <c r="C42" s="22" t="inlineStr">
+        <is>
+          <t>Efficacy assessments section</t>
+        </is>
+      </c>
+      <c r="D42" s="26" t="inlineStr"/>
+      <c r="E42" s="26" t="inlineStr"/>
+      <c r="F42" s="26" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="23" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>Whether tumor markers contribute to a complete response</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>Efficacy assessments; laboratory section</t>
+        </is>
+      </c>
+      <c r="D43" s="24" t="inlineStr"/>
+      <c r="E43" s="24" t="inlineStr"/>
+      <c r="F43" s="24" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="25" t="inlineStr">
+        <is>
+          <t>P12</t>
+        </is>
+      </c>
+      <c r="B44" s="22" t="inlineStr">
+        <is>
+          <t>Permitted imaging modalities</t>
+        </is>
+      </c>
+      <c r="C44" s="22" t="inlineStr">
+        <is>
+          <t>Imaging charter or imaging manual</t>
+        </is>
+      </c>
+      <c r="D44" s="26" t="inlineStr"/>
+      <c r="E44" s="26" t="inlineStr"/>
+      <c r="F44" s="26" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="23" t="inlineStr">
+        <is>
+          <t>P13</t>
+        </is>
+      </c>
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>Disease-site imaging the protocol requires — brain, for example</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>Imaging charter; eligibility criteria</t>
+        </is>
+      </c>
+      <c r="D45" s="24" t="inlineStr"/>
+      <c r="E45" s="24" t="inlineStr"/>
+      <c r="F45" s="24" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="25" t="inlineStr">
+        <is>
+          <t>P14</t>
+        </is>
+      </c>
+      <c r="B46" s="22" t="inlineStr">
+        <is>
+          <t>Whether independent central review is collected</t>
+        </is>
+      </c>
+      <c r="C46" s="22" t="inlineStr">
+        <is>
+          <t>BICR charter; efficacy assessments</t>
+        </is>
+      </c>
+      <c r="D46" s="26" t="inlineStr"/>
+      <c r="E46" s="26" t="inlineStr"/>
+      <c r="F46" s="26" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="23" t="inlineStr">
+        <is>
+          <t>P15</t>
+        </is>
+      </c>
+      <c r="B47" s="12" t="inlineStr">
+        <is>
+          <t>Reappearance of a resolved lesion — progression, or back into the sum (ID-01)</t>
+        </is>
+      </c>
+      <c r="C47" s="12" t="inlineStr">
+        <is>
+          <t>Tumor assessment section, often absent</t>
+        </is>
+      </c>
+      <c r="D47" s="24" t="inlineStr"/>
+      <c r="E47" s="24" t="inlineStr"/>
+      <c r="F47" s="24" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="25" t="inlineStr">
+        <is>
+          <t>P16</t>
+        </is>
+      </c>
+      <c r="B48" s="22" t="inlineStr">
+        <is>
+          <t>Too-small-to-measure convention (ID-02)</t>
+        </is>
+      </c>
+      <c r="C48" s="22" t="inlineStr">
+        <is>
+          <t>Imaging charter, often absent</t>
+        </is>
+      </c>
+      <c r="D48" s="26" t="inlineStr"/>
+      <c r="E48" s="26" t="inlineStr"/>
+      <c r="F48" s="26" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="23" t="inlineStr">
+        <is>
+          <t>P17</t>
+        </is>
+      </c>
+      <c r="B49" s="12" t="inlineStr">
+        <is>
+          <t>What counts as baseline (ID-06)</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>Schedule of assessments; CRF design</t>
+        </is>
+      </c>
+      <c r="D49" s="24" t="inlineStr"/>
+      <c r="E49" s="24" t="inlineStr"/>
+      <c r="F49" s="24" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="25" t="inlineStr">
+        <is>
+          <t>P18</t>
+        </is>
+      </c>
+      <c r="B50" s="22" t="inlineStr">
+        <is>
+          <t>Treatment beyond progression — permitted, and what must be documented</t>
+        </is>
+      </c>
+      <c r="C50" s="22" t="inlineStr">
+        <is>
+          <t>Treatment section</t>
+        </is>
+      </c>
+      <c r="D50" s="26" t="inlineStr"/>
+      <c r="E50" s="26" t="inlineStr"/>
+      <c r="F50" s="26" t="inlineStr"/>
+    </row>
+    <row r="52" ht="48" customHeight="1">
+      <c r="A52" s="30" t="inlineStr">
+        <is>
+          <t>Note on P15 to P17</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>These three are routinely absent from protocols altogether — they are the interpretation decisions, which is why they exist as ID-01, ID-02 and ID-06 with stated defaults. Expect the extract not to contain them, and expect AC-11 to mark them defaulted. That is correct behaviour, not a gap in the extract.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="48" customHeight="1">
+      <c r="A53" s="30" t="inlineStr">
+        <is>
+          <t>Sizing</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>An extract covering P1 to P18 is a few pages, not a hundred. Whatever the context limit turns out to be, it will fit — which is why this mitigation makes B2 stop mattering rather than merely deferring it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>How to read this list</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="42" customHeight="1">
-      <c r="A26" s="30" t="inlineStr">
-        <is>
-          <t>Blocking</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>B2 alone. If the protocol does not fit in one call, AC-11 needs redesigning and that is Step 5 scope, not configuration.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="42" customHeight="1">
-      <c r="A27" s="30" t="inlineStr">
+    <row r="56" ht="42" customHeight="1">
+      <c r="A56" s="30" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>B2 — cannot be tested now, carried as a checkpoint, and mitigated by the protocol extract above. Nothing on this list blocks Step 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="42" customHeight="1">
+      <c r="A57" s="30" t="inlineStr">
         <is>
           <t>Materially affects the build</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B57" s="7" t="inlineStr">
         <is>
           <t>A1, A2, B1, B3, B4, D1, E1 — adapter strategy, budget enforcement, provenance honesty and run sizing.</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="42" customHeight="1">
-      <c r="A28" s="30" t="inlineStr">
+    <row r="58" ht="42" customHeight="1">
+      <c r="A58" s="30" t="inlineStr">
         <is>
           <t>Good to know, not blocking</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B58" s="7" t="inlineStr">
         <is>
           <t>C1, C2, E2, E3 — narrative quality and reproducibility. Verdicts do not depend on any of them, because verdicts are not produced by the model.</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="42" customHeight="1">
-      <c r="A29" s="30" t="inlineStr">
+    <row r="59" ht="42" customHeight="1">
+      <c r="A59" s="30" t="inlineStr">
         <is>
           <t>Needed for the validation package</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t>D2, D3, F1, F2, F3, G1, G2 — mostly answerable by the platform team in one conversation.</t>
         </is>
@@ -1980,13 +2458,20 @@
     </row>
   </sheetData>
   <autoFilter ref="A3:F23"/>
-  <mergeCells count="6">
+  <mergeCells count="13">
+    <mergeCell ref="B53:F53"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="B56:F56"/>
     <mergeCell ref="B29:F29"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B25:F25"/>
     <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B59:F59"/>
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B52:F52"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5034,21 +5519,17 @@
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>What to confirm about GLM v5.2 before Step 5</t>
+          <t>GLM checks, plus the protocol extract spec</t>
         </is>
       </c>
       <c r="C24" s="16">
         <f>COUNTA(GLM_Verification!A4:A23)</f>
         <v/>
       </c>
-      <c r="D24" s="17" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="D24" s="14" t="inlineStr"/>
       <c r="E24" s="15" t="inlineStr">
         <is>
-          <t>B2 is blocking</t>
+          <t>B2 deferred + mitigated</t>
         </is>
       </c>
     </row>

--- a/docs/spec/TEA-SPEC-001_programming-specification.xlsx
+++ b/docs/spec/TEA-SPEC-001_programming-specification.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>2.3.0 — APPROVED, protocol extract mitigation</t>
+          <t>2.4.0 — APPROVED, protocol summary as a named input</t>
         </is>
       </c>
     </row>
@@ -890,7 +890,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>v2.2.0, issued 2026-08-22</t>
+          <t>v2.3.0, issued 2026-08-22</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1938,139 +1938,123 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>B2 cannot be tested at this stage and is carried as a future checkpoint. If the context limit turns out to be binding, the protocol is condensed before AC-11 sees it — prepared separately with the internal LLM, or by hand — so AC-11 reads a bounded extract rather than the full document.</t>
+          <t>B2 cannot be tested at this stage and is carried as a future checkpoint. The protocol is condensed before AC-11 sees it, so AC-11 reads a bounded summary rather than the full document — regardless of what the context limit turns out to be.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="54" customHeight="1">
       <c r="A26" s="30" t="inlineStr">
         <is>
-          <t>Why this is a good answer</t>
+          <t>Who prepares it — decided 2026-08-22</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>It removes the dependency rather than working around it. The extract is bounded and predictable in size, a human can read what the agent will read before it runs, and the run provenance can hash the extract so the configuration is traceable to an exact input.</t>
+          <t>The study data manager, by hand, against a content selection rule agreed with the Medical Monitor. The user who calls the agent is the same person who imported the summary, so the run is traceable to a named preparer.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="54" customHeight="1">
       <c r="A27" s="30" t="inlineStr">
         <is>
-          <t>The risk it introduces</t>
+          <t>Why the agreed rule matters more than the summary</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>One, and it is worse than the problem it solves if left unhandled. A truncation error is loud. A missing parameter is silent: AC-11 proposes the guideline default, the user confirms a plausible-looking checkpoint, and the study runs on a threshold the protocol never specified. Nobody sees it.</t>
+          <t>The summary is now an input to the system: what goes into it bounds what the agent can know. Agreed once as a rule, it is a control. Re-decided per study by whoever happens to prepare it, it is a variable nobody is tracking. P1 to P18 below is the proposed basis — tracked as OI-07.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="54" customHeight="1">
       <c r="A28" s="30" t="inlineStr">
         <is>
-          <t>So the extract is assembled against a list</t>
+          <t>Why this is a good answer</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Not summarised freely. The parameters AC-11 needs are known in advance and are listed below, with the section that normally carries each. Condensing to a list is a checkable task; condensing to a summary is not.</t>
+          <t>It removes the dependency rather than working around it. The extract is bounded and predictable in size, a human can read what the agent will read before it runs, and the run provenance can hash the extract so the configuration is traceable to an exact input.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="54" customHeight="1">
       <c r="A29" s="30" t="inlineStr">
         <is>
+          <t>The risk it introduces</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>One, and it is worse than the problem it solves if left unhandled. A truncation error is loud. A missing parameter is silent: AC-11 proposes the guideline default, the user confirms a plausible-looking checkpoint, and the study runs on a threshold the protocol never specified. Nobody sees it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="54" customHeight="1">
+      <c r="A30" s="30" t="inlineStr">
+        <is>
+          <t>So the extract is assembled against a list</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Not summarised freely. The parameters AC-11 needs are known in advance and are listed below, with the section that normally carries each. Condensing to a list is a checkable task; condensing to a summary is not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="54" customHeight="1">
+      <c r="A31" s="30" t="inlineStr">
+        <is>
           <t>And AC-11 must say what it could not find</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>NEW REQUIREMENT. Every checkpoint must carry its provenance — found in the document with a location, or defaulted because it was not found — and the two must be visually distinct at the intake screen. A parameter that was defaulted is the one a human most needs to look at, and today it looks identical to one the protocol stated explicitly.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>What must survive the condensation</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="10" t="inlineStr">
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="B32" s="10" t="inlineStr">
+      <c r="B34" s="10" t="inlineStr">
         <is>
           <t>Parameter AC-11 must resolve</t>
         </is>
       </c>
-      <c r="C32" s="10" t="inlineStr">
+      <c r="C34" s="10" t="inlineStr">
         <is>
           <t>Normally carried in</t>
         </is>
       </c>
-      <c r="D32" s="10" t="inlineStr"/>
-      <c r="E32" s="10" t="inlineStr"/>
-      <c r="F32" s="10" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="23" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="B33" s="12" t="inlineStr">
-        <is>
-          <t>Guideline version — RECIST 1.1, or RECIST 1.1 with iRECIST</t>
-        </is>
-      </c>
-      <c r="C33" s="12" t="inlineStr">
-        <is>
-          <t>Efficacy assessments section</t>
-        </is>
-      </c>
-      <c r="D33" s="24" t="inlineStr"/>
-      <c r="E33" s="24" t="inlineStr"/>
-      <c r="F33" s="24" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="25" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B34" s="22" t="inlineStr">
-        <is>
-          <t>Maximum target lesions, total and per organ</t>
-        </is>
-      </c>
-      <c r="C34" s="22" t="inlineStr">
-        <is>
-          <t>Tumor assessment section</t>
-        </is>
-      </c>
-      <c r="D34" s="26" t="inlineStr"/>
-      <c r="E34" s="26" t="inlineStr"/>
-      <c r="F34" s="26" t="inlineStr"/>
+      <c r="D34" s="10" t="inlineStr"/>
+      <c r="E34" s="10" t="inlineStr"/>
+      <c r="F34" s="10" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="23" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>Measurability thresholds — non-nodal, nodal short axis, chest X-ray, clinical exam</t>
+          <t>Guideline version — RECIST 1.1, or RECIST 1.1 with iRECIST</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Tumor assessment section; imaging charter</t>
+          <t>Efficacy assessments section</t>
         </is>
       </c>
       <c r="D35" s="24" t="inlineStr"/>
@@ -2080,12 +2064,12 @@
     <row r="36">
       <c r="A36" s="25" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="B36" s="22" t="inlineStr">
         <is>
-          <t>Progression thresholds — relative percent and absolute millimetres</t>
+          <t>Maximum target lesions, total and per organ</t>
         </is>
       </c>
       <c r="C36" s="22" t="inlineStr">
@@ -2100,17 +2084,17 @@
     <row r="37">
       <c r="A37" s="23" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>Partial response threshold — percent decrease</t>
+          <t>Measurability thresholds — non-nodal, nodal short axis, chest X-ray, clinical exam</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Tumor assessment section</t>
+          <t>Tumor assessment section; imaging charter</t>
         </is>
       </c>
       <c r="D37" s="24" t="inlineStr"/>
@@ -2120,17 +2104,17 @@
     <row r="38">
       <c r="A38" s="25" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="B38" s="22" t="inlineStr">
         <is>
-          <t>Whether response requires confirmation, and the minimum interval</t>
+          <t>Progression thresholds — relative percent and absolute millimetres</t>
         </is>
       </c>
       <c r="C38" s="22" t="inlineStr">
         <is>
-          <t>Efficacy assessments; statistical section</t>
+          <t>Tumor assessment section</t>
         </is>
       </c>
       <c r="D38" s="26" t="inlineStr"/>
@@ -2140,17 +2124,17 @@
     <row r="39">
       <c r="A39" s="23" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>Minimum duration for stable disease</t>
+          <t>Partial response threshold — percent decrease</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Statistical section — endpoint definitions</t>
+          <t>Tumor assessment section</t>
         </is>
       </c>
       <c r="D39" s="24" t="inlineStr"/>
@@ -2160,17 +2144,17 @@
     <row r="40">
       <c r="A40" s="25" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="B40" s="22" t="inlineStr">
         <is>
-          <t>Assessment schedule per visit, with the permitted window each side</t>
+          <t>Whether response requires confirmation, and the minimum interval</t>
         </is>
       </c>
       <c r="C40" s="22" t="inlineStr">
         <is>
-          <t>Schedule of assessments table</t>
+          <t>Efficacy assessments; statistical section</t>
         </is>
       </c>
       <c r="D40" s="26" t="inlineStr"/>
@@ -2180,17 +2164,17 @@
     <row r="41">
       <c r="A41" s="23" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>iRECIST confirmation window, where iRECIST applies</t>
+          <t>Minimum duration for stable disease</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Efficacy assessments section</t>
+          <t>Statistical section — endpoint definitions</t>
         </is>
       </c>
       <c r="D41" s="24" t="inlineStr"/>
@@ -2200,17 +2184,17 @@
     <row r="42">
       <c r="A42" s="25" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="B42" s="22" t="inlineStr">
         <is>
-          <t>New measurable lesion limits under iRECIST, total and per organ</t>
+          <t>Assessment schedule per visit, with the permitted window each side</t>
         </is>
       </c>
       <c r="C42" s="22" t="inlineStr">
         <is>
-          <t>Efficacy assessments section</t>
+          <t>Schedule of assessments table</t>
         </is>
       </c>
       <c r="D42" s="26" t="inlineStr"/>
@@ -2220,17 +2204,17 @@
     <row r="43">
       <c r="A43" s="23" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>Whether tumor markers contribute to a complete response</t>
+          <t>iRECIST confirmation window, where iRECIST applies</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Efficacy assessments; laboratory section</t>
+          <t>Efficacy assessments section</t>
         </is>
       </c>
       <c r="D43" s="24" t="inlineStr"/>
@@ -2240,17 +2224,17 @@
     <row r="44">
       <c r="A44" s="25" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="B44" s="22" t="inlineStr">
         <is>
-          <t>Permitted imaging modalities</t>
+          <t>New measurable lesion limits under iRECIST, total and per organ</t>
         </is>
       </c>
       <c r="C44" s="22" t="inlineStr">
         <is>
-          <t>Imaging charter or imaging manual</t>
+          <t>Efficacy assessments section</t>
         </is>
       </c>
       <c r="D44" s="26" t="inlineStr"/>
@@ -2260,17 +2244,17 @@
     <row r="45">
       <c r="A45" s="23" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>Disease-site imaging the protocol requires — brain, for example</t>
+          <t>Whether tumor markers contribute to a complete response</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Imaging charter; eligibility criteria</t>
+          <t>Efficacy assessments; laboratory section</t>
         </is>
       </c>
       <c r="D45" s="24" t="inlineStr"/>
@@ -2280,17 +2264,17 @@
     <row r="46">
       <c r="A46" s="25" t="inlineStr">
         <is>
-          <t>P14</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="B46" s="22" t="inlineStr">
         <is>
-          <t>Whether independent central review is collected</t>
+          <t>Permitted imaging modalities</t>
         </is>
       </c>
       <c r="C46" s="22" t="inlineStr">
         <is>
-          <t>BICR charter; efficacy assessments</t>
+          <t>Imaging charter or imaging manual</t>
         </is>
       </c>
       <c r="D46" s="26" t="inlineStr"/>
@@ -2300,17 +2284,17 @@
     <row r="47">
       <c r="A47" s="23" t="inlineStr">
         <is>
-          <t>P15</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>Reappearance of a resolved lesion — progression, or back into the sum (ID-01)</t>
+          <t>Disease-site imaging the protocol requires — brain, for example</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Tumor assessment section, often absent</t>
+          <t>Imaging charter; eligibility criteria</t>
         </is>
       </c>
       <c r="D47" s="24" t="inlineStr"/>
@@ -2320,17 +2304,17 @@
     <row r="48">
       <c r="A48" s="25" t="inlineStr">
         <is>
-          <t>P16</t>
+          <t>P14</t>
         </is>
       </c>
       <c r="B48" s="22" t="inlineStr">
         <is>
-          <t>Too-small-to-measure convention (ID-02)</t>
+          <t>Whether independent central review is collected</t>
         </is>
       </c>
       <c r="C48" s="22" t="inlineStr">
         <is>
-          <t>Imaging charter, often absent</t>
+          <t>BICR charter; efficacy assessments</t>
         </is>
       </c>
       <c r="D48" s="26" t="inlineStr"/>
@@ -2340,17 +2324,17 @@
     <row r="49">
       <c r="A49" s="23" t="inlineStr">
         <is>
-          <t>P17</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>What counts as baseline (ID-06)</t>
+          <t>Reappearance of a resolved lesion — progression, or back into the sum (ID-01)</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Schedule of assessments; CRF design</t>
+          <t>Tumor assessment section, often absent</t>
         </is>
       </c>
       <c r="D49" s="24" t="inlineStr"/>
@@ -2360,97 +2344,149 @@
     <row r="50">
       <c r="A50" s="25" t="inlineStr">
         <is>
-          <t>P18</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="B50" s="22" t="inlineStr">
         <is>
-          <t>Treatment beyond progression — permitted, and what must be documented</t>
+          <t>Too-small-to-measure convention (ID-02)</t>
         </is>
       </c>
       <c r="C50" s="22" t="inlineStr">
         <is>
-          <t>Treatment section</t>
+          <t>Imaging charter, often absent</t>
         </is>
       </c>
       <c r="D50" s="26" t="inlineStr"/>
       <c r="E50" s="26" t="inlineStr"/>
       <c r="F50" s="26" t="inlineStr"/>
     </row>
-    <row r="52" ht="48" customHeight="1">
-      <c r="A52" s="30" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="23" t="inlineStr">
+        <is>
+          <t>P17</t>
+        </is>
+      </c>
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t>What counts as baseline (ID-06)</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>Schedule of assessments; CRF design</t>
+        </is>
+      </c>
+      <c r="D51" s="24" t="inlineStr"/>
+      <c r="E51" s="24" t="inlineStr"/>
+      <c r="F51" s="24" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="25" t="inlineStr">
+        <is>
+          <t>P18</t>
+        </is>
+      </c>
+      <c r="B52" s="22" t="inlineStr">
+        <is>
+          <t>Treatment beyond progression — permitted, and what must be documented</t>
+        </is>
+      </c>
+      <c r="C52" s="22" t="inlineStr">
+        <is>
+          <t>Treatment section</t>
+        </is>
+      </c>
+      <c r="D52" s="26" t="inlineStr"/>
+      <c r="E52" s="26" t="inlineStr"/>
+      <c r="F52" s="26" t="inlineStr"/>
+    </row>
+    <row r="54" ht="48" customHeight="1">
+      <c r="A54" s="30" t="inlineStr">
         <is>
           <t>Note on P15 to P17</t>
         </is>
       </c>
-      <c r="B52" s="7" t="inlineStr">
+      <c r="B54" s="7" t="inlineStr">
         <is>
           <t>These three are routinely absent from protocols altogether — they are the interpretation decisions, which is why they exist as ID-01, ID-02 and ID-06 with stated defaults. Expect the extract not to contain them, and expect AC-11 to mark them defaulted. That is correct behaviour, not a gap in the extract.</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="48" customHeight="1">
-      <c r="A53" s="30" t="inlineStr">
+    <row r="55" ht="48" customHeight="1">
+      <c r="A55" s="30" t="inlineStr">
         <is>
           <t>Sizing</t>
         </is>
       </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>An extract covering P1 to P18 is a few pages, not a hundred. Whatever the context limit turns out to be, it will fit — which is why this mitigation makes B2 stop mattering rather than merely deferring it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>A summary covering P1 to P18 is a few pages, not a hundred. Whatever the context limit turns out to be, it will fit — which is why this makes B2 stop mattering rather than merely deferring it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="48" customHeight="1">
+      <c r="A56" s="30" t="inlineStr">
+        <is>
+          <t>What the run must record</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>The summary is configuration input, so the run provenance carries its identity: file name, a content hash, the preparer and the date. A protocol configuration that cannot be traced back to the exact document it came from is not reproducible, and reproducing a historical run is the point of the provenance stamp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>How to read this list</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="42" customHeight="1">
-      <c r="A56" s="30" t="inlineStr">
-        <is>
-          <t>Deferred</t>
-        </is>
-      </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>B2 — cannot be tested now, carried as a checkpoint, and mitigated by the protocol extract above. Nothing on this list blocks Step 3.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="42" customHeight="1">
-      <c r="A57" s="30" t="inlineStr">
-        <is>
-          <t>Materially affects the build</t>
-        </is>
-      </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>A1, A2, B1, B3, B4, D1, E1 — adapter strategy, budget enforcement, provenance honesty and run sizing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="42" customHeight="1">
-      <c r="A58" s="30" t="inlineStr">
-        <is>
-          <t>Good to know, not blocking</t>
-        </is>
-      </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>C1, C2, E2, E3 — narrative quality and reproducibility. Verdicts do not depend on any of them, because verdicts are not produced by the model.</t>
         </is>
       </c>
     </row>
     <row r="59" ht="42" customHeight="1">
       <c r="A59" s="30" t="inlineStr">
         <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>B2 — cannot be tested now, carried as a checkpoint, and mitigated by the protocol extract above. Nothing on this list blocks Step 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="42" customHeight="1">
+      <c r="A60" s="30" t="inlineStr">
+        <is>
+          <t>Materially affects the build</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>A1, A2, B1, B3, B4, D1, E1 — adapter strategy, budget enforcement, provenance honesty and run sizing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="42" customHeight="1">
+      <c r="A61" s="30" t="inlineStr">
+        <is>
+          <t>Good to know, not blocking</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>C1, C2, E2, E3 — narrative quality and reproducibility. Verdicts do not depend on any of them, because verdicts are not produced by the model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="42" customHeight="1">
+      <c r="A62" s="30" t="inlineStr">
+        <is>
           <t>Needed for the validation package</t>
         </is>
       </c>
-      <c r="B59" s="7" t="inlineStr">
+      <c r="B62" s="7" t="inlineStr">
         <is>
           <t>D2, D3, F1, F2, F3, G1, G2 — mostly answerable by the platform team in one conversation.</t>
         </is>
@@ -2458,20 +2494,23 @@
     </row>
   </sheetData>
   <autoFilter ref="A3:F23"/>
-  <mergeCells count="13">
-    <mergeCell ref="B53:F53"/>
+  <mergeCells count="16">
+    <mergeCell ref="B30:F30"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="B56:F56"/>
     <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B55:F55"/>
+    <mergeCell ref="B54:F54"/>
+    <mergeCell ref="B62:F62"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B25:F25"/>
     <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B58:F58"/>
     <mergeCell ref="B59:F59"/>
+    <mergeCell ref="B60:F60"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B61:F61"/>
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B52:F52"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3334,7 +3373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3697,36 +3736,63 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>protocol_summary</t>
+        </is>
+      </c>
+      <c r="B16" s="62" t="inlineStr">
+        <is>
+          <t>document_text, source_document_id, content_hash, prepared_by, prepared_date</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>NEW v2.4.0. The condensed protocol prepared by the study data manager against the rule agreed with the Medical Monitor (OI-07). Input to AC-11 in place of the full protocol. Its hash enters the run provenance, so a protocol configuration is always traceable to the exact document it came from.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>Ingestion rules</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>•  Units normalised to millimetres; original value and unit retained for evidence display.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>•  Lesion identity is (subject_id, lesion_link_id). Missing or duplicated link ids are structural findings, not silent failures.</t>
+          <t>•  Units normalised to millimetres; original value and unit retained for evidence display.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>•  Assessments group per (subject, visit, evaluator). Each evaluator stream derives independently.</t>
+          <t>•  Lesion identity is (subject_id, lesion_link_id). Missing or duplicated link ids are structural findings, not silent failures.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>•  Assessments group per (subject, visit, evaluator). Each evaluator stream derives independently.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>•  Dates are ISO-8601; partial dates stay partial and rules needing full precision declare themselves not evaluable for that record.</t>
         </is>
@@ -5353,7 +5419,7 @@
         </is>
       </c>
       <c r="C16" s="16">
-        <f>COUNTA(Input_Contract!B4:B15)</f>
+        <f>COUNTA(Input_Contract!B4:B16)</f>
         <v/>
       </c>
       <c r="D16" s="14" t="inlineStr"/>
@@ -10255,7 +10321,7 @@
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>NEW at review (AC-11). Reads the protocol and imaging charter, summarises the parameter checkpoints the rule pack depends on, and captures the user's confirmation. Runs once per study, before any review run.</t>
+          <t>AMENDED v2.4.0 (AC-11). Reads the protocol SUMMARY prepared by the study data manager, not the full protocol, and summarises the parameter checkpoints the rule pack depends on, and captures the user's confirmation. Runs once per study, before any review run.</t>
         </is>
       </c>
     </row>

--- a/docs/spec/TEA-SPEC-001_programming-specification.xlsx
+++ b/docs/spec/TEA-SPEC-001_programming-specification.xlsx
@@ -18,25 +18,27 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rule_Messages" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Approval" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GLM_Verification" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Query_Style" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Confidence_Model" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Query_Reconciliation" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prioritisation" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Input_Contract" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Finding_Contract" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LLM_Integration" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Testing" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Extensibility" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Log" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SDTM_Requirements" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Query_Style" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Confidence_Model" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Query_Reconciliation" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prioritisation" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Input_Contract" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Finding_Contract" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LLM_Integration" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Testing" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Extensibility" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Log" sheetId="25" state="visible" r:id="rId25"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Definitions'!$A$3:$C$50</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Rules'!$A$3:$U$88</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Rule_Messages'!$A$3:$J$88</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'GLM_Verification'!$A$3:$F$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'SDTM_Requirements'!$A$3:$F$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -45,7 +47,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -177,6 +179,12 @@
     </font>
     <font>
       <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="005C665F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <color rgb="006B7770"/>
       <sz val="9"/>
     </font>
@@ -250,7 +258,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -277,10 +285,10 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -414,15 +422,21 @@
     <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -842,7 +856,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>2.4.0 — APPROVED, protocol summary as a named input</t>
+          <t>2.5.0 — APPROVED, SDTM input requirements</t>
         </is>
       </c>
     </row>
@@ -890,7 +904,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>v2.3.0, issued 2026-08-22</t>
+          <t>v2.4.0, issued 2026-08-22</t>
         </is>
       </c>
     </row>
@@ -2522,6 +2536,1766 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G65"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="116" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>SDTM input requirements</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>TEA-CTR-003. What the agent needs from an SDTM delivery, derived from what the 83 live rules actually consume. R = required, the agent cannot run without it. C = conditional, named rules deactivate and report NOT_EVALUATED. O = optional, improves a finding but nothing depends on it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>R/C/O</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>Content the agent expects</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>Rules that depend on it</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>If absent</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="23" t="inlineStr">
+        <is>
+          <t>TU</t>
+        </is>
+      </c>
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>USUBJID</t>
+        </is>
+      </c>
+      <c r="C4" s="38" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>Subject identifier, consistent across every domain.</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>Cannot run.</t>
+        </is>
+      </c>
+      <c r="G4" s="24" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>TU</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>TULNKID</t>
+        </is>
+      </c>
+      <c r="C5" s="61" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>The lesion's permanent identity. Assigned ONCE when the lesion is first identified and repeated unchanged at every later visit. This is the single most important variable in the delivery.</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>all lesion-level rules — 60+</t>
+        </is>
+      </c>
+      <c r="F5" s="22" t="inlineStr">
+        <is>
+          <t>Cannot run. Lesion history collapses and nothing downstream is meaningful.</t>
+        </is>
+      </c>
+      <c r="G5" s="26" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>TU</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>TUTESTCD / TUTEST</t>
+        </is>
+      </c>
+      <c r="C6" s="38" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>TUMIDENT / Tumor Identification.</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>Cannot run.</t>
+        </is>
+      </c>
+      <c r="G6" s="24" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="25" t="inlineStr">
+        <is>
+          <t>TU</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>TUORRES</t>
+        </is>
+      </c>
+      <c r="C7" s="61" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>As collected: TARGET, NON-TARGET, NEW.</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>Cannot run.</t>
+        </is>
+      </c>
+      <c r="G7" s="26" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>TU</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>TUSTRESC</t>
+        </is>
+      </c>
+      <c r="C8" s="38" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>Standardised to exactly TARGET, NON-TARGET, NEW. One vocabulary across the whole study.</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>Cannot run.</t>
+        </is>
+      </c>
+      <c r="G8" s="24" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>TU</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>TULOC</t>
+        </is>
+      </c>
+      <c r="C9" s="61" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>Anatomical location, coded. Drives the per-organ target limit.</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>TE-BL-002, TE-BL-016, TE-ST-002, TE-IR-006</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>TE-BL-002 and TE-IR-006 deactivate — the per-organ limits cannot be evaluated.</t>
+        </is>
+      </c>
+      <c r="G9" s="26" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>TU</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>TULAT</t>
+        </is>
+      </c>
+      <c r="C10" s="31" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>Laterality where the organ is paired.</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>TE-ST-002, TE-BL-016</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>Duplicate-lesion detection weakens: left and right lesions in a paired organ look identical.</t>
+        </is>
+      </c>
+      <c r="G10" s="24" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="25" t="inlineStr">
+        <is>
+          <t>TU</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>TUMETHOD</t>
+        </is>
+      </c>
+      <c r="C11" s="27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>Imaging method used to identify the lesion: CT, MRI, PET-CT, X-RAY, CLINICAL EXAM, ULTRASOUND.</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>TE-BL-003, TE-BL-014, TE-XD-008</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>TE-XD-008 deactivates; measurability thresholds fall back to the CT/MRI default, which is wrong for chest X-ray and clinical exam.</t>
+        </is>
+      </c>
+      <c r="G11" s="26" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>TU</t>
+        </is>
+      </c>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>TUEVAL</t>
+        </is>
+      </c>
+      <c r="C12" s="31" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>INVESTIGATOR or INDEPENDENT ASSESSOR. Required if central review is collected.</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>TE-RS-020</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>Investigator and BICR records merge into one stream and the agent double-counts every lesion. If BICR exists, this is effectively R.</t>
+        </is>
+      </c>
+      <c r="G12" s="24" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="25" t="inlineStr">
+        <is>
+          <t>TU</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>TUDTC</t>
+        </is>
+      </c>
+      <c r="C13" s="61" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>Date the lesion was identified.</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>TE-FU-012, progression dating</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>TE-FU-012 deactivates; new-lesion dating becomes unreliable.</t>
+        </is>
+      </c>
+      <c r="G13" s="26" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>TU</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>VISIT / VISITNUM</t>
+        </is>
+      </c>
+      <c r="C14" s="38" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>Visit name and number, consistent with TR and RS.</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>assessment grouping</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>Cannot run.</t>
+        </is>
+      </c>
+      <c r="G14" s="24" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="25" t="inlineStr">
+        <is>
+          <t>TU</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>EPOCH</t>
+        </is>
+      </c>
+      <c r="C15" s="27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>SCREENING / TREATMENT / FOLLOW-UP. This is how baseline is identified — see ID-06.</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>baseline identification</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>Baseline falls back to the date rule relative to first dose. Workable but less reliable, and ID-06 chose the form-based definition deliberately.</t>
+        </is>
+      </c>
+      <c r="G15" s="26" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>TU</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>TUACPTFL</t>
+        </is>
+      </c>
+      <c r="C16" s="31" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>Accepted record flag, where more than one reader contributes.</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>all, if multiple readers</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>Duplicate readings are all treated as real, inflating lesion counts and the sum.</t>
+        </is>
+      </c>
+      <c r="G16" s="24" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="25" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>TRLNKID</t>
+        </is>
+      </c>
+      <c r="C17" s="61" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>Must match TULNKID exactly. This is the join.</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>all measurement rules</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>Cannot run.</t>
+        </is>
+      </c>
+      <c r="G17" s="26" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="23" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>TRTESTCD</t>
+        </is>
+      </c>
+      <c r="C18" s="38" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>LDIAM for non-nodal lesions, SAXIS for nodes, plus TUMSTATE for state. Choosing the right code per lesion type is the conversion decision that matters most.</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>TE-ST-003, TE-BL-004, TE-BL-005, TE-RS-006, TE-FU-009</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>Cannot run. A node measured as LDIAM silently breaks every nodal threshold.</t>
+        </is>
+      </c>
+      <c r="G18" s="24" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="25" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>TRORRES / TRORRESU</t>
+        </is>
+      </c>
+      <c r="C19" s="61" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>The value as collected, with its original unit.</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>TE-ST-004</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>Cannot run. Keep the original unit even after standardising — TE-ST-004 detects cm/mm confusion by comparing the two.</t>
+        </is>
+      </c>
+      <c r="G19" s="26" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="23" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>TRSTRESN / TRSTRESU</t>
+        </is>
+      </c>
+      <c r="C20" s="38" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>Numeric result standardised to MILLIMETER. Every derivation works in mm.</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>all numeric rules</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>Cannot run.</t>
+        </is>
+      </c>
+      <c r="G20" s="24" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="25" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>TRSTAT</t>
+        </is>
+      </c>
+      <c r="C21" s="61" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>NOT DONE where a planned measurement was not taken. A missing ROW is not the same as a recorded NOT DONE, and the agent must be able to tell them apart.</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>TE-FU-002, TE-FU-003, TE-FU-010</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>TE-FU-002 cannot distinguish a genuine omission from an intentional non-assessment, and will query both.</t>
+        </is>
+      </c>
+      <c r="G21" s="26" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="23" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>TRREASND</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>Reason not done, free text or coded.</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>TE-FU-002</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>Every not-done becomes a query rather than only the unexplained ones.</t>
+        </is>
+      </c>
+      <c r="G22" s="24" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="25" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>TUMSTATE result</t>
+        </is>
+      </c>
+      <c r="C23" s="61" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>Carried as TRTESTCD=TUMSTATE with TRSTRESC in PRESENT, ABSENT, TOO SMALL TO MEASURE, NOT EVALUABLE. This carries the non-target assessment and the disappearance of a lesion.</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>TE-FU-005, TE-FU-009, TE-FU-010, TE-RS-004, TE-RS-006, ID-01, ID-02</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>Non-target rules deactivate; complete-response checks cannot confirm lesion disappearance.</t>
+        </is>
+      </c>
+      <c r="G23" s="26" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="23" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="B24" s="18" t="inlineStr">
+        <is>
+          <t>TREVAL / TREVALID</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>Evaluator, matching TUEVAL. Required if BICR is collected.</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>TE-RS-020</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>As TUEVAL — streams merge and results are wrong rather than merely absent.</t>
+        </is>
+      </c>
+      <c r="G24" s="24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="25" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>TRDTC</t>
+        </is>
+      </c>
+      <c r="C25" s="61" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>Assessment date. The agent orders timepoints by this, not by VISITNUM.</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>all temporal rules</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
+        <is>
+          <t>Cannot run.</t>
+        </is>
+      </c>
+      <c r="G25" s="26" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="23" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="B26" s="18" t="inlineStr">
+        <is>
+          <t>TRACPTFL</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>As TUACPTFL.</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>all, if multiple readers</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>As TUACPTFL.</t>
+        </is>
+      </c>
+      <c r="G26" s="24" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="25" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>RSTESTCD</t>
+        </is>
+      </c>
+      <c r="C27" s="61" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>TRGRESP, NTRGRESP, NEWLPROG, OVRLRESP, BESTRESP. All five, at every assessment where collected.</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>TE-RS family — 19 rules</t>
+        </is>
+      </c>
+      <c r="F27" s="22" t="inlineStr">
+        <is>
+          <t>Cannot run. These are the values the agent compares its derivation against.</t>
+        </is>
+      </c>
+      <c r="G27" s="26" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="23" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="B28" s="18" t="inlineStr">
+        <is>
+          <t>RSORRES / RSSTRESC</t>
+        </is>
+      </c>
+      <c r="C28" s="38" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>CR, PR, SD, PD, NE, NON-CR/NON-PD. Standardised to one vocabulary. iRECIST values iCR, iPR, iSD, iUPD, iCPD where applicable.</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>TE-RS and TE-IR families</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>Cannot run.</t>
+        </is>
+      </c>
+      <c r="G28" s="24" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>RSCAT</t>
+        </is>
+      </c>
+      <c r="C29" s="61" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="inlineStr">
+        <is>
+          <t>The criteria the row was assessed under: RECIST 1.1 or iRECIST. This is how the agent tells the two response sets apart when both are collected in parallel.</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>TE-IR-001, TE-IR-009, TE-IR-010</t>
+        </is>
+      </c>
+      <c r="F29" s="22" t="inlineStr">
+        <is>
+          <t>The iRECIST family deactivates entirely — 10 rules. With both sets collected and no RSCAT, the agent cannot tell which row is which and would compare incomparable values.</t>
+        </is>
+      </c>
+      <c r="G29" s="26" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="23" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="B30" s="18" t="inlineStr">
+        <is>
+          <t>RSEVAL / RSEVALID</t>
+        </is>
+      </c>
+      <c r="C30" s="31" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>As TREVAL.</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t>TE-RS-020</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="inlineStr">
+        <is>
+          <t>As TREVAL.</t>
+        </is>
+      </c>
+      <c r="G30" s="24" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>RSDTC</t>
+        </is>
+      </c>
+      <c r="C31" s="61" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
+        <is>
+          <t>Assessment date, consistent with TRDTC for the same timepoint.</t>
+        </is>
+      </c>
+      <c r="E31" s="22" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="F31" s="22" t="inlineStr">
+        <is>
+          <t>Cannot run.</t>
+        </is>
+      </c>
+      <c r="G31" s="26" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="23" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="B32" s="18" t="inlineStr">
+        <is>
+          <t>RSSTAT / RSREASND</t>
+        </is>
+      </c>
+      <c r="C32" s="31" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>NOT DONE and its reason.</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>TE-FU-003, TE-XD-011</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>Unevaluable timepoints look like missing ones.</t>
+        </is>
+      </c>
+      <c r="G32" s="24" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>DM</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
+        <is>
+          <t>USUBJID, SITEID</t>
+        </is>
+      </c>
+      <c r="C33" s="61" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D33" s="22" t="inlineStr">
+        <is>
+          <t>Subject and site. SITEID drives the site-level pattern rule.</t>
+        </is>
+      </c>
+      <c r="E33" s="22" t="inlineStr">
+        <is>
+          <t>all, TE-XD-012</t>
+        </is>
+      </c>
+      <c r="F33" s="22" t="inlineStr">
+        <is>
+          <t>Cannot run without USUBJID; TE-XD-012 deactivates without SITEID.</t>
+        </is>
+      </c>
+      <c r="G33" s="26" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="23" t="inlineStr">
+        <is>
+          <t>DM</t>
+        </is>
+      </c>
+      <c r="B34" s="18" t="inlineStr">
+        <is>
+          <t>RFXSTDTC</t>
+        </is>
+      </c>
+      <c r="C34" s="38" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>First dose date. Baseline window and study-day arithmetic depend on it.</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="inlineStr">
+        <is>
+          <t>TE-BL-010, TE-XD-011</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="inlineStr">
+        <is>
+          <t>TE-BL-010 deactivates.</t>
+        </is>
+      </c>
+      <c r="G34" s="24" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>DM</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr">
+        <is>
+          <t>RFXENDTC</t>
+        </is>
+      </c>
+      <c r="C35" s="27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D35" s="22" t="inlineStr">
+        <is>
+          <t>Last dose date.</t>
+        </is>
+      </c>
+      <c r="E35" s="22" t="inlineStr">
+        <is>
+          <t>TE-XD-002, TE-FU-008</t>
+        </is>
+      </c>
+      <c r="F35" s="22" t="inlineStr">
+        <is>
+          <t>Treatment-continuation rules deactivate.</t>
+        </is>
+      </c>
+      <c r="G35" s="26" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="23" t="inlineStr">
+        <is>
+          <t>DM</t>
+        </is>
+      </c>
+      <c r="B36" s="18" t="inlineStr">
+        <is>
+          <t>DTHDTC / DTHFL</t>
+        </is>
+      </c>
+      <c r="C36" s="31" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>Death date and flag.</t>
+        </is>
+      </c>
+      <c r="E36" s="12" t="inlineStr">
+        <is>
+          <t>TE-XD-006, TE-FU-011, TE-XD-005</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="inlineStr">
+        <is>
+          <t>Assessments after death go undetected — a CRITICAL rule lost.</t>
+        </is>
+      </c>
+      <c r="G36" s="24" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="25" t="inlineStr">
+        <is>
+          <t>EX</t>
+        </is>
+      </c>
+      <c r="B37" s="20" t="inlineStr">
+        <is>
+          <t>EXSTDTC, EXENDTC, EXTRT, EXDOSE</t>
+        </is>
+      </c>
+      <c r="C37" s="27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D37" s="22" t="inlineStr">
+        <is>
+          <t>Study drug administration records.</t>
+        </is>
+      </c>
+      <c r="E37" s="22" t="inlineStr">
+        <is>
+          <t>TE-XD-002</t>
+        </is>
+      </c>
+      <c r="F37" s="22" t="inlineStr">
+        <is>
+          <t>Treatment beyond progression cannot be assessed.</t>
+        </is>
+      </c>
+      <c r="G37" s="26" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="23" t="inlineStr">
+        <is>
+          <t>DS</t>
+        </is>
+      </c>
+      <c r="B38" s="18" t="inlineStr">
+        <is>
+          <t>DSCAT, DSDECOD, DSSTDTC</t>
+        </is>
+      </c>
+      <c r="C38" s="31" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>Disposition events. DSDECOD carries the discontinuation reason, including progressive disease.</t>
+        </is>
+      </c>
+      <c r="E38" s="12" t="inlineStr">
+        <is>
+          <t>TE-XD-001</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>The strongest cross-domain check is lost: end of treatment for PD with no PD in the tumor data.</t>
+        </is>
+      </c>
+      <c r="G38" s="24" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="25" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="inlineStr">
+        <is>
+          <t>AEDECOD, AESTDTC, AEOUT</t>
+        </is>
+      </c>
+      <c r="C39" s="27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D39" s="22" t="inlineStr">
+        <is>
+          <t>Coded adverse events. Terms mapping to disease progression are the trigger.</t>
+        </is>
+      </c>
+      <c r="E39" s="22" t="inlineStr">
+        <is>
+          <t>TE-XD-005</t>
+        </is>
+      </c>
+      <c r="F39" s="22" t="inlineStr">
+        <is>
+          <t>Deactivates.</t>
+        </is>
+      </c>
+      <c r="G39" s="26" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="23" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="B40" s="18" t="inlineStr">
+        <is>
+          <t>CMDECOD, CMSTDTC, CMINDC, CMCAT</t>
+        </is>
+      </c>
+      <c r="C40" s="31" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>Concomitant and subsequent therapy. Needs enough detail to tell a systemic anticancer therapy from supportive care.</t>
+        </is>
+      </c>
+      <c r="E40" s="12" t="inlineStr">
+        <is>
+          <t>TE-XD-003</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="inlineStr">
+        <is>
+          <t>Deactivates. Note the amended guard needs the permitted-therapy list from the protocol summary, not from CM alone.</t>
+        </is>
+      </c>
+      <c r="G40" s="24" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="25" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="inlineStr">
+        <is>
+          <t>PRTRT, PRSTDTC, PRLOC</t>
+        </is>
+      </c>
+      <c r="C41" s="27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D41" s="22" t="inlineStr">
+        <is>
+          <t>Procedures — radiotherapy, surgery, ablation. PRLOC must be specific enough to match a lesion site.</t>
+        </is>
+      </c>
+      <c r="E41" s="22" t="inlineStr">
+        <is>
+          <t>TE-XD-004</t>
+        </is>
+      </c>
+      <c r="F41" s="22" t="inlineStr">
+        <is>
+          <t>Deactivates. Without PRLOC it fires on every procedure regardless of site, which is worse than deactivating.</t>
+        </is>
+      </c>
+      <c r="G41" s="26" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="23" t="inlineStr">
+        <is>
+          <t>LB</t>
+        </is>
+      </c>
+      <c r="B42" s="18" t="inlineStr">
+        <is>
+          <t>LBTESTCD, LBSTRESN, LBSTNRHI, LBDTC</t>
+        </is>
+      </c>
+      <c r="C42" s="31" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t>Tumor markers with their upper limit of normal.</t>
+        </is>
+      </c>
+      <c r="E42" s="12" t="inlineStr">
+        <is>
+          <t>TE-XD-007</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="inlineStr">
+        <is>
+          <t>Deactivates.</t>
+        </is>
+      </c>
+      <c r="G42" s="24" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="56" t="inlineStr">
+        <is>
+          <t>QUERY*</t>
+        </is>
+      </c>
+      <c r="B43" s="62" t="inlineStr">
+        <is>
+          <t>query_id, subject, form, field, text, answer, status, opened/answered/closed dates</t>
+        </is>
+      </c>
+      <c r="C43" s="60" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D43" s="33" t="inlineStr">
+        <is>
+          <t>NOT AN SDTM DOMAIN. A flat file alongside the delivery. SDTM has no home for query history.</t>
+        </is>
+      </c>
+      <c r="E43" s="33" t="inlineStr">
+        <is>
+          <t>TE-QM-001, 002, 004, 005, 006 and the whole of AC-06</t>
+        </is>
+      </c>
+      <c r="F43" s="33" t="inlineStr">
+        <is>
+          <t>5 rules deactivate AND query reconciliation stops working, so every finding is re-raised at every data cut — the behaviour OBJ-04 exists to prevent. This is the largest single gap in an SDTM-only delivery.</t>
+        </is>
+      </c>
+      <c r="G43" s="26" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="56" t="inlineStr">
+        <is>
+          <t>IMG*</t>
+        </is>
+      </c>
+      <c r="B44" s="62" t="inlineStr">
+        <is>
+          <t>lesion, visit, slice_thickness_mm, contrast, regions_imaged</t>
+        </is>
+      </c>
+      <c r="C44" s="63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D44" s="33" t="inlineStr">
+        <is>
+          <t>NOT STANDARD SDTM. Supply as a supplementary file if available.</t>
+        </is>
+      </c>
+      <c r="E44" s="33" t="inlineStr">
+        <is>
+          <t>TE-BL-006, TE-BL-014</t>
+        </is>
+      </c>
+      <c r="F44" s="33" t="inlineStr">
+        <is>
+          <t>Two rules deactivate. Acceptable — do not hold up a delivery for this.</t>
+        </is>
+      </c>
+      <c r="G44" s="24" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="56" t="inlineStr">
+        <is>
+          <t>PROT*</t>
+        </is>
+      </c>
+      <c r="B45" s="62" t="inlineStr">
+        <is>
+          <t>The protocol summary (P1-P18)</t>
+        </is>
+      </c>
+      <c r="C45" s="60" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D45" s="33" t="inlineStr">
+        <is>
+          <t>Not SDTM. Prepared by hand per OI-07 and imported by the caller.</t>
+        </is>
+      </c>
+      <c r="E45" s="33" t="inlineStr">
+        <is>
+          <t>AC-11, every threshold</t>
+        </is>
+      </c>
+      <c r="F45" s="33" t="inlineStr">
+        <is>
+          <t>The agent runs on guideline defaults and may silently use a threshold the protocol never specified.</t>
+        </is>
+      </c>
+      <c r="G45" s="26" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Ten things a conversion gets wrong</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>Trap</t>
+        </is>
+      </c>
+      <c r="C48" s="10" t="inlineStr">
+        <is>
+          <t>Why it matters</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr"/>
+      <c r="E48" s="10" t="inlineStr"/>
+      <c r="F48" s="10" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B49" s="12" t="inlineStr">
+        <is>
+          <t>TULNKID re-issued at every visit instead of once per lesion.</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>The commonest and most destructive error. Lesion history fragments into one-visit lesions: no nadir, no percent change, no response. Test it first — count distinct TULNKID per subject and compare against the number of lesions the site actually recorded.</t>
+        </is>
+      </c>
+      <c r="D49" s="24" t="inlineStr"/>
+      <c r="E49" s="24" t="inlineStr"/>
+      <c r="F49" s="24" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B50" s="22" t="inlineStr">
+        <is>
+          <t>Nodal lesions given TRTESTCD=LDIAM rather than SAXIS.</t>
+        </is>
+      </c>
+      <c r="C50" s="22" t="inlineStr">
+        <is>
+          <t>Silent. Every nodal threshold then compares the wrong axis, and a 12 mm node looks measurable when its short axis is 8 mm. The conversion must branch on lesion type, which means lesion type has to be known at TR time.</t>
+        </is>
+      </c>
+      <c r="D50" s="26" t="inlineStr"/>
+      <c r="E50" s="26" t="inlineStr"/>
+      <c r="F50" s="26" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t>Missing rows used where TRSTAT='NOT DONE' belongs.</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>A missing row means 'we do not know'. A NOT DONE row means 'we know it was not measured, and why'. The agent treats them differently and will query the first.</t>
+        </is>
+      </c>
+      <c r="D51" s="24" t="inlineStr"/>
+      <c r="E51" s="24" t="inlineStr"/>
+      <c r="F51" s="24" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B52" s="22" t="inlineStr">
+        <is>
+          <t>Original units dropped after standardising to mm.</t>
+        </is>
+      </c>
+      <c r="C52" s="22" t="inlineStr">
+        <is>
+          <t>TRORRESU is what lets TE-ST-004 catch a cm value entered in a mm field. Standardise TRSTRESN, but keep TRORRES and TRORRESU as collected.</t>
+        </is>
+      </c>
+      <c r="D52" s="26" t="inlineStr"/>
+      <c r="E52" s="26" t="inlineStr"/>
+      <c r="F52" s="26" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B53" s="12" t="inlineStr">
+        <is>
+          <t>RSCAT omitted when both RECIST 1.1 and iRECIST are collected.</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>The two response sets become indistinguishable. Ten iRECIST rules deactivate, and worse, the agent may compare a RECIST 1.1 value against an iRECIST expectation.</t>
+        </is>
+      </c>
+      <c r="D53" s="24" t="inlineStr"/>
+      <c r="E53" s="24" t="inlineStr"/>
+      <c r="F53" s="24" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B54" s="22" t="inlineStr">
+        <is>
+          <t>Investigator and central review merged into one stream.</t>
+        </is>
+      </c>
+      <c r="C54" s="22" t="inlineStr">
+        <is>
+          <t>Every lesion and every response is duplicated. This produces wrong answers rather than absent ones, which is the harder failure to notice.</t>
+        </is>
+      </c>
+      <c r="D54" s="26" t="inlineStr"/>
+      <c r="E54" s="26" t="inlineStr"/>
+      <c r="F54" s="26" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="23" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B55" s="12" t="inlineStr">
+        <is>
+          <t>TUMSTATE not carried, so ABSENT and TOO SMALL TO MEASURE are lost.</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="inlineStr">
+        <is>
+          <t>A lesion that disappeared and one that was never measured look the same. Complete response cannot be confirmed, and the ID-01 and ID-02 conventions have nothing to act on.</t>
+        </is>
+      </c>
+      <c r="D55" s="24" t="inlineStr"/>
+      <c r="E55" s="24" t="inlineStr"/>
+      <c r="F55" s="24" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B56" s="22" t="inlineStr">
+        <is>
+          <t>Visit dates taken from the visit definition rather than the actual assessment.</t>
+        </is>
+      </c>
+      <c r="C56" s="22" t="inlineStr">
+        <is>
+          <t>The agent orders timepoints by TRDTC and dates progression from it. A scheduled date instead of an actual one shifts every progression date and biases PFS.</t>
+        </is>
+      </c>
+      <c r="D56" s="26" t="inlineStr"/>
+      <c r="E56" s="26" t="inlineStr"/>
+      <c r="F56" s="26" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="23" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B57" s="12" t="inlineStr">
+        <is>
+          <t>Unscheduled visits given a VISITNUM that reorders the sequence.</t>
+        </is>
+      </c>
+      <c r="C57" s="12" t="inlineStr">
+        <is>
+          <t>Order by date, but keep VISITNUM honest — the assessment-window rule needs to know which visits were scheduled.</t>
+        </is>
+      </c>
+      <c r="D57" s="24" t="inlineStr"/>
+      <c r="E57" s="24" t="inlineStr"/>
+      <c r="F57" s="24" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B58" s="22" t="inlineStr">
+        <is>
+          <t>Derived values recomputed during conversion rather than carried across.</t>
+        </is>
+      </c>
+      <c r="C58" s="22" t="inlineStr">
+        <is>
+          <t>If the conversion recalculates the sum or the response, the agent compares its derivation against the conversion's, not against what the site recorded — and the whole point is lost. Carry RS and any collected sum through unchanged, however wrong they look.</t>
+        </is>
+      </c>
+      <c r="D58" s="26" t="inlineStr"/>
+      <c r="E58" s="26" t="inlineStr"/>
+      <c r="F58" s="26" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>How to use this while the agent is being built</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="48" customHeight="1">
+      <c r="A61" s="30" t="inlineStr">
+        <is>
+          <t>Build the dummy data to this sheet</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>Not to a guess. Every column here is a column the dummy data needs, so the synthetic study and the later conversion target the same contract and the conversion has something real to be checked against.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="48" customHeight="1">
+      <c r="A62" s="30" t="inlineStr">
+        <is>
+          <t>Use the CDISC structures as published</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>TU, TR and RS are defined in the SDTM IG. Use the real variable names and controlled terms rather than inventing shapes — the conversion is then a mapping exercise rather than a translation to a private format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="48" customHeight="1">
+      <c r="A63" s="30" t="inlineStr">
+        <is>
+          <t>Conformance-check before rules run</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>RSK-17. Validate an incoming delivery against this sheet and fail the run on a required-variable violation. A conformance failure is a defect in the delivery, not a finding about the data, and confusing the two is how the agent ends up querying mapping bugs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="48" customHeight="1">
+      <c r="A64" s="30" t="inlineStr">
+        <is>
+          <t>Expect the coverage report to matter more now</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>With SDTM, more rules are conditional than they were against an EDC extract. Every run must state which rules did not evaluate and why, or a reviewer will assume coverage the agent never had.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="48" customHeight="1">
+      <c r="A65" s="30" t="inlineStr">
+        <is>
+          <t>The three starred rows are not SDTM</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>Query history, imaging metadata and the protocol summary travel alongside. The query file is not optional — without it the agent has no memory between data cuts.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:F45"/>
+  <mergeCells count="7">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B63:G63"/>
+    <mergeCell ref="B61:G61"/>
+    <mergeCell ref="B65:G65"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="B62:G62"/>
+    <mergeCell ref="B64:G64"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2840,7 +4614,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2890,9 +4664,9 @@
 # so certainty is never total. A 100% display would invite unread query issuance.</t>
         </is>
       </c>
-      <c r="B4" s="61" t="n"/>
-      <c r="C4" s="61" t="n"/>
-      <c r="D4" s="61" t="n"/>
+      <c r="B4" s="64" t="n"/>
+      <c r="C4" s="64" t="n"/>
+      <c r="D4" s="64" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
@@ -3166,7 +4940,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3231,9 +5005,9 @@
         f.status = RECURRENT</t>
         </is>
       </c>
-      <c r="B4" s="61" t="n"/>
-      <c r="C4" s="61" t="n"/>
-      <c r="D4" s="61" t="n"/>
+      <c r="B4" s="64" t="n"/>
+      <c r="C4" s="64" t="n"/>
+      <c r="D4" s="64" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -3287,7 +5061,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3328,9 +5102,9 @@
 it necessarily causes, so the reviewer fixes the baseline once instead of querying ten visits.</t>
         </is>
       </c>
-      <c r="B4" s="61" t="n"/>
-      <c r="C4" s="61" t="n"/>
-      <c r="D4" s="61" t="n"/>
+      <c r="B4" s="64" t="n"/>
+      <c r="C4" s="64" t="n"/>
+      <c r="D4" s="64" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -3353,9 +5127,9 @@
 where it does rather than having to trust the ordering.</t>
         </is>
       </c>
-      <c r="B7" s="61" t="n"/>
-      <c r="C7" s="61" t="n"/>
-      <c r="D7" s="61" t="n"/>
+      <c r="B7" s="64" t="n"/>
+      <c r="C7" s="64" t="n"/>
+      <c r="D7" s="64" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3367,7 +5141,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3430,7 +5204,7 @@
           <t>study</t>
         </is>
       </c>
-      <c r="B4" s="62" t="inlineStr">
+      <c r="B4" s="65" t="inlineStr">
         <is>
           <t>study_id</t>
         </is>
@@ -3453,7 +5227,7 @@
           <t>study</t>
         </is>
       </c>
-      <c r="B5" s="63" t="inlineStr">
+      <c r="B5" s="66" t="inlineStr">
         <is>
           <t>indication</t>
         </is>
@@ -3480,7 +5254,7 @@
           <t>study</t>
         </is>
       </c>
-      <c r="B6" s="62" t="inlineStr">
+      <c r="B6" s="65" t="inlineStr">
         <is>
           <t>guideline_version</t>
         </is>
@@ -3507,7 +5281,7 @@
           <t>protocol_config</t>
         </is>
       </c>
-      <c r="B7" s="63" t="inlineStr">
+      <c r="B7" s="66" t="inlineStr">
         <is>
           <t>(28 parameters)</t>
         </is>
@@ -3534,7 +5308,7 @@
           <t>subjects</t>
         </is>
       </c>
-      <c r="B8" s="62" t="inlineStr">
+      <c r="B8" s="65" t="inlineStr">
         <is>
           <t>subject_id, site_id, first_dose_date, discontinuation_date, death_date, has_measurable_disease_at_baseline</t>
         </is>
@@ -3557,7 +5331,7 @@
           <t>lesions</t>
         </is>
       </c>
-      <c r="B9" s="63" t="inlineStr">
+      <c r="B9" s="66" t="inlineStr">
         <is>
           <t>lesion_id, category, is_nodal, organ, location_detail, laterality, method, new_lesion_certainty, previously_irradiated</t>
         </is>
@@ -3584,7 +5358,7 @@
           <t>assessments</t>
         </is>
       </c>
-      <c r="B10" s="62" t="inlineStr">
+      <c r="B10" s="65" t="inlineStr">
         <is>
           <t>assessment_id, visit_name, visit_number, assessment_date, scan_dates, is_baseline, evaluator</t>
         </is>
@@ -3607,7 +5381,7 @@
           <t>measurements</t>
         </is>
       </c>
-      <c r="B11" s="63" t="inlineStr">
+      <c r="B11" s="66" t="inlineStr">
         <is>
           <t>assessment_id, lesion_id, value_mm, original_unit, axis_recorded, state, non_target_state, comment_text</t>
         </is>
@@ -3634,7 +5408,7 @@
           <t>reported_responses</t>
         </is>
       </c>
-      <c r="B12" s="62" t="inlineStr">
+      <c r="B12" s="65" t="inlineStr">
         <is>
           <t>target, non_target, new_lesion, overall, irecist, sum_of_diameters_reported, best_overall_response, progression_date</t>
         </is>
@@ -3661,7 +5435,7 @@
           <t>queries</t>
         </is>
       </c>
-      <c r="B13" s="63" t="inlineStr">
+      <c r="B13" s="66" t="inlineStr">
         <is>
           <t>query_id, query_text, answer_text, status, opened/answered/closed dates, tea_rule_id</t>
         </is>
@@ -3688,7 +5462,7 @@
           <t>cross_domain</t>
         </is>
       </c>
-      <c r="B14" s="62" t="inlineStr">
+      <c r="B14" s="65" t="inlineStr">
         <is>
           <t>exposure, anticancer_therapy, radiotherapy, procedures, adverse_events, lab_markers, performance_status</t>
         </is>
@@ -3715,7 +5489,7 @@
           <t>imaging_metadata</t>
         </is>
       </c>
-      <c r="B15" s="63" t="inlineStr">
+      <c r="B15" s="66" t="inlineStr">
         <is>
           <t>modality, scan_date, slice_thickness_mm, regions_imaged, contrast_used</t>
         </is>
@@ -3742,7 +5516,7 @@
           <t>protocol_summary</t>
         </is>
       </c>
-      <c r="B16" s="62" t="inlineStr">
+      <c r="B16" s="65" t="inlineStr">
         <is>
           <t>document_text, source_document_id, content_hash, prepared_by, prepared_date</t>
         </is>
@@ -3807,7 +5581,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4351,7 +6125,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4418,7 +6192,7 @@
           <t>Lesion organ, laterality, location text, description text, method, guideline extract</t>
         </is>
       </c>
-      <c r="D5" s="62" t="inlineStr">
+      <c r="D5" s="65" t="inlineStr">
         <is>
           <t>{is_non_measurable, category, confidence, rationale}</t>
         </is>
@@ -4440,7 +6214,7 @@
           <t>Non-target descriptions at this and the previous timepoint, target response, sum change, guideline extract</t>
         </is>
       </c>
-      <c r="D6" s="63" t="inlineStr">
+      <c r="D6" s="66" t="inlineStr">
         <is>
           <t>{supports_unequivocal, magnitude_comment, confidence, rationale}</t>
         </is>
@@ -4462,7 +6236,7 @@
           <t>Candidate finding summary; historical queries for the subject</t>
         </is>
       </c>
-      <c r="D7" s="62" t="inlineStr">
+      <c r="D7" s="65" t="inlineStr">
         <is>
           <t>{matches:[{query_id, relation, confidence}]}</t>
         </is>
@@ -4484,7 +6258,7 @@
           <t>Query text, answer text, current values of the queried fields  (NEW at review)</t>
         </is>
       </c>
-      <c r="D8" s="63" t="inlineStr">
+      <c r="D8" s="66" t="inlineStr">
         <is>
           <t>{classification, confidence, rationale, quoted_span}</t>
         </is>
@@ -4506,7 +6280,7 @@
           <t>Evidence object, rule metadata, message templates, guideline citation, indication context</t>
         </is>
       </c>
-      <c r="D9" s="62" t="inlineStr">
+      <c r="D9" s="65" t="inlineStr">
         <is>
           <t>{five narrative fields}</t>
         </is>
@@ -4528,7 +6302,7 @@
           <t>Protocol and imaging charter text  (NEW at review, AC-11)</t>
         </is>
       </c>
-      <c r="D10" s="63" t="inlineStr">
+      <c r="D10" s="66" t="inlineStr">
         <is>
           <t>{checkpoints:[{parameter, value_found, page_ref, confidence}]}</t>
         </is>
@@ -4767,320 +6541,14 @@
 log the event. The finding is still produced, with template text.</t>
         </is>
       </c>
-      <c r="B28" s="61" t="n"/>
-      <c r="C28" s="61" t="n"/>
-      <c r="D28" s="61" t="n"/>
+      <c r="B28" s="64" t="n"/>
+      <c r="C28" s="64" t="n"/>
+      <c r="D28" s="64" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A28:D28"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="96" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>API surface</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="9" t="inlineStr">
-        <is>
-          <t>Read-only except where marked. Consumed by the web application.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>Method</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>Path</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
-        <is>
-          <t>Write</t>
-        </is>
-      </c>
-      <c r="D3" s="10" t="inlineStr">
-        <is>
-          <t>Purpose</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="18" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="inlineStr">
-        <is>
-          <t>/studies/{study_id}/intake</t>
-        </is>
-      </c>
-      <c r="C4" s="24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D4" s="12" t="inlineStr">
-        <is>
-          <t>NEW. Submit the protocol for checkpoint extraction and record the user's confirmation (AC-11).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="20" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="B5" s="21" t="inlineStr">
-        <is>
-          <t>/runs</t>
-        </is>
-      </c>
-      <c r="C5" s="26" t="inlineStr"/>
-      <c r="D5" s="22" t="inlineStr">
-        <is>
-          <t>Start a review run for a study and dataset snapshot.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="B6" s="19" t="inlineStr">
-        <is>
-          <t>/runs/{run_id}</t>
-        </is>
-      </c>
-      <c r="C6" s="24" t="inlineStr"/>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>Run metadata, provenance and coverage report.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="20" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>/runs/{run_id}/findings</t>
-        </is>
-      </c>
-      <c r="C7" s="26" t="inlineStr"/>
-      <c r="D7" s="22" t="inlineStr">
-        <is>
-          <t>Findings with filtering, sorting, pagination and faceting.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="18" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="B8" s="19" t="inlineStr">
-        <is>
-          <t>/findings/{finding_id}</t>
-        </is>
-      </c>
-      <c r="C8" s="24" t="inlineStr"/>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Full finding with evidence and derivation trace.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="20" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="B9" s="21" t="inlineStr">
-        <is>
-          <t>/findings/{finding_id}/history</t>
-        </is>
-      </c>
-      <c r="C9" s="26" t="inlineStr"/>
-      <c r="D9" s="22" t="inlineStr">
-        <is>
-          <t>The finding's dedupe-key history across runs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="18" t="inlineStr">
-        <is>
-          <t>PATCH</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>/findings/{finding_id}/disposition</t>
-        </is>
-      </c>
-      <c r="C10" s="24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Record a reviewer disposition with reason; appends to the audit trail.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="20" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="B11" s="21" t="inlineStr">
-        <is>
-          <t>/findings/{finding_id}/query-draft</t>
-        </is>
-      </c>
-      <c r="C11" s="26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D11" s="22" t="inlineStr">
-        <is>
-          <t>Persist the reviewer-edited query text and mark it issued.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="18" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>/subjects/{subject_id}/tumor-360</t>
-        </is>
-      </c>
-      <c r="C12" s="24" t="inlineStr"/>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>Lesion history, derived timepoints, responses reported and derived, findings and queries.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="20" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="B13" s="21" t="inlineStr">
-        <is>
-          <t>/studies/{study_id}/analytics</t>
-        </is>
-      </c>
-      <c r="C13" s="26" t="inlineStr"/>
-      <c r="D13" s="22" t="inlineStr">
-        <is>
-          <t>Waterfall, spider and swimmer series plus rule and site rates.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="18" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="inlineStr">
-        <is>
-          <t>/config/{study_id}</t>
-        </is>
-      </c>
-      <c r="C14" s="24" t="inlineStr"/>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>Effective protocol configuration and active rule pack.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="20" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="B15" s="21" t="inlineStr">
-        <is>
-          <t>/findings/{finding_id}/confidence</t>
-        </is>
-      </c>
-      <c r="C15" s="26" t="inlineStr"/>
-      <c r="D15" s="22" t="inlineStr">
-        <is>
-          <t>NEW. The confidence rate with its contributing factors.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="18" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>/runs/{run_id}/suppressed</t>
-        </is>
-      </c>
-      <c r="C16" s="24" t="inlineStr"/>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>NEW. Findings suppressed as justified by a query answer, with the justification.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5092,7 +6560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5558,87 +7026,113 @@
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
+          <t>SDTM_Requirements</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>What the agent needs from an SDTM delivery</t>
+        </is>
+      </c>
+      <c r="C23" s="16">
+        <f>COUNTA(SDTM_Requirements!B4:B45)</f>
+        <v/>
+      </c>
+      <c r="D23" s="17" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>TEA-CTR-003 — OI-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
           <t>Query_Style</t>
         </is>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>12 house rules for query text</t>
         </is>
       </c>
-      <c r="C23" s="16">
+      <c r="C24" s="16">
         <f>COUNTA(Query_Style!A4:A15)</f>
         <v/>
       </c>
-      <c r="D23" s="14" t="inlineStr"/>
-      <c r="E23" s="15" t="inlineStr">
+      <c r="D24" s="14" t="inlineStr"/>
+      <c r="E24" s="15" t="inlineStr">
         <is>
           <t>settles SQ-05</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>GLM_Verification</t>
         </is>
       </c>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>GLM checks, plus the protocol extract spec</t>
         </is>
       </c>
-      <c r="C24" s="16">
+      <c r="C25" s="16">
         <f>COUNTA(GLM_Verification!A4:A23)</f>
         <v/>
       </c>
-      <c r="D24" s="14" t="inlineStr"/>
-      <c r="E24" s="15" t="inlineStr">
+      <c r="D25" s="14" t="inlineStr"/>
+      <c r="E25" s="15" t="inlineStr">
         <is>
           <t>B2 deferred + mitigated</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>Approval</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>Gate record: basis, history, what was not confirmed</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="n"/>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>read this</t>
-        </is>
-      </c>
-      <c r="E25" s="15" t="inlineStr">
-        <is>
-          <t>2 items flagged</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
+          <t>Approval</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>Gate record: basis, history, what was not confirmed</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="n"/>
+      <c r="D26" s="17" t="inlineStr">
+        <is>
+          <t>read this</t>
+        </is>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>2 items flagged</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
           <t>Traceability</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>Plan requirement to specification to tests</t>
         </is>
       </c>
-      <c r="C26" s="16">
+      <c r="C27" s="16">
         <f>COUNTA(Traceability!A4:A23)</f>
         <v/>
       </c>
-      <c r="D26" s="14" t="inlineStr"/>
-      <c r="E26" s="15" t="inlineStr"/>
+      <c r="D27" s="14" t="inlineStr"/>
+      <c r="E27" s="15" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5665,16 +7159,323 @@
     <hyperlink ref="A20" location="Testing!A1"/>
     <hyperlink ref="A21" location="Extensibility!A1"/>
     <hyperlink ref="A22" location="Open_Questions!A1"/>
-    <hyperlink ref="A23" location="Query_Style!A1"/>
-    <hyperlink ref="A24" location="GLM_Verification!A1"/>
-    <hyperlink ref="A25" location="Approval!A1"/>
-    <hyperlink ref="A26" location="Traceability!A1"/>
+    <hyperlink ref="A23" location="SDTM_Requirements!A1"/>
+    <hyperlink ref="A24" location="Query_Style!A1"/>
+    <hyperlink ref="A25" location="GLM_Verification!A1"/>
+    <hyperlink ref="A26" location="Approval!A1"/>
+    <hyperlink ref="A27" location="Traceability!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="96" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>API surface</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>Read-only except where marked. Consumed by the web application.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Path</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Write</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>/studies/{study_id}/intake</t>
+        </is>
+      </c>
+      <c r="C4" s="24" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>NEW. Submit the protocol for checkpoint extraction and record the user's confirmation (AC-11).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>/runs</t>
+        </is>
+      </c>
+      <c r="C5" s="26" t="inlineStr"/>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>Start a review run for a study and dataset snapshot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>/runs/{run_id}</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr"/>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Run metadata, provenance and coverage report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>/runs/{run_id}/findings</t>
+        </is>
+      </c>
+      <c r="C7" s="26" t="inlineStr"/>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>Findings with filtering, sorting, pagination and faceting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>/findings/{finding_id}</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr"/>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>Full finding with evidence and derivation trace.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>/findings/{finding_id}/history</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="inlineStr"/>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>The finding's dedupe-key history across runs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>PATCH</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>/findings/{finding_id}/disposition</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>Record a reviewer disposition with reason; appends to the audit trail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>/findings/{finding_id}/query-draft</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>Persist the reviewer-edited query text and mark it issued.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>/subjects/{subject_id}/tumor-360</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr"/>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>Lesion history, derived timepoints, responses reported and derived, findings and queries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>/studies/{study_id}/analytics</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="inlineStr"/>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>Waterfall, spider and swimmer series plus rule and site rates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>/config/{study_id}</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr"/>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>Effective protocol configuration and active rule pack.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>/findings/{finding_id}/confidence</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="inlineStr"/>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>NEW. The confidence rate with its contributing factors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>/runs/{run_id}/suppressed</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr"/>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>NEW. Findings suppressed as justified by a query answer, with the justification.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5907,7 +7708,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6035,7 +7836,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6141,7 +7942,7 @@
           <t>Confirm the confidence base rate proposed for each rule (Open Item OI-02). These drive triage for every finding the agent produces.</t>
         </is>
       </c>
-      <c r="C5" s="64" t="inlineStr">
+      <c r="C5" s="61" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -6333,7 +8134,7 @@
           <t>Confirm whether the Veeva CRF collects a sum of diameters at all. If it is derived only, TE-BL-011 and TE-FU-001 do not apply and weight shifts onto TE-RS-001.</t>
         </is>
       </c>
-      <c r="C11" s="64" t="inlineStr">
+      <c r="C11" s="61" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -6441,7 +8242,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6941,7 +8742,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
